--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFB8D93-4145-420F-8BB8-7F0DDE1FC08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{420FD1BA-4020-43B1-BFF1-9F57AF2DBEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="295">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1110,6 +1110,55 @@
   </si>
   <si>
     <t>Non-Offshore</t>
+  </si>
+  <si>
+    <t>Lifting equipment onto the CTV</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sail to F2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attempted to push on at D-06, but failed.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attempted to push on at D-11, but failed.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Captain and Site Supervisor decided to cancel today's mission.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sailed back to Taichung Port.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D06</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D07</t>
+  </si>
+  <si>
+    <t>D08</t>
+  </si>
+  <si>
+    <t>D09</t>
+  </si>
+  <si>
+    <t>D10</t>
+  </si>
+  <si>
+    <t>D11</t>
+  </si>
+  <si>
+    <t>D12</t>
+  </si>
+  <si>
+    <t>D13</t>
   </si>
 </sst>
 </file>
@@ -1189,7 +1238,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1213,6 +1262,13 @@
     </xf>
     <xf numFmtId="20" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1495,7 +1551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F704"/>
+  <dimension ref="A1:F714"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.69921875" style="1" bestFit="1" customWidth="1"/>
@@ -10803,6 +10859,144 @@
       </c>
       <c r="E704" s="5"/>
     </row>
+    <row r="705" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A705" s="2">
+        <v>46278</v>
+      </c>
+      <c r="B705" s="10">
+        <v>0.21527777777777779</v>
+      </c>
+      <c r="C705" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="D705" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="E705" s="12"/>
+      <c r="F705" s="11"/>
+    </row>
+    <row r="706" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A706" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B706" s="10">
+        <v>0.2326388888888889</v>
+      </c>
+      <c r="C706" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="D706" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="E706" s="12"/>
+      <c r="F706" s="11"/>
+    </row>
+    <row r="707" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A707" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B707" s="10">
+        <v>0.31944444444444442</v>
+      </c>
+      <c r="C707" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="D707" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="E707" s="12"/>
+      <c r="F707" s="11"/>
+    </row>
+    <row r="708" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A708" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B708" s="10">
+        <v>0.3263888888888889</v>
+      </c>
+      <c r="C708" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="D708" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="E708" s="12"/>
+      <c r="F708" s="11"/>
+    </row>
+    <row r="709" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A709" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B709" s="10"/>
+      <c r="C709" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="D709" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="E709" s="12"/>
+      <c r="F709" s="11"/>
+    </row>
+    <row r="710" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A710" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B710" s="10">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C710" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="D710" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="E710" s="12"/>
+      <c r="F710" s="11"/>
+    </row>
+    <row r="711" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A711" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B711" s="10">
+        <v>0.4375</v>
+      </c>
+      <c r="C711" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="D711" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="E711" s="12"/>
+      <c r="F711" s="11"/>
+    </row>
+    <row r="712" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A712" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B712" s="10"/>
+      <c r="C712" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="D712" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E712" s="12"/>
+      <c r="F712" s="11"/>
+    </row>
+    <row r="713" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B713" s="11"/>
+      <c r="C713" s="11"/>
+      <c r="D713" s="11"/>
+      <c r="E713" s="11"/>
+      <c r="F713" s="11"/>
+    </row>
+    <row r="714" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B714" s="11"/>
+      <c r="C714" s="11"/>
+      <c r="D714" s="11"/>
+      <c r="E714" s="11"/>
+      <c r="F714" s="11"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{420FD1BA-4020-43B1-BFF1-9F57AF2DBEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4668BBA7-99C5-494D-97DC-DDBDDF818F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="288">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1138,27 +1138,6 @@
   <si>
     <t>D06</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>D07</t>
-  </si>
-  <si>
-    <t>D08</t>
-  </si>
-  <si>
-    <t>D09</t>
-  </si>
-  <si>
-    <t>D10</t>
-  </si>
-  <si>
-    <t>D11</t>
-  </si>
-  <si>
-    <t>D12</t>
-  </si>
-  <si>
-    <t>D13</t>
   </si>
 </sst>
 </file>
@@ -1238,7 +1217,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1263,12 +1242,8 @@
     <xf numFmtId="20" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1551,7 +1526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F714"/>
+  <dimension ref="A1:F712"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.69921875" style="1" bestFit="1" customWidth="1"/>
@@ -10859,143 +10834,121 @@
       </c>
       <c r="E704" s="5"/>
     </row>
-    <row r="705" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A705" s="2">
         <v>46278</v>
       </c>
       <c r="B705" s="10">
         <v>0.21527777777777779</v>
       </c>
-      <c r="C705" s="11" t="s">
+      <c r="C705" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D705" s="12" t="s">
+      <c r="D705" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="E705" s="12"/>
-      <c r="F705" s="11"/>
-    </row>
-    <row r="706" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E705" s="8"/>
+    </row>
+    <row r="706" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A706" s="2">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B706" s="10">
         <v>0.2326388888888889</v>
       </c>
-      <c r="C706" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="D706" s="12" t="s">
+      <c r="C706" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D706" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="E706" s="12"/>
-      <c r="F706" s="11"/>
-    </row>
-    <row r="707" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E706" s="8"/>
+    </row>
+    <row r="707" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A707" s="2">
-        <v>46280</v>
+        <v>46278</v>
       </c>
       <c r="B707" s="10">
         <v>0.31944444444444442</v>
       </c>
-      <c r="C707" s="11" t="s">
-        <v>289</v>
-      </c>
-      <c r="D707" s="12" t="s">
+      <c r="C707" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D707" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="E707" s="12"/>
-      <c r="F707" s="11"/>
-    </row>
-    <row r="708" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E707" s="8"/>
+    </row>
+    <row r="708" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A708" s="2">
-        <v>46281</v>
+        <v>46278</v>
       </c>
       <c r="B708" s="10">
         <v>0.3263888888888889</v>
       </c>
-      <c r="C708" s="11" t="s">
-        <v>290</v>
-      </c>
-      <c r="D708" s="12" t="s">
+      <c r="C708" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D708" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="E708" s="12"/>
-      <c r="F708" s="11"/>
-    </row>
-    <row r="709" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E708" s="8"/>
+    </row>
+    <row r="709" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A709" s="2">
-        <v>46282</v>
+        <v>46278</v>
       </c>
       <c r="B709" s="10"/>
-      <c r="C709" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="D709" s="12" t="s">
+      <c r="C709" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D709" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="E709" s="12"/>
-      <c r="F709" s="11"/>
-    </row>
-    <row r="710" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E709" s="8"/>
+    </row>
+    <row r="710" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A710" s="2">
-        <v>46283</v>
+        <v>46278</v>
       </c>
       <c r="B710" s="10">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C710" s="11" t="s">
-        <v>292</v>
-      </c>
-      <c r="D710" s="12" t="s">
+      <c r="C710" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D710" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="E710" s="12"/>
-      <c r="F710" s="11"/>
-    </row>
-    <row r="711" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E710" s="8"/>
+    </row>
+    <row r="711" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A711" s="2">
-        <v>46284</v>
+        <v>46278</v>
       </c>
       <c r="B711" s="10">
         <v>0.4375</v>
       </c>
-      <c r="C711" s="11" t="s">
-        <v>293</v>
-      </c>
-      <c r="D711" s="12" t="s">
+      <c r="C711" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D711" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="E711" s="12"/>
-      <c r="F711" s="11"/>
-    </row>
-    <row r="712" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E711" s="8"/>
+    </row>
+    <row r="712" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A712" s="2">
-        <v>46285</v>
+        <v>46278</v>
       </c>
       <c r="B712" s="10"/>
-      <c r="C712" s="11" t="s">
-        <v>294</v>
-      </c>
-      <c r="D712" s="12" t="s">
+      <c r="C712" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D712" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E712" s="12"/>
-      <c r="F712" s="11"/>
-    </row>
-    <row r="713" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B713" s="11"/>
-      <c r="C713" s="11"/>
-      <c r="D713" s="11"/>
-      <c r="E713" s="11"/>
-      <c r="F713" s="11"/>
-    </row>
-    <row r="714" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B714" s="11"/>
-      <c r="C714" s="11"/>
-      <c r="D714" s="11"/>
-      <c r="E714" s="11"/>
-      <c r="F714" s="11"/>
+      <c r="E712" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4668BBA7-99C5-494D-97DC-DDBDDF818F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B06413-7141-4A46-BE4F-A4AFC12750EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1480" uniqueCount="305">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1137,6 +1137,74 @@
   </si>
   <si>
     <t>D06</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>battery maintenance</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tether reel maintenance</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Comprehensive test on the vehicle (thrusters, main hull, navigation hull, fairings, etc.)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Comprehensive test on equipment(topside box, battery charge box)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>have lunch and take a small rest</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pre-dive test</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CP Calibration &amp; Basic Troubleshooting</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AIB flight simulation – GVI (Leg Down &amp; Leg Up, Brace, Scour, and Mosaic)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>transfer the equipment</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Introdution on AIB</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Connect vehicle/pre dive test/cp calibration</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Launch AIB</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pilot training:Basic moving(waypoint&amp;manual)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pilot training:pile inspection</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tetherline</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>lesson learn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>strong current</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1217,7 +1285,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1245,6 +1313,15 @@
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal 2" xfId="1" xr:uid="{71AF191C-2467-4F76-8A53-CA6D53E4DF10}"/>
@@ -1526,7 +1603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F712"/>
+  <dimension ref="A1:J739"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.69921875" style="1" bestFit="1" customWidth="1"/>
@@ -10834,7 +10911,7 @@
       </c>
       <c r="E704" s="5"/>
     </row>
-    <row r="705" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A705" s="2">
         <v>46278</v>
       </c>
@@ -10849,7 +10926,7 @@
       </c>
       <c r="E705" s="8"/>
     </row>
-    <row r="706" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A706" s="2">
         <v>46278</v>
       </c>
@@ -10864,7 +10941,7 @@
       </c>
       <c r="E706" s="8"/>
     </row>
-    <row r="707" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A707" s="2">
         <v>46278</v>
       </c>
@@ -10879,7 +10956,7 @@
       </c>
       <c r="E707" s="8"/>
     </row>
-    <row r="708" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A708" s="2">
         <v>46278</v>
       </c>
@@ -10894,7 +10971,7 @@
       </c>
       <c r="E708" s="8"/>
     </row>
-    <row r="709" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A709" s="2">
         <v>46278</v>
       </c>
@@ -10907,48 +10984,571 @@
       </c>
       <c r="E709" s="8"/>
     </row>
-    <row r="710" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A710" s="2">
+    <row r="710" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A710" s="11">
         <v>46278</v>
       </c>
-      <c r="B710" s="10">
+      <c r="B710" s="12">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C710" s="1" t="s">
+      <c r="C710" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="D710" s="8" t="s">
+      <c r="D710" s="14" t="s">
         <v>286</v>
       </c>
-      <c r="E710" s="8"/>
-    </row>
-    <row r="711" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A711" s="2">
+      <c r="E710" s="14"/>
+      <c r="F710" s="13"/>
+      <c r="G710" s="15"/>
+      <c r="H710" s="15"/>
+    </row>
+    <row r="711" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A711" s="11">
         <v>46278</v>
       </c>
-      <c r="B711" s="10">
+      <c r="B711" s="12">
         <v>0.4375</v>
       </c>
-      <c r="C711" s="1" t="s">
+      <c r="C711" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="D711" s="8" t="s">
+      <c r="D711" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="E711" s="8"/>
-    </row>
-    <row r="712" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A712" s="2">
+      <c r="E711" s="14"/>
+      <c r="F711" s="13"/>
+      <c r="G711" s="15"/>
+      <c r="H711" s="15"/>
+    </row>
+    <row r="712" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A712" s="11">
         <v>46278</v>
       </c>
-      <c r="B712" s="10"/>
-      <c r="C712" s="1" t="s">
+      <c r="B712" s="12"/>
+      <c r="C712" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="D712" s="8" t="s">
+      <c r="D712" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E712" s="8"/>
+      <c r="E712" s="14"/>
+      <c r="F712" s="13"/>
+      <c r="G712" s="15"/>
+      <c r="H712" s="15"/>
+    </row>
+    <row r="713" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A713" s="11">
+        <v>46279</v>
+      </c>
+      <c r="B713" s="12">
+        <v>0.375</v>
+      </c>
+      <c r="C713" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D713" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="E713" s="14"/>
+      <c r="F713" s="14"/>
+      <c r="G713" s="15"/>
+      <c r="H713" s="15"/>
+    </row>
+    <row r="714" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A714" s="11">
+        <v>46279</v>
+      </c>
+      <c r="B714" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="C714" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D714" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E714" s="14"/>
+      <c r="F714" s="14"/>
+      <c r="G714" s="15"/>
+      <c r="H714" s="15"/>
+    </row>
+    <row r="715" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A715" s="11">
+        <v>46279</v>
+      </c>
+      <c r="B715" s="12">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C715" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D715" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="E715" s="14"/>
+      <c r="F715" s="14"/>
+      <c r="G715" s="15"/>
+      <c r="H715" s="15"/>
+    </row>
+    <row r="716" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A716" s="11">
+        <v>46279</v>
+      </c>
+      <c r="B716" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="C716" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D716" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E716" s="14"/>
+      <c r="F716" s="14"/>
+      <c r="G716" s="15"/>
+      <c r="H716" s="15"/>
+    </row>
+    <row r="717" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A717" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B717" s="12">
+        <v>0.375</v>
+      </c>
+      <c r="C717" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D717" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="E717" s="14"/>
+      <c r="F717" s="14"/>
+      <c r="G717" s="15"/>
+      <c r="H717" s="15"/>
+      <c r="I717" s="15"/>
+    </row>
+    <row r="718" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A718" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B718" s="12">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C718" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D718" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="E718" s="14"/>
+      <c r="F718" s="14"/>
+      <c r="G718" s="15"/>
+      <c r="H718" s="15"/>
+      <c r="I718" s="15"/>
+    </row>
+    <row r="719" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A719" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B719" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C719" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D719" s="14" t="s">
+        <v>290</v>
+      </c>
+      <c r="E719" s="14"/>
+      <c r="F719" s="14"/>
+      <c r="G719" s="15"/>
+      <c r="H719" s="15"/>
+      <c r="I719" s="15"/>
+    </row>
+    <row r="720" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A720" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B720" s="12">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C720" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D720" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="E720" s="14"/>
+      <c r="F720" s="14"/>
+      <c r="G720" s="15"/>
+      <c r="H720" s="15"/>
+      <c r="I720" s="15"/>
+    </row>
+    <row r="721" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A721" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B721" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="C721" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D721" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="E721" s="14"/>
+      <c r="F721" s="14"/>
+      <c r="G721" s="15"/>
+      <c r="H721" s="15"/>
+      <c r="I721" s="15"/>
+    </row>
+    <row r="722" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A722" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B722" s="12">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C722" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D722" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="E722" s="14"/>
+      <c r="F722" s="14"/>
+      <c r="G722" s="15"/>
+      <c r="H722" s="15"/>
+      <c r="I722" s="15"/>
+    </row>
+    <row r="723" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A723" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B723" s="12">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C723" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D723" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="E723" s="14"/>
+      <c r="F723" s="14"/>
+      <c r="G723" s="15"/>
+      <c r="H723" s="15"/>
+      <c r="I723" s="15"/>
+    </row>
+    <row r="724" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A724" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B724" s="12">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C724" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D724" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="E724" s="14"/>
+      <c r="F724" s="14"/>
+      <c r="G724" s="15"/>
+      <c r="H724" s="15"/>
+      <c r="I724" s="15"/>
+    </row>
+    <row r="725" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A725" s="11">
+        <v>46281</v>
+      </c>
+      <c r="B725" s="12">
+        <v>0.375</v>
+      </c>
+      <c r="C725" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D725" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="E725" s="14"/>
+      <c r="F725" s="14"/>
+      <c r="G725" s="15"/>
+      <c r="H725" s="15"/>
+      <c r="I725" s="15"/>
+      <c r="J725" s="15"/>
+    </row>
+    <row r="726" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A726" s="11">
+        <v>46281</v>
+      </c>
+      <c r="B726" s="12">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C726" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D726" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="E726" s="14"/>
+      <c r="F726" s="14"/>
+      <c r="G726" s="15"/>
+      <c r="H726" s="15"/>
+      <c r="I726" s="15"/>
+      <c r="J726" s="15"/>
+    </row>
+    <row r="727" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A727" s="11">
+        <v>46281</v>
+      </c>
+      <c r="B727" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C727" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D727" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="E727" s="14"/>
+      <c r="F727" s="14"/>
+      <c r="G727" s="15"/>
+      <c r="H727" s="15"/>
+      <c r="I727" s="15"/>
+      <c r="J727" s="15"/>
+    </row>
+    <row r="728" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A728" s="11">
+        <v>46281</v>
+      </c>
+      <c r="B728" s="12">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C728" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D728" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="E728" s="14"/>
+      <c r="F728" s="14"/>
+      <c r="G728" s="15"/>
+      <c r="H728" s="15"/>
+      <c r="I728" s="15"/>
+      <c r="J728" s="15"/>
+    </row>
+    <row r="729" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A729" s="11">
+        <v>46281</v>
+      </c>
+      <c r="B729" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="C729" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D729" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="E729" s="14"/>
+      <c r="F729" s="14"/>
+      <c r="G729" s="15"/>
+      <c r="H729" s="15"/>
+      <c r="I729" s="15"/>
+      <c r="J729" s="15"/>
+    </row>
+    <row r="730" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A730" s="11">
+        <v>46281</v>
+      </c>
+      <c r="B730" s="12">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C730" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D730" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="E730" s="14"/>
+      <c r="F730" s="14"/>
+      <c r="G730" s="15"/>
+      <c r="H730" s="15"/>
+      <c r="I730" s="15"/>
+      <c r="J730" s="15"/>
+    </row>
+    <row r="731" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A731" s="11">
+        <v>46281</v>
+      </c>
+      <c r="B731" s="12">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C731" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D731" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="E731" s="14"/>
+      <c r="F731" s="14"/>
+      <c r="G731" s="15"/>
+      <c r="H731" s="15"/>
+      <c r="I731" s="15"/>
+      <c r="J731" s="15"/>
+    </row>
+    <row r="732" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A732" s="11">
+        <v>46281</v>
+      </c>
+      <c r="B732" s="12">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C732" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D732" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="E732" s="14"/>
+      <c r="F732" s="14"/>
+      <c r="G732" s="15"/>
+      <c r="H732" s="15"/>
+      <c r="I732" s="15"/>
+      <c r="J732" s="15"/>
+    </row>
+    <row r="733" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A733" s="11">
+        <v>46281</v>
+      </c>
+      <c r="B733" s="12">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C733" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D733" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="E733" s="14"/>
+      <c r="F733" s="14"/>
+      <c r="G733" s="15"/>
+      <c r="H733" s="15"/>
+      <c r="I733" s="15"/>
+      <c r="J733" s="15"/>
+    </row>
+    <row r="734" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A734" s="11">
+        <v>46282</v>
+      </c>
+      <c r="B734" s="12">
+        <v>0.2638888888888889</v>
+      </c>
+      <c r="C734" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="D734" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="E734" s="14"/>
+      <c r="F734" s="14"/>
+      <c r="G734" s="15"/>
+      <c r="H734" s="15"/>
+      <c r="I734" s="15"/>
+      <c r="J734" s="15"/>
+    </row>
+    <row r="735" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A735" s="11">
+        <v>46282</v>
+      </c>
+      <c r="B735" s="12">
+        <v>0.30555555555555558</v>
+      </c>
+      <c r="C735" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="D735" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="E735" s="14"/>
+      <c r="F735" s="14"/>
+      <c r="G735" s="15"/>
+      <c r="H735" s="15"/>
+      <c r="I735" s="15"/>
+      <c r="J735" s="15"/>
+    </row>
+    <row r="736" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A736" s="11">
+        <v>46282</v>
+      </c>
+      <c r="B736" s="12"/>
+      <c r="C736" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="D736" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="E736" s="14"/>
+      <c r="F736" s="14"/>
+      <c r="G736" s="15"/>
+      <c r="H736" s="15"/>
+      <c r="I736" s="15"/>
+      <c r="J736" s="15"/>
+    </row>
+    <row r="737" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A737" s="11">
+        <v>46282</v>
+      </c>
+      <c r="B737" s="12"/>
+      <c r="C737" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="D737" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="E737" s="14"/>
+      <c r="F737" s="14"/>
+      <c r="G737" s="15"/>
+      <c r="H737" s="15"/>
+      <c r="I737" s="15"/>
+      <c r="J737" s="15"/>
+    </row>
+    <row r="738" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A738" s="11">
+        <v>46282</v>
+      </c>
+      <c r="B738" s="12">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C738" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="D738" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="E738" s="14"/>
+      <c r="F738" s="14"/>
+      <c r="G738" s="15"/>
+      <c r="H738" s="15"/>
+      <c r="I738" s="15"/>
+      <c r="J738" s="15"/>
+    </row>
+    <row r="739" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A739" s="11">
+        <v>46282</v>
+      </c>
+      <c r="B739" s="12"/>
+      <c r="C739" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="D739" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E739" s="14"/>
+      <c r="F739" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B06413-7141-4A46-BE4F-A4AFC12750EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CCE4DC1-542A-413C-85D9-8B4347B9EECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1480" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="314">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1205,6 +1205,42 @@
   </si>
   <si>
     <t>strong current</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D05</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attempted to push on at D05, but failed.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sailed  to D08(seasight team)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attempted to push on at D08, but failed.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sailed  to A01(F2 team)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>push on A01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Standby, waiting for the F2 team to complete their work.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sail to D11(seasight team)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attempted to push on at D11, but failed.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1285,7 +1321,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1313,15 +1349,15 @@
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal 2" xfId="1" xr:uid="{71AF191C-2467-4F76-8A53-CA6D53E4DF10}"/>
@@ -1603,7 +1639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J739"/>
+  <dimension ref="A1:F752"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.69921875" style="1" bestFit="1" customWidth="1"/>
@@ -10911,7 +10947,7 @@
       </c>
       <c r="E704" s="5"/>
     </row>
-    <row r="705" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A705" s="2">
         <v>46278</v>
       </c>
@@ -10926,7 +10962,7 @@
       </c>
       <c r="E705" s="8"/>
     </row>
-    <row r="706" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A706" s="2">
         <v>46278</v>
       </c>
@@ -10941,7 +10977,7 @@
       </c>
       <c r="E706" s="8"/>
     </row>
-    <row r="707" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A707" s="2">
         <v>46278</v>
       </c>
@@ -10956,7 +10992,7 @@
       </c>
       <c r="E707" s="8"/>
     </row>
-    <row r="708" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A708" s="2">
         <v>46278</v>
       </c>
@@ -10971,7 +11007,7 @@
       </c>
       <c r="E708" s="8"/>
     </row>
-    <row r="709" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A709" s="2">
         <v>46278</v>
       </c>
@@ -10984,571 +11020,672 @@
       </c>
       <c r="E709" s="8"/>
     </row>
-    <row r="710" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A710" s="11">
+    <row r="710" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A710" s="2">
         <v>46278</v>
       </c>
-      <c r="B710" s="12">
+      <c r="B710" s="10">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C710" s="13" t="s">
+      <c r="C710" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D710" s="14" t="s">
+      <c r="D710" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="E710" s="14"/>
-      <c r="F710" s="13"/>
-      <c r="G710" s="15"/>
-      <c r="H710" s="15"/>
-    </row>
-    <row r="711" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A711" s="11">
+      <c r="E710" s="8"/>
+    </row>
+    <row r="711" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A711" s="2">
         <v>46278</v>
       </c>
-      <c r="B711" s="12">
+      <c r="B711" s="10">
         <v>0.4375</v>
       </c>
-      <c r="C711" s="13" t="s">
+      <c r="C711" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D711" s="14" t="s">
+      <c r="D711" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="E711" s="14"/>
-      <c r="F711" s="13"/>
-      <c r="G711" s="15"/>
-      <c r="H711" s="15"/>
-    </row>
-    <row r="712" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A712" s="11">
+      <c r="E711" s="8"/>
+    </row>
+    <row r="712" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A712" s="2">
         <v>46278</v>
       </c>
-      <c r="B712" s="12"/>
-      <c r="C712" s="13" t="s">
+      <c r="B712" s="10"/>
+      <c r="C712" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D712" s="14" t="s">
+      <c r="D712" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E712" s="14"/>
-      <c r="F712" s="13"/>
-      <c r="G712" s="15"/>
-      <c r="H712" s="15"/>
-    </row>
-    <row r="713" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A713" s="11">
+      <c r="E712" s="8"/>
+    </row>
+    <row r="713" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A713" s="2">
         <v>46279</v>
       </c>
-      <c r="B713" s="12">
+      <c r="B713" s="10">
         <v>0.375</v>
       </c>
       <c r="C713" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D713" s="14" t="s">
+      <c r="D713" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="E713" s="14"/>
-      <c r="F713" s="14"/>
-      <c r="G713" s="15"/>
-      <c r="H713" s="15"/>
-    </row>
-    <row r="714" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A714" s="11">
+      <c r="E713" s="8"/>
+      <c r="F713" s="8"/>
+    </row>
+    <row r="714" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A714" s="2">
         <v>46279</v>
       </c>
-      <c r="B714" s="12">
+      <c r="B714" s="10">
         <v>0.5</v>
       </c>
       <c r="C714" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D714" s="14" t="s">
+      <c r="D714" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="E714" s="14"/>
-      <c r="F714" s="14"/>
-      <c r="G714" s="15"/>
-      <c r="H714" s="15"/>
-    </row>
-    <row r="715" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A715" s="11">
+      <c r="E714" s="8"/>
+      <c r="F714" s="8"/>
+    </row>
+    <row r="715" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A715" s="2">
         <v>46279</v>
       </c>
-      <c r="B715" s="12">
+      <c r="B715" s="10">
         <v>0.54166666666666663</v>
       </c>
       <c r="C715" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D715" s="14" t="s">
+      <c r="D715" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="E715" s="14"/>
-      <c r="F715" s="14"/>
-      <c r="G715" s="15"/>
-      <c r="H715" s="15"/>
-    </row>
-    <row r="716" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A716" s="11">
+      <c r="E715" s="8"/>
+      <c r="F715" s="8"/>
+    </row>
+    <row r="716" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A716" s="2">
         <v>46279</v>
       </c>
-      <c r="B716" s="12">
+      <c r="B716" s="10">
         <v>0.75</v>
       </c>
       <c r="C716" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D716" s="14" t="s">
+      <c r="D716" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="E716" s="14"/>
-      <c r="F716" s="14"/>
-      <c r="G716" s="15"/>
-      <c r="H716" s="15"/>
-    </row>
-    <row r="717" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A717" s="11">
+      <c r="E716" s="8"/>
+      <c r="F716" s="8"/>
+    </row>
+    <row r="717" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A717" s="2">
         <v>46280</v>
       </c>
-      <c r="B717" s="12">
+      <c r="B717" s="10">
         <v>0.375</v>
       </c>
       <c r="C717" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D717" s="14" t="s">
+      <c r="D717" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="E717" s="14"/>
-      <c r="F717" s="14"/>
-      <c r="G717" s="15"/>
-      <c r="H717" s="15"/>
-      <c r="I717" s="15"/>
-    </row>
-    <row r="718" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A718" s="11">
+      <c r="E717" s="8"/>
+      <c r="F717" s="8"/>
+    </row>
+    <row r="718" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A718" s="2">
         <v>46280</v>
       </c>
-      <c r="B718" s="12">
+      <c r="B718" s="10">
         <v>0.39583333333333331</v>
       </c>
       <c r="C718" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D718" s="14" t="s">
+      <c r="D718" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="E718" s="14"/>
-      <c r="F718" s="14"/>
-      <c r="G718" s="15"/>
-      <c r="H718" s="15"/>
-      <c r="I718" s="15"/>
-    </row>
-    <row r="719" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A719" s="11">
+      <c r="E718" s="8"/>
+      <c r="F718" s="8"/>
+    </row>
+    <row r="719" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A719" s="2">
         <v>46280</v>
       </c>
-      <c r="B719" s="12">
+      <c r="B719" s="10">
         <v>0.41666666666666669</v>
       </c>
       <c r="C719" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D719" s="14" t="s">
+      <c r="D719" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="E719" s="14"/>
-      <c r="F719" s="14"/>
-      <c r="G719" s="15"/>
-      <c r="H719" s="15"/>
-      <c r="I719" s="15"/>
-    </row>
-    <row r="720" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A720" s="11">
+      <c r="E719" s="8"/>
+      <c r="F719" s="8"/>
+    </row>
+    <row r="720" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A720" s="2">
         <v>46280</v>
       </c>
-      <c r="B720" s="12">
+      <c r="B720" s="10">
         <v>0.45833333333333331</v>
       </c>
       <c r="C720" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D720" s="14" t="s">
+      <c r="D720" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="E720" s="14"/>
-      <c r="F720" s="14"/>
-      <c r="G720" s="15"/>
-      <c r="H720" s="15"/>
-      <c r="I720" s="15"/>
-    </row>
-    <row r="721" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A721" s="11">
+      <c r="E720" s="8"/>
+      <c r="F720" s="8"/>
+    </row>
+    <row r="721" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A721" s="2">
         <v>46280</v>
       </c>
-      <c r="B721" s="12">
+      <c r="B721" s="10">
         <v>0.5</v>
       </c>
       <c r="C721" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D721" s="14" t="s">
+      <c r="D721" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="E721" s="14"/>
-      <c r="F721" s="14"/>
-      <c r="G721" s="15"/>
-      <c r="H721" s="15"/>
-      <c r="I721" s="15"/>
-    </row>
-    <row r="722" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A722" s="11">
+      <c r="E721" s="8"/>
+      <c r="F721" s="8"/>
+    </row>
+    <row r="722" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A722" s="2">
         <v>46280</v>
       </c>
-      <c r="B722" s="12">
+      <c r="B722" s="10">
         <v>0.54166666666666663</v>
       </c>
       <c r="C722" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D722" s="14" t="s">
+      <c r="D722" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="E722" s="14"/>
-      <c r="F722" s="14"/>
-      <c r="G722" s="15"/>
-      <c r="H722" s="15"/>
-      <c r="I722" s="15"/>
-    </row>
-    <row r="723" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A723" s="11">
+      <c r="E722" s="8"/>
+      <c r="F722" s="8"/>
+    </row>
+    <row r="723" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A723" s="2">
         <v>46280</v>
       </c>
-      <c r="B723" s="12">
+      <c r="B723" s="10">
         <v>0.58333333333333337</v>
       </c>
       <c r="C723" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D723" s="14" t="s">
+      <c r="D723" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="E723" s="14"/>
-      <c r="F723" s="14"/>
-      <c r="G723" s="15"/>
-      <c r="H723" s="15"/>
-      <c r="I723" s="15"/>
-    </row>
-    <row r="724" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A724" s="11">
+      <c r="E723" s="8"/>
+      <c r="F723" s="8"/>
+    </row>
+    <row r="724" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A724" s="2">
         <v>46280</v>
       </c>
-      <c r="B724" s="12">
+      <c r="B724" s="10">
         <v>0.66666666666666663</v>
       </c>
       <c r="C724" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D724" s="14" t="s">
+      <c r="D724" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="E724" s="14"/>
-      <c r="F724" s="14"/>
-      <c r="G724" s="15"/>
-      <c r="H724" s="15"/>
-      <c r="I724" s="15"/>
-    </row>
-    <row r="725" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A725" s="11">
+      <c r="E724" s="8"/>
+      <c r="F724" s="8"/>
+    </row>
+    <row r="725" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A725" s="2">
         <v>46281</v>
       </c>
-      <c r="B725" s="12">
+      <c r="B725" s="10">
         <v>0.375</v>
       </c>
       <c r="C725" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D725" s="14" t="s">
+      <c r="D725" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="E725" s="14"/>
-      <c r="F725" s="14"/>
-      <c r="G725" s="15"/>
-      <c r="H725" s="15"/>
-      <c r="I725" s="15"/>
-      <c r="J725" s="15"/>
-    </row>
-    <row r="726" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A726" s="11">
+      <c r="E725" s="8"/>
+      <c r="F725" s="8"/>
+    </row>
+    <row r="726" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A726" s="2">
         <v>46281</v>
       </c>
-      <c r="B726" s="12">
+      <c r="B726" s="10">
         <v>0.39583333333333331</v>
       </c>
       <c r="C726" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D726" s="14" t="s">
+      <c r="D726" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="E726" s="14"/>
-      <c r="F726" s="14"/>
-      <c r="G726" s="15"/>
-      <c r="H726" s="15"/>
-      <c r="I726" s="15"/>
-      <c r="J726" s="15"/>
-    </row>
-    <row r="727" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A727" s="11">
+      <c r="E726" s="8"/>
+      <c r="F726" s="8"/>
+    </row>
+    <row r="727" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A727" s="2">
         <v>46281</v>
       </c>
-      <c r="B727" s="12">
+      <c r="B727" s="10">
         <v>0.41666666666666669</v>
       </c>
       <c r="C727" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D727" s="14" t="s">
+      <c r="D727" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="E727" s="14"/>
-      <c r="F727" s="14"/>
-      <c r="G727" s="15"/>
-      <c r="H727" s="15"/>
-      <c r="I727" s="15"/>
-      <c r="J727" s="15"/>
-    </row>
-    <row r="728" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A728" s="11">
+      <c r="E727" s="8"/>
+      <c r="F727" s="8"/>
+    </row>
+    <row r="728" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A728" s="2">
         <v>46281</v>
       </c>
-      <c r="B728" s="12">
+      <c r="B728" s="10">
         <v>0.45833333333333331</v>
       </c>
       <c r="C728" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D728" s="14" t="s">
+      <c r="D728" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="E728" s="14"/>
-      <c r="F728" s="14"/>
-      <c r="G728" s="15"/>
-      <c r="H728" s="15"/>
-      <c r="I728" s="15"/>
-      <c r="J728" s="15"/>
-    </row>
-    <row r="729" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A729" s="11">
+      <c r="E728" s="8"/>
+      <c r="F728" s="8"/>
+    </row>
+    <row r="729" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A729" s="2">
         <v>46281</v>
       </c>
-      <c r="B729" s="12">
+      <c r="B729" s="10">
         <v>0.5</v>
       </c>
       <c r="C729" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D729" s="14" t="s">
+      <c r="D729" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="E729" s="14"/>
-      <c r="F729" s="14"/>
-      <c r="G729" s="15"/>
-      <c r="H729" s="15"/>
-      <c r="I729" s="15"/>
-      <c r="J729" s="15"/>
-    </row>
-    <row r="730" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A730" s="11">
+      <c r="E729" s="8"/>
+      <c r="F729" s="8"/>
+    </row>
+    <row r="730" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A730" s="2">
         <v>46281</v>
       </c>
-      <c r="B730" s="12">
+      <c r="B730" s="10">
         <v>0.54166666666666663</v>
       </c>
       <c r="C730" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D730" s="14" t="s">
+      <c r="D730" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="E730" s="14"/>
-      <c r="F730" s="14"/>
-      <c r="G730" s="15"/>
-      <c r="H730" s="15"/>
-      <c r="I730" s="15"/>
-      <c r="J730" s="15"/>
-    </row>
-    <row r="731" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A731" s="11">
+      <c r="E730" s="8"/>
+      <c r="F730" s="8"/>
+    </row>
+    <row r="731" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A731" s="2">
         <v>46281</v>
       </c>
-      <c r="B731" s="12">
+      <c r="B731" s="10">
         <v>0.58333333333333337</v>
       </c>
       <c r="C731" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D731" s="14" t="s">
+      <c r="D731" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="E731" s="14"/>
-      <c r="F731" s="14"/>
-      <c r="G731" s="15"/>
-      <c r="H731" s="15"/>
-      <c r="I731" s="15"/>
-      <c r="J731" s="15"/>
-    </row>
-    <row r="732" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A732" s="11">
+      <c r="E731" s="8"/>
+      <c r="F731" s="8"/>
+    </row>
+    <row r="732" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A732" s="2">
         <v>46281</v>
       </c>
-      <c r="B732" s="12">
+      <c r="B732" s="10">
         <v>0.66666666666666663</v>
       </c>
       <c r="C732" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D732" s="14" t="s">
+      <c r="D732" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="E732" s="14"/>
-      <c r="F732" s="14"/>
-      <c r="G732" s="15"/>
-      <c r="H732" s="15"/>
-      <c r="I732" s="15"/>
-      <c r="J732" s="15"/>
-    </row>
-    <row r="733" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A733" s="11">
+      <c r="E732" s="8"/>
+      <c r="F732" s="8"/>
+    </row>
+    <row r="733" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A733" s="2">
         <v>46281</v>
       </c>
-      <c r="B733" s="12">
+      <c r="B733" s="10">
         <v>0.70833333333333337</v>
       </c>
       <c r="C733" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D733" s="14" t="s">
+      <c r="D733" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="E733" s="14"/>
-      <c r="F733" s="14"/>
-      <c r="G733" s="15"/>
-      <c r="H733" s="15"/>
-      <c r="I733" s="15"/>
-      <c r="J733" s="15"/>
-    </row>
-    <row r="734" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A734" s="11">
+      <c r="E733" s="8"/>
+      <c r="F733" s="8"/>
+    </row>
+    <row r="734" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A734" s="2">
         <v>46282</v>
       </c>
-      <c r="B734" s="12">
+      <c r="B734" s="10">
         <v>0.2638888888888889</v>
       </c>
-      <c r="C734" s="13" t="s">
+      <c r="C734" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D734" s="14" t="s">
+      <c r="D734" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="E734" s="14"/>
-      <c r="F734" s="14"/>
-      <c r="G734" s="15"/>
-      <c r="H734" s="15"/>
-      <c r="I734" s="15"/>
-      <c r="J734" s="15"/>
-    </row>
-    <row r="735" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A735" s="11">
+      <c r="E734" s="8"/>
+      <c r="F734" s="8"/>
+    </row>
+    <row r="735" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A735" s="2">
         <v>46282</v>
       </c>
-      <c r="B735" s="12">
+      <c r="B735" s="10">
         <v>0.30555555555555558</v>
       </c>
-      <c r="C735" s="13" t="s">
+      <c r="C735" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D735" s="14" t="s">
+      <c r="D735" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="E735" s="14"/>
-      <c r="F735" s="14"/>
-      <c r="G735" s="15"/>
-      <c r="H735" s="15"/>
-      <c r="I735" s="15"/>
-      <c r="J735" s="15"/>
-    </row>
-    <row r="736" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A736" s="11">
+      <c r="E735" s="8"/>
+      <c r="F735" s="8"/>
+    </row>
+    <row r="736" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A736" s="2">
         <v>46282</v>
       </c>
-      <c r="B736" s="12"/>
-      <c r="C736" s="13" t="s">
+      <c r="B736" s="10"/>
+      <c r="C736" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D736" s="14" t="s">
+      <c r="D736" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="E736" s="14"/>
-      <c r="F736" s="14"/>
-      <c r="G736" s="15"/>
-      <c r="H736" s="15"/>
-      <c r="I736" s="15"/>
-      <c r="J736" s="15"/>
-    </row>
-    <row r="737" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A737" s="11">
+      <c r="E736" s="8"/>
+      <c r="F736" s="8"/>
+    </row>
+    <row r="737" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A737" s="2">
         <v>46282</v>
       </c>
-      <c r="B737" s="12"/>
-      <c r="C737" s="13" t="s">
+      <c r="B737" s="10"/>
+      <c r="C737" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D737" s="14" t="s">
+      <c r="D737" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="E737" s="14"/>
-      <c r="F737" s="14"/>
-      <c r="G737" s="15"/>
-      <c r="H737" s="15"/>
-      <c r="I737" s="15"/>
-      <c r="J737" s="15"/>
-    </row>
-    <row r="738" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A738" s="11">
+      <c r="E737" s="8"/>
+      <c r="F737" s="8"/>
+    </row>
+    <row r="738" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A738" s="2">
         <v>46282</v>
       </c>
-      <c r="B738" s="12">
+      <c r="B738" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="C738" s="13" t="s">
+      <c r="C738" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D738" s="14" t="s">
+      <c r="D738" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="E738" s="14"/>
-      <c r="F738" s="14"/>
-      <c r="G738" s="15"/>
-      <c r="H738" s="15"/>
-      <c r="I738" s="15"/>
-      <c r="J738" s="15"/>
-    </row>
-    <row r="739" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A739" s="11">
+      <c r="E738" s="8"/>
+      <c r="F738" s="8"/>
+    </row>
+    <row r="739" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A739" s="2">
         <v>46282</v>
       </c>
-      <c r="B739" s="12"/>
-      <c r="C739" s="13" t="s">
+      <c r="B739" s="10"/>
+      <c r="C739" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D739" s="14" t="s">
+      <c r="D739" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E739" s="14"/>
-      <c r="F739" s="14"/>
+      <c r="E739" s="8"/>
+      <c r="F739" s="8"/>
+    </row>
+    <row r="740" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A740" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B740" s="11">
+        <v>0.2638888888888889</v>
+      </c>
+      <c r="C740" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D740" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="E740" s="12"/>
+      <c r="F740" s="12"/>
+    </row>
+    <row r="741" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A741" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B741" s="11">
+        <v>0.30555555555555558</v>
+      </c>
+      <c r="C741" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D741" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="E741" s="12"/>
+      <c r="F741" s="12"/>
+    </row>
+    <row r="742" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A742" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B742" s="11"/>
+      <c r="C742" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D742" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="E742" s="12"/>
+      <c r="F742" s="12"/>
+    </row>
+    <row r="743" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A743" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B743" s="11"/>
+      <c r="C743" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D743" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="E743" s="12"/>
+      <c r="F743" s="12"/>
+    </row>
+    <row r="744" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A744" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B744" s="11">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C744" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D744" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="E744" s="12"/>
+      <c r="F744" s="12"/>
+    </row>
+    <row r="745" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A745" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B745" s="11"/>
+      <c r="C745" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D745" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="E745" s="12"/>
+      <c r="F745" s="12"/>
+    </row>
+    <row r="746" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A746" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B746" s="11">
+        <v>0.34722222222222221</v>
+      </c>
+      <c r="C746" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D746" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="E746" s="12"/>
+      <c r="F746" s="12"/>
+    </row>
+    <row r="747" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A747" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B747" s="11"/>
+      <c r="C747" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D747" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="E747" s="12"/>
+      <c r="F747" s="12"/>
+    </row>
+    <row r="748" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A748" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B748" s="11">
+        <v>0.36805555555555558</v>
+      </c>
+      <c r="C748" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D748" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="E748" s="12"/>
+      <c r="F748" s="12"/>
+    </row>
+    <row r="749" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A749" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B749" s="11">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C749" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D749" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="E749" s="12"/>
+      <c r="F749" s="12"/>
+    </row>
+    <row r="750" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A750" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B750" s="11">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C750" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D750" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="E750" s="13"/>
+      <c r="F750" s="13"/>
+    </row>
+    <row r="751" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A751" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B751" s="11">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="C751" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D751" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="E751" s="13"/>
+      <c r="F751" s="13"/>
+    </row>
+    <row r="752" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A752" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B752" s="11"/>
+      <c r="C752" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D752" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E752" s="12"/>
+      <c r="F752" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CCE4DC1-542A-413C-85D9-8B4347B9EECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31E4B12B-3160-46F1-8387-BA50A33B3158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="326">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1241,6 +1241,44 @@
   </si>
   <si>
     <t>Attempted to push on at D11, but failed.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>C09</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sail to F2-C09</t>
+  </si>
+  <si>
+    <t>strong current and big wave,the boat's speed is only about 8 knots.</t>
+  </si>
+  <si>
+    <t>Pushing on F2-C09</t>
+  </si>
+  <si>
+    <t>LegA(GVI&amp; Anode &amp; scour &amp; mosaic )</t>
+  </si>
+  <si>
+    <t>RecoveryAIB-009</t>
+  </si>
+  <si>
+    <t>Waiting for Vesse</t>
+  </si>
+  <si>
+    <t>Replace Tetherline</t>
+  </si>
+  <si>
+    <t>Face DA1.2.3(GVI &amp; Anode )</t>
+  </si>
+  <si>
+    <t>Pushing on F2-C09,but failed</t>
+  </si>
+  <si>
+    <t>The weather conditions at the site remain unstable, so we are returning to port.</t>
+  </si>
+  <si>
+    <t>AIB-009 launch,but failed and Tetherline damaged and needs to be replaced</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1321,7 +1359,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1349,15 +1387,18 @@
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal 2" xfId="1" xr:uid="{71AF191C-2467-4F76-8A53-CA6D53E4DF10}"/>
@@ -1639,7 +1680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F752"/>
+  <dimension ref="A1:G794"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.69921875" style="1" bestFit="1" customWidth="1"/>
@@ -11445,7 +11486,7 @@
       <c r="E736" s="8"/>
       <c r="F736" s="8"/>
     </row>
-    <row r="737" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A737" s="2">
         <v>46282</v>
       </c>
@@ -11459,7 +11500,7 @@
       <c r="E737" s="8"/>
       <c r="F737" s="8"/>
     </row>
-    <row r="738" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A738" s="2">
         <v>46282</v>
       </c>
@@ -11475,7 +11516,7 @@
       <c r="E738" s="8"/>
       <c r="F738" s="8"/>
     </row>
-    <row r="739" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A739" s="2">
         <v>46282</v>
       </c>
@@ -11489,203 +11530,880 @@
       <c r="E739" s="8"/>
       <c r="F739" s="8"/>
     </row>
-    <row r="740" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A740" s="2">
         <v>46283</v>
       </c>
-      <c r="B740" s="11">
+      <c r="B740" s="10">
         <v>0.2638888888888889</v>
       </c>
       <c r="C740" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D740" s="12" t="s">
+      <c r="D740" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="E740" s="12"/>
-      <c r="F740" s="12"/>
-    </row>
-    <row r="741" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E740" s="8"/>
+      <c r="F740" s="8"/>
+    </row>
+    <row r="741" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A741" s="2">
         <v>46283</v>
       </c>
-      <c r="B741" s="11">
+      <c r="B741" s="10">
         <v>0.30555555555555558</v>
       </c>
       <c r="C741" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D741" s="12" t="s">
+      <c r="D741" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="E741" s="12"/>
-      <c r="F741" s="12"/>
-    </row>
-    <row r="742" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E741" s="8"/>
+      <c r="F741" s="8"/>
+    </row>
+    <row r="742" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A742" s="2">
         <v>46283</v>
       </c>
-      <c r="B742" s="11"/>
+      <c r="B742" s="10"/>
       <c r="C742" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D742" s="12" t="s">
+      <c r="D742" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="E742" s="12"/>
-      <c r="F742" s="12"/>
-    </row>
-    <row r="743" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E742" s="8"/>
+      <c r="F742" s="8"/>
+    </row>
+    <row r="743" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A743" s="2">
         <v>46283</v>
       </c>
-      <c r="B743" s="11"/>
+      <c r="B743" s="10"/>
       <c r="C743" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D743" s="12" t="s">
+      <c r="D743" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="E743" s="12"/>
-      <c r="F743" s="12"/>
-    </row>
-    <row r="744" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E743" s="8"/>
+      <c r="F743" s="8"/>
+    </row>
+    <row r="744" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A744" s="2">
         <v>46283</v>
       </c>
-      <c r="B744" s="11">
+      <c r="B744" s="10">
         <v>0.33333333333333331</v>
       </c>
       <c r="C744" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D744" s="12" t="s">
+      <c r="D744" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="E744" s="12"/>
-      <c r="F744" s="12"/>
-    </row>
-    <row r="745" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E744" s="8"/>
+      <c r="F744" s="8"/>
+    </row>
+    <row r="745" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A745" s="2">
         <v>46283</v>
       </c>
-      <c r="B745" s="11"/>
+      <c r="B745" s="10"/>
       <c r="C745" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D745" s="12" t="s">
+      <c r="D745" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="E745" s="12"/>
-      <c r="F745" s="12"/>
-    </row>
-    <row r="746" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E745" s="8"/>
+      <c r="F745" s="8"/>
+    </row>
+    <row r="746" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A746" s="2">
         <v>46283</v>
       </c>
-      <c r="B746" s="11">
+      <c r="B746" s="10">
         <v>0.34722222222222221</v>
       </c>
       <c r="C746" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D746" s="12" t="s">
+      <c r="D746" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="E746" s="12"/>
-      <c r="F746" s="12"/>
-    </row>
-    <row r="747" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E746" s="8"/>
+      <c r="F746" s="8"/>
+    </row>
+    <row r="747" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A747" s="2">
         <v>46283</v>
       </c>
-      <c r="B747" s="11"/>
+      <c r="B747" s="10"/>
       <c r="C747" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D747" s="12" t="s">
+      <c r="D747" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="E747" s="12"/>
-      <c r="F747" s="12"/>
-    </row>
-    <row r="748" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E747" s="8"/>
+      <c r="F747" s="8"/>
+    </row>
+    <row r="748" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A748" s="2">
         <v>46283</v>
       </c>
-      <c r="B748" s="11">
+      <c r="B748" s="10">
         <v>0.36805555555555558</v>
       </c>
       <c r="C748" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D748" s="12" t="s">
+      <c r="D748" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="E748" s="12"/>
-      <c r="F748" s="12"/>
-    </row>
-    <row r="749" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E748" s="8"/>
+      <c r="F748" s="8"/>
+    </row>
+    <row r="749" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A749" s="2">
         <v>46283</v>
       </c>
-      <c r="B749" s="11">
+      <c r="B749" s="10">
         <v>0.3923611111111111</v>
       </c>
       <c r="C749" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D749" s="12" t="s">
+      <c r="D749" s="8" t="s">
         <v>313</v>
       </c>
-      <c r="E749" s="12"/>
-      <c r="F749" s="12"/>
-    </row>
-    <row r="750" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E749" s="8"/>
+      <c r="F749" s="8"/>
+    </row>
+    <row r="750" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A750" s="2">
         <v>46283</v>
       </c>
-      <c r="B750" s="11">
+      <c r="B750" s="10">
         <v>0.39583333333333331</v>
       </c>
       <c r="C750" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D750" s="13" t="s">
+      <c r="D750" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="E750" s="13"/>
-      <c r="F750" s="13"/>
-    </row>
-    <row r="751" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E750" s="11"/>
+      <c r="F750" s="11"/>
+    </row>
+    <row r="751" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A751" s="2">
         <v>46283</v>
       </c>
-      <c r="B751" s="11">
+      <c r="B751" s="10">
         <v>0.4861111111111111</v>
       </c>
       <c r="C751" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D751" s="13" t="s">
+      <c r="D751" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="E751" s="13"/>
-      <c r="F751" s="13"/>
-    </row>
-    <row r="752" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A752" s="2">
+      <c r="E751" s="11"/>
+      <c r="F751" s="11"/>
+    </row>
+    <row r="752" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A752" s="12">
         <v>46283</v>
       </c>
-      <c r="B752" s="11"/>
-      <c r="C752" s="1" t="s">
+      <c r="B752" s="13"/>
+      <c r="C752" s="14" t="s">
         <v>305</v>
       </c>
-      <c r="D752" s="12" t="s">
+      <c r="D752" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="E752" s="12"/>
-      <c r="F752" s="12"/>
+      <c r="E752" s="15"/>
+      <c r="F752" s="15"/>
+      <c r="G752" s="16"/>
+    </row>
+    <row r="753" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A753" s="12">
+        <v>46284</v>
+      </c>
+      <c r="B753" s="13">
+        <v>0.21458333333333332</v>
+      </c>
+      <c r="C753" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D753" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="E753" s="15"/>
+      <c r="F753" s="15"/>
+      <c r="G753" s="16"/>
+    </row>
+    <row r="754" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A754" s="12">
+        <v>46284</v>
+      </c>
+      <c r="B754" s="13"/>
+      <c r="C754" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D754" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="E754" s="15"/>
+      <c r="F754" s="15"/>
+      <c r="G754" s="16"/>
+    </row>
+    <row r="755" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A755" s="12">
+        <v>46284</v>
+      </c>
+      <c r="B755" s="13">
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="C755" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D755" s="15" t="s">
+        <v>317</v>
+      </c>
+      <c r="E755" s="15"/>
+      <c r="F755" s="15"/>
+      <c r="G755" s="16"/>
+    </row>
+    <row r="756" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A756" s="12">
+        <v>46284</v>
+      </c>
+      <c r="B756" s="13"/>
+      <c r="C756" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D756" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="E756" s="15"/>
+      <c r="F756" s="15"/>
+      <c r="G756" s="16"/>
+    </row>
+    <row r="757" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A757" s="12">
+        <v>46284</v>
+      </c>
+      <c r="B757" s="13">
+        <v>0.43402777777777779</v>
+      </c>
+      <c r="C757" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D757" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="E757" s="15"/>
+      <c r="F757" s="15"/>
+      <c r="G757" s="16"/>
+    </row>
+    <row r="758" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A758" s="12">
+        <v>46284</v>
+      </c>
+      <c r="B758" s="13">
+        <v>0.45694444444444443</v>
+      </c>
+      <c r="C758" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D758" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="E758" s="15"/>
+      <c r="F758" s="15"/>
+      <c r="G758" s="16"/>
+    </row>
+    <row r="759" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A759" s="12">
+        <v>46284</v>
+      </c>
+      <c r="B759" s="13"/>
+      <c r="C759" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D759" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="E759" s="15"/>
+      <c r="F759" s="15"/>
+      <c r="G759" s="16"/>
+    </row>
+    <row r="760" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A760" s="12">
+        <v>46284</v>
+      </c>
+      <c r="B760" s="13">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="C760" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D760" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="E760" s="15"/>
+      <c r="F760" s="15"/>
+      <c r="G760" s="16"/>
+    </row>
+    <row r="761" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A761" s="12">
+        <v>46284</v>
+      </c>
+      <c r="B761" s="13"/>
+      <c r="C761" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D761" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="E761" s="15"/>
+      <c r="F761" s="15"/>
+      <c r="G761" s="16"/>
+    </row>
+    <row r="762" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A762" s="12">
+        <v>46284</v>
+      </c>
+      <c r="B762" s="13"/>
+      <c r="C762" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D762" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="E762" s="15"/>
+      <c r="F762" s="15"/>
+      <c r="G762" s="16"/>
+    </row>
+    <row r="763" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A763" s="12">
+        <v>46284</v>
+      </c>
+      <c r="B763" s="13">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C763" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D763" s="15" t="s">
+        <v>320</v>
+      </c>
+      <c r="E763" s="15"/>
+      <c r="F763" s="15"/>
+      <c r="G763" s="16"/>
+    </row>
+    <row r="764" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A764" s="12">
+        <v>46284</v>
+      </c>
+      <c r="B764" s="13">
+        <v>0.55138888888888893</v>
+      </c>
+      <c r="C764" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D764" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="E764" s="15"/>
+      <c r="F764" s="15"/>
+      <c r="G764" s="16"/>
+    </row>
+    <row r="765" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A765" s="12">
+        <v>46284</v>
+      </c>
+      <c r="B765" s="13"/>
+      <c r="C765" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D765" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="E765" s="15"/>
+      <c r="F765" s="15"/>
+      <c r="G765" s="16"/>
+    </row>
+    <row r="766" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A766" s="12">
+        <v>46284</v>
+      </c>
+      <c r="B766" s="13">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C766" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D766" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="E766" s="15"/>
+      <c r="F766" s="15"/>
+      <c r="G766" s="16"/>
+    </row>
+    <row r="767" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A767" s="12">
+        <v>46284</v>
+      </c>
+      <c r="B767" s="13"/>
+      <c r="C767" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D767" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E767" s="15"/>
+      <c r="F767" s="15"/>
+      <c r="G767" s="16"/>
+    </row>
+    <row r="768" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A768" s="12">
+        <v>46285</v>
+      </c>
+      <c r="B768" s="13">
+        <v>0.25347222222222221</v>
+      </c>
+      <c r="C768" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D768" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="E768" s="15"/>
+      <c r="F768" s="15"/>
+      <c r="G768" s="16"/>
+    </row>
+    <row r="769" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A769" s="12">
+        <v>46285</v>
+      </c>
+      <c r="B769" s="13">
+        <v>0.3527777777777778</v>
+      </c>
+      <c r="C769" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D769" s="15" t="s">
+        <v>317</v>
+      </c>
+      <c r="E769" s="15"/>
+      <c r="F769" s="15"/>
+      <c r="G769" s="16"/>
+    </row>
+    <row r="770" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A770" s="12">
+        <v>46285</v>
+      </c>
+      <c r="B770" s="13"/>
+      <c r="C770" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D770" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="E770" s="15"/>
+      <c r="F770" s="15"/>
+      <c r="G770" s="16"/>
+    </row>
+    <row r="771" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+      <c r="A771" s="12">
+        <v>46285</v>
+      </c>
+      <c r="B771" s="13">
+        <v>0.38611111111111113</v>
+      </c>
+      <c r="C771" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D771" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="E771" s="15"/>
+      <c r="F771" s="15"/>
+      <c r="G771" s="16"/>
+    </row>
+    <row r="772" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A772" s="12">
+        <v>46285</v>
+      </c>
+      <c r="B772" s="13">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C772" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D772" s="15" t="s">
+        <v>321</v>
+      </c>
+      <c r="E772" s="15"/>
+      <c r="F772" s="15"/>
+      <c r="G772" s="16"/>
+    </row>
+    <row r="773" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A773" s="12">
+        <v>46285</v>
+      </c>
+      <c r="B773" s="13">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C773" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D773" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="E773" s="15"/>
+      <c r="F773" s="15"/>
+      <c r="G773" s="16"/>
+    </row>
+    <row r="774" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A774" s="12">
+        <v>46285</v>
+      </c>
+      <c r="B774" s="13"/>
+      <c r="C774" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D774" s="15" t="s">
+        <v>322</v>
+      </c>
+      <c r="E774" s="15"/>
+      <c r="F774" s="15"/>
+      <c r="G774" s="16"/>
+    </row>
+    <row r="775" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A775" s="12">
+        <v>46285</v>
+      </c>
+      <c r="B775" s="13">
+        <v>0.46111111111111114</v>
+      </c>
+      <c r="C775" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D775" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="E775" s="15"/>
+      <c r="F775" s="15"/>
+      <c r="G775" s="16"/>
+    </row>
+    <row r="776" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A776" s="12">
+        <v>46285</v>
+      </c>
+      <c r="B776" s="13"/>
+      <c r="C776" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D776" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="E776" s="15"/>
+      <c r="F776" s="15"/>
+      <c r="G776" s="16"/>
+    </row>
+    <row r="777" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A777" s="12">
+        <v>46285</v>
+      </c>
+      <c r="B777" s="13"/>
+      <c r="C777" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D777" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="E777" s="15"/>
+      <c r="F777" s="15"/>
+      <c r="G777" s="16"/>
+    </row>
+    <row r="778" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A778" s="12">
+        <v>46285</v>
+      </c>
+      <c r="B778" s="13">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="C778" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D778" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="E778" s="15"/>
+      <c r="F778" s="15"/>
+      <c r="G778" s="16"/>
+    </row>
+    <row r="779" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A779" s="12">
+        <v>46285</v>
+      </c>
+      <c r="B779" s="13"/>
+      <c r="C779" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D779" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="E779" s="15"/>
+      <c r="F779" s="15"/>
+      <c r="G779" s="16"/>
+    </row>
+    <row r="780" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A780" s="12">
+        <v>46285</v>
+      </c>
+      <c r="B780" s="13">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C780" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D780" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="E780" s="15"/>
+      <c r="F780" s="15"/>
+      <c r="G780" s="16"/>
+    </row>
+    <row r="781" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A781" s="12">
+        <v>46285</v>
+      </c>
+      <c r="B781" s="13"/>
+      <c r="C781" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D781" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E781" s="15"/>
+      <c r="F781" s="15"/>
+      <c r="G781" s="16"/>
+    </row>
+    <row r="782" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A782" s="12">
+        <v>46286</v>
+      </c>
+      <c r="B782" s="13">
+        <v>0.27430555555555558</v>
+      </c>
+      <c r="C782" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D782" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="E782" s="15"/>
+      <c r="F782" s="15"/>
+      <c r="G782" s="16"/>
+    </row>
+    <row r="783" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A783" s="12">
+        <v>46286</v>
+      </c>
+      <c r="B783" s="13">
+        <v>0.37847222222222221</v>
+      </c>
+      <c r="C783" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D783" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="E783" s="15"/>
+      <c r="F783" s="15"/>
+      <c r="G783" s="16"/>
+    </row>
+    <row r="784" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A784" s="12">
+        <v>46286</v>
+      </c>
+      <c r="B784" s="13"/>
+      <c r="C784" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D784" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E784" s="15"/>
+      <c r="F784" s="15"/>
+      <c r="G784" s="16"/>
+    </row>
+    <row r="785" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A785" s="12">
+        <v>46286</v>
+      </c>
+      <c r="B785" s="13">
+        <v>0.39791666666666664</v>
+      </c>
+      <c r="C785" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D785" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="E785" s="15"/>
+      <c r="F785" s="15"/>
+      <c r="G785" s="16"/>
+    </row>
+    <row r="786" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A786" s="12">
+        <v>46286</v>
+      </c>
+      <c r="B786" s="13"/>
+      <c r="C786" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D786" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="E786" s="15"/>
+      <c r="F786" s="15"/>
+      <c r="G786" s="16"/>
+    </row>
+    <row r="787" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A787" s="12">
+        <v>46286</v>
+      </c>
+      <c r="B787" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="C787" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D787" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="E787" s="15"/>
+      <c r="F787" s="15"/>
+      <c r="G787" s="16"/>
+    </row>
+    <row r="788" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A788" s="12">
+        <v>46286</v>
+      </c>
+      <c r="B788" s="13"/>
+      <c r="C788" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D788" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E788" s="15"/>
+      <c r="F788" s="15"/>
+      <c r="G788" s="16"/>
+    </row>
+    <row r="789" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A789" s="12">
+        <v>46287</v>
+      </c>
+      <c r="B789" s="13">
+        <v>0.27430555555555558</v>
+      </c>
+      <c r="C789" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D789" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="E789" s="15"/>
+      <c r="F789" s="15"/>
+      <c r="G789" s="16"/>
+    </row>
+    <row r="790" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A790" s="12">
+        <v>46287</v>
+      </c>
+      <c r="B790" s="13">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C790" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D790" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="E790" s="15"/>
+      <c r="F790" s="15"/>
+      <c r="G790" s="16"/>
+    </row>
+    <row r="791" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A791" s="12">
+        <v>46287</v>
+      </c>
+      <c r="B791" s="13"/>
+      <c r="C791" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D791" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E791" s="15"/>
+      <c r="F791" s="15"/>
+      <c r="G791" s="16"/>
+    </row>
+    <row r="792" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A792" s="12">
+        <v>46287</v>
+      </c>
+      <c r="B792" s="13"/>
+      <c r="C792" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D792" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="E792" s="15"/>
+      <c r="F792" s="15"/>
+      <c r="G792" s="16"/>
+    </row>
+    <row r="793" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A793" s="12">
+        <v>46287</v>
+      </c>
+      <c r="B793" s="13">
+        <v>0.32291666666666669</v>
+      </c>
+      <c r="C793" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D793" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="E793" s="15"/>
+      <c r="F793" s="15"/>
+      <c r="G793" s="16"/>
+    </row>
+    <row r="794" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A794" s="12">
+        <v>46287</v>
+      </c>
+      <c r="B794" s="13"/>
+      <c r="C794" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D794" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E794" s="15"/>
+      <c r="F794" s="15"/>
+      <c r="G794" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31E4B12B-3160-46F1-8387-BA50A33B3158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A3CEA4-42E1-4D14-8CE8-1B494D6BF397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="326">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1680,7 +1680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G794"/>
+  <dimension ref="A1:K801"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.69921875" style="1" bestFit="1" customWidth="1"/>
@@ -11486,7 +11486,7 @@
       <c r="E736" s="8"/>
       <c r="F736" s="8"/>
     </row>
-    <row r="737" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A737" s="2">
         <v>46282</v>
       </c>
@@ -11500,7 +11500,7 @@
       <c r="E737" s="8"/>
       <c r="F737" s="8"/>
     </row>
-    <row r="738" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A738" s="2">
         <v>46282</v>
       </c>
@@ -11516,7 +11516,7 @@
       <c r="E738" s="8"/>
       <c r="F738" s="8"/>
     </row>
-    <row r="739" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A739" s="2">
         <v>46282</v>
       </c>
@@ -11530,7 +11530,7 @@
       <c r="E739" s="8"/>
       <c r="F739" s="8"/>
     </row>
-    <row r="740" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A740" s="2">
         <v>46283</v>
       </c>
@@ -11546,7 +11546,7 @@
       <c r="E740" s="8"/>
       <c r="F740" s="8"/>
     </row>
-    <row r="741" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A741" s="2">
         <v>46283</v>
       </c>
@@ -11562,7 +11562,7 @@
       <c r="E741" s="8"/>
       <c r="F741" s="8"/>
     </row>
-    <row r="742" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A742" s="2">
         <v>46283</v>
       </c>
@@ -11576,7 +11576,7 @@
       <c r="E742" s="8"/>
       <c r="F742" s="8"/>
     </row>
-    <row r="743" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A743" s="2">
         <v>46283</v>
       </c>
@@ -11590,7 +11590,7 @@
       <c r="E743" s="8"/>
       <c r="F743" s="8"/>
     </row>
-    <row r="744" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A744" s="2">
         <v>46283</v>
       </c>
@@ -11606,7 +11606,7 @@
       <c r="E744" s="8"/>
       <c r="F744" s="8"/>
     </row>
-    <row r="745" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A745" s="2">
         <v>46283</v>
       </c>
@@ -11620,7 +11620,7 @@
       <c r="E745" s="8"/>
       <c r="F745" s="8"/>
     </row>
-    <row r="746" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A746" s="2">
         <v>46283</v>
       </c>
@@ -11636,7 +11636,7 @@
       <c r="E746" s="8"/>
       <c r="F746" s="8"/>
     </row>
-    <row r="747" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A747" s="2">
         <v>46283</v>
       </c>
@@ -11650,7 +11650,7 @@
       <c r="E747" s="8"/>
       <c r="F747" s="8"/>
     </row>
-    <row r="748" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A748" s="2">
         <v>46283</v>
       </c>
@@ -11666,7 +11666,7 @@
       <c r="E748" s="8"/>
       <c r="F748" s="8"/>
     </row>
-    <row r="749" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A749" s="2">
         <v>46283</v>
       </c>
@@ -11682,7 +11682,7 @@
       <c r="E749" s="8"/>
       <c r="F749" s="8"/>
     </row>
-    <row r="750" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A750" s="2">
         <v>46283</v>
       </c>
@@ -11698,7 +11698,7 @@
       <c r="E750" s="11"/>
       <c r="F750" s="11"/>
     </row>
-    <row r="751" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A751" s="2">
         <v>46283</v>
       </c>
@@ -11714,696 +11714,776 @@
       <c r="E751" s="11"/>
       <c r="F751" s="11"/>
     </row>
-    <row r="752" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A752" s="12">
+    <row r="752" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A752" s="2">
         <v>46283</v>
       </c>
-      <c r="B752" s="13"/>
-      <c r="C752" s="14" t="s">
+      <c r="B752" s="10"/>
+      <c r="C752" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D752" s="15" t="s">
+      <c r="D752" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E752" s="15"/>
-      <c r="F752" s="15"/>
-      <c r="G752" s="16"/>
-    </row>
-    <row r="753" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A753" s="12">
+      <c r="E752" s="8"/>
+      <c r="F752" s="8"/>
+    </row>
+    <row r="753" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A753" s="2">
         <v>46284</v>
       </c>
-      <c r="B753" s="13">
+      <c r="B753" s="10">
         <v>0.21458333333333332</v>
       </c>
-      <c r="C753" s="14" t="s">
+      <c r="C753" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D753" s="15" t="s">
+      <c r="D753" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="E753" s="15"/>
-      <c r="F753" s="15"/>
-      <c r="G753" s="16"/>
-    </row>
-    <row r="754" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A754" s="12">
+      <c r="E753" s="8"/>
+      <c r="F753" s="8"/>
+    </row>
+    <row r="754" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A754" s="2">
         <v>46284</v>
       </c>
-      <c r="B754" s="13"/>
-      <c r="C754" s="14" t="s">
+      <c r="B754" s="10"/>
+      <c r="C754" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D754" s="15" t="s">
+      <c r="D754" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="E754" s="15"/>
-      <c r="F754" s="15"/>
-      <c r="G754" s="16"/>
-    </row>
-    <row r="755" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A755" s="12">
+      <c r="E754" s="8"/>
+      <c r="F754" s="8"/>
+    </row>
+    <row r="755" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A755" s="2">
         <v>46284</v>
       </c>
-      <c r="B755" s="13">
+      <c r="B755" s="10">
         <v>0.40972222222222221</v>
       </c>
-      <c r="C755" s="14" t="s">
+      <c r="C755" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D755" s="15" t="s">
+      <c r="D755" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="E755" s="15"/>
-      <c r="F755" s="15"/>
-      <c r="G755" s="16"/>
-    </row>
-    <row r="756" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A756" s="12">
+      <c r="E755" s="8"/>
+      <c r="F755" s="8"/>
+    </row>
+    <row r="756" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A756" s="2">
         <v>46284</v>
       </c>
-      <c r="B756" s="13"/>
-      <c r="C756" s="14" t="s">
+      <c r="B756" s="10"/>
+      <c r="C756" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D756" s="15" t="s">
+      <c r="D756" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="E756" s="15"/>
-      <c r="F756" s="15"/>
-      <c r="G756" s="16"/>
-    </row>
-    <row r="757" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A757" s="12">
+      <c r="E756" s="8"/>
+      <c r="F756" s="8"/>
+    </row>
+    <row r="757" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A757" s="2">
         <v>46284</v>
       </c>
-      <c r="B757" s="13">
+      <c r="B757" s="10">
         <v>0.43402777777777779</v>
       </c>
-      <c r="C757" s="14" t="s">
+      <c r="C757" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D757" s="15" t="s">
+      <c r="D757" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="E757" s="15"/>
-      <c r="F757" s="15"/>
-      <c r="G757" s="16"/>
-    </row>
-    <row r="758" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A758" s="12">
+      <c r="E757" s="8"/>
+      <c r="F757" s="8"/>
+    </row>
+    <row r="758" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A758" s="2">
         <v>46284</v>
       </c>
-      <c r="B758" s="13">
+      <c r="B758" s="10">
         <v>0.45694444444444443</v>
       </c>
-      <c r="C758" s="14" t="s">
+      <c r="C758" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D758" s="15" t="s">
+      <c r="D758" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="E758" s="15"/>
-      <c r="F758" s="15"/>
-      <c r="G758" s="16"/>
-    </row>
-    <row r="759" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A759" s="12">
+      <c r="E758" s="8"/>
+      <c r="F758" s="8"/>
+    </row>
+    <row r="759" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A759" s="2">
         <v>46284</v>
       </c>
-      <c r="B759" s="13"/>
-      <c r="C759" s="14" t="s">
+      <c r="B759" s="10"/>
+      <c r="C759" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D759" s="15" t="s">
+      <c r="D759" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="E759" s="15"/>
-      <c r="F759" s="15"/>
-      <c r="G759" s="16"/>
-    </row>
-    <row r="760" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A760" s="12">
+      <c r="E759" s="8"/>
+      <c r="F759" s="8"/>
+    </row>
+    <row r="760" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A760" s="2">
         <v>46284</v>
       </c>
-      <c r="B760" s="13">
+      <c r="B760" s="10">
         <v>0.48958333333333331</v>
       </c>
-      <c r="C760" s="14" t="s">
+      <c r="C760" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D760" s="15" t="s">
+      <c r="D760" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="E760" s="15"/>
-      <c r="F760" s="15"/>
-      <c r="G760" s="16"/>
-    </row>
-    <row r="761" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A761" s="12">
+      <c r="E760" s="8"/>
+      <c r="F760" s="8"/>
+    </row>
+    <row r="761" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A761" s="2">
         <v>46284</v>
       </c>
-      <c r="B761" s="13"/>
-      <c r="C761" s="14" t="s">
+      <c r="B761" s="10"/>
+      <c r="C761" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D761" s="15" t="s">
+      <c r="D761" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="E761" s="15"/>
-      <c r="F761" s="15"/>
-      <c r="G761" s="16"/>
-    </row>
-    <row r="762" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A762" s="12">
+      <c r="E761" s="8"/>
+      <c r="F761" s="8"/>
+    </row>
+    <row r="762" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A762" s="2">
         <v>46284</v>
       </c>
-      <c r="B762" s="13"/>
-      <c r="C762" s="14" t="s">
+      <c r="B762" s="10"/>
+      <c r="C762" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D762" s="15" t="s">
+      <c r="D762" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="E762" s="15"/>
-      <c r="F762" s="15"/>
-      <c r="G762" s="16"/>
-    </row>
-    <row r="763" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A763" s="12">
+      <c r="E762" s="8"/>
+      <c r="F762" s="8"/>
+    </row>
+    <row r="763" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A763" s="2">
         <v>46284</v>
       </c>
-      <c r="B763" s="13">
+      <c r="B763" s="10">
         <v>0.52083333333333337</v>
       </c>
-      <c r="C763" s="14" t="s">
+      <c r="C763" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D763" s="15" t="s">
+      <c r="D763" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="E763" s="15"/>
-      <c r="F763" s="15"/>
-      <c r="G763" s="16"/>
-    </row>
-    <row r="764" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A764" s="12">
+      <c r="E763" s="8"/>
+      <c r="F763" s="8"/>
+    </row>
+    <row r="764" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A764" s="2">
         <v>46284</v>
       </c>
-      <c r="B764" s="13">
+      <c r="B764" s="10">
         <v>0.55138888888888893</v>
       </c>
-      <c r="C764" s="14" t="s">
+      <c r="C764" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D764" s="15" t="s">
+      <c r="D764" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="E764" s="15"/>
-      <c r="F764" s="15"/>
-      <c r="G764" s="16"/>
-    </row>
-    <row r="765" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A765" s="12">
+      <c r="E764" s="8"/>
+      <c r="F764" s="8"/>
+    </row>
+    <row r="765" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A765" s="2">
         <v>46284</v>
       </c>
-      <c r="B765" s="13"/>
-      <c r="C765" s="14" t="s">
+      <c r="B765" s="10"/>
+      <c r="C765" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D765" s="15" t="s">
+      <c r="D765" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="E765" s="15"/>
-      <c r="F765" s="15"/>
-      <c r="G765" s="16"/>
-    </row>
-    <row r="766" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A766" s="12">
+      <c r="E765" s="8"/>
+      <c r="F765" s="8"/>
+    </row>
+    <row r="766" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A766" s="2">
         <v>46284</v>
       </c>
-      <c r="B766" s="13">
+      <c r="B766" s="10">
         <v>0.66666666666666663</v>
       </c>
-      <c r="C766" s="14" t="s">
+      <c r="C766" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D766" s="15" t="s">
+      <c r="D766" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="E766" s="15"/>
-      <c r="F766" s="15"/>
-      <c r="G766" s="16"/>
-    </row>
-    <row r="767" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A767" s="12">
+      <c r="E766" s="8"/>
+      <c r="F766" s="8"/>
+    </row>
+    <row r="767" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A767" s="2">
         <v>46284</v>
       </c>
-      <c r="B767" s="13"/>
-      <c r="C767" s="14" t="s">
+      <c r="B767" s="10"/>
+      <c r="C767" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D767" s="15" t="s">
+      <c r="D767" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E767" s="15"/>
-      <c r="F767" s="15"/>
-      <c r="G767" s="16"/>
-    </row>
-    <row r="768" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A768" s="12">
+      <c r="E767" s="8"/>
+      <c r="F767" s="8"/>
+    </row>
+    <row r="768" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A768" s="2">
         <v>46285</v>
       </c>
-      <c r="B768" s="13">
+      <c r="B768" s="10">
         <v>0.25347222222222221</v>
       </c>
-      <c r="C768" s="14" t="s">
+      <c r="C768" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D768" s="15" t="s">
+      <c r="D768" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="E768" s="15"/>
-      <c r="F768" s="15"/>
-      <c r="G768" s="16"/>
-    </row>
-    <row r="769" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A769" s="12">
+      <c r="E768" s="8"/>
+      <c r="F768" s="8"/>
+    </row>
+    <row r="769" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A769" s="2">
         <v>46285</v>
       </c>
-      <c r="B769" s="13">
+      <c r="B769" s="10">
         <v>0.3527777777777778</v>
       </c>
-      <c r="C769" s="14" t="s">
+      <c r="C769" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D769" s="15" t="s">
+      <c r="D769" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="E769" s="15"/>
-      <c r="F769" s="15"/>
-      <c r="G769" s="16"/>
-    </row>
-    <row r="770" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A770" s="12">
+      <c r="E769" s="8"/>
+      <c r="F769" s="8"/>
+    </row>
+    <row r="770" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A770" s="2">
         <v>46285</v>
       </c>
-      <c r="B770" s="13"/>
-      <c r="C770" s="14" t="s">
+      <c r="B770" s="10"/>
+      <c r="C770" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D770" s="15" t="s">
+      <c r="D770" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="E770" s="15"/>
-      <c r="F770" s="15"/>
-      <c r="G770" s="16"/>
-    </row>
-    <row r="771" spans="1:7" ht="26" x14ac:dyDescent="0.3">
-      <c r="A771" s="12">
+      <c r="E770" s="8"/>
+      <c r="F770" s="8"/>
+    </row>
+    <row r="771" spans="1:6" ht="26" x14ac:dyDescent="0.3">
+      <c r="A771" s="2">
         <v>46285</v>
       </c>
-      <c r="B771" s="13">
+      <c r="B771" s="10">
         <v>0.38611111111111113</v>
       </c>
-      <c r="C771" s="14" t="s">
+      <c r="C771" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D771" s="15" t="s">
+      <c r="D771" s="8" t="s">
         <v>325</v>
       </c>
-      <c r="E771" s="15"/>
-      <c r="F771" s="15"/>
-      <c r="G771" s="16"/>
-    </row>
-    <row r="772" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A772" s="12">
+      <c r="E771" s="8"/>
+      <c r="F771" s="8"/>
+    </row>
+    <row r="772" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A772" s="2">
         <v>46285</v>
       </c>
-      <c r="B772" s="13">
+      <c r="B772" s="10">
         <v>0.3923611111111111</v>
       </c>
-      <c r="C772" s="14" t="s">
+      <c r="C772" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D772" s="15" t="s">
+      <c r="D772" s="8" t="s">
         <v>321</v>
       </c>
-      <c r="E772" s="15"/>
-      <c r="F772" s="15"/>
-      <c r="G772" s="16"/>
-    </row>
-    <row r="773" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A773" s="12">
+      <c r="E772" s="8"/>
+      <c r="F772" s="8"/>
+    </row>
+    <row r="773" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A773" s="2">
         <v>46285</v>
       </c>
-      <c r="B773" s="13">
+      <c r="B773" s="10">
         <v>0.41666666666666669</v>
       </c>
-      <c r="C773" s="14" t="s">
+      <c r="C773" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D773" s="15" t="s">
+      <c r="D773" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="E773" s="15"/>
-      <c r="F773" s="15"/>
-      <c r="G773" s="16"/>
-    </row>
-    <row r="774" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A774" s="12">
+      <c r="E773" s="8"/>
+      <c r="F773" s="8"/>
+    </row>
+    <row r="774" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A774" s="2">
         <v>46285</v>
       </c>
-      <c r="B774" s="13"/>
-      <c r="C774" s="14" t="s">
+      <c r="B774" s="10"/>
+      <c r="C774" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D774" s="15" t="s">
+      <c r="D774" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="E774" s="15"/>
-      <c r="F774" s="15"/>
-      <c r="G774" s="16"/>
-    </row>
-    <row r="775" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A775" s="12">
+      <c r="E774" s="8"/>
+      <c r="F774" s="8"/>
+    </row>
+    <row r="775" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A775" s="2">
         <v>46285</v>
       </c>
-      <c r="B775" s="13">
+      <c r="B775" s="10">
         <v>0.46111111111111114</v>
       </c>
-      <c r="C775" s="14" t="s">
+      <c r="C775" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D775" s="15" t="s">
+      <c r="D775" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="E775" s="15"/>
-      <c r="F775" s="15"/>
-      <c r="G775" s="16"/>
-    </row>
-    <row r="776" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A776" s="12">
+      <c r="E775" s="8"/>
+      <c r="F775" s="8"/>
+    </row>
+    <row r="776" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A776" s="2">
         <v>46285</v>
       </c>
-      <c r="B776" s="13"/>
-      <c r="C776" s="14" t="s">
+      <c r="B776" s="10"/>
+      <c r="C776" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D776" s="15" t="s">
+      <c r="D776" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="E776" s="15"/>
-      <c r="F776" s="15"/>
-      <c r="G776" s="16"/>
-    </row>
-    <row r="777" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A777" s="12">
+      <c r="E776" s="8"/>
+      <c r="F776" s="8"/>
+    </row>
+    <row r="777" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A777" s="2">
         <v>46285</v>
       </c>
-      <c r="B777" s="13"/>
-      <c r="C777" s="14" t="s">
+      <c r="B777" s="10"/>
+      <c r="C777" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D777" s="15" t="s">
+      <c r="D777" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="E777" s="15"/>
-      <c r="F777" s="15"/>
-      <c r="G777" s="16"/>
-    </row>
-    <row r="778" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A778" s="12">
+      <c r="E777" s="8"/>
+      <c r="F777" s="8"/>
+    </row>
+    <row r="778" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A778" s="2">
         <v>46285</v>
       </c>
-      <c r="B778" s="13">
+      <c r="B778" s="10">
         <v>0.4861111111111111</v>
       </c>
-      <c r="C778" s="14" t="s">
+      <c r="C778" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D778" s="15" t="s">
+      <c r="D778" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="E778" s="15"/>
-      <c r="F778" s="15"/>
-      <c r="G778" s="16"/>
-    </row>
-    <row r="779" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A779" s="12">
+      <c r="E778" s="8"/>
+      <c r="F778" s="8"/>
+    </row>
+    <row r="779" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A779" s="2">
         <v>46285</v>
       </c>
-      <c r="B779" s="13"/>
-      <c r="C779" s="14" t="s">
+      <c r="B779" s="10"/>
+      <c r="C779" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D779" s="15" t="s">
+      <c r="D779" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="E779" s="15"/>
-      <c r="F779" s="15"/>
-      <c r="G779" s="16"/>
-    </row>
-    <row r="780" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A780" s="12">
+      <c r="E779" s="8"/>
+      <c r="F779" s="8"/>
+    </row>
+    <row r="780" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A780" s="2">
         <v>46285</v>
       </c>
-      <c r="B780" s="13">
+      <c r="B780" s="10">
         <v>0.58333333333333337</v>
       </c>
-      <c r="C780" s="14" t="s">
+      <c r="C780" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D780" s="15" t="s">
+      <c r="D780" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="E780" s="15"/>
-      <c r="F780" s="15"/>
-      <c r="G780" s="16"/>
-    </row>
-    <row r="781" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A781" s="12">
+      <c r="E780" s="8"/>
+      <c r="F780" s="8"/>
+    </row>
+    <row r="781" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A781" s="2">
         <v>46285</v>
       </c>
-      <c r="B781" s="13"/>
-      <c r="C781" s="14" t="s">
+      <c r="B781" s="10"/>
+      <c r="C781" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D781" s="15" t="s">
+      <c r="D781" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E781" s="15"/>
-      <c r="F781" s="15"/>
-      <c r="G781" s="16"/>
-    </row>
-    <row r="782" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A782" s="12">
+      <c r="E781" s="8"/>
+      <c r="F781" s="8"/>
+    </row>
+    <row r="782" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A782" s="2">
         <v>46286</v>
       </c>
-      <c r="B782" s="13">
+      <c r="B782" s="10">
         <v>0.27430555555555558</v>
       </c>
-      <c r="C782" s="14" t="s">
+      <c r="C782" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D782" s="15" t="s">
+      <c r="D782" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="E782" s="15"/>
-      <c r="F782" s="15"/>
-      <c r="G782" s="16"/>
-    </row>
-    <row r="783" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A783" s="12">
+      <c r="E782" s="8"/>
+      <c r="F782" s="8"/>
+    </row>
+    <row r="783" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A783" s="2">
         <v>46286</v>
       </c>
-      <c r="B783" s="13">
+      <c r="B783" s="10">
         <v>0.37847222222222221</v>
       </c>
-      <c r="C783" s="14" t="s">
+      <c r="C783" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D783" s="15" t="s">
+      <c r="D783" s="8" t="s">
         <v>323</v>
       </c>
-      <c r="E783" s="15"/>
-      <c r="F783" s="15"/>
-      <c r="G783" s="16"/>
-    </row>
-    <row r="784" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A784" s="12">
+      <c r="E783" s="8"/>
+      <c r="F783" s="8"/>
+    </row>
+    <row r="784" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A784" s="2">
         <v>46286</v>
       </c>
-      <c r="B784" s="13"/>
-      <c r="C784" s="14" t="s">
+      <c r="B784" s="10"/>
+      <c r="C784" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D784" s="15" t="s">
+      <c r="D784" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="E784" s="15"/>
-      <c r="F784" s="15"/>
-      <c r="G784" s="16"/>
-    </row>
-    <row r="785" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A785" s="12">
+      <c r="E784" s="8"/>
+      <c r="F784" s="8"/>
+    </row>
+    <row r="785" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A785" s="2">
         <v>46286</v>
       </c>
-      <c r="B785" s="13">
+      <c r="B785" s="10">
         <v>0.39791666666666664</v>
       </c>
-      <c r="C785" s="14" t="s">
+      <c r="C785" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D785" s="15" t="s">
+      <c r="D785" s="8" t="s">
         <v>324</v>
       </c>
-      <c r="E785" s="15"/>
-      <c r="F785" s="15"/>
-      <c r="G785" s="16"/>
-    </row>
-    <row r="786" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A786" s="12">
+      <c r="E785" s="8"/>
+      <c r="F785" s="8"/>
+    </row>
+    <row r="786" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A786" s="2">
         <v>46286</v>
       </c>
-      <c r="B786" s="13"/>
-      <c r="C786" s="14" t="s">
+      <c r="B786" s="10"/>
+      <c r="C786" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D786" s="15" t="s">
+      <c r="D786" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="E786" s="15"/>
-      <c r="F786" s="15"/>
-      <c r="G786" s="16"/>
-    </row>
-    <row r="787" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A787" s="12">
+      <c r="E786" s="8"/>
+      <c r="F786" s="8"/>
+    </row>
+    <row r="787" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A787" s="2">
         <v>46286</v>
       </c>
-      <c r="B787" s="13">
+      <c r="B787" s="10">
         <v>0.5</v>
       </c>
-      <c r="C787" s="14" t="s">
+      <c r="C787" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D787" s="15" t="s">
+      <c r="D787" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="E787" s="15"/>
-      <c r="F787" s="15"/>
-      <c r="G787" s="16"/>
-    </row>
-    <row r="788" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A788" s="12">
+      <c r="E787" s="8"/>
+      <c r="F787" s="8"/>
+    </row>
+    <row r="788" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A788" s="2">
         <v>46286</v>
       </c>
-      <c r="B788" s="13"/>
-      <c r="C788" s="14" t="s">
+      <c r="B788" s="10"/>
+      <c r="C788" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D788" s="15" t="s">
+      <c r="D788" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E788" s="15"/>
-      <c r="F788" s="15"/>
-      <c r="G788" s="16"/>
-    </row>
-    <row r="789" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A789" s="12">
+      <c r="E788" s="8"/>
+      <c r="F788" s="8"/>
+    </row>
+    <row r="789" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A789" s="2">
         <v>46287</v>
       </c>
-      <c r="B789" s="13">
+      <c r="B789" s="10">
         <v>0.27430555555555558</v>
       </c>
-      <c r="C789" s="14" t="s">
+      <c r="C789" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D789" s="15" t="s">
+      <c r="D789" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="E789" s="15"/>
-      <c r="F789" s="15"/>
-      <c r="G789" s="16"/>
-    </row>
-    <row r="790" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A790" s="12">
+      <c r="E789" s="8"/>
+      <c r="F789" s="8"/>
+    </row>
+    <row r="790" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A790" s="2">
         <v>46287</v>
       </c>
-      <c r="B790" s="13">
+      <c r="B790" s="10">
         <v>0.29166666666666669</v>
       </c>
-      <c r="C790" s="14" t="s">
+      <c r="C790" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D790" s="15" t="s">
+      <c r="D790" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="E790" s="15"/>
-      <c r="F790" s="15"/>
-      <c r="G790" s="16"/>
-    </row>
-    <row r="791" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A791" s="12">
+      <c r="E790" s="8"/>
+      <c r="F790" s="8"/>
+    </row>
+    <row r="791" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A791" s="2">
         <v>46287</v>
       </c>
-      <c r="B791" s="13"/>
-      <c r="C791" s="14" t="s">
+      <c r="B791" s="10"/>
+      <c r="C791" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D791" s="15" t="s">
+      <c r="D791" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="E791" s="15"/>
-      <c r="F791" s="15"/>
-      <c r="G791" s="16"/>
-    </row>
-    <row r="792" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A792" s="12">
+      <c r="E791" s="8"/>
+      <c r="F791" s="8"/>
+    </row>
+    <row r="792" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A792" s="2">
         <v>46287</v>
       </c>
-      <c r="B792" s="13"/>
-      <c r="C792" s="14" t="s">
+      <c r="B792" s="10"/>
+      <c r="C792" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D792" s="15" t="s">
+      <c r="D792" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="E792" s="15"/>
-      <c r="F792" s="15"/>
-      <c r="G792" s="16"/>
-    </row>
-    <row r="793" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A793" s="12">
+      <c r="E792" s="8"/>
+      <c r="F792" s="8"/>
+    </row>
+    <row r="793" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A793" s="2">
         <v>46287</v>
       </c>
-      <c r="B793" s="13">
+      <c r="B793" s="10">
         <v>0.32291666666666669</v>
       </c>
-      <c r="C793" s="14" t="s">
+      <c r="C793" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D793" s="15" t="s">
+      <c r="D793" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="E793" s="15"/>
-      <c r="F793" s="15"/>
-      <c r="G793" s="16"/>
-    </row>
-    <row r="794" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A794" s="12">
+      <c r="E793" s="8"/>
+      <c r="F793" s="8"/>
+    </row>
+    <row r="794" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A794" s="2">
         <v>46287</v>
       </c>
-      <c r="B794" s="13"/>
-      <c r="C794" s="14" t="s">
+      <c r="B794" s="10"/>
+      <c r="C794" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D794" s="15" t="s">
+      <c r="D794" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E794" s="15"/>
-      <c r="F794" s="15"/>
-      <c r="G794" s="16"/>
+      <c r="E794" s="8"/>
+      <c r="F794" s="8"/>
+    </row>
+    <row r="795" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A795" s="12">
+        <v>46288</v>
+      </c>
+      <c r="B795" s="13">
+        <v>0.375</v>
+      </c>
+      <c r="C795" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="D795" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E795" s="15"/>
+      <c r="F795" s="15"/>
+      <c r="G795" s="16"/>
+      <c r="H795" s="16"/>
+      <c r="I795" s="16"/>
+      <c r="J795" s="16"/>
+      <c r="K795" s="16"/>
+    </row>
+    <row r="796" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A796" s="12">
+        <v>46288</v>
+      </c>
+      <c r="B796" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="C796" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="D796" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="E796" s="15"/>
+      <c r="F796" s="15"/>
+      <c r="G796" s="16"/>
+      <c r="H796" s="16"/>
+      <c r="I796" s="16"/>
+      <c r="J796" s="16"/>
+      <c r="K796" s="16"/>
+    </row>
+    <row r="797" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A797" s="12">
+        <v>46288</v>
+      </c>
+      <c r="B797" s="13">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C797" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="D797" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E797" s="15"/>
+      <c r="F797" s="15"/>
+      <c r="G797" s="16"/>
+      <c r="H797" s="16"/>
+      <c r="I797" s="16"/>
+      <c r="J797" s="16"/>
+      <c r="K797" s="16"/>
+    </row>
+    <row r="798" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A798" s="12">
+        <v>46288</v>
+      </c>
+      <c r="B798" s="13">
+        <v>0.75</v>
+      </c>
+      <c r="C798" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="D798" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="E798" s="15"/>
+      <c r="F798" s="15"/>
+      <c r="G798" s="16"/>
+      <c r="H798" s="16"/>
+      <c r="I798" s="16"/>
+      <c r="J798" s="16"/>
+      <c r="K798" s="16"/>
+    </row>
+    <row r="799" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A799" s="14"/>
+      <c r="B799" s="13"/>
+      <c r="C799" s="14"/>
+      <c r="D799" s="14"/>
+      <c r="E799" s="14"/>
+      <c r="F799" s="14"/>
+      <c r="G799" s="16"/>
+      <c r="H799" s="16"/>
+      <c r="I799" s="16"/>
+      <c r="J799" s="16"/>
+      <c r="K799" s="16"/>
+    </row>
+    <row r="800" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A800" s="14"/>
+      <c r="B800" s="14"/>
+      <c r="C800" s="14"/>
+      <c r="D800" s="14"/>
+      <c r="E800" s="14"/>
+      <c r="F800" s="14"/>
+      <c r="G800" s="16"/>
+      <c r="H800" s="16"/>
+      <c r="I800" s="16"/>
+      <c r="J800" s="16"/>
+      <c r="K800" s="16"/>
+    </row>
+    <row r="801" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A801" s="14"/>
+      <c r="B801" s="14"/>
+      <c r="C801" s="14"/>
+      <c r="D801" s="14"/>
+      <c r="E801" s="14"/>
+      <c r="F801" s="14"/>
+      <c r="G801" s="16"/>
+      <c r="H801" s="16"/>
+      <c r="I801" s="16"/>
+      <c r="J801" s="16"/>
+      <c r="K801" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A3CEA4-42E1-4D14-8CE8-1B494D6BF397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB5FE37-DC19-46AD-A3F3-A4537C3B8AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="350">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1279,6 +1279,102 @@
   </si>
   <si>
     <t>AIB-009 launch,but failed and Tetherline damaged and needs to be replaced</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>push on D05</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>climb up D05</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>set up AIB-006, current meter, pre dive check</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">launch AIB-006 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brace D2A(GVI+CPM+Anode)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brace A1D(GVI+CPM+Anode)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brace D1A(GVI+CPM+Anode)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brace A2D(GVI+CPM+Anode)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>recovery AIB-006</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>change battery</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>some problem about AIB diving (strong current)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>current peak up</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait for weather</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>data trsnsfer</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sail back to taichung port</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DPR</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sail to F2-C09.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pushing on F2-C09.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Take out and disassembly AIB to start maintence sequence.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Housekeeping and lunch time.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wait for vessel.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Climb down F2-C09.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sail to pick out other teams and back to Taichung Port.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Arrived at Taichung Port.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1359,7 +1455,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1398,7 +1494,6 @@
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal 2" xfId="1" xr:uid="{71AF191C-2467-4F76-8A53-CA6D53E4DF10}"/>
@@ -1680,7 +1775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K801"/>
+  <dimension ref="A1:F828"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.69921875" style="1" bestFit="1" customWidth="1"/>
@@ -12212,7 +12307,7 @@
       <c r="E784" s="8"/>
       <c r="F784" s="8"/>
     </row>
-    <row r="785" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A785" s="2">
         <v>46286</v>
       </c>
@@ -12228,7 +12323,7 @@
       <c r="E785" s="8"/>
       <c r="F785" s="8"/>
     </row>
-    <row r="786" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A786" s="2">
         <v>46286</v>
       </c>
@@ -12242,7 +12337,7 @@
       <c r="E786" s="8"/>
       <c r="F786" s="8"/>
     </row>
-    <row r="787" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A787" s="2">
         <v>46286</v>
       </c>
@@ -12258,7 +12353,7 @@
       <c r="E787" s="8"/>
       <c r="F787" s="8"/>
     </row>
-    <row r="788" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A788" s="2">
         <v>46286</v>
       </c>
@@ -12272,7 +12367,7 @@
       <c r="E788" s="8"/>
       <c r="F788" s="8"/>
     </row>
-    <row r="789" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A789" s="2">
         <v>46287</v>
       </c>
@@ -12288,7 +12383,7 @@
       <c r="E789" s="8"/>
       <c r="F789" s="8"/>
     </row>
-    <row r="790" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A790" s="2">
         <v>46287</v>
       </c>
@@ -12304,7 +12399,7 @@
       <c r="E790" s="8"/>
       <c r="F790" s="8"/>
     </row>
-    <row r="791" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A791" s="2">
         <v>46287</v>
       </c>
@@ -12318,7 +12413,7 @@
       <c r="E791" s="8"/>
       <c r="F791" s="8"/>
     </row>
-    <row r="792" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A792" s="2">
         <v>46287</v>
       </c>
@@ -12332,7 +12427,7 @@
       <c r="E792" s="8"/>
       <c r="F792" s="8"/>
     </row>
-    <row r="793" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A793" s="2">
         <v>46287</v>
       </c>
@@ -12348,7 +12443,7 @@
       <c r="E793" s="8"/>
       <c r="F793" s="8"/>
     </row>
-    <row r="794" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A794" s="2">
         <v>46287</v>
       </c>
@@ -12362,128 +12457,506 @@
       <c r="E794" s="8"/>
       <c r="F794" s="8"/>
     </row>
-    <row r="795" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A795" s="12">
+    <row r="795" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A795" s="2">
         <v>46288</v>
       </c>
-      <c r="B795" s="13">
+      <c r="B795" s="10">
         <v>0.375</v>
       </c>
-      <c r="C795" s="14" t="s">
+      <c r="C795" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D795" s="15" t="s">
+      <c r="D795" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="E795" s="15"/>
-      <c r="F795" s="15"/>
-      <c r="G795" s="16"/>
-      <c r="H795" s="16"/>
-      <c r="I795" s="16"/>
-      <c r="J795" s="16"/>
-      <c r="K795" s="16"/>
-    </row>
-    <row r="796" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A796" s="12">
+      <c r="E795" s="8"/>
+      <c r="F795" s="8"/>
+    </row>
+    <row r="796" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A796" s="2">
         <v>46288</v>
       </c>
-      <c r="B796" s="13">
+      <c r="B796" s="10">
         <v>0.5</v>
       </c>
-      <c r="C796" s="14" t="s">
+      <c r="C796" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D796" s="15" t="s">
+      <c r="D796" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="E796" s="15"/>
-      <c r="F796" s="15"/>
-      <c r="G796" s="16"/>
-      <c r="H796" s="16"/>
-      <c r="I796" s="16"/>
-      <c r="J796" s="16"/>
-      <c r="K796" s="16"/>
-    </row>
-    <row r="797" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A797" s="12">
+      <c r="E796" s="8"/>
+      <c r="F796" s="8"/>
+    </row>
+    <row r="797" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A797" s="2">
         <v>46288</v>
       </c>
-      <c r="B797" s="13">
+      <c r="B797" s="10">
         <v>0.54166666666666663</v>
       </c>
-      <c r="C797" s="14" t="s">
+      <c r="C797" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D797" s="15" t="s">
+      <c r="D797" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="E797" s="15"/>
-      <c r="F797" s="15"/>
-      <c r="G797" s="16"/>
-      <c r="H797" s="16"/>
-      <c r="I797" s="16"/>
-      <c r="J797" s="16"/>
-      <c r="K797" s="16"/>
-    </row>
-    <row r="798" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A798" s="12">
+      <c r="E797" s="8"/>
+      <c r="F797" s="8"/>
+    </row>
+    <row r="798" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A798" s="2">
         <v>46288</v>
       </c>
-      <c r="B798" s="13">
+      <c r="B798" s="10">
         <v>0.75</v>
       </c>
-      <c r="C798" s="14" t="s">
+      <c r="C798" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D798" s="15" t="s">
+      <c r="D798" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="E798" s="15"/>
-      <c r="F798" s="15"/>
-      <c r="G798" s="16"/>
-      <c r="H798" s="16"/>
-      <c r="I798" s="16"/>
-      <c r="J798" s="16"/>
-      <c r="K798" s="16"/>
-    </row>
-    <row r="799" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A799" s="14"/>
-      <c r="B799" s="13"/>
-      <c r="C799" s="14"/>
-      <c r="D799" s="14"/>
-      <c r="E799" s="14"/>
-      <c r="F799" s="14"/>
-      <c r="G799" s="16"/>
-      <c r="H799" s="16"/>
-      <c r="I799" s="16"/>
-      <c r="J799" s="16"/>
-      <c r="K799" s="16"/>
-    </row>
-    <row r="800" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A800" s="14"/>
-      <c r="B800" s="14"/>
-      <c r="C800" s="14"/>
-      <c r="D800" s="14"/>
-      <c r="E800" s="14"/>
-      <c r="F800" s="14"/>
-      <c r="G800" s="16"/>
-      <c r="H800" s="16"/>
-      <c r="I800" s="16"/>
-      <c r="J800" s="16"/>
-      <c r="K800" s="16"/>
-    </row>
-    <row r="801" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A801" s="14"/>
-      <c r="B801" s="14"/>
-      <c r="C801" s="14"/>
-      <c r="D801" s="14"/>
-      <c r="E801" s="14"/>
-      <c r="F801" s="14"/>
-      <c r="G801" s="16"/>
-      <c r="H801" s="16"/>
-      <c r="I801" s="16"/>
-      <c r="J801" s="16"/>
-      <c r="K801" s="16"/>
+      <c r="E798" s="8"/>
+      <c r="F798" s="8"/>
+    </row>
+    <row r="799" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A799" s="12">
+        <v>46289</v>
+      </c>
+      <c r="B799" s="13">
+        <v>0.26597222222222222</v>
+      </c>
+      <c r="C799" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D799" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="E799" s="15"/>
+      <c r="F799" s="15"/>
+    </row>
+    <row r="800" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A800" s="12">
+        <v>46289</v>
+      </c>
+      <c r="B800" s="13">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="C800" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D800" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="E800" s="15"/>
+      <c r="F800" s="15"/>
+    </row>
+    <row r="801" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A801" s="12">
+        <v>46289</v>
+      </c>
+      <c r="B801" s="13">
+        <v>0.3659722222222222</v>
+      </c>
+      <c r="C801" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D801" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="E801" s="15"/>
+      <c r="F801" s="15"/>
+    </row>
+    <row r="802" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A802" s="12">
+        <v>46289</v>
+      </c>
+      <c r="B802" s="13">
+        <v>0.49375000000000002</v>
+      </c>
+      <c r="C802" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D802" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="E802" s="15"/>
+      <c r="F802" s="15"/>
+    </row>
+    <row r="803" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A803" s="12">
+        <v>46289</v>
+      </c>
+      <c r="B803" s="13">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C803" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D803" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="E803" s="15"/>
+      <c r="F803" s="15"/>
+    </row>
+    <row r="804" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A804" s="12">
+        <v>46289</v>
+      </c>
+      <c r="B804" s="13">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="C804" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D804" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="E804" s="15"/>
+      <c r="F804" s="15"/>
+    </row>
+    <row r="805" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A805" s="12">
+        <v>46289</v>
+      </c>
+      <c r="B805" s="13">
+        <v>0.54791666666666672</v>
+      </c>
+      <c r="C805" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D805" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="E805" s="15"/>
+      <c r="F805" s="15"/>
+    </row>
+    <row r="806" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A806" s="12">
+        <v>46289</v>
+      </c>
+      <c r="B806" s="13">
+        <v>0.69166666666666665</v>
+      </c>
+      <c r="C806" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D806" s="15" t="s">
+        <v>349</v>
+      </c>
+      <c r="E806" s="15"/>
+      <c r="F806" s="15"/>
+    </row>
+    <row r="807" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A807" s="12">
+        <v>46289</v>
+      </c>
+      <c r="B807" s="13"/>
+      <c r="C807" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D807" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E807" s="15"/>
+      <c r="F807" s="15"/>
+    </row>
+    <row r="808" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A808" s="12">
+        <v>46290</v>
+      </c>
+      <c r="B808" s="10">
+        <v>0.26527777777777778</v>
+      </c>
+      <c r="C808" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D808" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="E808" s="8"/>
+      <c r="F808" s="8"/>
+    </row>
+    <row r="809" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A809" s="12">
+        <v>46290</v>
+      </c>
+      <c r="B809" s="10">
+        <v>0.3576388888888889</v>
+      </c>
+      <c r="C809" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D809" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="E809" s="8"/>
+      <c r="F809" s="8"/>
+    </row>
+    <row r="810" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A810" s="12">
+        <v>46290</v>
+      </c>
+      <c r="B810" s="10"/>
+      <c r="C810" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D810" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="E810" s="8"/>
+      <c r="F810" s="8"/>
+    </row>
+    <row r="811" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A811" s="12">
+        <v>46290</v>
+      </c>
+      <c r="B811" s="10">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="C811" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D811" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="E811" s="8"/>
+      <c r="F811" s="8"/>
+    </row>
+    <row r="812" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A812" s="12">
+        <v>46290</v>
+      </c>
+      <c r="B812" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="C812" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D812" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="E812" s="8"/>
+      <c r="F812" s="8"/>
+    </row>
+    <row r="813" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A813" s="12">
+        <v>46290</v>
+      </c>
+      <c r="B813" s="10"/>
+      <c r="C813" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D813" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="E813" s="8"/>
+      <c r="F813" s="8"/>
+    </row>
+    <row r="814" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A814" s="12">
+        <v>46290</v>
+      </c>
+      <c r="B814" s="10"/>
+      <c r="C814" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D814" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="E814" s="8"/>
+      <c r="F814" s="8"/>
+    </row>
+    <row r="815" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A815" s="12">
+        <v>46290</v>
+      </c>
+      <c r="B815" s="10"/>
+      <c r="C815" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D815" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="E815" s="8"/>
+      <c r="F815" s="8"/>
+    </row>
+    <row r="816" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A816" s="12">
+        <v>46290</v>
+      </c>
+      <c r="B816" s="10"/>
+      <c r="C816" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D816" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="E816" s="8"/>
+      <c r="F816" s="8"/>
+    </row>
+    <row r="817" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A817" s="12">
+        <v>46290</v>
+      </c>
+      <c r="B817" s="10">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="C817" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D817" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="E817" s="8"/>
+      <c r="F817" s="8"/>
+    </row>
+    <row r="818" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A818" s="12">
+        <v>46290</v>
+      </c>
+      <c r="B818" s="10"/>
+      <c r="C818" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D818" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="E818" s="8"/>
+      <c r="F818" s="8"/>
+    </row>
+    <row r="819" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A819" s="12">
+        <v>46290</v>
+      </c>
+      <c r="B819" s="10">
+        <v>0.46319444444444446</v>
+      </c>
+      <c r="C819" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D819" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="E819" s="8"/>
+      <c r="F819" s="8"/>
+    </row>
+    <row r="820" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A820" s="12">
+        <v>46290</v>
+      </c>
+      <c r="B820" s="10"/>
+      <c r="C820" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D820" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="E820" s="11"/>
+      <c r="F820" s="11"/>
+    </row>
+    <row r="821" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A821" s="12">
+        <v>46290</v>
+      </c>
+      <c r="B821" s="10"/>
+      <c r="C821" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D821" s="8" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="822" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A822" s="12">
+        <v>46290</v>
+      </c>
+      <c r="B822" s="10">
+        <v>0.49027777777777776</v>
+      </c>
+      <c r="C822" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D822" s="8" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="823" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A823" s="12">
+        <v>46290</v>
+      </c>
+      <c r="B823" s="10"/>
+      <c r="C823" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D823" s="8" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="824" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A824" s="12">
+        <v>46290</v>
+      </c>
+      <c r="B824" s="10"/>
+      <c r="C824" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D824" s="8" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="825" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A825" s="12">
+        <v>46290</v>
+      </c>
+      <c r="B825" s="10"/>
+      <c r="C825" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D825" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="826" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A826" s="12">
+        <v>46290</v>
+      </c>
+      <c r="B826" s="10">
+        <v>0.59791666666666665</v>
+      </c>
+      <c r="C826" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D826" s="8" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="827" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A827" s="12">
+        <v>46290</v>
+      </c>
+      <c r="B827" s="10">
+        <v>0.68402777777777779</v>
+      </c>
+      <c r="C827" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D827" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="828" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A828" s="12">
+        <v>46290</v>
+      </c>
+      <c r="C828" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D828" s="8" t="s">
+        <v>341</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB5FE37-DC19-46AD-A3F3-A4537C3B8AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1192F42-5D78-4647-A55C-AB8D508D0B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1706" uniqueCount="363">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1376,6 +1376,53 @@
   <si>
     <t>Arrived at Taichung Port.</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brace A3B(GVI+CPM+Anode)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brace B2A(GVI+CPM+Anode)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait on current</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brace C3D(GVI+CPM+Anode)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brace D2C(GVI+CPM+Anode)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OCC come in, contact for temporary shutdown</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D05 power recovered</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>confirm with OCC</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait on current</t>
+  </si>
+  <si>
+    <t>current keep going up, 0.6~0.8m/s</t>
+  </si>
+  <si>
+    <t>data transfer, wash down, housekeeping</t>
+  </si>
+  <si>
+    <t>climb down D05</t>
+  </si>
+  <si>
+    <t>sail to Taichung Port</t>
   </si>
 </sst>
 </file>
@@ -1455,7 +1502,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1486,14 +1533,13 @@
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal 2" xfId="1" xr:uid="{71AF191C-2467-4F76-8A53-CA6D53E4DF10}"/>
@@ -1775,7 +1821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F828"/>
+  <dimension ref="A1:G852"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.69921875" style="1" bestFit="1" customWidth="1"/>
@@ -12522,149 +12568,149 @@
       <c r="F798" s="8"/>
     </row>
     <row r="799" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A799" s="12">
+      <c r="A799" s="2">
         <v>46289</v>
       </c>
-      <c r="B799" s="13">
+      <c r="B799" s="10">
         <v>0.26597222222222222</v>
       </c>
-      <c r="C799" s="14" t="s">
+      <c r="C799" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D799" s="15" t="s">
+      <c r="D799" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="E799" s="15"/>
-      <c r="F799" s="15"/>
+      <c r="E799" s="8"/>
+      <c r="F799" s="8"/>
     </row>
     <row r="800" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A800" s="12">
+      <c r="A800" s="2">
         <v>46289</v>
       </c>
-      <c r="B800" s="13">
+      <c r="B800" s="10">
         <v>0.3611111111111111</v>
       </c>
-      <c r="C800" s="14" t="s">
+      <c r="C800" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D800" s="15" t="s">
+      <c r="D800" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="E800" s="15"/>
-      <c r="F800" s="15"/>
+      <c r="E800" s="8"/>
+      <c r="F800" s="8"/>
     </row>
     <row r="801" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A801" s="12">
+      <c r="A801" s="2">
         <v>46289</v>
       </c>
-      <c r="B801" s="13">
+      <c r="B801" s="10">
         <v>0.3659722222222222</v>
       </c>
-      <c r="C801" s="14" t="s">
+      <c r="C801" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D801" s="15" t="s">
+      <c r="D801" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="E801" s="15"/>
-      <c r="F801" s="15"/>
+      <c r="E801" s="8"/>
+      <c r="F801" s="8"/>
     </row>
     <row r="802" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A802" s="12">
+      <c r="A802" s="2">
         <v>46289</v>
       </c>
-      <c r="B802" s="13">
+      <c r="B802" s="10">
         <v>0.49375000000000002</v>
       </c>
-      <c r="C802" s="14" t="s">
+      <c r="C802" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D802" s="15" t="s">
+      <c r="D802" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="E802" s="15"/>
-      <c r="F802" s="15"/>
+      <c r="E802" s="8"/>
+      <c r="F802" s="8"/>
     </row>
     <row r="803" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A803" s="12">
+      <c r="A803" s="2">
         <v>46289</v>
       </c>
-      <c r="B803" s="13">
+      <c r="B803" s="10">
         <v>0.52083333333333337</v>
       </c>
-      <c r="C803" s="14" t="s">
+      <c r="C803" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D803" s="15" t="s">
+      <c r="D803" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="E803" s="15"/>
-      <c r="F803" s="15"/>
+      <c r="E803" s="8"/>
+      <c r="F803" s="8"/>
     </row>
     <row r="804" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A804" s="12">
+      <c r="A804" s="2">
         <v>46289</v>
       </c>
-      <c r="B804" s="13">
+      <c r="B804" s="10">
         <v>0.54236111111111107</v>
       </c>
-      <c r="C804" s="14" t="s">
+      <c r="C804" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D804" s="15" t="s">
+      <c r="D804" s="8" t="s">
         <v>347</v>
       </c>
-      <c r="E804" s="15"/>
-      <c r="F804" s="15"/>
+      <c r="E804" s="8"/>
+      <c r="F804" s="8"/>
     </row>
     <row r="805" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A805" s="12">
+      <c r="A805" s="2">
         <v>46289</v>
       </c>
-      <c r="B805" s="13">
+      <c r="B805" s="10">
         <v>0.54791666666666672</v>
       </c>
-      <c r="C805" s="14" t="s">
+      <c r="C805" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D805" s="15" t="s">
+      <c r="D805" s="8" t="s">
         <v>348</v>
       </c>
-      <c r="E805" s="15"/>
-      <c r="F805" s="15"/>
+      <c r="E805" s="8"/>
+      <c r="F805" s="8"/>
     </row>
     <row r="806" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A806" s="12">
+      <c r="A806" s="2">
         <v>46289</v>
       </c>
-      <c r="B806" s="13">
+      <c r="B806" s="10">
         <v>0.69166666666666665</v>
       </c>
-      <c r="C806" s="14" t="s">
+      <c r="C806" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D806" s="15" t="s">
+      <c r="D806" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="E806" s="15"/>
-      <c r="F806" s="15"/>
+      <c r="E806" s="8"/>
+      <c r="F806" s="8"/>
     </row>
     <row r="807" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A807" s="12">
+      <c r="A807" s="2">
         <v>46289</v>
       </c>
-      <c r="B807" s="13"/>
-      <c r="C807" s="14" t="s">
+      <c r="B807" s="10"/>
+      <c r="C807" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D807" s="15" t="s">
+      <c r="D807" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E807" s="15"/>
-      <c r="F807" s="15"/>
+      <c r="E807" s="8"/>
+      <c r="F807" s="8"/>
     </row>
     <row r="808" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A808" s="12">
+      <c r="A808" s="2">
         <v>46290</v>
       </c>
       <c r="B808" s="10">
@@ -12680,7 +12726,7 @@
       <c r="F808" s="8"/>
     </row>
     <row r="809" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A809" s="12">
+      <c r="A809" s="2">
         <v>46290</v>
       </c>
       <c r="B809" s="10">
@@ -12696,7 +12742,7 @@
       <c r="F809" s="8"/>
     </row>
     <row r="810" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A810" s="12">
+      <c r="A810" s="2">
         <v>46290</v>
       </c>
       <c r="B810" s="10"/>
@@ -12710,7 +12756,7 @@
       <c r="F810" s="8"/>
     </row>
     <row r="811" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A811" s="12">
+      <c r="A811" s="2">
         <v>46290</v>
       </c>
       <c r="B811" s="10">
@@ -12726,7 +12772,7 @@
       <c r="F811" s="8"/>
     </row>
     <row r="812" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A812" s="12">
+      <c r="A812" s="2">
         <v>46290</v>
       </c>
       <c r="B812" s="10">
@@ -12742,7 +12788,7 @@
       <c r="F812" s="8"/>
     </row>
     <row r="813" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A813" s="12">
+      <c r="A813" s="2">
         <v>46290</v>
       </c>
       <c r="B813" s="10"/>
@@ -12756,7 +12802,7 @@
       <c r="F813" s="8"/>
     </row>
     <row r="814" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A814" s="12">
+      <c r="A814" s="2">
         <v>46290</v>
       </c>
       <c r="B814" s="10"/>
@@ -12770,7 +12816,7 @@
       <c r="F814" s="8"/>
     </row>
     <row r="815" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A815" s="12">
+      <c r="A815" s="2">
         <v>46290</v>
       </c>
       <c r="B815" s="10"/>
@@ -12784,7 +12830,7 @@
       <c r="F815" s="8"/>
     </row>
     <row r="816" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A816" s="12">
+      <c r="A816" s="2">
         <v>46290</v>
       </c>
       <c r="B816" s="10"/>
@@ -12797,8 +12843,8 @@
       <c r="E816" s="8"/>
       <c r="F816" s="8"/>
     </row>
-    <row r="817" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A817" s="12">
+    <row r="817" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A817" s="2">
         <v>46290</v>
       </c>
       <c r="B817" s="10">
@@ -12813,8 +12859,8 @@
       <c r="E817" s="8"/>
       <c r="F817" s="8"/>
     </row>
-    <row r="818" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A818" s="12">
+    <row r="818" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A818" s="2">
         <v>46290</v>
       </c>
       <c r="B818" s="10"/>
@@ -12827,8 +12873,8 @@
       <c r="E818" s="8"/>
       <c r="F818" s="8"/>
     </row>
-    <row r="819" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A819" s="12">
+    <row r="819" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A819" s="2">
         <v>46290</v>
       </c>
       <c r="B819" s="10">
@@ -12843,8 +12889,8 @@
       <c r="E819" s="8"/>
       <c r="F819" s="8"/>
     </row>
-    <row r="820" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A820" s="12">
+    <row r="820" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A820" s="2">
         <v>46290</v>
       </c>
       <c r="B820" s="10"/>
@@ -12857,8 +12903,8 @@
       <c r="E820" s="11"/>
       <c r="F820" s="11"/>
     </row>
-    <row r="821" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A821" s="12">
+    <row r="821" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A821" s="2">
         <v>46290</v>
       </c>
       <c r="B821" s="10"/>
@@ -12869,8 +12915,8 @@
         <v>337</v>
       </c>
     </row>
-    <row r="822" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A822" s="12">
+    <row r="822" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A822" s="2">
         <v>46290</v>
       </c>
       <c r="B822" s="10">
@@ -12883,8 +12929,8 @@
         <v>334</v>
       </c>
     </row>
-    <row r="823" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A823" s="12">
+    <row r="823" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A823" s="2">
         <v>46290</v>
       </c>
       <c r="B823" s="10"/>
@@ -12895,8 +12941,8 @@
         <v>338</v>
       </c>
     </row>
-    <row r="824" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A824" s="12">
+    <row r="824" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A824" s="2">
         <v>46290</v>
       </c>
       <c r="B824" s="10"/>
@@ -12907,8 +12953,8 @@
         <v>339</v>
       </c>
     </row>
-    <row r="825" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A825" s="12">
+    <row r="825" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A825" s="2">
         <v>46290</v>
       </c>
       <c r="B825" s="10"/>
@@ -12919,8 +12965,8 @@
         <v>104</v>
       </c>
     </row>
-    <row r="826" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A826" s="12">
+    <row r="826" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A826" s="2">
         <v>46290</v>
       </c>
       <c r="B826" s="10">
@@ -12933,8 +12979,8 @@
         <v>340</v>
       </c>
     </row>
-    <row r="827" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A827" s="12">
+    <row r="827" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A827" s="2">
         <v>46290</v>
       </c>
       <c r="B827" s="10">
@@ -12947,8 +12993,8 @@
         <v>172</v>
       </c>
     </row>
-    <row r="828" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A828" s="12">
+    <row r="828" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A828" s="2">
         <v>46290</v>
       </c>
       <c r="C828" s="1" t="s">
@@ -12957,6 +13003,396 @@
       <c r="D828" s="8" t="s">
         <v>341</v>
       </c>
+    </row>
+    <row r="829" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A829" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B829" s="12">
+        <v>0.25624999999999998</v>
+      </c>
+      <c r="C829" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D829" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="E829" s="13"/>
+      <c r="F829" s="13"/>
+      <c r="G829" s="14"/>
+    </row>
+    <row r="830" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A830" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B830" s="12">
+        <v>0.33402777777777776</v>
+      </c>
+      <c r="C830" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D830" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="E830" s="13"/>
+      <c r="F830" s="13"/>
+      <c r="G830" s="14"/>
+    </row>
+    <row r="831" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A831" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B831" s="12">
+        <v>0.33958333333333335</v>
+      </c>
+      <c r="C831" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D831" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="E831" s="13"/>
+      <c r="F831" s="13"/>
+      <c r="G831" s="14"/>
+    </row>
+    <row r="832" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A832" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B832" s="12"/>
+      <c r="C832" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D832" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="E832" s="13"/>
+      <c r="F832" s="13"/>
+      <c r="G832" s="14"/>
+    </row>
+    <row r="833" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A833" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B833" s="12">
+        <v>0.36666666666666664</v>
+      </c>
+      <c r="C833" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D833" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="E833" s="13"/>
+      <c r="F833" s="13"/>
+      <c r="G833" s="14"/>
+    </row>
+    <row r="834" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A834" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B834" s="12"/>
+      <c r="C834" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D834" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="E834" s="13"/>
+      <c r="F834" s="13"/>
+      <c r="G834" s="14"/>
+    </row>
+    <row r="835" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A835" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B835" s="12"/>
+      <c r="C835" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D835" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="E835" s="13"/>
+      <c r="F835" s="13"/>
+      <c r="G835" s="14"/>
+    </row>
+    <row r="836" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A836" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B836" s="12">
+        <v>0.40416666666666667</v>
+      </c>
+      <c r="C836" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D836" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="E836" s="13"/>
+      <c r="F836" s="13"/>
+      <c r="G836" s="14"/>
+    </row>
+    <row r="837" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A837" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B837" s="12"/>
+      <c r="C837" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D837" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="E837" s="13"/>
+      <c r="F837" s="13"/>
+      <c r="G837" s="14"/>
+    </row>
+    <row r="838" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A838" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B838" s="12">
+        <v>0.41249999999999998</v>
+      </c>
+      <c r="C838" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D838" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="E838" s="13"/>
+      <c r="F838" s="13"/>
+      <c r="G838" s="14"/>
+    </row>
+    <row r="839" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A839" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B839" s="12">
+        <v>0.42638888888888887</v>
+      </c>
+      <c r="C839" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D839" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="E839" s="13"/>
+      <c r="F839" s="13"/>
+      <c r="G839" s="14"/>
+    </row>
+    <row r="840" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A840" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B840" s="12"/>
+      <c r="C840" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D840" s="13" t="s">
+        <v>353</v>
+      </c>
+      <c r="E840" s="13"/>
+      <c r="F840" s="13"/>
+      <c r="G840" s="14"/>
+    </row>
+    <row r="841" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A841" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B841" s="12"/>
+      <c r="C841" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D841" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="E841" s="13"/>
+      <c r="F841" s="13"/>
+      <c r="G841" s="14"/>
+    </row>
+    <row r="842" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A842" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B842" s="12">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="C842" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D842" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="E842" s="13"/>
+      <c r="F842" s="13"/>
+      <c r="G842" s="14"/>
+    </row>
+    <row r="843" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A843" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B843" s="12">
+        <v>0.45</v>
+      </c>
+      <c r="C843" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D843" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="E843" s="13"/>
+      <c r="F843" s="13"/>
+      <c r="G843" s="14"/>
+    </row>
+    <row r="844" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A844" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B844" s="12">
+        <v>0.48680555555555555</v>
+      </c>
+      <c r="C844" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D844" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="E844" s="13"/>
+      <c r="F844" s="13"/>
+      <c r="G844" s="14"/>
+    </row>
+    <row r="845" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A845" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B845" s="12"/>
+      <c r="C845" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D845" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="E845" s="13"/>
+      <c r="F845" s="13"/>
+      <c r="G845" s="14"/>
+    </row>
+    <row r="846" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A846" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B846" s="12">
+        <v>0.49791666666666667</v>
+      </c>
+      <c r="C846" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D846" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="E846" s="13"/>
+      <c r="F846" s="13"/>
+      <c r="G846" s="14"/>
+    </row>
+    <row r="847" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A847" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B847" s="12"/>
+      <c r="C847" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D847" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="E847" s="13"/>
+      <c r="F847" s="13"/>
+      <c r="G847" s="14"/>
+    </row>
+    <row r="848" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A848" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B848" s="12">
+        <v>0.56805555555555554</v>
+      </c>
+      <c r="C848" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D848" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="E848" s="13"/>
+      <c r="F848" s="13"/>
+      <c r="G848" s="14"/>
+    </row>
+    <row r="849" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A849" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B849" s="12">
+        <v>0.60138888888888886</v>
+      </c>
+      <c r="C849" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D849" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="E849" s="13"/>
+      <c r="F849" s="13"/>
+      <c r="G849" s="14"/>
+    </row>
+    <row r="850" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A850" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B850" s="12">
+        <v>0.60902777777777772</v>
+      </c>
+      <c r="C850" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D850" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="E850" s="13"/>
+      <c r="F850" s="13"/>
+      <c r="G850" s="14"/>
+    </row>
+    <row r="851" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A851" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B851" s="12">
+        <v>0.70208333333333328</v>
+      </c>
+      <c r="C851" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D851" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="E851" s="13"/>
+      <c r="F851" s="13"/>
+      <c r="G851" s="14"/>
+    </row>
+    <row r="852" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A852" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B852" s="12"/>
+      <c r="C852" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D852" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="E852" s="13"/>
+      <c r="F852" s="13"/>
+      <c r="G852" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1192F42-5D78-4647-A55C-AB8D508D0B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F7BB4DE-F56E-4EC5-86BD-10863D321801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1706" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="398">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1423,6 +1423,137 @@
   </si>
   <si>
     <t>sail to Taichung Port</t>
+  </si>
+  <si>
+    <t>launch AIB-006 at west side</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brace B3C, C2B, B1C(GVI+CPM+Anode)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>recovery AIB-006</t>
+  </si>
+  <si>
+    <t>change battery</t>
+  </si>
+  <si>
+    <t>strong swell current</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AIB check</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>climb down D05</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sail to Taichung Port</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sail to F2</t>
+  </si>
+  <si>
+    <t>push on D05</t>
+  </si>
+  <si>
+    <t>climb up D05</t>
+  </si>
+  <si>
+    <t>set up AIB-006, current meter, pre dive check</t>
+  </si>
+  <si>
+    <t>launch AIB-006 at west side</t>
+  </si>
+  <si>
+    <t>C1B, Leg C (GVI+CPM+Anode)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D1C, C1D, leg C (GVI+CPM+Anode), Scouring</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>stroung current</t>
+  </si>
+  <si>
+    <t>at port</t>
+  </si>
+  <si>
+    <t>C09</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D05 team climb(BeeX &amp; Michael)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sail to C09</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>push on C09</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>clim tower</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>set up AIB-009, current meter</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait for weather(strong current)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>lauch AIB-009</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brace C2D(GVI+CPM+Anode)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brace D1C(GVI+CPM+Anode)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brace C1D(GVI+CPM+Anode)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>recovery AiB-009</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Leg C(GVI+CPM+Anode)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>data transfer</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>climb down C09</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sail to D05</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait D05 team</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sail back taichung port</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1502,7 +1633,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1533,13 +1664,15 @@
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal 2" xfId="1" xr:uid="{71AF191C-2467-4F76-8A53-CA6D53E4DF10}"/>
@@ -1821,7 +1954,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G852"/>
+  <dimension ref="A1:G918"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.69921875" style="1" bestFit="1" customWidth="1"/>
@@ -12843,7 +12976,7 @@
       <c r="E816" s="8"/>
       <c r="F816" s="8"/>
     </row>
-    <row r="817" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A817" s="2">
         <v>46290</v>
       </c>
@@ -12859,7 +12992,7 @@
       <c r="E817" s="8"/>
       <c r="F817" s="8"/>
     </row>
-    <row r="818" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A818" s="2">
         <v>46290</v>
       </c>
@@ -12873,7 +13006,7 @@
       <c r="E818" s="8"/>
       <c r="F818" s="8"/>
     </row>
-    <row r="819" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A819" s="2">
         <v>46290</v>
       </c>
@@ -12889,7 +13022,7 @@
       <c r="E819" s="8"/>
       <c r="F819" s="8"/>
     </row>
-    <row r="820" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A820" s="2">
         <v>46290</v>
       </c>
@@ -12903,7 +13036,7 @@
       <c r="E820" s="11"/>
       <c r="F820" s="11"/>
     </row>
-    <row r="821" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A821" s="2">
         <v>46290</v>
       </c>
@@ -12915,7 +13048,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="822" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A822" s="2">
         <v>46290</v>
       </c>
@@ -12929,7 +13062,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="823" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A823" s="2">
         <v>46290</v>
       </c>
@@ -12941,7 +13074,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="824" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A824" s="2">
         <v>46290</v>
       </c>
@@ -12953,7 +13086,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="825" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A825" s="2">
         <v>46290</v>
       </c>
@@ -12965,7 +13098,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="826" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A826" s="2">
         <v>46290</v>
       </c>
@@ -12979,7 +13112,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="827" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A827" s="2">
         <v>46290</v>
       </c>
@@ -12993,7 +13126,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="828" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A828" s="2">
         <v>46290</v>
       </c>
@@ -13004,395 +13137,1439 @@
         <v>341</v>
       </c>
     </row>
-    <row r="829" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A829" s="2">
         <v>46291</v>
       </c>
-      <c r="B829" s="12">
+      <c r="B829" s="10">
         <v>0.25624999999999998</v>
       </c>
       <c r="C829" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D829" s="13" t="s">
+      <c r="D829" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="E829" s="13"/>
-      <c r="F829" s="13"/>
-      <c r="G829" s="14"/>
-    </row>
-    <row r="830" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E829" s="8"/>
+      <c r="F829" s="8"/>
+    </row>
+    <row r="830" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A830" s="2">
         <v>46291</v>
       </c>
-      <c r="B830" s="12">
+      <c r="B830" s="10">
         <v>0.33402777777777776</v>
       </c>
       <c r="C830" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D830" s="13" t="s">
+      <c r="D830" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="E830" s="13"/>
-      <c r="F830" s="13"/>
-      <c r="G830" s="14"/>
-    </row>
-    <row r="831" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E830" s="8"/>
+      <c r="F830" s="8"/>
+    </row>
+    <row r="831" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A831" s="2">
         <v>46291</v>
       </c>
-      <c r="B831" s="12">
+      <c r="B831" s="10">
         <v>0.33958333333333335</v>
       </c>
       <c r="C831" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D831" s="13" t="s">
+      <c r="D831" s="8" t="s">
         <v>327</v>
       </c>
-      <c r="E831" s="13"/>
-      <c r="F831" s="13"/>
-      <c r="G831" s="14"/>
-    </row>
-    <row r="832" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E831" s="8"/>
+      <c r="F831" s="8"/>
+    </row>
+    <row r="832" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A832" s="2">
         <v>46291</v>
       </c>
-      <c r="B832" s="12"/>
+      <c r="B832" s="10"/>
       <c r="C832" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D832" s="13" t="s">
+      <c r="D832" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="E832" s="13"/>
-      <c r="F832" s="13"/>
-      <c r="G832" s="14"/>
-    </row>
-    <row r="833" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E832" s="8"/>
+      <c r="F832" s="8"/>
+    </row>
+    <row r="833" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A833" s="2">
         <v>46291</v>
       </c>
-      <c r="B833" s="12">
+      <c r="B833" s="10">
         <v>0.36666666666666664</v>
       </c>
       <c r="C833" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D833" s="13" t="s">
+      <c r="D833" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="E833" s="13"/>
-      <c r="F833" s="13"/>
-      <c r="G833" s="14"/>
-    </row>
-    <row r="834" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E833" s="8"/>
+      <c r="F833" s="8"/>
+    </row>
+    <row r="834" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A834" s="2">
         <v>46291</v>
       </c>
-      <c r="B834" s="12"/>
+      <c r="B834" s="10"/>
       <c r="C834" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D834" s="13" t="s">
+      <c r="D834" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="E834" s="13"/>
-      <c r="F834" s="13"/>
-      <c r="G834" s="14"/>
-    </row>
-    <row r="835" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E834" s="8"/>
+      <c r="F834" s="8"/>
+    </row>
+    <row r="835" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A835" s="2">
         <v>46291</v>
       </c>
-      <c r="B835" s="12"/>
+      <c r="B835" s="10"/>
       <c r="C835" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D835" s="13" t="s">
+      <c r="D835" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="E835" s="13"/>
-      <c r="F835" s="13"/>
-      <c r="G835" s="14"/>
-    </row>
-    <row r="836" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E835" s="8"/>
+      <c r="F835" s="8"/>
+    </row>
+    <row r="836" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A836" s="2">
         <v>46291</v>
       </c>
-      <c r="B836" s="12">
+      <c r="B836" s="10">
         <v>0.40416666666666667</v>
       </c>
       <c r="C836" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D836" s="13" t="s">
+      <c r="D836" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="E836" s="13"/>
-      <c r="F836" s="13"/>
-      <c r="G836" s="14"/>
-    </row>
-    <row r="837" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E836" s="8"/>
+      <c r="F836" s="8"/>
+    </row>
+    <row r="837" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A837" s="2">
         <v>46291</v>
       </c>
-      <c r="B837" s="12"/>
+      <c r="B837" s="10"/>
       <c r="C837" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D837" s="13" t="s">
+      <c r="D837" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="E837" s="13"/>
-      <c r="F837" s="13"/>
-      <c r="G837" s="14"/>
-    </row>
-    <row r="838" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E837" s="8"/>
+      <c r="F837" s="8"/>
+    </row>
+    <row r="838" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A838" s="2">
         <v>46291</v>
       </c>
-      <c r="B838" s="12">
+      <c r="B838" s="10">
         <v>0.41249999999999998</v>
       </c>
       <c r="C838" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D838" s="13" t="s">
+      <c r="D838" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="E838" s="13"/>
-      <c r="F838" s="13"/>
-      <c r="G838" s="14"/>
-    </row>
-    <row r="839" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E838" s="8"/>
+      <c r="F838" s="8"/>
+    </row>
+    <row r="839" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A839" s="2">
         <v>46291</v>
       </c>
-      <c r="B839" s="12">
+      <c r="B839" s="10">
         <v>0.42638888888888887</v>
       </c>
       <c r="C839" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D839" s="13" t="s">
+      <c r="D839" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="E839" s="13"/>
-      <c r="F839" s="13"/>
-      <c r="G839" s="14"/>
-    </row>
-    <row r="840" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E839" s="8"/>
+      <c r="F839" s="8"/>
+    </row>
+    <row r="840" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A840" s="2">
         <v>46291</v>
       </c>
-      <c r="B840" s="12"/>
+      <c r="B840" s="10"/>
       <c r="C840" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D840" s="13" t="s">
+      <c r="D840" s="8" t="s">
         <v>353</v>
       </c>
-      <c r="E840" s="13"/>
-      <c r="F840" s="13"/>
-      <c r="G840" s="14"/>
-    </row>
-    <row r="841" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E840" s="8"/>
+      <c r="F840" s="8"/>
+    </row>
+    <row r="841" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A841" s="2">
         <v>46291</v>
       </c>
-      <c r="B841" s="12"/>
+      <c r="B841" s="10"/>
       <c r="C841" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D841" s="13" t="s">
+      <c r="D841" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="E841" s="13"/>
-      <c r="F841" s="13"/>
-      <c r="G841" s="14"/>
-    </row>
-    <row r="842" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E841" s="8"/>
+      <c r="F841" s="8"/>
+    </row>
+    <row r="842" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A842" s="2">
         <v>46291</v>
       </c>
-      <c r="B842" s="12">
+      <c r="B842" s="10">
         <v>0.44374999999999998</v>
       </c>
       <c r="C842" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D842" s="13" t="s">
+      <c r="D842" s="8" t="s">
         <v>355</v>
       </c>
-      <c r="E842" s="13"/>
-      <c r="F842" s="13"/>
-      <c r="G842" s="14"/>
-    </row>
-    <row r="843" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E842" s="8"/>
+      <c r="F842" s="8"/>
+    </row>
+    <row r="843" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A843" s="2">
         <v>46291</v>
       </c>
-      <c r="B843" s="12">
+      <c r="B843" s="10">
         <v>0.45</v>
       </c>
       <c r="C843" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D843" s="13" t="s">
+      <c r="D843" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="E843" s="13"/>
-      <c r="F843" s="13"/>
-      <c r="G843" s="14"/>
-    </row>
-    <row r="844" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E843" s="8"/>
+      <c r="F843" s="8"/>
+    </row>
+    <row r="844" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A844" s="2">
         <v>46291</v>
       </c>
-      <c r="B844" s="12">
+      <c r="B844" s="10">
         <v>0.48680555555555555</v>
       </c>
       <c r="C844" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D844" s="13" t="s">
+      <c r="D844" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="E844" s="13"/>
-      <c r="F844" s="13"/>
-      <c r="G844" s="14"/>
-    </row>
-    <row r="845" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E844" s="8"/>
+      <c r="F844" s="8"/>
+    </row>
+    <row r="845" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A845" s="2">
         <v>46291</v>
       </c>
-      <c r="B845" s="12"/>
+      <c r="B845" s="10"/>
       <c r="C845" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D845" s="13" t="s">
+      <c r="D845" s="8" t="s">
         <v>357</v>
       </c>
-      <c r="E845" s="13"/>
-      <c r="F845" s="13"/>
-      <c r="G845" s="14"/>
-    </row>
-    <row r="846" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E845" s="8"/>
+      <c r="F845" s="8"/>
+    </row>
+    <row r="846" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A846" s="2">
         <v>46291</v>
       </c>
-      <c r="B846" s="12">
+      <c r="B846" s="10">
         <v>0.49791666666666667</v>
       </c>
       <c r="C846" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D846" s="13" t="s">
+      <c r="D846" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="E846" s="13"/>
-      <c r="F846" s="13"/>
-      <c r="G846" s="14"/>
-    </row>
-    <row r="847" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E846" s="8"/>
+      <c r="F846" s="8"/>
+    </row>
+    <row r="847" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A847" s="2">
         <v>46291</v>
       </c>
-      <c r="B847" s="12"/>
+      <c r="B847" s="10"/>
       <c r="C847" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D847" s="13" t="s">
+      <c r="D847" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="E847" s="13"/>
-      <c r="F847" s="13"/>
-      <c r="G847" s="14"/>
-    </row>
-    <row r="848" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E847" s="8"/>
+      <c r="F847" s="8"/>
+    </row>
+    <row r="848" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A848" s="2">
         <v>46291</v>
       </c>
-      <c r="B848" s="12">
+      <c r="B848" s="10">
         <v>0.56805555555555554</v>
       </c>
       <c r="C848" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D848" s="13" t="s">
+      <c r="D848" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="E848" s="13"/>
-      <c r="F848" s="13"/>
-      <c r="G848" s="14"/>
+      <c r="E848" s="8"/>
+      <c r="F848" s="8"/>
     </row>
     <row r="849" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A849" s="2">
         <v>46291</v>
       </c>
-      <c r="B849" s="12">
+      <c r="B849" s="10">
         <v>0.60138888888888886</v>
       </c>
       <c r="C849" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D849" s="13" t="s">
+      <c r="D849" s="8" t="s">
         <v>361</v>
       </c>
-      <c r="E849" s="13"/>
-      <c r="F849" s="13"/>
-      <c r="G849" s="14"/>
+      <c r="E849" s="8"/>
+      <c r="F849" s="8"/>
     </row>
     <row r="850" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A850" s="2">
         <v>46291</v>
       </c>
-      <c r="B850" s="12">
+      <c r="B850" s="10">
         <v>0.60902777777777772</v>
       </c>
       <c r="C850" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D850" s="13" t="s">
+      <c r="D850" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="E850" s="13"/>
-      <c r="F850" s="13"/>
-      <c r="G850" s="14"/>
+      <c r="E850" s="8"/>
+      <c r="F850" s="8"/>
     </row>
     <row r="851" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A851" s="2">
         <v>46291</v>
       </c>
-      <c r="B851" s="12">
+      <c r="B851" s="10">
         <v>0.70208333333333328</v>
       </c>
       <c r="C851" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D851" s="13" t="s">
+      <c r="D851" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="E851" s="13"/>
-      <c r="F851" s="13"/>
-      <c r="G851" s="14"/>
+      <c r="E851" s="8"/>
+      <c r="F851" s="8"/>
     </row>
     <row r="852" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A852" s="2">
         <v>46291</v>
       </c>
-      <c r="B852" s="12"/>
+      <c r="B852" s="10"/>
       <c r="C852" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D852" s="13" t="s">
+      <c r="D852" s="8" t="s">
         <v>341</v>
       </c>
-      <c r="E852" s="13"/>
-      <c r="F852" s="13"/>
-      <c r="G852" s="14"/>
+      <c r="E852" s="8"/>
+      <c r="F852" s="8"/>
+    </row>
+    <row r="853" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A853" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B853" s="14">
+        <v>0.2673611111111111</v>
+      </c>
+      <c r="C853" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D853" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="E853" s="16"/>
+      <c r="F853" s="16"/>
+      <c r="G853" s="15"/>
+    </row>
+    <row r="854" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A854" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B854" s="14">
+        <v>0.34305555555555556</v>
+      </c>
+      <c r="C854" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D854" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="E854" s="16"/>
+      <c r="F854" s="16"/>
+      <c r="G854" s="15"/>
+    </row>
+    <row r="855" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A855" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B855" s="14"/>
+      <c r="C855" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D855" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="E855" s="16"/>
+      <c r="F855" s="16"/>
+      <c r="G855" s="15"/>
+    </row>
+    <row r="856" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A856" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B856" s="14"/>
+      <c r="C856" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D856" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="E856" s="16"/>
+      <c r="F856" s="16"/>
+      <c r="G856" s="15"/>
+    </row>
+    <row r="857" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A857" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B857" s="14">
+        <v>0.36388888888888887</v>
+      </c>
+      <c r="C857" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D857" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="E857" s="16"/>
+      <c r="F857" s="16"/>
+      <c r="G857" s="15"/>
+    </row>
+    <row r="858" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A858" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B858" s="14"/>
+      <c r="C858" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D858" s="16" t="s">
+        <v>364</v>
+      </c>
+      <c r="E858" s="16"/>
+      <c r="F858" s="16"/>
+      <c r="G858" s="15"/>
+    </row>
+    <row r="859" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A859" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B859" s="14">
+        <v>0.43472222222222223</v>
+      </c>
+      <c r="C859" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D859" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="E859" s="16"/>
+      <c r="F859" s="16"/>
+      <c r="G859" s="15"/>
+    </row>
+    <row r="860" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A860" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B860" s="14"/>
+      <c r="C860" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D860" s="16" t="s">
+        <v>366</v>
+      </c>
+      <c r="E860" s="16"/>
+      <c r="F860" s="16"/>
+      <c r="G860" s="15"/>
+    </row>
+    <row r="861" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A861" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B861" s="14">
+        <v>0.43888888888888888</v>
+      </c>
+      <c r="C861" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D861" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="E861" s="16"/>
+      <c r="F861" s="16"/>
+      <c r="G861" s="15"/>
+    </row>
+    <row r="862" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A862" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B862" s="14">
+        <v>0.45555555555555555</v>
+      </c>
+      <c r="C862" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D862" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="E862" s="16"/>
+      <c r="F862" s="16"/>
+      <c r="G862" s="15"/>
+    </row>
+    <row r="863" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A863" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B863" s="14"/>
+      <c r="C863" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D863" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="E863" s="16"/>
+      <c r="F863" s="16"/>
+      <c r="G863" s="15"/>
+    </row>
+    <row r="864" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A864" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B864" s="14">
+        <v>0.47152777777777777</v>
+      </c>
+      <c r="C864" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D864" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="E864" s="16"/>
+      <c r="F864" s="16"/>
+      <c r="G864" s="15"/>
+    </row>
+    <row r="865" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A865" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B865" s="14"/>
+      <c r="C865" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D865" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="E865" s="16"/>
+      <c r="F865" s="16"/>
+      <c r="G865" s="15"/>
+    </row>
+    <row r="866" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A866" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B866" s="14"/>
+      <c r="C866" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D866" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="E866" s="16"/>
+      <c r="F866" s="16"/>
+      <c r="G866" s="15"/>
+    </row>
+    <row r="867" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A867" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B867" s="14">
+        <v>0.54305555555555551</v>
+      </c>
+      <c r="C867" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D867" s="16" t="s">
+        <v>360</v>
+      </c>
+      <c r="E867" s="16"/>
+      <c r="F867" s="16"/>
+      <c r="G867" s="15"/>
+    </row>
+    <row r="868" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A868" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B868" s="14">
+        <v>0.57847222222222228</v>
+      </c>
+      <c r="C868" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D868" s="16" t="s">
+        <v>369</v>
+      </c>
+      <c r="E868" s="16"/>
+      <c r="F868" s="16"/>
+      <c r="G868" s="15"/>
+    </row>
+    <row r="869" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A869" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B869" s="14">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C869" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D869" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="E869" s="16"/>
+      <c r="F869" s="16"/>
+      <c r="G869" s="15"/>
+    </row>
+    <row r="870" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A870" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B870" s="14">
+        <v>0.67986111111111114</v>
+      </c>
+      <c r="C870" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D870" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="E870" s="16"/>
+      <c r="F870" s="16"/>
+      <c r="G870" s="15"/>
+    </row>
+    <row r="871" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A871" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B871" s="12"/>
+      <c r="C871" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D871" s="16" t="s">
+        <v>341</v>
+      </c>
+      <c r="E871" s="12"/>
+      <c r="F871" s="12"/>
+      <c r="G871" s="15"/>
+    </row>
+    <row r="872" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A872" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B872" s="14">
+        <v>0.25694444444444442</v>
+      </c>
+      <c r="C872" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D872" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="E872" s="16"/>
+      <c r="F872" s="16"/>
+      <c r="G872" s="15"/>
+    </row>
+    <row r="873" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A873" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B873" s="14">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C873" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D873" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="E873" s="16"/>
+      <c r="F873" s="16"/>
+      <c r="G873" s="15"/>
+    </row>
+    <row r="874" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A874" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B874" s="14"/>
+      <c r="C874" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D874" s="16" t="s">
+        <v>373</v>
+      </c>
+      <c r="E874" s="16"/>
+      <c r="F874" s="16"/>
+      <c r="G874" s="15"/>
+    </row>
+    <row r="875" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A875" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B875" s="14"/>
+      <c r="C875" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D875" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="E875" s="16"/>
+      <c r="F875" s="16"/>
+      <c r="G875" s="15"/>
+    </row>
+    <row r="876" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A876" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B876" s="14">
+        <v>0.35833333333333334</v>
+      </c>
+      <c r="C876" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D876" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="E876" s="16"/>
+      <c r="F876" s="16"/>
+      <c r="G876" s="15"/>
+    </row>
+    <row r="877" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A877" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B877" s="14"/>
+      <c r="C877" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D877" s="16" t="s">
+        <v>376</v>
+      </c>
+      <c r="E877" s="16"/>
+      <c r="F877" s="16"/>
+      <c r="G877" s="15"/>
+    </row>
+    <row r="878" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A878" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B878" s="14">
+        <v>0.4201388888888889</v>
+      </c>
+      <c r="C878" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D878" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="E878" s="16"/>
+      <c r="F878" s="16"/>
+      <c r="G878" s="15"/>
+    </row>
+    <row r="879" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A879" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B879" s="14"/>
+      <c r="C879" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D879" s="16" t="s">
+        <v>366</v>
+      </c>
+      <c r="E879" s="16"/>
+      <c r="F879" s="16"/>
+      <c r="G879" s="15"/>
+    </row>
+    <row r="880" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A880" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B880" s="14">
+        <v>0.43194444444444446</v>
+      </c>
+      <c r="C880" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D880" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="E880" s="16"/>
+      <c r="F880" s="16"/>
+      <c r="G880" s="15"/>
+    </row>
+    <row r="881" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A881" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B881" s="14"/>
+      <c r="C881" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D881" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="E881" s="16"/>
+      <c r="F881" s="16"/>
+      <c r="G881" s="15"/>
+    </row>
+    <row r="882" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A882" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B882" s="14">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="C882" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D882" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="E882" s="16"/>
+      <c r="F882" s="16"/>
+      <c r="G882" s="15"/>
+    </row>
+    <row r="883" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A883" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B883" s="14"/>
+      <c r="C883" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D883" s="16" t="s">
+        <v>366</v>
+      </c>
+      <c r="E883" s="16"/>
+      <c r="F883" s="16"/>
+      <c r="G883" s="15"/>
+    </row>
+    <row r="884" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A884" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B884" s="14">
+        <v>0.49444444444444446</v>
+      </c>
+      <c r="C884" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D884" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="E884" s="16"/>
+      <c r="F884" s="16"/>
+      <c r="G884" s="15"/>
+    </row>
+    <row r="885" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A885" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B885" s="14"/>
+      <c r="C885" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D885" s="16" t="s">
+        <v>378</v>
+      </c>
+      <c r="E885" s="16"/>
+      <c r="F885" s="16"/>
+      <c r="G885" s="15"/>
+    </row>
+    <row r="886" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A886" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B886" s="14">
+        <v>0.5131944444444444</v>
+      </c>
+      <c r="C886" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D886" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="E886" s="16"/>
+      <c r="F886" s="16"/>
+      <c r="G886" s="15"/>
+    </row>
+    <row r="887" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A887" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B887" s="14"/>
+      <c r="C887" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D887" s="16" t="s">
+        <v>358</v>
+      </c>
+      <c r="E887" s="16"/>
+      <c r="F887" s="16"/>
+      <c r="G887" s="15"/>
+    </row>
+    <row r="888" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A888" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B888" s="14">
+        <v>0.53402777777777777</v>
+      </c>
+      <c r="C888" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D888" s="16" t="s">
+        <v>360</v>
+      </c>
+      <c r="E888" s="16"/>
+      <c r="F888" s="16"/>
+      <c r="G888" s="15"/>
+    </row>
+    <row r="889" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A889" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B889" s="14">
+        <v>0.58888888888888891</v>
+      </c>
+      <c r="C889" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D889" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="E889" s="16"/>
+      <c r="F889" s="16"/>
+      <c r="G889" s="15"/>
+    </row>
+    <row r="890" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A890" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B890" s="14">
+        <v>0.59027777777777779</v>
+      </c>
+      <c r="C890" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D890" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="E890" s="16"/>
+      <c r="F890" s="16"/>
+      <c r="G890" s="15"/>
+    </row>
+    <row r="891" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A891" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B891" s="14">
+        <v>0.68402777777777779</v>
+      </c>
+      <c r="C891" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D891" s="16" t="s">
+        <v>379</v>
+      </c>
+      <c r="E891" s="16"/>
+      <c r="F891" s="16"/>
+      <c r="G891" s="15"/>
+    </row>
+    <row r="892" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A892" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B892" s="12"/>
+      <c r="C892" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D892" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E892" s="16"/>
+      <c r="F892" s="16"/>
+      <c r="G892" s="15"/>
+    </row>
+    <row r="893" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A893" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B893" s="14">
+        <v>0.25694444444444442</v>
+      </c>
+      <c r="C893" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D893" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="E893" s="16"/>
+      <c r="F893" s="16"/>
+      <c r="G893" s="15"/>
+    </row>
+    <row r="894" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A894" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B894" s="14">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C894" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D894" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="E894" s="16"/>
+      <c r="F894" s="16"/>
+      <c r="G894" s="15"/>
+    </row>
+    <row r="895" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A895" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B895" s="14"/>
+      <c r="C895" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D895" s="16" t="s">
+        <v>381</v>
+      </c>
+      <c r="E895" s="16"/>
+      <c r="F895" s="16"/>
+      <c r="G895" s="15"/>
+    </row>
+    <row r="896" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A896" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B896" s="14">
+        <v>0.34722222222222221</v>
+      </c>
+      <c r="C896" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D896" s="16" t="s">
+        <v>382</v>
+      </c>
+      <c r="E896" s="16"/>
+      <c r="F896" s="16"/>
+      <c r="G896" s="15"/>
+    </row>
+    <row r="897" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A897" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B897" s="14">
+        <v>0.3576388888888889</v>
+      </c>
+      <c r="C897" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D897" s="16" t="s">
+        <v>383</v>
+      </c>
+      <c r="E897" s="16"/>
+      <c r="F897" s="16"/>
+      <c r="G897" s="15"/>
+    </row>
+    <row r="898" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A898" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B898" s="14"/>
+      <c r="C898" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D898" s="16" t="s">
+        <v>384</v>
+      </c>
+      <c r="E898" s="16"/>
+      <c r="F898" s="16"/>
+      <c r="G898" s="15"/>
+    </row>
+    <row r="899" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A899" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B899" s="14">
+        <v>0.36805555555555558</v>
+      </c>
+      <c r="C899" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D899" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="E899" s="16"/>
+      <c r="F899" s="16"/>
+      <c r="G899" s="15"/>
+    </row>
+    <row r="900" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A900" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B900" s="14">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="C900" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D900" s="16" t="s">
+        <v>386</v>
+      </c>
+      <c r="E900" s="16"/>
+      <c r="F900" s="16"/>
+      <c r="G900" s="15"/>
+    </row>
+    <row r="901" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A901" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B901" s="14">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C901" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D901" s="16" t="s">
+        <v>387</v>
+      </c>
+      <c r="E901" s="16"/>
+      <c r="F901" s="16"/>
+      <c r="G901" s="15"/>
+    </row>
+    <row r="902" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A902" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B902" s="14"/>
+      <c r="C902" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D902" s="16" t="s">
+        <v>388</v>
+      </c>
+      <c r="E902" s="16"/>
+      <c r="F902" s="16"/>
+      <c r="G902" s="15"/>
+    </row>
+    <row r="903" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A903" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B903" s="14"/>
+      <c r="C903" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D903" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="E903" s="16"/>
+      <c r="F903" s="16"/>
+      <c r="G903" s="15"/>
+    </row>
+    <row r="904" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A904" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B904" s="14"/>
+      <c r="C904" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D904" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="E904" s="16"/>
+      <c r="F904" s="16"/>
+      <c r="G904" s="15"/>
+    </row>
+    <row r="905" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A905" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B905" s="14"/>
+      <c r="C905" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D905" s="16" t="s">
+        <v>354</v>
+      </c>
+      <c r="E905" s="16"/>
+      <c r="F905" s="16"/>
+      <c r="G905" s="15"/>
+    </row>
+    <row r="906" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A906" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B906" s="14">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C906" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D906" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="E906" s="16"/>
+      <c r="F906" s="16"/>
+      <c r="G906" s="15"/>
+    </row>
+    <row r="907" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A907" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B907" s="14"/>
+      <c r="C907" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D907" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="E907" s="16"/>
+      <c r="F907" s="16"/>
+      <c r="G907" s="15"/>
+    </row>
+    <row r="908" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A908" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B908" s="14">
+        <v>0.46527777777777779</v>
+      </c>
+      <c r="C908" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D908" s="16" t="s">
+        <v>392</v>
+      </c>
+      <c r="E908" s="16"/>
+      <c r="F908" s="16"/>
+      <c r="G908" s="15"/>
+    </row>
+    <row r="909" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A909" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B909" s="14">
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="C909" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D909" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="E909" s="16"/>
+      <c r="F909" s="16"/>
+      <c r="G909" s="15"/>
+    </row>
+    <row r="910" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A910" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B910" s="14"/>
+      <c r="C910" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D910" s="16" t="s">
+        <v>386</v>
+      </c>
+      <c r="E910" s="16"/>
+      <c r="F910" s="16"/>
+      <c r="G910" s="15"/>
+    </row>
+    <row r="911" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A911" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B911" s="14">
+        <v>0.52777777777777779</v>
+      </c>
+      <c r="C911" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D911" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="E911" s="16"/>
+      <c r="F911" s="16"/>
+      <c r="G911" s="15"/>
+    </row>
+    <row r="912" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A912" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B912" s="14"/>
+      <c r="C912" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D912" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="E912" s="16"/>
+      <c r="F912" s="16"/>
+      <c r="G912" s="15"/>
+    </row>
+    <row r="913" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A913" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B913" s="14">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="C913" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D913" s="16" t="s">
+        <v>394</v>
+      </c>
+      <c r="E913" s="16"/>
+      <c r="F913" s="16"/>
+      <c r="G913" s="15"/>
+    </row>
+    <row r="914" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A914" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B914" s="14">
+        <v>0.5625</v>
+      </c>
+      <c r="C914" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D914" s="16" t="s">
+        <v>395</v>
+      </c>
+      <c r="E914" s="16"/>
+      <c r="F914" s="16"/>
+      <c r="G914" s="15"/>
+    </row>
+    <row r="915" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A915" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B915" s="14">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="C915" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D915" s="16" t="s">
+        <v>396</v>
+      </c>
+      <c r="E915" s="16"/>
+      <c r="F915" s="16"/>
+      <c r="G915" s="15"/>
+    </row>
+    <row r="916" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A916" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B916" s="14">
+        <v>0.59027777777777779</v>
+      </c>
+      <c r="C916" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D916" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="E916" s="16"/>
+      <c r="F916" s="16"/>
+      <c r="G916" s="15"/>
+    </row>
+    <row r="917" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A917" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B917" s="14">
+        <v>0.68402777777777779</v>
+      </c>
+      <c r="C917" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D917" s="16" t="s">
+        <v>379</v>
+      </c>
+      <c r="E917" s="16"/>
+      <c r="F917" s="16"/>
+      <c r="G917" s="15"/>
+    </row>
+    <row r="918" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A918" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B918" s="12"/>
+      <c r="C918" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D918" s="16" t="s">
+        <v>341</v>
+      </c>
+      <c r="E918" s="16"/>
+      <c r="F918" s="16"/>
+      <c r="G918" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F7BB4DE-F56E-4EC5-86BD-10863D321801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF59147-0A53-4E30-8F06-3A02D87D7A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="405">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1500,59 +1500,87 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>set up AIB-009, current meter</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait for weather(strong current)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>lauch AIB-009</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brace C2D(GVI+CPM+Anode)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brace D1C(GVI+CPM+Anode)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brace C1D(GVI+CPM+Anode)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>data transfer</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>climb down C09</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sail to D05</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait D05 team</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sail back taichung port</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>climb tower</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Leg C(GVI+CPM+Anode+scour+mosaic)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>clim tower</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>set up AIB-009, current meter</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait for weather(strong current)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>lauch AIB-009</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Brace C2D(GVI+CPM+Anode)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Brace D1C(GVI+CPM+Anode)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Brace C1D(GVI+CPM+Anode)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>recovery AiB-009</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Leg C(GVI+CPM+Anode)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>data transfer</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>climb down C09</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>sail to D05</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait D05 team</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>sail back taichung port</t>
+    <t>set up AIB-009, current meter, pre dive check</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brace B2C(GVI+CPM+Anode)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brace C1B(GVI+CPM+Anode)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brace B1C(GVI+CPM+Anode)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brace C2B(GVI+CPM+Anode)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Leg D(GVI+CPM+Anode+Scour+Mosaic)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LegC - CPS</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1664,14 +1692,14 @@
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1954,7 +1982,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G918"/>
+  <dimension ref="A1:G946"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.69921875" style="1" bestFit="1" customWidth="1"/>
@@ -13441,7 +13469,7 @@
       <c r="E848" s="8"/>
       <c r="F848" s="8"/>
     </row>
-    <row r="849" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="849" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A849" s="2">
         <v>46291</v>
       </c>
@@ -13457,7 +13485,7 @@
       <c r="E849" s="8"/>
       <c r="F849" s="8"/>
     </row>
-    <row r="850" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="850" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A850" s="2">
         <v>46291</v>
       </c>
@@ -13473,7 +13501,7 @@
       <c r="E850" s="8"/>
       <c r="F850" s="8"/>
     </row>
-    <row r="851" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="851" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A851" s="2">
         <v>46291</v>
       </c>
@@ -13489,7 +13517,7 @@
       <c r="E851" s="8"/>
       <c r="F851" s="8"/>
     </row>
-    <row r="852" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="852" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A852" s="2">
         <v>46291</v>
       </c>
@@ -13503,1073 +13531,1440 @@
       <c r="E852" s="8"/>
       <c r="F852" s="8"/>
     </row>
-    <row r="853" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A853" s="13">
+    <row r="853" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A853" s="2">
         <v>46292</v>
       </c>
-      <c r="B853" s="14">
+      <c r="B853" s="10">
         <v>0.2673611111111111</v>
       </c>
-      <c r="C853" s="12" t="s">
+      <c r="C853" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D853" s="16" t="s">
+      <c r="D853" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="E853" s="16"/>
-      <c r="F853" s="16"/>
-      <c r="G853" s="15"/>
-    </row>
-    <row r="854" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A854" s="13">
+      <c r="E853" s="8"/>
+      <c r="F853" s="8"/>
+    </row>
+    <row r="854" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A854" s="2">
         <v>46292</v>
       </c>
-      <c r="B854" s="14">
+      <c r="B854" s="10">
         <v>0.34305555555555556</v>
       </c>
-      <c r="C854" s="12" t="s">
+      <c r="C854" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D854" s="16" t="s">
+      <c r="D854" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="E854" s="16"/>
-      <c r="F854" s="16"/>
-      <c r="G854" s="15"/>
-    </row>
-    <row r="855" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A855" s="13">
+      <c r="E854" s="8"/>
+      <c r="F854" s="8"/>
+    </row>
+    <row r="855" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A855" s="2">
         <v>46292</v>
       </c>
-      <c r="B855" s="14"/>
-      <c r="C855" s="12" t="s">
+      <c r="B855" s="10"/>
+      <c r="C855" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D855" s="16" t="s">
+      <c r="D855" s="8" t="s">
         <v>327</v>
       </c>
-      <c r="E855" s="16"/>
-      <c r="F855" s="16"/>
-      <c r="G855" s="15"/>
-    </row>
-    <row r="856" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A856" s="13">
+      <c r="E855" s="8"/>
+      <c r="F855" s="8"/>
+    </row>
+    <row r="856" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A856" s="2">
         <v>46292</v>
       </c>
-      <c r="B856" s="14"/>
-      <c r="C856" s="12" t="s">
+      <c r="B856" s="10"/>
+      <c r="C856" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D856" s="16" t="s">
+      <c r="D856" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="E856" s="16"/>
-      <c r="F856" s="16"/>
-      <c r="G856" s="15"/>
-    </row>
-    <row r="857" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A857" s="13">
+      <c r="E856" s="8"/>
+      <c r="F856" s="8"/>
+    </row>
+    <row r="857" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A857" s="2">
         <v>46292</v>
       </c>
-      <c r="B857" s="14">
+      <c r="B857" s="10">
         <v>0.36388888888888887</v>
       </c>
-      <c r="C857" s="12" t="s">
+      <c r="C857" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D857" s="16" t="s">
+      <c r="D857" s="8" t="s">
         <v>363</v>
       </c>
-      <c r="E857" s="16"/>
-      <c r="F857" s="16"/>
-      <c r="G857" s="15"/>
-    </row>
-    <row r="858" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A858" s="13">
+      <c r="E857" s="8"/>
+      <c r="F857" s="8"/>
+    </row>
+    <row r="858" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A858" s="2">
         <v>46292</v>
       </c>
-      <c r="B858" s="14"/>
-      <c r="C858" s="12" t="s">
+      <c r="B858" s="10"/>
+      <c r="C858" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D858" s="16" t="s">
+      <c r="D858" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="E858" s="16"/>
-      <c r="F858" s="16"/>
-      <c r="G858" s="15"/>
-    </row>
-    <row r="859" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A859" s="13">
+      <c r="E858" s="8"/>
+      <c r="F858" s="8"/>
+    </row>
+    <row r="859" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A859" s="2">
         <v>46292</v>
       </c>
-      <c r="B859" s="14">
+      <c r="B859" s="10">
         <v>0.43472222222222223</v>
       </c>
-      <c r="C859" s="12" t="s">
+      <c r="C859" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D859" s="16" t="s">
+      <c r="D859" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="E859" s="16"/>
-      <c r="F859" s="16"/>
-      <c r="G859" s="15"/>
-    </row>
-    <row r="860" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A860" s="13">
+      <c r="E859" s="8"/>
+      <c r="F859" s="8"/>
+    </row>
+    <row r="860" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A860" s="2">
         <v>46292</v>
       </c>
-      <c r="B860" s="14"/>
-      <c r="C860" s="12" t="s">
+      <c r="B860" s="10"/>
+      <c r="C860" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D860" s="16" t="s">
+      <c r="D860" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="E860" s="16"/>
-      <c r="F860" s="16"/>
-      <c r="G860" s="15"/>
-    </row>
-    <row r="861" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A861" s="13">
+      <c r="E860" s="8"/>
+      <c r="F860" s="8"/>
+    </row>
+    <row r="861" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A861" s="2">
         <v>46292</v>
       </c>
-      <c r="B861" s="14">
+      <c r="B861" s="10">
         <v>0.43888888888888888</v>
       </c>
-      <c r="C861" s="12" t="s">
+      <c r="C861" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D861" s="16" t="s">
+      <c r="D861" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="E861" s="16"/>
-      <c r="F861" s="16"/>
-      <c r="G861" s="15"/>
-    </row>
-    <row r="862" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A862" s="13">
+      <c r="E861" s="8"/>
+      <c r="F861" s="8"/>
+    </row>
+    <row r="862" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A862" s="2">
         <v>46292</v>
       </c>
-      <c r="B862" s="14">
+      <c r="B862" s="10">
         <v>0.45555555555555555</v>
       </c>
-      <c r="C862" s="12" t="s">
+      <c r="C862" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D862" s="16" t="s">
+      <c r="D862" s="8" t="s">
         <v>363</v>
       </c>
-      <c r="E862" s="16"/>
-      <c r="F862" s="16"/>
-      <c r="G862" s="15"/>
-    </row>
-    <row r="863" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A863" s="13">
+      <c r="E862" s="8"/>
+      <c r="F862" s="8"/>
+    </row>
+    <row r="863" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A863" s="2">
         <v>46292</v>
       </c>
-      <c r="B863" s="14"/>
-      <c r="C863" s="12" t="s">
+      <c r="B863" s="10"/>
+      <c r="C863" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D863" s="16" t="s">
+      <c r="D863" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="E863" s="16"/>
-      <c r="F863" s="16"/>
-      <c r="G863" s="15"/>
-    </row>
-    <row r="864" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A864" s="13">
+      <c r="E863" s="8"/>
+      <c r="F863" s="8"/>
+    </row>
+    <row r="864" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A864" s="2">
         <v>46292</v>
       </c>
-      <c r="B864" s="14">
+      <c r="B864" s="10">
         <v>0.47152777777777777</v>
       </c>
-      <c r="C864" s="12" t="s">
+      <c r="C864" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D864" s="16" t="s">
+      <c r="D864" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="E864" s="16"/>
-      <c r="F864" s="16"/>
-      <c r="G864" s="15"/>
-    </row>
-    <row r="865" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A865" s="13">
+      <c r="E864" s="8"/>
+      <c r="F864" s="8"/>
+    </row>
+    <row r="865" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A865" s="2">
         <v>46292</v>
       </c>
-      <c r="B865" s="14"/>
-      <c r="C865" s="12" t="s">
+      <c r="B865" s="10"/>
+      <c r="C865" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D865" s="16" t="s">
+      <c r="D865" s="8" t="s">
         <v>368</v>
       </c>
-      <c r="E865" s="16"/>
-      <c r="F865" s="16"/>
-      <c r="G865" s="15"/>
-    </row>
-    <row r="866" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A866" s="13">
+      <c r="E865" s="8"/>
+      <c r="F865" s="8"/>
+    </row>
+    <row r="866" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A866" s="2">
         <v>46292</v>
       </c>
-      <c r="B866" s="14"/>
-      <c r="C866" s="12" t="s">
+      <c r="B866" s="10"/>
+      <c r="C866" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D866" s="16" t="s">
+      <c r="D866" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="E866" s="16"/>
-      <c r="F866" s="16"/>
-      <c r="G866" s="15"/>
-    </row>
-    <row r="867" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A867" s="13">
+      <c r="E866" s="8"/>
+      <c r="F866" s="8"/>
+    </row>
+    <row r="867" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A867" s="2">
         <v>46292</v>
       </c>
-      <c r="B867" s="14">
+      <c r="B867" s="10">
         <v>0.54305555555555551</v>
       </c>
-      <c r="C867" s="12" t="s">
+      <c r="C867" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D867" s="16" t="s">
+      <c r="D867" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="E867" s="16"/>
-      <c r="F867" s="16"/>
-      <c r="G867" s="15"/>
-    </row>
-    <row r="868" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A868" s="13">
+      <c r="E867" s="8"/>
+      <c r="F867" s="8"/>
+    </row>
+    <row r="868" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A868" s="2">
         <v>46292</v>
       </c>
-      <c r="B868" s="14">
+      <c r="B868" s="10">
         <v>0.57847222222222228</v>
       </c>
-      <c r="C868" s="12" t="s">
+      <c r="C868" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D868" s="16" t="s">
+      <c r="D868" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="E868" s="16"/>
-      <c r="F868" s="16"/>
-      <c r="G868" s="15"/>
-    </row>
-    <row r="869" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A869" s="13">
+      <c r="E868" s="8"/>
+      <c r="F868" s="8"/>
+    </row>
+    <row r="869" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A869" s="2">
         <v>46292</v>
       </c>
-      <c r="B869" s="14">
+      <c r="B869" s="10">
         <v>0.58333333333333337</v>
       </c>
-      <c r="C869" s="12" t="s">
+      <c r="C869" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D869" s="16" t="s">
+      <c r="D869" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="E869" s="16"/>
-      <c r="F869" s="16"/>
-      <c r="G869" s="15"/>
-    </row>
-    <row r="870" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A870" s="13">
+      <c r="E869" s="8"/>
+      <c r="F869" s="8"/>
+    </row>
+    <row r="870" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A870" s="2">
         <v>46292</v>
       </c>
-      <c r="B870" s="14">
+      <c r="B870" s="10">
         <v>0.67986111111111114</v>
       </c>
-      <c r="C870" s="12" t="s">
+      <c r="C870" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D870" s="16" t="s">
+      <c r="D870" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="E870" s="16"/>
-      <c r="F870" s="16"/>
-      <c r="G870" s="15"/>
-    </row>
-    <row r="871" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A871" s="13">
+      <c r="E870" s="8"/>
+      <c r="F870" s="8"/>
+    </row>
+    <row r="871" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A871" s="2">
         <v>46292</v>
       </c>
-      <c r="B871" s="12"/>
-      <c r="C871" s="12" t="s">
+      <c r="C871" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D871" s="16" t="s">
+      <c r="D871" s="8" t="s">
         <v>341</v>
       </c>
-      <c r="E871" s="12"/>
-      <c r="F871" s="12"/>
-      <c r="G871" s="15"/>
-    </row>
-    <row r="872" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A872" s="13">
+    </row>
+    <row r="872" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A872" s="2">
         <v>46293</v>
       </c>
-      <c r="B872" s="14">
+      <c r="B872" s="10">
         <v>0.25694444444444442</v>
       </c>
-      <c r="C872" s="12" t="s">
+      <c r="C872" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D872" s="16" t="s">
+      <c r="D872" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="E872" s="16"/>
-      <c r="F872" s="16"/>
-      <c r="G872" s="15"/>
-    </row>
-    <row r="873" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A873" s="13">
+      <c r="E872" s="8"/>
+      <c r="F872" s="8"/>
+    </row>
+    <row r="873" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A873" s="2">
         <v>46293</v>
       </c>
-      <c r="B873" s="14">
+      <c r="B873" s="10">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C873" s="12" t="s">
+      <c r="C873" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D873" s="16" t="s">
+      <c r="D873" s="8" t="s">
         <v>372</v>
       </c>
-      <c r="E873" s="16"/>
-      <c r="F873" s="16"/>
-      <c r="G873" s="15"/>
-    </row>
-    <row r="874" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A874" s="13">
+      <c r="E873" s="8"/>
+      <c r="F873" s="8"/>
+    </row>
+    <row r="874" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A874" s="2">
         <v>46293</v>
       </c>
-      <c r="B874" s="14"/>
-      <c r="C874" s="12" t="s">
+      <c r="B874" s="10"/>
+      <c r="C874" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D874" s="16" t="s">
+      <c r="D874" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="E874" s="16"/>
-      <c r="F874" s="16"/>
-      <c r="G874" s="15"/>
-    </row>
-    <row r="875" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A875" s="13">
+      <c r="E874" s="8"/>
+      <c r="F874" s="8"/>
+    </row>
+    <row r="875" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A875" s="2">
         <v>46293</v>
       </c>
-      <c r="B875" s="14"/>
-      <c r="C875" s="12" t="s">
+      <c r="B875" s="10"/>
+      <c r="C875" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D875" s="16" t="s">
+      <c r="D875" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="E875" s="16"/>
-      <c r="F875" s="16"/>
-      <c r="G875" s="15"/>
-    </row>
-    <row r="876" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A876" s="13">
+      <c r="E875" s="8"/>
+      <c r="F875" s="8"/>
+    </row>
+    <row r="876" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A876" s="2">
         <v>46293</v>
       </c>
-      <c r="B876" s="14">
+      <c r="B876" s="10">
         <v>0.35833333333333334</v>
       </c>
-      <c r="C876" s="12" t="s">
+      <c r="C876" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D876" s="16" t="s">
+      <c r="D876" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="E876" s="16"/>
-      <c r="F876" s="16"/>
-      <c r="G876" s="15"/>
-    </row>
-    <row r="877" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A877" s="13">
+      <c r="E876" s="8"/>
+      <c r="F876" s="8"/>
+    </row>
+    <row r="877" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A877" s="2">
         <v>46293</v>
       </c>
-      <c r="B877" s="14"/>
-      <c r="C877" s="12" t="s">
+      <c r="B877" s="10"/>
+      <c r="C877" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D877" s="16" t="s">
+      <c r="D877" s="8" t="s">
         <v>376</v>
       </c>
-      <c r="E877" s="16"/>
-      <c r="F877" s="16"/>
-      <c r="G877" s="15"/>
-    </row>
-    <row r="878" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A878" s="13">
+      <c r="E877" s="8"/>
+      <c r="F877" s="8"/>
+    </row>
+    <row r="878" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A878" s="2">
         <v>46293</v>
       </c>
-      <c r="B878" s="14">
+      <c r="B878" s="10">
         <v>0.4201388888888889</v>
       </c>
-      <c r="C878" s="12" t="s">
+      <c r="C878" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D878" s="16" t="s">
+      <c r="D878" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="E878" s="16"/>
-      <c r="F878" s="16"/>
-      <c r="G878" s="15"/>
-    </row>
-    <row r="879" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A879" s="13">
+      <c r="E878" s="8"/>
+      <c r="F878" s="8"/>
+    </row>
+    <row r="879" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A879" s="2">
         <v>46293</v>
       </c>
-      <c r="B879" s="14"/>
-      <c r="C879" s="12" t="s">
+      <c r="B879" s="10"/>
+      <c r="C879" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D879" s="16" t="s">
+      <c r="D879" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="E879" s="16"/>
-      <c r="F879" s="16"/>
-      <c r="G879" s="15"/>
-    </row>
-    <row r="880" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A880" s="13">
+      <c r="E879" s="8"/>
+      <c r="F879" s="8"/>
+    </row>
+    <row r="880" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A880" s="2">
         <v>46293</v>
       </c>
-      <c r="B880" s="14">
+      <c r="B880" s="10">
         <v>0.43194444444444446</v>
       </c>
-      <c r="C880" s="12" t="s">
+      <c r="C880" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D880" s="16" t="s">
+      <c r="D880" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="E880" s="16"/>
-      <c r="F880" s="16"/>
-      <c r="G880" s="15"/>
-    </row>
-    <row r="881" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A881" s="13">
+      <c r="E880" s="8"/>
+      <c r="F880" s="8"/>
+    </row>
+    <row r="881" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A881" s="2">
         <v>46293</v>
       </c>
-      <c r="B881" s="14"/>
-      <c r="C881" s="12" t="s">
+      <c r="B881" s="10"/>
+      <c r="C881" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D881" s="16" t="s">
+      <c r="D881" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="E881" s="16"/>
-      <c r="F881" s="16"/>
-      <c r="G881" s="15"/>
-    </row>
-    <row r="882" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A882" s="13">
+      <c r="E881" s="8"/>
+      <c r="F881" s="8"/>
+    </row>
+    <row r="882" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A882" s="2">
         <v>46293</v>
       </c>
-      <c r="B882" s="14">
+      <c r="B882" s="10">
         <v>0.48958333333333331</v>
       </c>
-      <c r="C882" s="12" t="s">
+      <c r="C882" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D882" s="16" t="s">
+      <c r="D882" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="E882" s="16"/>
-      <c r="F882" s="16"/>
-      <c r="G882" s="15"/>
-    </row>
-    <row r="883" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A883" s="13">
+      <c r="E882" s="8"/>
+      <c r="F882" s="8"/>
+    </row>
+    <row r="883" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A883" s="2">
         <v>46293</v>
       </c>
-      <c r="B883" s="14"/>
-      <c r="C883" s="12" t="s">
+      <c r="B883" s="10"/>
+      <c r="C883" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D883" s="16" t="s">
+      <c r="D883" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="E883" s="16"/>
-      <c r="F883" s="16"/>
-      <c r="G883" s="15"/>
-    </row>
-    <row r="884" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A884" s="13">
+      <c r="E883" s="8"/>
+      <c r="F883" s="8"/>
+    </row>
+    <row r="884" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A884" s="2">
         <v>46293</v>
       </c>
-      <c r="B884" s="14">
+      <c r="B884" s="10">
         <v>0.49444444444444446</v>
       </c>
-      <c r="C884" s="12" t="s">
+      <c r="C884" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D884" s="16" t="s">
+      <c r="D884" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="E884" s="16"/>
-      <c r="F884" s="16"/>
-      <c r="G884" s="15"/>
-    </row>
-    <row r="885" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A885" s="13">
+      <c r="E884" s="8"/>
+      <c r="F884" s="8"/>
+    </row>
+    <row r="885" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A885" s="2">
         <v>46293</v>
       </c>
-      <c r="B885" s="14"/>
-      <c r="C885" s="12" t="s">
+      <c r="B885" s="10"/>
+      <c r="C885" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D885" s="16" t="s">
+      <c r="D885" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="E885" s="16"/>
-      <c r="F885" s="16"/>
-      <c r="G885" s="15"/>
-    </row>
-    <row r="886" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A886" s="13">
+      <c r="E885" s="8"/>
+      <c r="F885" s="8"/>
+    </row>
+    <row r="886" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A886" s="2">
         <v>46293</v>
       </c>
-      <c r="B886" s="14">
+      <c r="B886" s="10">
         <v>0.5131944444444444</v>
       </c>
-      <c r="C886" s="12" t="s">
+      <c r="C886" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D886" s="16" t="s">
+      <c r="D886" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="E886" s="16"/>
-      <c r="F886" s="16"/>
-      <c r="G886" s="15"/>
-    </row>
-    <row r="887" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A887" s="13">
+      <c r="E886" s="8"/>
+      <c r="F886" s="8"/>
+    </row>
+    <row r="887" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A887" s="2">
         <v>46293</v>
       </c>
-      <c r="B887" s="14"/>
-      <c r="C887" s="12" t="s">
+      <c r="B887" s="10"/>
+      <c r="C887" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D887" s="16" t="s">
+      <c r="D887" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="E887" s="16"/>
-      <c r="F887" s="16"/>
-      <c r="G887" s="15"/>
-    </row>
-    <row r="888" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A888" s="13">
+      <c r="E887" s="8"/>
+      <c r="F887" s="8"/>
+    </row>
+    <row r="888" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A888" s="2">
         <v>46293</v>
       </c>
-      <c r="B888" s="14">
+      <c r="B888" s="10">
         <v>0.53402777777777777</v>
       </c>
-      <c r="C888" s="12" t="s">
+      <c r="C888" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D888" s="16" t="s">
+      <c r="D888" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="E888" s="16"/>
-      <c r="F888" s="16"/>
-      <c r="G888" s="15"/>
-    </row>
-    <row r="889" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A889" s="13">
+      <c r="E888" s="8"/>
+      <c r="F888" s="8"/>
+    </row>
+    <row r="889" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A889" s="2">
         <v>46293</v>
       </c>
-      <c r="B889" s="14">
+      <c r="B889" s="10">
         <v>0.58888888888888891</v>
       </c>
-      <c r="C889" s="12" t="s">
+      <c r="C889" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D889" s="16" t="s">
+      <c r="D889" s="8" t="s">
         <v>361</v>
       </c>
-      <c r="E889" s="16"/>
-      <c r="F889" s="16"/>
-      <c r="G889" s="15"/>
-    </row>
-    <row r="890" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A890" s="13">
+      <c r="E889" s="8"/>
+      <c r="F889" s="8"/>
+    </row>
+    <row r="890" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A890" s="2">
         <v>46293</v>
       </c>
-      <c r="B890" s="14">
+      <c r="B890" s="10">
         <v>0.59027777777777779</v>
       </c>
-      <c r="C890" s="12" t="s">
+      <c r="C890" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D890" s="16" t="s">
+      <c r="D890" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="E890" s="16"/>
-      <c r="F890" s="16"/>
-      <c r="G890" s="15"/>
-    </row>
-    <row r="891" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A891" s="13">
+      <c r="E890" s="8"/>
+      <c r="F890" s="8"/>
+    </row>
+    <row r="891" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A891" s="2">
         <v>46293</v>
       </c>
-      <c r="B891" s="14">
+      <c r="B891" s="10">
         <v>0.68402777777777779</v>
       </c>
-      <c r="C891" s="12" t="s">
+      <c r="C891" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D891" s="16" t="s">
+      <c r="D891" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="E891" s="16"/>
-      <c r="F891" s="16"/>
-      <c r="G891" s="15"/>
-    </row>
-    <row r="892" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A892" s="13">
+      <c r="E891" s="8"/>
+      <c r="F891" s="8"/>
+    </row>
+    <row r="892" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A892" s="2">
         <v>46293</v>
       </c>
-      <c r="B892" s="12"/>
-      <c r="C892" s="12" t="s">
+      <c r="C892" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D892" s="16" t="s">
+      <c r="D892" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E892" s="16"/>
-      <c r="F892" s="16"/>
-      <c r="G892" s="15"/>
-    </row>
-    <row r="893" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A893" s="13">
+      <c r="E892" s="8"/>
+      <c r="F892" s="8"/>
+    </row>
+    <row r="893" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A893" s="2">
         <v>46293</v>
       </c>
-      <c r="B893" s="14">
+      <c r="B893" s="10">
         <v>0.25694444444444442</v>
       </c>
-      <c r="C893" s="12" t="s">
+      <c r="C893" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="D893" s="16" t="s">
+      <c r="D893" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="E893" s="16"/>
-      <c r="F893" s="16"/>
-      <c r="G893" s="15"/>
-    </row>
-    <row r="894" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A894" s="13">
+      <c r="E893" s="8"/>
+      <c r="F893" s="8"/>
+    </row>
+    <row r="894" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A894" s="2">
         <v>46293</v>
       </c>
-      <c r="B894" s="14">
+      <c r="B894" s="10">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C894" s="12" t="s">
+      <c r="C894" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="D894" s="16" t="s">
+      <c r="D894" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="E894" s="16"/>
-      <c r="F894" s="16"/>
-      <c r="G894" s="15"/>
-    </row>
-    <row r="895" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A895" s="13">
+      <c r="E894" s="8"/>
+      <c r="F894" s="8"/>
+    </row>
+    <row r="895" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A895" s="2">
         <v>46293</v>
       </c>
-      <c r="B895" s="14"/>
-      <c r="C895" s="12" t="s">
+      <c r="B895" s="10"/>
+      <c r="C895" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="D895" s="16" t="s">
+      <c r="D895" s="8" t="s">
         <v>381</v>
       </c>
-      <c r="E895" s="16"/>
-      <c r="F895" s="16"/>
-      <c r="G895" s="15"/>
-    </row>
-    <row r="896" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A896" s="13">
+      <c r="E895" s="8"/>
+      <c r="F895" s="8"/>
+    </row>
+    <row r="896" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A896" s="2">
         <v>46293</v>
       </c>
-      <c r="B896" s="14">
+      <c r="B896" s="10">
         <v>0.34722222222222221</v>
       </c>
-      <c r="C896" s="12" t="s">
+      <c r="C896" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="D896" s="16" t="s">
+      <c r="D896" s="8" t="s">
         <v>382</v>
       </c>
-      <c r="E896" s="16"/>
-      <c r="F896" s="16"/>
-      <c r="G896" s="15"/>
-    </row>
-    <row r="897" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A897" s="13">
+      <c r="E896" s="8"/>
+      <c r="F896" s="8"/>
+    </row>
+    <row r="897" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A897" s="2">
         <v>46293</v>
       </c>
-      <c r="B897" s="14">
+      <c r="B897" s="10">
         <v>0.3576388888888889</v>
       </c>
-      <c r="C897" s="12" t="s">
+      <c r="C897" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="D897" s="16" t="s">
+      <c r="D897" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="E897" s="16"/>
-      <c r="F897" s="16"/>
-      <c r="G897" s="15"/>
-    </row>
-    <row r="898" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A898" s="13">
+      <c r="E897" s="8"/>
+      <c r="F897" s="8"/>
+    </row>
+    <row r="898" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A898" s="2">
         <v>46293</v>
       </c>
-      <c r="B898" s="14"/>
-      <c r="C898" s="12" t="s">
+      <c r="B898" s="10"/>
+      <c r="C898" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="D898" s="16" t="s">
+      <c r="D898" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="E898" s="8"/>
+      <c r="F898" s="8"/>
+    </row>
+    <row r="899" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A899" s="2">
+        <v>46293</v>
+      </c>
+      <c r="B899" s="10">
+        <v>0.36805555555555558</v>
+      </c>
+      <c r="C899" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D899" s="8" t="s">
         <v>384</v>
       </c>
-      <c r="E898" s="16"/>
-      <c r="F898" s="16"/>
-      <c r="G898" s="15"/>
-    </row>
-    <row r="899" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A899" s="13">
+      <c r="E899" s="8"/>
+      <c r="F899" s="8"/>
+    </row>
+    <row r="900" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A900" s="2">
         <v>46293</v>
       </c>
-      <c r="B899" s="14">
+      <c r="B900" s="10">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="C900" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D900" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="E900" s="8"/>
+      <c r="F900" s="8"/>
+    </row>
+    <row r="901" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A901" s="2">
+        <v>46293</v>
+      </c>
+      <c r="B901" s="10">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C901" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D901" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="E901" s="8"/>
+      <c r="F901" s="8"/>
+    </row>
+    <row r="902" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A902" s="2">
+        <v>46293</v>
+      </c>
+      <c r="B902" s="10"/>
+      <c r="C902" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D902" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="E902" s="8"/>
+      <c r="F902" s="8"/>
+    </row>
+    <row r="903" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A903" s="2">
+        <v>46293</v>
+      </c>
+      <c r="B903" s="10"/>
+      <c r="C903" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D903" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="E903" s="8"/>
+      <c r="F903" s="8"/>
+    </row>
+    <row r="904" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A904" s="2">
+        <v>46293</v>
+      </c>
+      <c r="B904" s="10"/>
+      <c r="C904" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D904" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="E904" s="8"/>
+      <c r="F904" s="8"/>
+    </row>
+    <row r="905" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A905" s="2">
+        <v>46293</v>
+      </c>
+      <c r="B905" s="10"/>
+      <c r="C905" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D905" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="E905" s="8"/>
+      <c r="F905" s="8"/>
+    </row>
+    <row r="906" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A906" s="2">
+        <v>46293</v>
+      </c>
+      <c r="B906" s="10">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C906" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D906" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E906" s="8"/>
+      <c r="F906" s="8"/>
+    </row>
+    <row r="907" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A907" s="2">
+        <v>46293</v>
+      </c>
+      <c r="B907" s="10"/>
+      <c r="C907" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D907" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="E907" s="8"/>
+      <c r="F907" s="8"/>
+    </row>
+    <row r="908" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A908" s="2">
+        <v>46293</v>
+      </c>
+      <c r="B908" s="10">
+        <v>0.46527777777777779</v>
+      </c>
+      <c r="C908" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D908" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="E908" s="8"/>
+      <c r="F908" s="8"/>
+    </row>
+    <row r="909" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A909" s="2">
+        <v>46293</v>
+      </c>
+      <c r="B909" s="10">
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="C909" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D909" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E909" s="8"/>
+      <c r="F909" s="8"/>
+    </row>
+    <row r="910" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A910" s="2">
+        <v>46293</v>
+      </c>
+      <c r="B910" s="10"/>
+      <c r="C910" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D910" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="E910" s="8"/>
+      <c r="F910" s="8"/>
+    </row>
+    <row r="911" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A911" s="2">
+        <v>46293</v>
+      </c>
+      <c r="B911" s="10">
+        <v>0.52777777777777779</v>
+      </c>
+      <c r="C911" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D911" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="E911" s="8"/>
+      <c r="F911" s="8"/>
+    </row>
+    <row r="912" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A912" s="2">
+        <v>46293</v>
+      </c>
+      <c r="B912" s="10"/>
+      <c r="C912" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D912" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E912" s="8"/>
+      <c r="F912" s="8"/>
+    </row>
+    <row r="913" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A913" s="2">
+        <v>46293</v>
+      </c>
+      <c r="B913" s="10">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="C913" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D913" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="E913" s="8"/>
+      <c r="F913" s="8"/>
+    </row>
+    <row r="914" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A914" s="2">
+        <v>46293</v>
+      </c>
+      <c r="B914" s="10">
+        <v>0.5625</v>
+      </c>
+      <c r="C914" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D914" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="E914" s="8"/>
+      <c r="F914" s="8"/>
+    </row>
+    <row r="915" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A915" s="2">
+        <v>46293</v>
+      </c>
+      <c r="B915" s="10">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="C915" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D915" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="E915" s="8"/>
+      <c r="F915" s="8"/>
+    </row>
+    <row r="916" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A916" s="2">
+        <v>46293</v>
+      </c>
+      <c r="B916" s="10">
+        <v>0.59027777777777779</v>
+      </c>
+      <c r="C916" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D916" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="E916" s="8"/>
+      <c r="F916" s="8"/>
+    </row>
+    <row r="917" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A917" s="2">
+        <v>46293</v>
+      </c>
+      <c r="B917" s="10">
+        <v>0.68402777777777779</v>
+      </c>
+      <c r="C917" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D917" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="E917" s="8"/>
+      <c r="F917" s="8"/>
+    </row>
+    <row r="918" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A918" s="12">
+        <v>46293</v>
+      </c>
+      <c r="B918" s="13"/>
+      <c r="C918" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="D918" s="14" t="s">
+        <v>341</v>
+      </c>
+      <c r="E918" s="14"/>
+      <c r="F918" s="14"/>
+      <c r="G918" s="15"/>
+    </row>
+    <row r="919" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A919" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B919" s="16">
+        <v>0.26805555555555555</v>
+      </c>
+      <c r="C919" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D919" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="E919" s="14"/>
+      <c r="F919" s="14"/>
+      <c r="G919" s="15"/>
+    </row>
+    <row r="920" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A920" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B920" s="16">
+        <v>0.34375</v>
+      </c>
+      <c r="C920" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D920" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="E920" s="14"/>
+      <c r="F920" s="14"/>
+      <c r="G920" s="15"/>
+    </row>
+    <row r="921" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A921" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B921" s="16"/>
+      <c r="C921" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D921" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="E921" s="14"/>
+      <c r="F921" s="14"/>
+      <c r="G921" s="15"/>
+    </row>
+    <row r="922" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A922" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B922" s="16">
+        <v>0.35694444444444445</v>
+      </c>
+      <c r="C922" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D922" s="14" t="s">
+        <v>382</v>
+      </c>
+      <c r="E922" s="14"/>
+      <c r="F922" s="14"/>
+      <c r="G922" s="15"/>
+    </row>
+    <row r="923" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A923" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B923" s="16">
         <v>0.36805555555555558</v>
       </c>
-      <c r="C899" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="D899" s="16" t="s">
-        <v>385</v>
-      </c>
-      <c r="E899" s="16"/>
-      <c r="F899" s="16"/>
-      <c r="G899" s="15"/>
-    </row>
-    <row r="900" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A900" s="13">
-        <v>46293</v>
-      </c>
-      <c r="B900" s="14">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="C900" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="D900" s="16" t="s">
+      <c r="C923" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D923" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="E923" s="14"/>
+      <c r="F923" s="14"/>
+      <c r="G923" s="15"/>
+    </row>
+    <row r="924" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A924" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B924" s="16"/>
+      <c r="C924" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D924" s="14" t="s">
+        <v>397</v>
+      </c>
+      <c r="E924" s="14"/>
+      <c r="F924" s="14"/>
+      <c r="G924" s="15"/>
+    </row>
+    <row r="925" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A925" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B925" s="16">
+        <v>0.375</v>
+      </c>
+      <c r="C925" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D925" s="14" t="s">
+        <v>398</v>
+      </c>
+      <c r="E925" s="14"/>
+      <c r="F925" s="14"/>
+      <c r="G925" s="15"/>
+    </row>
+    <row r="926" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A926" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B926" s="16">
+        <v>0.40277777777777779</v>
+      </c>
+      <c r="C926" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D926" s="14" t="s">
         <v>386</v>
       </c>
-      <c r="E900" s="16"/>
-      <c r="F900" s="16"/>
-      <c r="G900" s="15"/>
-    </row>
-    <row r="901" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A901" s="13">
-        <v>46293</v>
-      </c>
-      <c r="B901" s="14">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="C901" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="D901" s="16" t="s">
-        <v>387</v>
-      </c>
-      <c r="E901" s="16"/>
-      <c r="F901" s="16"/>
-      <c r="G901" s="15"/>
-    </row>
-    <row r="902" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A902" s="13">
-        <v>46293</v>
-      </c>
-      <c r="B902" s="14"/>
-      <c r="C902" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="D902" s="16" t="s">
-        <v>388</v>
-      </c>
-      <c r="E902" s="16"/>
-      <c r="F902" s="16"/>
-      <c r="G902" s="15"/>
-    </row>
-    <row r="903" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A903" s="13">
-        <v>46293</v>
-      </c>
-      <c r="B903" s="14"/>
-      <c r="C903" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="D903" s="16" t="s">
-        <v>389</v>
-      </c>
-      <c r="E903" s="16"/>
-      <c r="F903" s="16"/>
-      <c r="G903" s="15"/>
-    </row>
-    <row r="904" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A904" s="13">
-        <v>46293</v>
-      </c>
-      <c r="B904" s="14"/>
-      <c r="C904" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="D904" s="16" t="s">
+      <c r="E926" s="14"/>
+      <c r="F926" s="14"/>
+      <c r="G926" s="15"/>
+    </row>
+    <row r="927" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A927" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B927" s="16"/>
+      <c r="C927" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D927" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="E927" s="14"/>
+      <c r="F927" s="14"/>
+      <c r="G927" s="15"/>
+    </row>
+    <row r="928" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A928" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B928" s="16"/>
+      <c r="C928" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D928" s="14" t="s">
+        <v>400</v>
+      </c>
+      <c r="E928" s="14"/>
+      <c r="F928" s="14"/>
+      <c r="G928" s="15"/>
+    </row>
+    <row r="929" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A929" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B929" s="16"/>
+      <c r="C929" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D929" s="14" t="s">
+        <v>401</v>
+      </c>
+      <c r="E929" s="14"/>
+      <c r="F929" s="14"/>
+      <c r="G929" s="15"/>
+    </row>
+    <row r="930" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A930" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B930" s="16"/>
+      <c r="C930" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D930" s="14" t="s">
+        <v>402</v>
+      </c>
+      <c r="E930" s="14"/>
+      <c r="F930" s="14"/>
+      <c r="G930" s="15"/>
+    </row>
+    <row r="931" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A931" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B931" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C931" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D931" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E931" s="14"/>
+      <c r="F931" s="14"/>
+      <c r="G931" s="15"/>
+    </row>
+    <row r="932" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A932" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B932" s="16"/>
+      <c r="C932" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D932" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="E932" s="14"/>
+      <c r="F932" s="14"/>
+      <c r="G932" s="15"/>
+    </row>
+    <row r="933" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A933" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B933" s="16">
+        <v>0.46875</v>
+      </c>
+      <c r="C933" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D933" s="14" t="s">
+        <v>386</v>
+      </c>
+      <c r="E933" s="14"/>
+      <c r="F933" s="14"/>
+      <c r="G933" s="15"/>
+    </row>
+    <row r="934" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A934" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B934" s="16"/>
+      <c r="C934" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D934" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="E934" s="14"/>
+      <c r="F934" s="14"/>
+      <c r="G934" s="15"/>
+    </row>
+    <row r="935" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A935" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B935" s="16"/>
+      <c r="C935" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D935" s="14" t="s">
+        <v>404</v>
+      </c>
+      <c r="E935" s="14"/>
+      <c r="F935" s="14"/>
+      <c r="G935" s="15"/>
+    </row>
+    <row r="936" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A936" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B936" s="16">
+        <v>0.52777777777777779</v>
+      </c>
+      <c r="C936" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D936" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E936" s="14"/>
+      <c r="F936" s="14"/>
+      <c r="G936" s="15"/>
+    </row>
+    <row r="937" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A937" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B937" s="16"/>
+      <c r="C937" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D937" s="14" t="s">
         <v>390</v>
       </c>
-      <c r="E904" s="16"/>
-      <c r="F904" s="16"/>
-      <c r="G904" s="15"/>
-    </row>
-    <row r="905" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A905" s="13">
-        <v>46293</v>
-      </c>
-      <c r="B905" s="14"/>
-      <c r="C905" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="D905" s="16" t="s">
-        <v>354</v>
-      </c>
-      <c r="E905" s="16"/>
-      <c r="F905" s="16"/>
-      <c r="G905" s="15"/>
-    </row>
-    <row r="906" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A906" s="13">
-        <v>46293</v>
-      </c>
-      <c r="B906" s="14">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="C906" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="D906" s="16" t="s">
+      <c r="E937" s="14"/>
+      <c r="F937" s="14"/>
+      <c r="G937" s="15"/>
+    </row>
+    <row r="938" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A938" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B938" s="16"/>
+      <c r="C938" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D938" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="E938" s="14"/>
+      <c r="F938" s="14"/>
+      <c r="G938" s="15"/>
+    </row>
+    <row r="939" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A939" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B939" s="16">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="C939" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D939" s="14" t="s">
         <v>391</v>
       </c>
-      <c r="E906" s="16"/>
-      <c r="F906" s="16"/>
-      <c r="G906" s="15"/>
-    </row>
-    <row r="907" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A907" s="13">
-        <v>46293</v>
-      </c>
-      <c r="B907" s="14"/>
-      <c r="C907" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="D907" s="16" t="s">
-        <v>335</v>
-      </c>
-      <c r="E907" s="16"/>
-      <c r="F907" s="16"/>
-      <c r="G907" s="15"/>
-    </row>
-    <row r="908" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A908" s="13">
-        <v>46293</v>
-      </c>
-      <c r="B908" s="14">
-        <v>0.46527777777777779</v>
-      </c>
-      <c r="C908" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="D908" s="16" t="s">
+      <c r="E939" s="14"/>
+      <c r="F939" s="14"/>
+      <c r="G939" s="15"/>
+    </row>
+    <row r="940" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A940" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B940" s="16">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="C940" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D940" s="14" t="s">
         <v>392</v>
       </c>
-      <c r="E908" s="16"/>
-      <c r="F908" s="16"/>
-      <c r="G908" s="15"/>
-    </row>
-    <row r="909" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A909" s="13">
-        <v>46293</v>
-      </c>
-      <c r="B909" s="14">
-        <v>0.50694444444444442</v>
-      </c>
-      <c r="C909" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="D909" s="16" t="s">
-        <v>391</v>
-      </c>
-      <c r="E909" s="16"/>
-      <c r="F909" s="16"/>
-      <c r="G909" s="15"/>
-    </row>
-    <row r="910" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A910" s="13">
-        <v>46293</v>
-      </c>
-      <c r="B910" s="14"/>
-      <c r="C910" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="D910" s="16" t="s">
-        <v>386</v>
-      </c>
-      <c r="E910" s="16"/>
-      <c r="F910" s="16"/>
-      <c r="G910" s="15"/>
-    </row>
-    <row r="911" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A911" s="13">
-        <v>46293</v>
-      </c>
-      <c r="B911" s="14">
-        <v>0.52777777777777779</v>
-      </c>
-      <c r="C911" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="D911" s="16" t="s">
+      <c r="E940" s="14"/>
+      <c r="F940" s="14"/>
+      <c r="G940" s="15"/>
+    </row>
+    <row r="941" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A941" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B941" s="16">
+        <v>0.56666666666666665</v>
+      </c>
+      <c r="C941" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D941" s="14" t="s">
         <v>393</v>
       </c>
-      <c r="E911" s="16"/>
-      <c r="F911" s="16"/>
-      <c r="G911" s="15"/>
-    </row>
-    <row r="912" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A912" s="13">
-        <v>46293</v>
-      </c>
-      <c r="B912" s="14"/>
-      <c r="C912" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="D912" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="E912" s="16"/>
-      <c r="F912" s="16"/>
-      <c r="G912" s="15"/>
-    </row>
-    <row r="913" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A913" s="13">
-        <v>46293</v>
-      </c>
-      <c r="B913" s="14">
-        <v>0.54861111111111116</v>
-      </c>
-      <c r="C913" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="D913" s="16" t="s">
+      <c r="E941" s="14"/>
+      <c r="F941" s="14"/>
+      <c r="G941" s="15"/>
+    </row>
+    <row r="942" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A942" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B942" s="16">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C942" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D942" s="14" t="s">
         <v>394</v>
       </c>
-      <c r="E913" s="16"/>
-      <c r="F913" s="16"/>
-      <c r="G913" s="15"/>
-    </row>
-    <row r="914" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A914" s="13">
-        <v>46293</v>
-      </c>
-      <c r="B914" s="14">
-        <v>0.5625</v>
-      </c>
-      <c r="C914" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="D914" s="16" t="s">
-        <v>395</v>
-      </c>
-      <c r="E914" s="16"/>
-      <c r="F914" s="16"/>
-      <c r="G914" s="15"/>
-    </row>
-    <row r="915" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A915" s="13">
-        <v>46293</v>
-      </c>
-      <c r="B915" s="14">
-        <v>0.57638888888888884</v>
-      </c>
-      <c r="C915" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="D915" s="16" t="s">
-        <v>396</v>
-      </c>
-      <c r="E915" s="16"/>
-      <c r="F915" s="16"/>
-      <c r="G915" s="15"/>
-    </row>
-    <row r="916" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A916" s="13">
-        <v>46293</v>
-      </c>
-      <c r="B916" s="14">
-        <v>0.59027777777777779</v>
-      </c>
-      <c r="C916" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="D916" s="16" t="s">
-        <v>397</v>
-      </c>
-      <c r="E916" s="16"/>
-      <c r="F916" s="16"/>
-      <c r="G916" s="15"/>
-    </row>
-    <row r="917" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A917" s="13">
-        <v>46293</v>
-      </c>
-      <c r="B917" s="14">
-        <v>0.68402777777777779</v>
-      </c>
-      <c r="C917" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="D917" s="16" t="s">
+      <c r="E942" s="14"/>
+      <c r="F942" s="14"/>
+      <c r="G942" s="15"/>
+    </row>
+    <row r="943" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A943" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B943" s="16">
+        <v>0.68055555555555558</v>
+      </c>
+      <c r="C943" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D943" s="14" t="s">
         <v>379</v>
       </c>
-      <c r="E917" s="16"/>
-      <c r="F917" s="16"/>
-      <c r="G917" s="15"/>
-    </row>
-    <row r="918" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A918" s="13">
-        <v>46293</v>
-      </c>
-      <c r="B918" s="12"/>
-      <c r="C918" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="D918" s="16" t="s">
-        <v>341</v>
-      </c>
-      <c r="E918" s="16"/>
-      <c r="F918" s="16"/>
-      <c r="G918" s="15"/>
+      <c r="E943" s="14"/>
+      <c r="F943" s="14"/>
+      <c r="G943" s="15"/>
+    </row>
+    <row r="944" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A944" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B944" s="16"/>
+      <c r="C944" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D944" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E944" s="14"/>
+      <c r="F944" s="14"/>
+      <c r="G944" s="15"/>
+    </row>
+    <row r="945" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A945" s="13"/>
+      <c r="B945" s="13"/>
+      <c r="C945" s="13"/>
+      <c r="D945" s="13"/>
+      <c r="E945" s="13"/>
+      <c r="F945" s="13"/>
+      <c r="G945" s="15"/>
+    </row>
+    <row r="946" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A946" s="13"/>
+      <c r="B946" s="13"/>
+      <c r="C946" s="13"/>
+      <c r="D946" s="13"/>
+      <c r="E946" s="13"/>
+      <c r="F946" s="13"/>
+      <c r="G946" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF59147-0A53-4E30-8F06-3A02D87D7A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA4E78F0-BBA6-493C-B161-779B22B00D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1978" uniqueCount="416">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1581,6 +1581,46 @@
   </si>
   <si>
     <t>LegC - CPS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>launch AIB-006</t>
+  </si>
+  <si>
+    <t>A1B, B1A, Leg B(GVI+CPM+Anode)</t>
+  </si>
+  <si>
+    <t>Leg B, CPS(GVI+CPM+Anode)</t>
+  </si>
+  <si>
+    <t>Leg B, Boatlanding(GVI+CPM+Anode)</t>
+  </si>
+  <si>
+    <t>push on D03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D03 team climb(vento)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brace A2B(GVI+CPM+Anode)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brace B1A(GVI+CPM+Anode)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brace A1B(GVI+CPM+Anode)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Leg B(GVI+CPM+Anode+Scour+Mosaic+Boatlanding)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LegB - CPS</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1661,7 +1701,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1693,13 +1733,16 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1982,7 +2025,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G946"/>
+  <dimension ref="A1:H989"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.69921875" style="1" bestFit="1" customWidth="1"/>
@@ -14435,7 +14478,7 @@
       <c r="E912" s="8"/>
       <c r="F912" s="8"/>
     </row>
-    <row r="913" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="913" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A913" s="2">
         <v>46293</v>
       </c>
@@ -14451,7 +14494,7 @@
       <c r="E913" s="8"/>
       <c r="F913" s="8"/>
     </row>
-    <row r="914" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="914" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A914" s="2">
         <v>46293</v>
       </c>
@@ -14467,7 +14510,7 @@
       <c r="E914" s="8"/>
       <c r="F914" s="8"/>
     </row>
-    <row r="915" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="915" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A915" s="2">
         <v>46293</v>
       </c>
@@ -14483,7 +14526,7 @@
       <c r="E915" s="8"/>
       <c r="F915" s="8"/>
     </row>
-    <row r="916" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="916" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A916" s="2">
         <v>46293</v>
       </c>
@@ -14499,7 +14542,7 @@
       <c r="E916" s="8"/>
       <c r="F916" s="8"/>
     </row>
-    <row r="917" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="917" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A917" s="2">
         <v>46293</v>
       </c>
@@ -14515,458 +14558,1162 @@
       <c r="E917" s="8"/>
       <c r="F917" s="8"/>
     </row>
-    <row r="918" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A918" s="12">
+    <row r="918" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A918" s="2">
         <v>46293</v>
       </c>
-      <c r="B918" s="13"/>
-      <c r="C918" s="13" t="s">
+      <c r="C918" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="D918" s="14" t="s">
+      <c r="D918" s="8" t="s">
         <v>341</v>
       </c>
-      <c r="E918" s="14"/>
-      <c r="F918" s="14"/>
-      <c r="G918" s="15"/>
-    </row>
-    <row r="919" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A919" s="12">
+      <c r="E918" s="8"/>
+      <c r="F918" s="8"/>
+    </row>
+    <row r="919" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A919" s="2">
         <v>46294</v>
       </c>
-      <c r="B919" s="16">
+      <c r="B919" s="10">
         <v>0.26805555555555555</v>
       </c>
-      <c r="C919" s="13" t="s">
+      <c r="C919" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D919" s="14" t="s">
+      <c r="D919" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="E919" s="14"/>
-      <c r="F919" s="14"/>
-      <c r="G919" s="15"/>
-    </row>
-    <row r="920" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A920" s="12">
+      <c r="E919" s="8"/>
+      <c r="F919" s="8"/>
+    </row>
+    <row r="920" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A920" s="2">
         <v>46294</v>
       </c>
-      <c r="B920" s="16">
+      <c r="B920" s="10">
         <v>0.34375</v>
       </c>
-      <c r="C920" s="13" t="s">
+      <c r="C920" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D920" s="14" t="s">
+      <c r="D920" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="E920" s="14"/>
-      <c r="F920" s="14"/>
-      <c r="G920" s="15"/>
-    </row>
-    <row r="921" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A921" s="12">
+      <c r="E920" s="8"/>
+      <c r="F920" s="8"/>
+    </row>
+    <row r="921" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A921" s="2">
         <v>46294</v>
       </c>
-      <c r="B921" s="16"/>
-      <c r="C921" s="13" t="s">
+      <c r="B921" s="10"/>
+      <c r="C921" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D921" s="14" t="s">
+      <c r="D921" s="8" t="s">
         <v>381</v>
       </c>
-      <c r="E921" s="14"/>
-      <c r="F921" s="14"/>
-      <c r="G921" s="15"/>
-    </row>
-    <row r="922" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A922" s="12">
+      <c r="E921" s="8"/>
+      <c r="F921" s="8"/>
+    </row>
+    <row r="922" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A922" s="2">
         <v>46294</v>
       </c>
-      <c r="B922" s="16">
+      <c r="B922" s="10">
         <v>0.35694444444444445</v>
       </c>
-      <c r="C922" s="13" t="s">
+      <c r="C922" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D922" s="14" t="s">
+      <c r="D922" s="8" t="s">
         <v>382</v>
       </c>
-      <c r="E922" s="14"/>
-      <c r="F922" s="14"/>
-      <c r="G922" s="15"/>
-    </row>
-    <row r="923" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A923" s="12">
+      <c r="E922" s="8"/>
+      <c r="F922" s="8"/>
+    </row>
+    <row r="923" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A923" s="2">
         <v>46294</v>
       </c>
-      <c r="B923" s="16">
+      <c r="B923" s="10">
         <v>0.36805555555555558</v>
       </c>
-      <c r="C923" s="13" t="s">
+      <c r="C923" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D923" s="14" t="s">
+      <c r="D923" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="E923" s="14"/>
-      <c r="F923" s="14"/>
-      <c r="G923" s="15"/>
-    </row>
-    <row r="924" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A924" s="12">
+      <c r="E923" s="8"/>
+      <c r="F923" s="8"/>
+    </row>
+    <row r="924" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A924" s="2">
         <v>46294</v>
       </c>
-      <c r="B924" s="16"/>
-      <c r="C924" s="13" t="s">
+      <c r="B924" s="10"/>
+      <c r="C924" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D924" s="14" t="s">
+      <c r="D924" s="8" t="s">
         <v>397</v>
       </c>
-      <c r="E924" s="14"/>
-      <c r="F924" s="14"/>
-      <c r="G924" s="15"/>
-    </row>
-    <row r="925" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A925" s="12">
+      <c r="E924" s="8"/>
+      <c r="F924" s="8"/>
+    </row>
+    <row r="925" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A925" s="2">
         <v>46294</v>
       </c>
-      <c r="B925" s="16">
+      <c r="B925" s="10">
         <v>0.375</v>
       </c>
-      <c r="C925" s="13" t="s">
+      <c r="C925" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D925" s="14" t="s">
+      <c r="D925" s="8" t="s">
         <v>398</v>
       </c>
-      <c r="E925" s="14"/>
-      <c r="F925" s="14"/>
-      <c r="G925" s="15"/>
-    </row>
-    <row r="926" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A926" s="12">
+      <c r="E925" s="8"/>
+      <c r="F925" s="8"/>
+    </row>
+    <row r="926" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A926" s="2">
         <v>46294</v>
       </c>
-      <c r="B926" s="16">
+      <c r="B926" s="10">
         <v>0.40277777777777779</v>
       </c>
-      <c r="C926" s="13" t="s">
+      <c r="C926" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D926" s="14" t="s">
+      <c r="D926" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="E926" s="14"/>
-      <c r="F926" s="14"/>
-      <c r="G926" s="15"/>
-    </row>
-    <row r="927" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A927" s="12">
+      <c r="E926" s="8"/>
+      <c r="F926" s="8"/>
+    </row>
+    <row r="927" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A927" s="2">
         <v>46294</v>
       </c>
-      <c r="B927" s="16"/>
-      <c r="C927" s="13" t="s">
+      <c r="B927" s="10"/>
+      <c r="C927" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D927" s="14" t="s">
+      <c r="D927" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="E927" s="14"/>
-      <c r="F927" s="14"/>
-      <c r="G927" s="15"/>
-    </row>
-    <row r="928" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A928" s="12">
+      <c r="E927" s="8"/>
+      <c r="F927" s="8"/>
+    </row>
+    <row r="928" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A928" s="2">
         <v>46294</v>
       </c>
-      <c r="B928" s="16"/>
-      <c r="C928" s="13" t="s">
+      <c r="B928" s="10"/>
+      <c r="C928" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D928" s="14" t="s">
+      <c r="D928" s="8" t="s">
         <v>400</v>
       </c>
-      <c r="E928" s="14"/>
-      <c r="F928" s="14"/>
-      <c r="G928" s="15"/>
-    </row>
-    <row r="929" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A929" s="12">
+      <c r="E928" s="8"/>
+      <c r="F928" s="8"/>
+    </row>
+    <row r="929" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A929" s="2">
         <v>46294</v>
       </c>
-      <c r="B929" s="16"/>
-      <c r="C929" s="13" t="s">
+      <c r="B929" s="10"/>
+      <c r="C929" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D929" s="14" t="s">
+      <c r="D929" s="8" t="s">
         <v>401</v>
       </c>
-      <c r="E929" s="14"/>
-      <c r="F929" s="14"/>
-      <c r="G929" s="15"/>
-    </row>
-    <row r="930" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A930" s="12">
+      <c r="E929" s="8"/>
+      <c r="F929" s="8"/>
+    </row>
+    <row r="930" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A930" s="2">
         <v>46294</v>
       </c>
-      <c r="B930" s="16"/>
-      <c r="C930" s="13" t="s">
+      <c r="B930" s="10"/>
+      <c r="C930" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D930" s="14" t="s">
+      <c r="D930" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="E930" s="14"/>
-      <c r="F930" s="14"/>
-      <c r="G930" s="15"/>
-    </row>
-    <row r="931" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A931" s="12">
+      <c r="E930" s="8"/>
+      <c r="F930" s="8"/>
+    </row>
+    <row r="931" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A931" s="2">
         <v>46294</v>
       </c>
-      <c r="B931" s="16">
+      <c r="B931" s="10">
         <v>0.45833333333333331</v>
       </c>
-      <c r="C931" s="13" t="s">
+      <c r="C931" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D931" s="14" t="s">
+      <c r="D931" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E931" s="14"/>
-      <c r="F931" s="14"/>
-      <c r="G931" s="15"/>
-    </row>
-    <row r="932" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A932" s="12">
+      <c r="E931" s="8"/>
+      <c r="F931" s="8"/>
+    </row>
+    <row r="932" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A932" s="2">
         <v>46294</v>
       </c>
-      <c r="B932" s="16"/>
-      <c r="C932" s="13" t="s">
+      <c r="B932" s="10"/>
+      <c r="C932" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D932" s="14" t="s">
+      <c r="D932" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="E932" s="14"/>
-      <c r="F932" s="14"/>
-      <c r="G932" s="15"/>
-    </row>
-    <row r="933" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A933" s="12">
+      <c r="E932" s="8"/>
+      <c r="F932" s="8"/>
+    </row>
+    <row r="933" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A933" s="2">
         <v>46294</v>
       </c>
-      <c r="B933" s="16">
+      <c r="B933" s="10">
         <v>0.46875</v>
       </c>
-      <c r="C933" s="13" t="s">
+      <c r="C933" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D933" s="14" t="s">
+      <c r="D933" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="E933" s="14"/>
-      <c r="F933" s="14"/>
-      <c r="G933" s="15"/>
-    </row>
-    <row r="934" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A934" s="12">
+      <c r="E933" s="8"/>
+      <c r="F933" s="8"/>
+    </row>
+    <row r="934" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A934" s="2">
         <v>46294</v>
       </c>
-      <c r="B934" s="16"/>
-      <c r="C934" s="13" t="s">
+      <c r="B934" s="10"/>
+      <c r="C934" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D934" s="14" t="s">
+      <c r="D934" s="8" t="s">
         <v>403</v>
       </c>
-      <c r="E934" s="14"/>
-      <c r="F934" s="14"/>
-      <c r="G934" s="15"/>
-    </row>
-    <row r="935" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A935" s="12">
+      <c r="E934" s="8"/>
+      <c r="F934" s="8"/>
+    </row>
+    <row r="935" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A935" s="2">
         <v>46294</v>
       </c>
-      <c r="B935" s="16"/>
-      <c r="C935" s="13" t="s">
+      <c r="B935" s="10"/>
+      <c r="C935" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D935" s="14" t="s">
+      <c r="D935" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="E935" s="14"/>
-      <c r="F935" s="14"/>
-      <c r="G935" s="15"/>
-    </row>
-    <row r="936" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A936" s="12">
+      <c r="E935" s="8"/>
+      <c r="F935" s="8"/>
+    </row>
+    <row r="936" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A936" s="2">
         <v>46294</v>
       </c>
-      <c r="B936" s="16">
+      <c r="B936" s="10">
         <v>0.52777777777777779</v>
       </c>
-      <c r="C936" s="13" t="s">
+      <c r="C936" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D936" s="14" t="s">
+      <c r="D936" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E936" s="14"/>
-      <c r="F936" s="14"/>
-      <c r="G936" s="15"/>
-    </row>
-    <row r="937" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A937" s="12">
+      <c r="E936" s="8"/>
+      <c r="F936" s="8"/>
+    </row>
+    <row r="937" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A937" s="2">
         <v>46294</v>
       </c>
-      <c r="B937" s="16"/>
-      <c r="C937" s="13" t="s">
+      <c r="B937" s="10"/>
+      <c r="C937" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D937" s="14" t="s">
+      <c r="D937" s="8" t="s">
         <v>390</v>
       </c>
-      <c r="E937" s="14"/>
-      <c r="F937" s="14"/>
-      <c r="G937" s="15"/>
-    </row>
-    <row r="938" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E937" s="8"/>
+      <c r="F937" s="8"/>
+    </row>
+    <row r="938" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A938" s="12">
         <v>46294</v>
       </c>
-      <c r="B938" s="16"/>
-      <c r="C938" s="13" t="s">
+      <c r="B938" s="13"/>
+      <c r="C938" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="D938" s="14" t="s">
+      <c r="D938" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="E938" s="14"/>
-      <c r="F938" s="14"/>
-      <c r="G938" s="15"/>
-    </row>
-    <row r="939" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E938" s="15"/>
+      <c r="F938" s="15"/>
+    </row>
+    <row r="939" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A939" s="12">
         <v>46294</v>
       </c>
-      <c r="B939" s="16">
+      <c r="B939" s="13">
         <v>0.54861111111111116</v>
       </c>
-      <c r="C939" s="13" t="s">
+      <c r="C939" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="D939" s="14" t="s">
+      <c r="D939" s="15" t="s">
         <v>391</v>
       </c>
-      <c r="E939" s="14"/>
-      <c r="F939" s="14"/>
-      <c r="G939" s="15"/>
-    </row>
-    <row r="940" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E939" s="15"/>
+      <c r="F939" s="15"/>
+    </row>
+    <row r="940" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A940" s="12">
         <v>46294</v>
       </c>
-      <c r="B940" s="16">
+      <c r="B940" s="13">
         <v>0.55555555555555558</v>
       </c>
-      <c r="C940" s="13" t="s">
+      <c r="C940" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="D940" s="14" t="s">
+      <c r="D940" s="15" t="s">
         <v>392</v>
       </c>
-      <c r="E940" s="14"/>
-      <c r="F940" s="14"/>
-      <c r="G940" s="15"/>
-    </row>
-    <row r="941" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E940" s="15"/>
+      <c r="F940" s="15"/>
+    </row>
+    <row r="941" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A941" s="12">
         <v>46294</v>
       </c>
-      <c r="B941" s="16">
+      <c r="B941" s="13">
         <v>0.56666666666666665</v>
       </c>
-      <c r="C941" s="13" t="s">
+      <c r="C941" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="D941" s="14" t="s">
+      <c r="D941" s="15" t="s">
         <v>393</v>
       </c>
-      <c r="E941" s="14"/>
-      <c r="F941" s="14"/>
-      <c r="G941" s="15"/>
-    </row>
-    <row r="942" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E941" s="15"/>
+      <c r="F941" s="15"/>
+    </row>
+    <row r="942" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A942" s="12">
         <v>46294</v>
       </c>
-      <c r="B942" s="16">
+      <c r="B942" s="13">
         <v>0.58333333333333337</v>
       </c>
-      <c r="C942" s="13" t="s">
+      <c r="C942" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="D942" s="14" t="s">
+      <c r="D942" s="15" t="s">
         <v>394</v>
       </c>
-      <c r="E942" s="14"/>
-      <c r="F942" s="14"/>
-      <c r="G942" s="15"/>
-    </row>
-    <row r="943" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E942" s="15"/>
+      <c r="F942" s="15"/>
+    </row>
+    <row r="943" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A943" s="12">
         <v>46294</v>
       </c>
-      <c r="B943" s="16">
+      <c r="B943" s="13">
         <v>0.68055555555555558</v>
       </c>
-      <c r="C943" s="13" t="s">
+      <c r="C943" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="D943" s="14" t="s">
+      <c r="D943" s="15" t="s">
         <v>379</v>
       </c>
-      <c r="E943" s="14"/>
-      <c r="F943" s="14"/>
-      <c r="G943" s="15"/>
-    </row>
-    <row r="944" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E943" s="15"/>
+      <c r="F943" s="15"/>
+    </row>
+    <row r="944" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A944" s="12">
         <v>46294</v>
       </c>
-      <c r="B944" s="16"/>
-      <c r="C944" s="13" t="s">
+      <c r="B944" s="13"/>
+      <c r="C944" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="D944" s="14" t="s">
+      <c r="D944" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="E944" s="14"/>
-      <c r="F944" s="14"/>
-      <c r="G944" s="15"/>
-    </row>
-    <row r="945" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A945" s="13"/>
-      <c r="B945" s="13"/>
-      <c r="C945" s="13"/>
-      <c r="D945" s="13"/>
-      <c r="E945" s="13"/>
-      <c r="F945" s="13"/>
-      <c r="G945" s="15"/>
-    </row>
-    <row r="946" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A946" s="13"/>
-      <c r="B946" s="13"/>
-      <c r="C946" s="13"/>
-      <c r="D946" s="13"/>
-      <c r="E946" s="13"/>
-      <c r="F946" s="13"/>
-      <c r="G946" s="15"/>
+      <c r="E944" s="15"/>
+      <c r="F944" s="15"/>
+    </row>
+    <row r="945" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A945" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B945" s="13">
+        <v>0.26805555555555555</v>
+      </c>
+      <c r="C945" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="D945" s="15" t="s">
+        <v>371</v>
+      </c>
+      <c r="E945" s="15"/>
+      <c r="F945" s="15"/>
+    </row>
+    <row r="946" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A946" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B946" s="13">
+        <v>0.34375</v>
+      </c>
+      <c r="C946" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="D946" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="E946" s="15"/>
+      <c r="F946" s="15"/>
+    </row>
+    <row r="947" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A947" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B947" s="13"/>
+      <c r="C947" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="D947" s="15" t="s">
+        <v>373</v>
+      </c>
+      <c r="E947" s="15"/>
+      <c r="F947" s="15"/>
+    </row>
+    <row r="948" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A948" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B948" s="13"/>
+      <c r="C948" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="D948" s="15" t="s">
+        <v>374</v>
+      </c>
+      <c r="E948" s="15"/>
+      <c r="F948" s="15"/>
+    </row>
+    <row r="949" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A949" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B949" s="13">
+        <v>0.37916666666666665</v>
+      </c>
+      <c r="C949" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="D949" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="E949" s="15"/>
+      <c r="F949" s="15"/>
+    </row>
+    <row r="950" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A950" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B950" s="13"/>
+      <c r="C950" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="D950" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="E950" s="15"/>
+      <c r="F950" s="15"/>
+    </row>
+    <row r="951" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A951" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B951" s="13">
+        <v>0.42083333333333334</v>
+      </c>
+      <c r="C951" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="D951" s="15" t="s">
+        <v>365</v>
+      </c>
+      <c r="E951" s="15"/>
+      <c r="F951" s="15"/>
+    </row>
+    <row r="952" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A952" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B952" s="13"/>
+      <c r="C952" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="D952" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="E952" s="15"/>
+      <c r="F952" s="15"/>
+    </row>
+    <row r="953" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A953" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B953" s="13">
+        <v>0.43194444444444446</v>
+      </c>
+      <c r="C953" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="D953" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="E953" s="15"/>
+      <c r="F953" s="15"/>
+    </row>
+    <row r="954" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A954" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B954" s="13"/>
+      <c r="C954" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="D954" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="E954" s="15"/>
+      <c r="F954" s="15"/>
+    </row>
+    <row r="955" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A955" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B955" s="13">
+        <v>0.49166666666666664</v>
+      </c>
+      <c r="C955" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="D955" s="15" t="s">
+        <v>365</v>
+      </c>
+      <c r="E955" s="15"/>
+      <c r="F955" s="15"/>
+    </row>
+    <row r="956" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A956" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B956" s="13"/>
+      <c r="C956" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="D956" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="E956" s="15"/>
+      <c r="F956" s="15"/>
+    </row>
+    <row r="957" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A957" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B957" s="13">
+        <v>0.50277777777777777</v>
+      </c>
+      <c r="C957" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="D957" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="E957" s="15"/>
+      <c r="F957" s="15"/>
+    </row>
+    <row r="958" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A958" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B958" s="13"/>
+      <c r="C958" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="D958" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="E958" s="15"/>
+      <c r="F958" s="15"/>
+    </row>
+    <row r="959" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A959" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B959" s="13">
+        <v>0.5493055555555556</v>
+      </c>
+      <c r="C959" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="D959" s="15" t="s">
+        <v>365</v>
+      </c>
+      <c r="E959" s="15"/>
+      <c r="F959" s="15"/>
+    </row>
+    <row r="960" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A960" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B960" s="13"/>
+      <c r="C960" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="D960" s="15" t="s">
+        <v>360</v>
+      </c>
+      <c r="E960" s="15"/>
+      <c r="F960" s="15"/>
+    </row>
+    <row r="961" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A961" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B961" s="13">
+        <v>0.58125000000000004</v>
+      </c>
+      <c r="C961" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="D961" s="15" t="s">
+        <v>361</v>
+      </c>
+      <c r="E961" s="15"/>
+      <c r="F961" s="15"/>
+    </row>
+    <row r="962" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A962" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B962" s="13">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C962" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="D962" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="E962" s="15"/>
+      <c r="F962" s="15"/>
+    </row>
+    <row r="963" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A963" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B963" s="13">
+        <v>0.68055555555555558</v>
+      </c>
+      <c r="C963" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="D963" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="E963" s="15"/>
+      <c r="F963" s="15"/>
+      <c r="G963" s="16"/>
+      <c r="H963" s="16"/>
+    </row>
+    <row r="964" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A964" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B964" s="14"/>
+      <c r="C964" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="D964" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E964" s="15"/>
+      <c r="F964" s="15"/>
+      <c r="G964" s="16"/>
+      <c r="H964" s="16"/>
+    </row>
+    <row r="965" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A965" s="12">
+        <v>46295</v>
+      </c>
+      <c r="B965" s="13">
+        <v>0.25694444444444442</v>
+      </c>
+      <c r="C965" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D965" s="17" t="s">
+        <v>282</v>
+      </c>
+      <c r="E965" s="17"/>
+      <c r="F965" s="17"/>
+      <c r="G965" s="16"/>
+      <c r="H965" s="16"/>
+    </row>
+    <row r="966" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A966" s="12">
+        <v>46295</v>
+      </c>
+      <c r="B966" s="13">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C966" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D966" s="17" t="s">
+        <v>409</v>
+      </c>
+      <c r="E966" s="17"/>
+      <c r="F966" s="17"/>
+      <c r="G966" s="16"/>
+      <c r="H966" s="16"/>
+    </row>
+    <row r="967" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A967" s="12">
+        <v>46295</v>
+      </c>
+      <c r="B967" s="13"/>
+      <c r="C967" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D967" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="E967" s="17"/>
+      <c r="F967" s="17"/>
+      <c r="G967" s="16"/>
+      <c r="H967" s="16"/>
+    </row>
+    <row r="968" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A968" s="12">
+        <v>46295</v>
+      </c>
+      <c r="B968" s="13">
+        <v>0.3576388888888889</v>
+      </c>
+      <c r="C968" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D968" s="17" t="s">
+        <v>382</v>
+      </c>
+      <c r="E968" s="17"/>
+      <c r="F968" s="17"/>
+      <c r="G968" s="16"/>
+      <c r="H968" s="16"/>
+    </row>
+    <row r="969" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A969" s="12">
+        <v>46295</v>
+      </c>
+      <c r="B969" s="13">
+        <v>0.3659722222222222</v>
+      </c>
+      <c r="C969" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D969" s="17" t="s">
+        <v>383</v>
+      </c>
+      <c r="E969" s="17"/>
+      <c r="F969" s="17"/>
+      <c r="G969" s="16"/>
+      <c r="H969" s="16"/>
+    </row>
+    <row r="970" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A970" s="12">
+        <v>46295</v>
+      </c>
+      <c r="B970" s="13"/>
+      <c r="C970" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D970" s="17" t="s">
+        <v>397</v>
+      </c>
+      <c r="E970" s="17"/>
+      <c r="F970" s="17"/>
+      <c r="G970" s="16"/>
+      <c r="H970" s="16"/>
+    </row>
+    <row r="971" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A971" s="12">
+        <v>46295</v>
+      </c>
+      <c r="B971" s="13">
+        <v>0.375</v>
+      </c>
+      <c r="C971" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D971" s="17" t="s">
+        <v>398</v>
+      </c>
+      <c r="E971" s="17"/>
+      <c r="F971" s="17"/>
+      <c r="G971" s="16"/>
+      <c r="H971" s="16"/>
+    </row>
+    <row r="972" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A972" s="12">
+        <v>46295</v>
+      </c>
+      <c r="B972" s="13">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C972" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D972" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="E972" s="17"/>
+      <c r="F972" s="17"/>
+      <c r="G972" s="16"/>
+      <c r="H972" s="16"/>
+    </row>
+    <row r="973" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A973" s="12">
+        <v>46295</v>
+      </c>
+      <c r="B973" s="13"/>
+      <c r="C973" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D973" s="17" t="s">
+        <v>411</v>
+      </c>
+      <c r="E973" s="17"/>
+      <c r="F973" s="17"/>
+      <c r="G973" s="16"/>
+      <c r="H973" s="16"/>
+    </row>
+    <row r="974" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A974" s="12">
+        <v>46295</v>
+      </c>
+      <c r="B974" s="13"/>
+      <c r="C974" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D974" s="17" t="s">
+        <v>412</v>
+      </c>
+      <c r="E974" s="17"/>
+      <c r="F974" s="17"/>
+      <c r="G974" s="16"/>
+      <c r="H974" s="16"/>
+    </row>
+    <row r="975" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A975" s="12">
+        <v>46295</v>
+      </c>
+      <c r="B975" s="13"/>
+      <c r="C975" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D975" s="17" t="s">
+        <v>413</v>
+      </c>
+      <c r="E975" s="17"/>
+      <c r="F975" s="17"/>
+      <c r="G975" s="16"/>
+      <c r="H975" s="16"/>
+    </row>
+    <row r="976" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A976" s="12">
+        <v>46295</v>
+      </c>
+      <c r="B976" s="13"/>
+      <c r="C976" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D976" s="17" t="s">
+        <v>351</v>
+      </c>
+      <c r="E976" s="17"/>
+      <c r="F976" s="17"/>
+      <c r="G976" s="16"/>
+      <c r="H976" s="16"/>
+    </row>
+    <row r="977" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A977" s="12">
+        <v>46295</v>
+      </c>
+      <c r="B977" s="13">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C977" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D977" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E977" s="17"/>
+      <c r="F977" s="17"/>
+      <c r="G977" s="16"/>
+      <c r="H977" s="16"/>
+    </row>
+    <row r="978" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A978" s="12">
+        <v>46295</v>
+      </c>
+      <c r="B978" s="13"/>
+      <c r="C978" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D978" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="E978" s="17"/>
+      <c r="F978" s="17"/>
+      <c r="G978" s="16"/>
+      <c r="H978" s="16"/>
+    </row>
+    <row r="979" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A979" s="12">
+        <v>46295</v>
+      </c>
+      <c r="B979" s="13">
+        <v>0.46527777777777779</v>
+      </c>
+      <c r="C979" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D979" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="E979" s="17"/>
+      <c r="F979" s="17"/>
+      <c r="G979" s="16"/>
+      <c r="H979" s="16"/>
+    </row>
+    <row r="980" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A980" s="12">
+        <v>46295</v>
+      </c>
+      <c r="B980" s="13"/>
+      <c r="C980" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D980" s="17" t="s">
+        <v>414</v>
+      </c>
+      <c r="E980" s="17"/>
+      <c r="F980" s="17"/>
+      <c r="G980" s="16"/>
+      <c r="H980" s="16"/>
+    </row>
+    <row r="981" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A981" s="12">
+        <v>46295</v>
+      </c>
+      <c r="B981" s="13"/>
+      <c r="C981" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D981" s="17" t="s">
+        <v>415</v>
+      </c>
+      <c r="E981" s="17"/>
+      <c r="F981" s="17"/>
+      <c r="G981" s="16"/>
+      <c r="H981" s="16"/>
+    </row>
+    <row r="982" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A982" s="12">
+        <v>46295</v>
+      </c>
+      <c r="B982" s="13">
+        <v>0.52777777777777779</v>
+      </c>
+      <c r="C982" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D982" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E982" s="17"/>
+      <c r="F982" s="17"/>
+      <c r="G982" s="16"/>
+      <c r="H982" s="16"/>
+    </row>
+    <row r="983" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A983" s="12">
+        <v>46295</v>
+      </c>
+      <c r="B983" s="13"/>
+      <c r="C983" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D983" s="17" t="s">
+        <v>390</v>
+      </c>
+      <c r="E983" s="17"/>
+      <c r="F983" s="17"/>
+      <c r="G983" s="16"/>
+      <c r="H983" s="16"/>
+    </row>
+    <row r="984" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A984" s="12">
+        <v>46295</v>
+      </c>
+      <c r="B984" s="13"/>
+      <c r="C984" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D984" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="E984" s="17"/>
+      <c r="F984" s="17"/>
+      <c r="G984" s="16"/>
+      <c r="H984" s="16"/>
+    </row>
+    <row r="985" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A985" s="12">
+        <v>46295</v>
+      </c>
+      <c r="B985" s="13">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C985" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D985" s="17" t="s">
+        <v>391</v>
+      </c>
+      <c r="E985" s="17"/>
+      <c r="F985" s="17"/>
+      <c r="G985" s="16"/>
+      <c r="H985" s="16"/>
+    </row>
+    <row r="986" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A986" s="12">
+        <v>46295</v>
+      </c>
+      <c r="B986" s="13">
+        <v>0.59375</v>
+      </c>
+      <c r="C986" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D986" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="E986" s="17"/>
+      <c r="F986" s="17"/>
+      <c r="G986" s="16"/>
+      <c r="H986" s="16"/>
+    </row>
+    <row r="987" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A987" s="12">
+        <v>46295</v>
+      </c>
+      <c r="B987" s="13">
+        <v>0.69444444444444442</v>
+      </c>
+      <c r="C987" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D987" s="17" t="s">
+        <v>379</v>
+      </c>
+      <c r="E987" s="17"/>
+      <c r="F987" s="17"/>
+      <c r="G987" s="16"/>
+      <c r="H987" s="16"/>
+    </row>
+    <row r="988" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A988" s="12">
+        <v>46295</v>
+      </c>
+      <c r="B988" s="13"/>
+      <c r="C988" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D988" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="E988" s="17"/>
+      <c r="F988" s="17"/>
+      <c r="G988" s="16"/>
+      <c r="H988" s="16"/>
+    </row>
+    <row r="989" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A989" s="14"/>
+      <c r="B989" s="14"/>
+      <c r="C989" s="14"/>
+      <c r="D989" s="14"/>
+      <c r="E989" s="14"/>
+      <c r="F989" s="14"/>
+      <c r="G989" s="16"/>
+      <c r="H989" s="16"/>
     </row>
   </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="D987:F987"/>
+    <mergeCell ref="D988:F988"/>
+    <mergeCell ref="D981:F981"/>
+    <mergeCell ref="D982:F982"/>
+    <mergeCell ref="D983:F983"/>
+    <mergeCell ref="D984:F984"/>
+    <mergeCell ref="D985:F985"/>
+    <mergeCell ref="D986:F986"/>
+    <mergeCell ref="D975:F975"/>
+    <mergeCell ref="D976:F976"/>
+    <mergeCell ref="D977:F977"/>
+    <mergeCell ref="D978:F978"/>
+    <mergeCell ref="D979:F979"/>
+    <mergeCell ref="D980:F980"/>
+    <mergeCell ref="D969:F969"/>
+    <mergeCell ref="D970:F970"/>
+    <mergeCell ref="D971:F971"/>
+    <mergeCell ref="D972:F972"/>
+    <mergeCell ref="D973:F973"/>
+    <mergeCell ref="D974:F974"/>
+    <mergeCell ref="D965:F965"/>
+    <mergeCell ref="D966:F966"/>
+    <mergeCell ref="D967:F967"/>
+    <mergeCell ref="D968:F968"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA4E78F0-BBA6-493C-B161-779B22B00D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E24C868-E943-472F-8499-DA4D2AF74099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1978" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2026" uniqueCount="427">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1621,6 +1621,50 @@
   </si>
   <si>
     <t>LegB - CPS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D05</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>push on D11</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D11 team climb(seasight)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>lauch AIB-006</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Leg B(GVI+CPM+Anode+Scour+Mosaic)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Leg A(GVI+CPM+Anode+Scour+Mosaic)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>recovery AIB-006/fishing net entangled with the thruster</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LegD (GVI+CPM+Anode+Scour+Mosaic+Boatlanding)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LegD - CPS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sail to D11</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait D11 team</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1701,7 +1745,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1732,15 +1776,21 @@
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2025,7 +2075,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H989"/>
+  <dimension ref="A1:H1014"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.69921875" style="1" bestFit="1" customWidth="1"/>
@@ -14856,839 +14906,1226 @@
       <c r="F937" s="8"/>
     </row>
     <row r="938" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A938" s="12">
+      <c r="A938" s="2">
         <v>46294</v>
       </c>
-      <c r="B938" s="13"/>
-      <c r="C938" s="14" t="s">
+      <c r="B938" s="10"/>
+      <c r="C938" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D938" s="15" t="s">
+      <c r="D938" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="E938" s="15"/>
-      <c r="F938" s="15"/>
+      <c r="E938" s="8"/>
+      <c r="F938" s="8"/>
     </row>
     <row r="939" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A939" s="12">
+      <c r="A939" s="2">
         <v>46294</v>
       </c>
-      <c r="B939" s="13">
+      <c r="B939" s="10">
         <v>0.54861111111111116</v>
       </c>
-      <c r="C939" s="14" t="s">
+      <c r="C939" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D939" s="15" t="s">
+      <c r="D939" s="8" t="s">
         <v>391</v>
       </c>
-      <c r="E939" s="15"/>
-      <c r="F939" s="15"/>
+      <c r="E939" s="8"/>
+      <c r="F939" s="8"/>
     </row>
     <row r="940" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A940" s="12">
+      <c r="A940" s="2">
         <v>46294</v>
       </c>
-      <c r="B940" s="13">
+      <c r="B940" s="10">
         <v>0.55555555555555558</v>
       </c>
-      <c r="C940" s="14" t="s">
+      <c r="C940" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D940" s="15" t="s">
+      <c r="D940" s="8" t="s">
         <v>392</v>
       </c>
-      <c r="E940" s="15"/>
-      <c r="F940" s="15"/>
+      <c r="E940" s="8"/>
+      <c r="F940" s="8"/>
     </row>
     <row r="941" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A941" s="12">
+      <c r="A941" s="2">
         <v>46294</v>
       </c>
-      <c r="B941" s="13">
+      <c r="B941" s="10">
         <v>0.56666666666666665</v>
       </c>
-      <c r="C941" s="14" t="s">
+      <c r="C941" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D941" s="15" t="s">
+      <c r="D941" s="8" t="s">
         <v>393</v>
       </c>
-      <c r="E941" s="15"/>
-      <c r="F941" s="15"/>
+      <c r="E941" s="8"/>
+      <c r="F941" s="8"/>
     </row>
     <row r="942" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A942" s="12">
+      <c r="A942" s="2">
         <v>46294</v>
       </c>
-      <c r="B942" s="13">
+      <c r="B942" s="10">
         <v>0.58333333333333337</v>
       </c>
-      <c r="C942" s="14" t="s">
+      <c r="C942" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D942" s="15" t="s">
+      <c r="D942" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="E942" s="15"/>
-      <c r="F942" s="15"/>
+      <c r="E942" s="8"/>
+      <c r="F942" s="8"/>
     </row>
     <row r="943" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A943" s="12">
+      <c r="A943" s="2">
         <v>46294</v>
       </c>
-      <c r="B943" s="13">
+      <c r="B943" s="10">
         <v>0.68055555555555558</v>
       </c>
-      <c r="C943" s="14" t="s">
+      <c r="C943" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D943" s="15" t="s">
+      <c r="D943" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="E943" s="15"/>
-      <c r="F943" s="15"/>
+      <c r="E943" s="8"/>
+      <c r="F943" s="8"/>
     </row>
     <row r="944" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A944" s="12">
+      <c r="A944" s="2">
         <v>46294</v>
       </c>
-      <c r="B944" s="13"/>
-      <c r="C944" s="14" t="s">
+      <c r="B944" s="10"/>
+      <c r="C944" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D944" s="15" t="s">
+      <c r="D944" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E944" s="15"/>
-      <c r="F944" s="15"/>
+      <c r="E944" s="8"/>
+      <c r="F944" s="8"/>
     </row>
     <row r="945" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A945" s="12">
+      <c r="A945" s="2">
         <v>46294</v>
       </c>
-      <c r="B945" s="13">
+      <c r="B945" s="10">
         <v>0.26805555555555555</v>
       </c>
-      <c r="C945" s="14" t="s">
+      <c r="C945" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D945" s="15" t="s">
+      <c r="D945" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="E945" s="15"/>
-      <c r="F945" s="15"/>
+      <c r="E945" s="8"/>
+      <c r="F945" s="8"/>
     </row>
     <row r="946" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A946" s="12">
+      <c r="A946" s="2">
         <v>46294</v>
       </c>
-      <c r="B946" s="13">
+      <c r="B946" s="10">
         <v>0.34375</v>
       </c>
-      <c r="C946" s="14" t="s">
+      <c r="C946" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D946" s="15" t="s">
+      <c r="D946" s="8" t="s">
         <v>372</v>
       </c>
-      <c r="E946" s="15"/>
-      <c r="F946" s="15"/>
+      <c r="E946" s="8"/>
+      <c r="F946" s="8"/>
     </row>
     <row r="947" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A947" s="12">
+      <c r="A947" s="2">
         <v>46294</v>
       </c>
-      <c r="B947" s="13"/>
-      <c r="C947" s="14" t="s">
+      <c r="B947" s="10"/>
+      <c r="C947" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D947" s="15" t="s">
+      <c r="D947" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="E947" s="15"/>
-      <c r="F947" s="15"/>
+      <c r="E947" s="8"/>
+      <c r="F947" s="8"/>
     </row>
     <row r="948" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A948" s="12">
+      <c r="A948" s="2">
         <v>46294</v>
       </c>
-      <c r="B948" s="13"/>
-      <c r="C948" s="14" t="s">
+      <c r="B948" s="10"/>
+      <c r="C948" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D948" s="15" t="s">
+      <c r="D948" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="E948" s="15"/>
-      <c r="F948" s="15"/>
+      <c r="E948" s="8"/>
+      <c r="F948" s="8"/>
     </row>
     <row r="949" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A949" s="12">
+      <c r="A949" s="2">
         <v>46294</v>
       </c>
-      <c r="B949" s="13">
+      <c r="B949" s="10">
         <v>0.37916666666666665</v>
       </c>
-      <c r="C949" s="14" t="s">
+      <c r="C949" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D949" s="15" t="s">
+      <c r="D949" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="E949" s="15"/>
-      <c r="F949" s="15"/>
+      <c r="E949" s="8"/>
+      <c r="F949" s="8"/>
     </row>
     <row r="950" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A950" s="12">
+      <c r="A950" s="2">
         <v>46294</v>
       </c>
-      <c r="B950" s="13"/>
-      <c r="C950" s="14" t="s">
+      <c r="B950" s="10"/>
+      <c r="C950" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D950" s="15" t="s">
+      <c r="D950" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="E950" s="15"/>
-      <c r="F950" s="15"/>
+      <c r="E950" s="8"/>
+      <c r="F950" s="8"/>
     </row>
     <row r="951" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A951" s="12">
+      <c r="A951" s="2">
         <v>46294</v>
       </c>
-      <c r="B951" s="13">
+      <c r="B951" s="10">
         <v>0.42083333333333334</v>
       </c>
-      <c r="C951" s="14" t="s">
+      <c r="C951" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D951" s="15" t="s">
+      <c r="D951" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="E951" s="15"/>
-      <c r="F951" s="15"/>
+      <c r="E951" s="8"/>
+      <c r="F951" s="8"/>
     </row>
     <row r="952" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A952" s="12">
+      <c r="A952" s="2">
         <v>46294</v>
       </c>
-      <c r="B952" s="13"/>
-      <c r="C952" s="14" t="s">
+      <c r="B952" s="10"/>
+      <c r="C952" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D952" s="15" t="s">
+      <c r="D952" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="E952" s="15"/>
-      <c r="F952" s="15"/>
+      <c r="E952" s="8"/>
+      <c r="F952" s="8"/>
     </row>
     <row r="953" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A953" s="12">
+      <c r="A953" s="2">
         <v>46294</v>
       </c>
-      <c r="B953" s="13">
+      <c r="B953" s="10">
         <v>0.43194444444444446</v>
       </c>
-      <c r="C953" s="14" t="s">
+      <c r="C953" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D953" s="15" t="s">
+      <c r="D953" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="E953" s="15"/>
-      <c r="F953" s="15"/>
+      <c r="E953" s="8"/>
+      <c r="F953" s="8"/>
     </row>
     <row r="954" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A954" s="12">
+      <c r="A954" s="2">
         <v>46294</v>
       </c>
-      <c r="B954" s="13"/>
-      <c r="C954" s="14" t="s">
+      <c r="B954" s="10"/>
+      <c r="C954" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D954" s="15" t="s">
+      <c r="D954" s="8" t="s">
         <v>407</v>
       </c>
-      <c r="E954" s="15"/>
-      <c r="F954" s="15"/>
+      <c r="E954" s="8"/>
+      <c r="F954" s="8"/>
     </row>
     <row r="955" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A955" s="12">
+      <c r="A955" s="2">
         <v>46294</v>
       </c>
-      <c r="B955" s="13">
+      <c r="B955" s="10">
         <v>0.49166666666666664</v>
       </c>
-      <c r="C955" s="14" t="s">
+      <c r="C955" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D955" s="15" t="s">
+      <c r="D955" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="E955" s="15"/>
-      <c r="F955" s="15"/>
+      <c r="E955" s="8"/>
+      <c r="F955" s="8"/>
     </row>
     <row r="956" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A956" s="12">
+      <c r="A956" s="2">
         <v>46294</v>
       </c>
-      <c r="B956" s="13"/>
-      <c r="C956" s="14" t="s">
+      <c r="B956" s="10"/>
+      <c r="C956" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D956" s="15" t="s">
+      <c r="D956" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="E956" s="15"/>
-      <c r="F956" s="15"/>
+      <c r="E956" s="8"/>
+      <c r="F956" s="8"/>
     </row>
     <row r="957" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A957" s="12">
+      <c r="A957" s="2">
         <v>46294</v>
       </c>
-      <c r="B957" s="13">
+      <c r="B957" s="10">
         <v>0.50277777777777777</v>
       </c>
-      <c r="C957" s="14" t="s">
+      <c r="C957" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D957" s="15" t="s">
+      <c r="D957" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="E957" s="15"/>
-      <c r="F957" s="15"/>
+      <c r="E957" s="8"/>
+      <c r="F957" s="8"/>
     </row>
     <row r="958" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A958" s="12">
+      <c r="A958" s="2">
         <v>46294</v>
       </c>
-      <c r="B958" s="13"/>
-      <c r="C958" s="14" t="s">
+      <c r="B958" s="10"/>
+      <c r="C958" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D958" s="15" t="s">
+      <c r="D958" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="E958" s="15"/>
-      <c r="F958" s="15"/>
+      <c r="E958" s="8"/>
+      <c r="F958" s="8"/>
     </row>
     <row r="959" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A959" s="12">
+      <c r="A959" s="2">
         <v>46294</v>
       </c>
-      <c r="B959" s="13">
+      <c r="B959" s="10">
         <v>0.5493055555555556</v>
       </c>
-      <c r="C959" s="14" t="s">
+      <c r="C959" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D959" s="15" t="s">
+      <c r="D959" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="E959" s="15"/>
-      <c r="F959" s="15"/>
+      <c r="E959" s="8"/>
+      <c r="F959" s="8"/>
     </row>
     <row r="960" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A960" s="12">
+      <c r="A960" s="2">
         <v>46294</v>
       </c>
-      <c r="B960" s="13"/>
-      <c r="C960" s="14" t="s">
+      <c r="B960" s="10"/>
+      <c r="C960" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D960" s="15" t="s">
+      <c r="D960" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="E960" s="15"/>
-      <c r="F960" s="15"/>
-    </row>
-    <row r="961" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A961" s="12">
+      <c r="E960" s="8"/>
+      <c r="F960" s="8"/>
+    </row>
+    <row r="961" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A961" s="2">
         <v>46294</v>
       </c>
-      <c r="B961" s="13">
+      <c r="B961" s="10">
         <v>0.58125000000000004</v>
       </c>
-      <c r="C961" s="14" t="s">
+      <c r="C961" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D961" s="15" t="s">
+      <c r="D961" s="8" t="s">
         <v>361</v>
       </c>
-      <c r="E961" s="15"/>
-      <c r="F961" s="15"/>
-    </row>
-    <row r="962" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A962" s="12">
+      <c r="E961" s="8"/>
+      <c r="F961" s="8"/>
+    </row>
+    <row r="962" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A962" s="2">
         <v>46294</v>
       </c>
-      <c r="B962" s="13">
+      <c r="B962" s="10">
         <v>0.58333333333333337</v>
       </c>
-      <c r="C962" s="14" t="s">
+      <c r="C962" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D962" s="15" t="s">
+      <c r="D962" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="E962" s="15"/>
-      <c r="F962" s="15"/>
-    </row>
-    <row r="963" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A963" s="12">
+      <c r="E962" s="8"/>
+      <c r="F962" s="8"/>
+    </row>
+    <row r="963" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A963" s="2">
         <v>46294</v>
       </c>
-      <c r="B963" s="13">
+      <c r="B963" s="10">
         <v>0.68055555555555558</v>
       </c>
-      <c r="C963" s="14" t="s">
+      <c r="C963" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D963" s="15" t="s">
+      <c r="D963" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="E963" s="15"/>
-      <c r="F963" s="15"/>
-      <c r="G963" s="16"/>
-      <c r="H963" s="16"/>
-    </row>
-    <row r="964" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A964" s="12">
+      <c r="E963" s="8"/>
+      <c r="F963" s="8"/>
+    </row>
+    <row r="964" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A964" s="2">
         <v>46294</v>
       </c>
-      <c r="B964" s="14"/>
-      <c r="C964" s="14" t="s">
+      <c r="C964" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D964" s="15" t="s">
+      <c r="D964" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E964" s="15"/>
-      <c r="F964" s="15"/>
-      <c r="G964" s="16"/>
-      <c r="H964" s="16"/>
-    </row>
-    <row r="965" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A965" s="12">
+      <c r="E964" s="8"/>
+      <c r="F964" s="8"/>
+    </row>
+    <row r="965" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A965" s="2">
         <v>46295</v>
       </c>
-      <c r="B965" s="13">
+      <c r="B965" s="10">
         <v>0.25694444444444442</v>
       </c>
-      <c r="C965" s="14" t="s">
+      <c r="C965" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D965" s="17" t="s">
+      <c r="D965" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="E965" s="17"/>
-      <c r="F965" s="17"/>
-      <c r="G965" s="16"/>
-      <c r="H965" s="16"/>
-    </row>
-    <row r="966" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A966" s="12">
+      <c r="E965" s="12"/>
+      <c r="F965" s="12"/>
+    </row>
+    <row r="966" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A966" s="2">
         <v>46295</v>
       </c>
-      <c r="B966" s="13">
+      <c r="B966" s="10">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C966" s="14" t="s">
+      <c r="C966" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D966" s="17" t="s">
+      <c r="D966" s="12" t="s">
         <v>409</v>
       </c>
-      <c r="E966" s="17"/>
-      <c r="F966" s="17"/>
-      <c r="G966" s="16"/>
-      <c r="H966" s="16"/>
-    </row>
-    <row r="967" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A967" s="12">
+      <c r="E966" s="12"/>
+      <c r="F966" s="12"/>
+    </row>
+    <row r="967" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A967" s="2">
         <v>46295</v>
       </c>
-      <c r="B967" s="13"/>
-      <c r="C967" s="14" t="s">
+      <c r="B967" s="10"/>
+      <c r="C967" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D967" s="17" t="s">
+      <c r="D967" s="12" t="s">
         <v>410</v>
       </c>
-      <c r="E967" s="17"/>
-      <c r="F967" s="17"/>
-      <c r="G967" s="16"/>
-      <c r="H967" s="16"/>
-    </row>
-    <row r="968" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A968" s="12">
+      <c r="E967" s="12"/>
+      <c r="F967" s="12"/>
+    </row>
+    <row r="968" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A968" s="2">
         <v>46295</v>
       </c>
-      <c r="B968" s="13">
+      <c r="B968" s="10">
         <v>0.3576388888888889</v>
       </c>
-      <c r="C968" s="14" t="s">
+      <c r="C968" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D968" s="17" t="s">
+      <c r="D968" s="12" t="s">
         <v>382</v>
       </c>
-      <c r="E968" s="17"/>
-      <c r="F968" s="17"/>
-      <c r="G968" s="16"/>
-      <c r="H968" s="16"/>
-    </row>
-    <row r="969" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A969" s="12">
+      <c r="E968" s="12"/>
+      <c r="F968" s="12"/>
+    </row>
+    <row r="969" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A969" s="2">
         <v>46295</v>
       </c>
-      <c r="B969" s="13">
+      <c r="B969" s="10">
         <v>0.3659722222222222</v>
       </c>
-      <c r="C969" s="14" t="s">
+      <c r="C969" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D969" s="17" t="s">
+      <c r="D969" s="12" t="s">
         <v>383</v>
       </c>
-      <c r="E969" s="17"/>
-      <c r="F969" s="17"/>
-      <c r="G969" s="16"/>
-      <c r="H969" s="16"/>
-    </row>
-    <row r="970" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A970" s="12">
+      <c r="E969" s="12"/>
+      <c r="F969" s="12"/>
+    </row>
+    <row r="970" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A970" s="2">
         <v>46295</v>
       </c>
-      <c r="B970" s="13"/>
-      <c r="C970" s="14" t="s">
+      <c r="B970" s="10"/>
+      <c r="C970" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D970" s="17" t="s">
+      <c r="D970" s="12" t="s">
         <v>397</v>
       </c>
-      <c r="E970" s="17"/>
-      <c r="F970" s="17"/>
-      <c r="G970" s="16"/>
-      <c r="H970" s="16"/>
-    </row>
-    <row r="971" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A971" s="12">
+      <c r="E970" s="12"/>
+      <c r="F970" s="12"/>
+    </row>
+    <row r="971" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A971" s="2">
         <v>46295</v>
       </c>
-      <c r="B971" s="13">
+      <c r="B971" s="10">
         <v>0.375</v>
       </c>
-      <c r="C971" s="14" t="s">
+      <c r="C971" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D971" s="17" t="s">
+      <c r="D971" s="12" t="s">
         <v>398</v>
       </c>
-      <c r="E971" s="17"/>
-      <c r="F971" s="17"/>
-      <c r="G971" s="16"/>
-      <c r="H971" s="16"/>
-    </row>
-    <row r="972" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A972" s="12">
+      <c r="E971" s="12"/>
+      <c r="F971" s="12"/>
+    </row>
+    <row r="972" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A972" s="2">
         <v>46295</v>
       </c>
-      <c r="B972" s="13">
+      <c r="B972" s="10">
         <v>0.39583333333333331</v>
       </c>
-      <c r="C972" s="14" t="s">
+      <c r="C972" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D972" s="17" t="s">
+      <c r="D972" s="12" t="s">
         <v>386</v>
       </c>
-      <c r="E972" s="17"/>
-      <c r="F972" s="17"/>
-      <c r="G972" s="16"/>
-      <c r="H972" s="16"/>
-    </row>
-    <row r="973" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A973" s="12">
+      <c r="E972" s="12"/>
+      <c r="F972" s="12"/>
+    </row>
+    <row r="973" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A973" s="2">
         <v>46295</v>
       </c>
-      <c r="B973" s="13"/>
-      <c r="C973" s="14" t="s">
+      <c r="B973" s="10"/>
+      <c r="C973" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D973" s="17" t="s">
+      <c r="D973" s="12" t="s">
         <v>411</v>
       </c>
-      <c r="E973" s="17"/>
-      <c r="F973" s="17"/>
-      <c r="G973" s="16"/>
-      <c r="H973" s="16"/>
-    </row>
-    <row r="974" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A974" s="12">
+      <c r="E973" s="12"/>
+      <c r="F973" s="12"/>
+    </row>
+    <row r="974" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A974" s="2">
         <v>46295</v>
       </c>
-      <c r="B974" s="13"/>
-      <c r="C974" s="14" t="s">
+      <c r="B974" s="10"/>
+      <c r="C974" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D974" s="17" t="s">
+      <c r="D974" s="12" t="s">
         <v>412</v>
       </c>
-      <c r="E974" s="17"/>
-      <c r="F974" s="17"/>
-      <c r="G974" s="16"/>
-      <c r="H974" s="16"/>
-    </row>
-    <row r="975" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A975" s="12">
+      <c r="E974" s="12"/>
+      <c r="F974" s="12"/>
+    </row>
+    <row r="975" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A975" s="2">
         <v>46295</v>
       </c>
-      <c r="B975" s="13"/>
-      <c r="C975" s="14" t="s">
+      <c r="B975" s="10"/>
+      <c r="C975" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D975" s="17" t="s">
+      <c r="D975" s="12" t="s">
         <v>413</v>
       </c>
-      <c r="E975" s="17"/>
-      <c r="F975" s="17"/>
-      <c r="G975" s="16"/>
-      <c r="H975" s="16"/>
-    </row>
-    <row r="976" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A976" s="12">
+      <c r="E975" s="12"/>
+      <c r="F975" s="12"/>
+    </row>
+    <row r="976" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A976" s="2">
         <v>46295</v>
       </c>
-      <c r="B976" s="13"/>
-      <c r="C976" s="14" t="s">
+      <c r="B976" s="10"/>
+      <c r="C976" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D976" s="17" t="s">
+      <c r="D976" s="12" t="s">
         <v>351</v>
       </c>
-      <c r="E976" s="17"/>
-      <c r="F976" s="17"/>
-      <c r="G976" s="16"/>
-      <c r="H976" s="16"/>
+      <c r="E976" s="12"/>
+      <c r="F976" s="12"/>
     </row>
     <row r="977" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A977" s="12">
+      <c r="A977" s="2">
         <v>46295</v>
       </c>
-      <c r="B977" s="13">
+      <c r="B977" s="10">
         <v>0.45833333333333331</v>
       </c>
-      <c r="C977" s="14" t="s">
+      <c r="C977" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D977" s="17" t="s">
+      <c r="D977" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E977" s="17"/>
-      <c r="F977" s="17"/>
-      <c r="G977" s="16"/>
-      <c r="H977" s="16"/>
+      <c r="E977" s="12"/>
+      <c r="F977" s="12"/>
     </row>
     <row r="978" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A978" s="12">
+      <c r="A978" s="2">
         <v>46295</v>
       </c>
-      <c r="B978" s="13"/>
-      <c r="C978" s="14" t="s">
+      <c r="B978" s="10"/>
+      <c r="C978" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D978" s="17" t="s">
+      <c r="D978" s="12" t="s">
         <v>335</v>
       </c>
-      <c r="E978" s="17"/>
-      <c r="F978" s="17"/>
-      <c r="G978" s="16"/>
-      <c r="H978" s="16"/>
+      <c r="E978" s="12"/>
+      <c r="F978" s="12"/>
     </row>
     <row r="979" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A979" s="12">
+      <c r="A979" s="2">
         <v>46295</v>
       </c>
-      <c r="B979" s="13">
+      <c r="B979" s="10">
         <v>0.46527777777777779</v>
       </c>
-      <c r="C979" s="14" t="s">
+      <c r="C979" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D979" s="17" t="s">
+      <c r="D979" s="12" t="s">
         <v>386</v>
       </c>
-      <c r="E979" s="17"/>
-      <c r="F979" s="17"/>
-      <c r="G979" s="16"/>
-      <c r="H979" s="16"/>
+      <c r="E979" s="12"/>
+      <c r="F979" s="12"/>
     </row>
     <row r="980" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A980" s="12">
+      <c r="A980" s="2">
         <v>46295</v>
       </c>
-      <c r="B980" s="13"/>
-      <c r="C980" s="14" t="s">
+      <c r="B980" s="10"/>
+      <c r="C980" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D980" s="17" t="s">
+      <c r="D980" s="12" t="s">
         <v>414</v>
       </c>
-      <c r="E980" s="17"/>
-      <c r="F980" s="17"/>
-      <c r="G980" s="16"/>
-      <c r="H980" s="16"/>
+      <c r="E980" s="12"/>
+      <c r="F980" s="12"/>
     </row>
     <row r="981" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A981" s="12">
+      <c r="A981" s="2">
         <v>46295</v>
       </c>
-      <c r="B981" s="13"/>
-      <c r="C981" s="14" t="s">
+      <c r="B981" s="10"/>
+      <c r="C981" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D981" s="17" t="s">
+      <c r="D981" s="12" t="s">
         <v>415</v>
       </c>
-      <c r="E981" s="17"/>
-      <c r="F981" s="17"/>
-      <c r="G981" s="16"/>
-      <c r="H981" s="16"/>
+      <c r="E981" s="12"/>
+      <c r="F981" s="12"/>
     </row>
     <row r="982" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A982" s="12">
+      <c r="A982" s="2">
         <v>46295</v>
       </c>
-      <c r="B982" s="13">
+      <c r="B982" s="10">
         <v>0.52777777777777779</v>
       </c>
-      <c r="C982" s="14" t="s">
+      <c r="C982" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D982" s="17" t="s">
+      <c r="D982" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E982" s="17"/>
-      <c r="F982" s="17"/>
-      <c r="G982" s="16"/>
-      <c r="H982" s="16"/>
+      <c r="E982" s="12"/>
+      <c r="F982" s="12"/>
     </row>
     <row r="983" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A983" s="12">
+      <c r="A983" s="2">
         <v>46295</v>
       </c>
-      <c r="B983" s="13"/>
-      <c r="C983" s="14" t="s">
+      <c r="B983" s="10"/>
+      <c r="C983" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D983" s="17" t="s">
+      <c r="D983" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="E983" s="17"/>
-      <c r="F983" s="17"/>
-      <c r="G983" s="16"/>
-      <c r="H983" s="16"/>
+      <c r="E983" s="12"/>
+      <c r="F983" s="12"/>
     </row>
     <row r="984" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A984" s="12">
+      <c r="A984" s="2">
         <v>46295</v>
       </c>
-      <c r="B984" s="13"/>
-      <c r="C984" s="14" t="s">
+      <c r="B984" s="10"/>
+      <c r="C984" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D984" s="17" t="s">
+      <c r="D984" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="E984" s="17"/>
-      <c r="F984" s="17"/>
-      <c r="G984" s="16"/>
-      <c r="H984" s="16"/>
+      <c r="E984" s="12"/>
+      <c r="F984" s="12"/>
     </row>
     <row r="985" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A985" s="12">
+      <c r="A985" s="2">
         <v>46295</v>
       </c>
-      <c r="B985" s="13">
+      <c r="B985" s="10">
         <v>0.58333333333333337</v>
       </c>
-      <c r="C985" s="14" t="s">
+      <c r="C985" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D985" s="17" t="s">
+      <c r="D985" s="12" t="s">
         <v>391</v>
       </c>
-      <c r="E985" s="17"/>
-      <c r="F985" s="17"/>
-      <c r="G985" s="16"/>
-      <c r="H985" s="16"/>
+      <c r="E985" s="12"/>
+      <c r="F985" s="12"/>
     </row>
     <row r="986" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A986" s="12">
+      <c r="A986" s="2">
         <v>46295</v>
       </c>
-      <c r="B986" s="13">
+      <c r="B986" s="10">
         <v>0.59375</v>
       </c>
-      <c r="C986" s="14" t="s">
+      <c r="C986" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D986" s="17" t="s">
+      <c r="D986" s="12" t="s">
         <v>394</v>
       </c>
-      <c r="E986" s="17"/>
-      <c r="F986" s="17"/>
-      <c r="G986" s="16"/>
-      <c r="H986" s="16"/>
+      <c r="E986" s="12"/>
+      <c r="F986" s="12"/>
     </row>
     <row r="987" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A987" s="12">
+      <c r="A987" s="2">
         <v>46295</v>
       </c>
-      <c r="B987" s="13">
+      <c r="B987" s="10">
         <v>0.69444444444444442</v>
       </c>
-      <c r="C987" s="14" t="s">
+      <c r="C987" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D987" s="17" t="s">
+      <c r="D987" s="12" t="s">
         <v>379</v>
       </c>
-      <c r="E987" s="17"/>
-      <c r="F987" s="17"/>
-      <c r="G987" s="16"/>
-      <c r="H987" s="16"/>
+      <c r="E987" s="12"/>
+      <c r="F987" s="12"/>
     </row>
     <row r="988" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A988" s="12">
+      <c r="A988" s="13">
         <v>46295</v>
       </c>
-      <c r="B988" s="13"/>
-      <c r="C988" s="14" t="s">
+      <c r="B988" s="14"/>
+      <c r="C988" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="D988" s="17" t="s">
+      <c r="D988" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="E988" s="17"/>
-      <c r="F988" s="17"/>
-      <c r="G988" s="16"/>
-      <c r="H988" s="16"/>
+      <c r="E988" s="16"/>
+      <c r="F988" s="16"/>
+      <c r="G988" s="17"/>
+      <c r="H988" s="17"/>
     </row>
     <row r="989" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A989" s="14"/>
-      <c r="B989" s="14"/>
-      <c r="C989" s="14"/>
-      <c r="D989" s="14"/>
-      <c r="E989" s="14"/>
-      <c r="F989" s="14"/>
-      <c r="G989" s="16"/>
-      <c r="H989" s="16"/>
+      <c r="A989" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B989" s="14">
+        <v>0.26874999999999999</v>
+      </c>
+      <c r="C989" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="D989" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="E989" s="18"/>
+      <c r="F989" s="18"/>
+      <c r="G989" s="17"/>
+      <c r="H989" s="17"/>
+    </row>
+    <row r="990" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A990" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B990" s="14">
+        <v>0.34027777777777779</v>
+      </c>
+      <c r="C990" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="D990" s="18" t="s">
+        <v>417</v>
+      </c>
+      <c r="E990" s="18"/>
+      <c r="F990" s="18"/>
+      <c r="G990" s="17"/>
+      <c r="H990" s="17"/>
+    </row>
+    <row r="991" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A991" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B991" s="14"/>
+      <c r="C991" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="D991" s="18" t="s">
+        <v>418</v>
+      </c>
+      <c r="E991" s="18"/>
+      <c r="F991" s="18"/>
+      <c r="G991" s="17"/>
+      <c r="H991" s="17"/>
+    </row>
+    <row r="992" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A992" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B992" s="14">
+        <v>0.35902777777777778</v>
+      </c>
+      <c r="C992" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="D992" s="18" t="s">
+        <v>382</v>
+      </c>
+      <c r="E992" s="18"/>
+      <c r="F992" s="18"/>
+      <c r="G992" s="17"/>
+      <c r="H992" s="17"/>
+    </row>
+    <row r="993" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A993" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B993" s="14">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="C993" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="D993" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="E993" s="18"/>
+      <c r="F993" s="18"/>
+      <c r="G993" s="17"/>
+      <c r="H993" s="17"/>
+    </row>
+    <row r="994" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A994" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B994" s="14"/>
+      <c r="C994" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="D994" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="E994" s="18"/>
+      <c r="F994" s="18"/>
+      <c r="G994" s="17"/>
+      <c r="H994" s="17"/>
+    </row>
+    <row r="995" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A995" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B995" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="C995" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="D995" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E995" s="18"/>
+      <c r="F995" s="18"/>
+      <c r="G995" s="17"/>
+      <c r="H995" s="17"/>
+    </row>
+    <row r="996" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A996" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B996" s="14">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C996" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="D996" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="E996" s="18"/>
+      <c r="F996" s="18"/>
+      <c r="G996" s="17"/>
+      <c r="H996" s="17"/>
+    </row>
+    <row r="997" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A997" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B997" s="14"/>
+      <c r="C997" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="D997" s="18" t="s">
+        <v>420</v>
+      </c>
+      <c r="E997" s="18"/>
+      <c r="F997" s="18"/>
+      <c r="G997" s="17"/>
+      <c r="H997" s="17"/>
+    </row>
+    <row r="998" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A998" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B998" s="14"/>
+      <c r="C998" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="D998" s="18" t="s">
+        <v>421</v>
+      </c>
+      <c r="E998" s="18"/>
+      <c r="F998" s="18"/>
+      <c r="G998" s="17"/>
+      <c r="H998" s="17"/>
+    </row>
+    <row r="999" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A999" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B999" s="14">
+        <v>0.4375</v>
+      </c>
+      <c r="C999" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="D999" s="18" t="s">
+        <v>422</v>
+      </c>
+      <c r="E999" s="18"/>
+      <c r="F999" s="18"/>
+      <c r="G999" s="17"/>
+      <c r="H999" s="17"/>
+    </row>
+    <row r="1000" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1000" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B1000" s="14"/>
+      <c r="C1000" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="D1000" s="19" t="s">
+        <v>335</v>
+      </c>
+      <c r="E1000" s="19"/>
+      <c r="F1000" s="19"/>
+      <c r="G1000" s="17"/>
+      <c r="H1000" s="17"/>
+    </row>
+    <row r="1001" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1001" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B1001" s="14">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C1001" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="D1001" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="E1001" s="18"/>
+      <c r="F1001" s="18"/>
+      <c r="G1001" s="17"/>
+      <c r="H1001" s="17"/>
+    </row>
+    <row r="1002" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1002" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B1002" s="14"/>
+      <c r="C1002" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="D1002" s="18" t="s">
+        <v>423</v>
+      </c>
+      <c r="E1002" s="18"/>
+      <c r="F1002" s="18"/>
+      <c r="G1002" s="17"/>
+      <c r="H1002" s="17"/>
+    </row>
+    <row r="1003" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1003" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B1003" s="14"/>
+      <c r="C1003" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="D1003" s="18" t="s">
+        <v>424</v>
+      </c>
+      <c r="E1003" s="18"/>
+      <c r="F1003" s="18"/>
+      <c r="G1003" s="17"/>
+      <c r="H1003" s="17"/>
+    </row>
+    <row r="1004" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1004" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B1004" s="14">
+        <v>0.52777777777777779</v>
+      </c>
+      <c r="C1004" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="D1004" s="18" t="s">
+        <v>334</v>
+      </c>
+      <c r="E1004" s="18"/>
+      <c r="F1004" s="18"/>
+      <c r="G1004" s="17"/>
+      <c r="H1004" s="17"/>
+    </row>
+    <row r="1005" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1005" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B1005" s="14"/>
+      <c r="C1005" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="D1005" s="18" t="s">
+        <v>390</v>
+      </c>
+      <c r="E1005" s="18"/>
+      <c r="F1005" s="18"/>
+      <c r="G1005" s="17"/>
+      <c r="H1005" s="17"/>
+    </row>
+    <row r="1006" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1006" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B1006" s="14"/>
+      <c r="C1006" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="D1006" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1006" s="18"/>
+      <c r="F1006" s="18"/>
+      <c r="G1006" s="17"/>
+      <c r="H1006" s="17"/>
+    </row>
+    <row r="1007" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1007" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B1007" s="14">
+        <v>0.59027777777777779</v>
+      </c>
+      <c r="C1007" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="D1007" s="18" t="s">
+        <v>369</v>
+      </c>
+      <c r="E1007" s="18"/>
+      <c r="F1007" s="18"/>
+      <c r="G1007" s="17"/>
+      <c r="H1007" s="17"/>
+    </row>
+    <row r="1008" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1008" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B1008" s="14">
+        <v>0.60069444444444442</v>
+      </c>
+      <c r="C1008" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="D1008" s="18" t="s">
+        <v>425</v>
+      </c>
+      <c r="E1008" s="18"/>
+      <c r="F1008" s="18"/>
+      <c r="G1008" s="17"/>
+      <c r="H1008" s="17"/>
+    </row>
+    <row r="1009" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1009" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B1009" s="14">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C1009" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="D1009" s="18" t="s">
+        <v>426</v>
+      </c>
+      <c r="E1009" s="18"/>
+      <c r="F1009" s="18"/>
+      <c r="G1009" s="17"/>
+      <c r="H1009" s="17"/>
+    </row>
+    <row r="1010" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1010" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B1010" s="14">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="C1010" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="D1010" s="18" t="s">
+        <v>394</v>
+      </c>
+      <c r="E1010" s="18"/>
+      <c r="F1010" s="18"/>
+      <c r="G1010" s="17"/>
+      <c r="H1010" s="17"/>
+    </row>
+    <row r="1011" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1011" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B1011" s="14">
+        <v>0.70138888888888884</v>
+      </c>
+      <c r="C1011" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="D1011" s="18" t="s">
+        <v>379</v>
+      </c>
+      <c r="E1011" s="18"/>
+      <c r="F1011" s="18"/>
+      <c r="G1011" s="17"/>
+      <c r="H1011" s="17"/>
+    </row>
+    <row r="1012" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1012" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B1012" s="14"/>
+      <c r="C1012" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="D1012" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1012" s="18"/>
+      <c r="F1012" s="18"/>
+      <c r="G1012" s="17"/>
+      <c r="H1012" s="17"/>
+    </row>
+    <row r="1013" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1013" s="15"/>
+      <c r="B1013" s="15"/>
+      <c r="C1013" s="15"/>
+      <c r="D1013" s="15"/>
+      <c r="E1013" s="15"/>
+      <c r="F1013" s="15"/>
+      <c r="G1013" s="17"/>
+      <c r="H1013" s="17"/>
+    </row>
+    <row r="1014" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1014" s="15"/>
+      <c r="B1014" s="15"/>
+      <c r="C1014" s="15"/>
+      <c r="D1014" s="15"/>
+      <c r="E1014" s="15"/>
+      <c r="F1014" s="15"/>
+      <c r="G1014" s="17"/>
+      <c r="H1014" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="D965:F965"/>
+    <mergeCell ref="D966:F966"/>
+    <mergeCell ref="D967:F967"/>
+    <mergeCell ref="D968:F968"/>
+    <mergeCell ref="D980:F980"/>
+    <mergeCell ref="D969:F969"/>
+    <mergeCell ref="D970:F970"/>
+    <mergeCell ref="D971:F971"/>
+    <mergeCell ref="D972:F972"/>
+    <mergeCell ref="D973:F973"/>
+    <mergeCell ref="D974:F974"/>
+    <mergeCell ref="D975:F975"/>
+    <mergeCell ref="D976:F976"/>
+    <mergeCell ref="D977:F977"/>
+    <mergeCell ref="D978:F978"/>
+    <mergeCell ref="D979:F979"/>
     <mergeCell ref="D987:F987"/>
     <mergeCell ref="D988:F988"/>
     <mergeCell ref="D981:F981"/>
@@ -15697,22 +16134,6 @@
     <mergeCell ref="D984:F984"/>
     <mergeCell ref="D985:F985"/>
     <mergeCell ref="D986:F986"/>
-    <mergeCell ref="D975:F975"/>
-    <mergeCell ref="D976:F976"/>
-    <mergeCell ref="D977:F977"/>
-    <mergeCell ref="D978:F978"/>
-    <mergeCell ref="D979:F979"/>
-    <mergeCell ref="D980:F980"/>
-    <mergeCell ref="D969:F969"/>
-    <mergeCell ref="D970:F970"/>
-    <mergeCell ref="D971:F971"/>
-    <mergeCell ref="D972:F972"/>
-    <mergeCell ref="D973:F973"/>
-    <mergeCell ref="D974:F974"/>
-    <mergeCell ref="D965:F965"/>
-    <mergeCell ref="D966:F966"/>
-    <mergeCell ref="D967:F967"/>
-    <mergeCell ref="D968:F968"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E24C868-E943-472F-8499-DA4D2AF74099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E645D7E2-55AF-4873-8082-AE2A52FACBD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2026" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2054" uniqueCount="432">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1665,6 +1665,26 @@
   </si>
   <si>
     <t>wait D11 team</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D12</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>try to push on D12(failed)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Waiting for OCC to cancel today's mission.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cancel today's mission.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D08</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1745,7 +1765,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1785,14 +1805,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2075,7 +2088,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1014"/>
+  <dimension ref="A1:F1028"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.69921875" style="1" bestFit="1" customWidth="1"/>
@@ -15494,7 +15507,7 @@
       <c r="E976" s="12"/>
       <c r="F976" s="12"/>
     </row>
-    <row r="977" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="977" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A977" s="2">
         <v>46295</v>
       </c>
@@ -15510,7 +15523,7 @@
       <c r="E977" s="12"/>
       <c r="F977" s="12"/>
     </row>
-    <row r="978" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="978" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A978" s="2">
         <v>46295</v>
       </c>
@@ -15524,7 +15537,7 @@
       <c r="E978" s="12"/>
       <c r="F978" s="12"/>
     </row>
-    <row r="979" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="979" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A979" s="2">
         <v>46295</v>
       </c>
@@ -15540,7 +15553,7 @@
       <c r="E979" s="12"/>
       <c r="F979" s="12"/>
     </row>
-    <row r="980" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="980" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A980" s="2">
         <v>46295</v>
       </c>
@@ -15554,7 +15567,7 @@
       <c r="E980" s="12"/>
       <c r="F980" s="12"/>
     </row>
-    <row r="981" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="981" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A981" s="2">
         <v>46295</v>
       </c>
@@ -15568,7 +15581,7 @@
       <c r="E981" s="12"/>
       <c r="F981" s="12"/>
     </row>
-    <row r="982" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="982" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A982" s="2">
         <v>46295</v>
       </c>
@@ -15584,7 +15597,7 @@
       <c r="E982" s="12"/>
       <c r="F982" s="12"/>
     </row>
-    <row r="983" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="983" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A983" s="2">
         <v>46295</v>
       </c>
@@ -15598,7 +15611,7 @@
       <c r="E983" s="12"/>
       <c r="F983" s="12"/>
     </row>
-    <row r="984" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="984" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A984" s="2">
         <v>46295</v>
       </c>
@@ -15612,7 +15625,7 @@
       <c r="E984" s="12"/>
       <c r="F984" s="12"/>
     </row>
-    <row r="985" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="985" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A985" s="2">
         <v>46295</v>
       </c>
@@ -15628,7 +15641,7 @@
       <c r="E985" s="12"/>
       <c r="F985" s="12"/>
     </row>
-    <row r="986" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="986" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A986" s="2">
         <v>46295</v>
       </c>
@@ -15644,7 +15657,7 @@
       <c r="E986" s="12"/>
       <c r="F986" s="12"/>
     </row>
-    <row r="987" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="987" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A987" s="2">
         <v>46295</v>
       </c>
@@ -15660,383 +15673,339 @@
       <c r="E987" s="12"/>
       <c r="F987" s="12"/>
     </row>
-    <row r="988" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A988" s="13">
+    <row r="988" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A988" s="2">
         <v>46295</v>
       </c>
-      <c r="B988" s="14"/>
-      <c r="C988" s="15" t="s">
+      <c r="B988" s="10"/>
+      <c r="C988" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D988" s="16" t="s">
+      <c r="D988" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="E988" s="16"/>
-      <c r="F988" s="16"/>
-      <c r="G988" s="17"/>
-      <c r="H988" s="17"/>
-    </row>
-    <row r="989" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A989" s="13">
+      <c r="E988" s="12"/>
+      <c r="F988" s="12"/>
+    </row>
+    <row r="989" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A989" s="2">
         <v>46296</v>
       </c>
-      <c r="B989" s="14">
+      <c r="B989" s="10">
         <v>0.26874999999999999</v>
       </c>
-      <c r="C989" s="15" t="s">
+      <c r="C989" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D989" s="18" t="s">
+      <c r="D989" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="E989" s="18"/>
-      <c r="F989" s="18"/>
-      <c r="G989" s="17"/>
-      <c r="H989" s="17"/>
-    </row>
-    <row r="990" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A990" s="13">
+      <c r="E989" s="8"/>
+      <c r="F989" s="8"/>
+    </row>
+    <row r="990" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A990" s="2">
         <v>46296</v>
       </c>
-      <c r="B990" s="14">
+      <c r="B990" s="10">
         <v>0.34027777777777779</v>
       </c>
-      <c r="C990" s="15" t="s">
+      <c r="C990" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D990" s="18" t="s">
+      <c r="D990" s="8" t="s">
         <v>417</v>
       </c>
-      <c r="E990" s="18"/>
-      <c r="F990" s="18"/>
-      <c r="G990" s="17"/>
-      <c r="H990" s="17"/>
-    </row>
-    <row r="991" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A991" s="13">
+      <c r="E990" s="8"/>
+      <c r="F990" s="8"/>
+    </row>
+    <row r="991" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A991" s="2">
         <v>46296</v>
       </c>
-      <c r="B991" s="14"/>
-      <c r="C991" s="15" t="s">
+      <c r="B991" s="10"/>
+      <c r="C991" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D991" s="18" t="s">
+      <c r="D991" s="8" t="s">
         <v>418</v>
       </c>
-      <c r="E991" s="18"/>
-      <c r="F991" s="18"/>
-      <c r="G991" s="17"/>
-      <c r="H991" s="17"/>
-    </row>
-    <row r="992" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A992" s="13">
+      <c r="E991" s="8"/>
+      <c r="F991" s="8"/>
+    </row>
+    <row r="992" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A992" s="2">
         <v>46296</v>
       </c>
-      <c r="B992" s="14">
+      <c r="B992" s="10">
         <v>0.35902777777777778</v>
       </c>
-      <c r="C992" s="15" t="s">
+      <c r="C992" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D992" s="18" t="s">
+      <c r="D992" s="8" t="s">
         <v>382</v>
       </c>
-      <c r="E992" s="18"/>
-      <c r="F992" s="18"/>
-      <c r="G992" s="17"/>
-      <c r="H992" s="17"/>
-    </row>
-    <row r="993" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A993" s="13">
+      <c r="E992" s="8"/>
+      <c r="F992" s="8"/>
+    </row>
+    <row r="993" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A993" s="2">
         <v>46296</v>
       </c>
-      <c r="B993" s="14">
+      <c r="B993" s="10">
         <v>0.3611111111111111</v>
       </c>
-      <c r="C993" s="15" t="s">
+      <c r="C993" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D993" s="18" t="s">
+      <c r="D993" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="E993" s="18"/>
-      <c r="F993" s="18"/>
-      <c r="G993" s="17"/>
-      <c r="H993" s="17"/>
-    </row>
-    <row r="994" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A994" s="13">
+      <c r="E993" s="8"/>
+      <c r="F993" s="8"/>
+    </row>
+    <row r="994" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A994" s="2">
         <v>46296</v>
       </c>
-      <c r="B994" s="14"/>
-      <c r="C994" s="15" t="s">
+      <c r="B994" s="10"/>
+      <c r="C994" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D994" s="18" t="s">
+      <c r="D994" s="8" t="s">
         <v>397</v>
       </c>
-      <c r="E994" s="18"/>
-      <c r="F994" s="18"/>
-      <c r="G994" s="17"/>
-      <c r="H994" s="17"/>
-    </row>
-    <row r="995" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A995" s="13">
+      <c r="E994" s="8"/>
+      <c r="F994" s="8"/>
+    </row>
+    <row r="995" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A995" s="2">
         <v>46296</v>
       </c>
-      <c r="B995" s="14">
+      <c r="B995" s="10">
         <v>0.375</v>
       </c>
-      <c r="C995" s="15" t="s">
+      <c r="C995" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D995" s="18" t="s">
+      <c r="D995" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="E995" s="18"/>
-      <c r="F995" s="18"/>
-      <c r="G995" s="17"/>
-      <c r="H995" s="17"/>
-    </row>
-    <row r="996" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A996" s="13">
+      <c r="E995" s="8"/>
+      <c r="F995" s="8"/>
+    </row>
+    <row r="996" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A996" s="2">
         <v>46296</v>
       </c>
-      <c r="B996" s="14">
+      <c r="B996" s="10">
         <v>0.39583333333333331</v>
       </c>
-      <c r="C996" s="15" t="s">
+      <c r="C996" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D996" s="18" t="s">
+      <c r="D996" s="8" t="s">
         <v>419</v>
       </c>
-      <c r="E996" s="18"/>
-      <c r="F996" s="18"/>
-      <c r="G996" s="17"/>
-      <c r="H996" s="17"/>
-    </row>
-    <row r="997" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A997" s="13">
+      <c r="E996" s="8"/>
+      <c r="F996" s="8"/>
+    </row>
+    <row r="997" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A997" s="2">
         <v>46296</v>
       </c>
-      <c r="B997" s="14"/>
-      <c r="C997" s="15" t="s">
+      <c r="B997" s="10"/>
+      <c r="C997" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D997" s="18" t="s">
+      <c r="D997" s="8" t="s">
         <v>420</v>
       </c>
-      <c r="E997" s="18"/>
-      <c r="F997" s="18"/>
-      <c r="G997" s="17"/>
-      <c r="H997" s="17"/>
-    </row>
-    <row r="998" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A998" s="13">
+      <c r="E997" s="8"/>
+      <c r="F997" s="8"/>
+    </row>
+    <row r="998" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A998" s="2">
         <v>46296</v>
       </c>
-      <c r="B998" s="14"/>
-      <c r="C998" s="15" t="s">
+      <c r="B998" s="10"/>
+      <c r="C998" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D998" s="18" t="s">
+      <c r="D998" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="E998" s="18"/>
-      <c r="F998" s="18"/>
-      <c r="G998" s="17"/>
-      <c r="H998" s="17"/>
-    </row>
-    <row r="999" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A999" s="13">
+      <c r="E998" s="8"/>
+      <c r="F998" s="8"/>
+    </row>
+    <row r="999" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A999" s="2">
         <v>46296</v>
       </c>
-      <c r="B999" s="14">
+      <c r="B999" s="10">
         <v>0.4375</v>
       </c>
-      <c r="C999" s="15" t="s">
+      <c r="C999" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D999" s="18" t="s">
+      <c r="D999" s="8" t="s">
         <v>422</v>
       </c>
-      <c r="E999" s="18"/>
-      <c r="F999" s="18"/>
-      <c r="G999" s="17"/>
-      <c r="H999" s="17"/>
-    </row>
-    <row r="1000" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1000" s="13">
+      <c r="E999" s="8"/>
+      <c r="F999" s="8"/>
+    </row>
+    <row r="1000" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1000" s="2">
         <v>46296</v>
       </c>
-      <c r="B1000" s="14"/>
-      <c r="C1000" s="15" t="s">
+      <c r="B1000" s="10"/>
+      <c r="C1000" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D1000" s="19" t="s">
+      <c r="D1000" s="11" t="s">
         <v>335</v>
       </c>
-      <c r="E1000" s="19"/>
-      <c r="F1000" s="19"/>
-      <c r="G1000" s="17"/>
-      <c r="H1000" s="17"/>
-    </row>
-    <row r="1001" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1001" s="13">
+      <c r="E1000" s="11"/>
+      <c r="F1000" s="11"/>
+    </row>
+    <row r="1001" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1001" s="2">
         <v>46296</v>
       </c>
-      <c r="B1001" s="14">
+      <c r="B1001" s="10">
         <v>0.45833333333333331</v>
       </c>
-      <c r="C1001" s="15" t="s">
+      <c r="C1001" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D1001" s="18" t="s">
+      <c r="D1001" s="8" t="s">
         <v>419</v>
       </c>
-      <c r="E1001" s="18"/>
-      <c r="F1001" s="18"/>
-      <c r="G1001" s="17"/>
-      <c r="H1001" s="17"/>
-    </row>
-    <row r="1002" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1002" s="13">
+      <c r="E1001" s="8"/>
+      <c r="F1001" s="8"/>
+    </row>
+    <row r="1002" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1002" s="2">
         <v>46296</v>
       </c>
-      <c r="B1002" s="14"/>
-      <c r="C1002" s="15" t="s">
+      <c r="B1002" s="10"/>
+      <c r="C1002" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D1002" s="18" t="s">
+      <c r="D1002" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="E1002" s="18"/>
-      <c r="F1002" s="18"/>
-      <c r="G1002" s="17"/>
-      <c r="H1002" s="17"/>
-    </row>
-    <row r="1003" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1003" s="13">
+      <c r="E1002" s="8"/>
+      <c r="F1002" s="8"/>
+    </row>
+    <row r="1003" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1003" s="2">
         <v>46296</v>
       </c>
-      <c r="B1003" s="14"/>
-      <c r="C1003" s="15" t="s">
+      <c r="B1003" s="10"/>
+      <c r="C1003" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D1003" s="18" t="s">
+      <c r="D1003" s="8" t="s">
         <v>424</v>
       </c>
-      <c r="E1003" s="18"/>
-      <c r="F1003" s="18"/>
-      <c r="G1003" s="17"/>
-      <c r="H1003" s="17"/>
-    </row>
-    <row r="1004" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1004" s="13">
+      <c r="E1003" s="8"/>
+      <c r="F1003" s="8"/>
+    </row>
+    <row r="1004" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1004" s="2">
         <v>46296</v>
       </c>
-      <c r="B1004" s="14">
+      <c r="B1004" s="10">
         <v>0.52777777777777779</v>
       </c>
-      <c r="C1004" s="15" t="s">
+      <c r="C1004" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D1004" s="18" t="s">
+      <c r="D1004" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="E1004" s="18"/>
-      <c r="F1004" s="18"/>
-      <c r="G1004" s="17"/>
-      <c r="H1004" s="17"/>
-    </row>
-    <row r="1005" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1005" s="13">
+      <c r="E1004" s="8"/>
+      <c r="F1004" s="8"/>
+    </row>
+    <row r="1005" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1005" s="2">
         <v>46296</v>
       </c>
-      <c r="B1005" s="14"/>
-      <c r="C1005" s="15" t="s">
+      <c r="B1005" s="10"/>
+      <c r="C1005" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D1005" s="18" t="s">
+      <c r="D1005" s="8" t="s">
         <v>390</v>
       </c>
-      <c r="E1005" s="18"/>
-      <c r="F1005" s="18"/>
-      <c r="G1005" s="17"/>
-      <c r="H1005" s="17"/>
-    </row>
-    <row r="1006" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1006" s="13">
+      <c r="E1005" s="8"/>
+      <c r="F1005" s="8"/>
+    </row>
+    <row r="1006" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1006" s="2">
         <v>46296</v>
       </c>
-      <c r="B1006" s="14"/>
-      <c r="C1006" s="15" t="s">
+      <c r="B1006" s="10"/>
+      <c r="C1006" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D1006" s="18" t="s">
+      <c r="D1006" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="E1006" s="18"/>
-      <c r="F1006" s="18"/>
-      <c r="G1006" s="17"/>
-      <c r="H1006" s="17"/>
-    </row>
-    <row r="1007" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1007" s="13">
+      <c r="E1006" s="8"/>
+      <c r="F1006" s="8"/>
+    </row>
+    <row r="1007" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1007" s="2">
         <v>46296</v>
       </c>
-      <c r="B1007" s="14">
+      <c r="B1007" s="10">
         <v>0.59027777777777779</v>
       </c>
-      <c r="C1007" s="15" t="s">
+      <c r="C1007" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D1007" s="18" t="s">
+      <c r="D1007" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="E1007" s="18"/>
-      <c r="F1007" s="18"/>
-      <c r="G1007" s="17"/>
-      <c r="H1007" s="17"/>
-    </row>
-    <row r="1008" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1008" s="13">
+      <c r="E1007" s="8"/>
+      <c r="F1007" s="8"/>
+    </row>
+    <row r="1008" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1008" s="2">
         <v>46296</v>
       </c>
-      <c r="B1008" s="14">
+      <c r="B1008" s="10">
         <v>0.60069444444444442</v>
       </c>
-      <c r="C1008" s="15" t="s">
+      <c r="C1008" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D1008" s="18" t="s">
+      <c r="D1008" s="8" t="s">
         <v>425</v>
       </c>
-      <c r="E1008" s="18"/>
-      <c r="F1008" s="18"/>
-      <c r="G1008" s="17"/>
-      <c r="H1008" s="17"/>
-    </row>
-    <row r="1009" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1009" s="13">
+      <c r="E1008" s="8"/>
+      <c r="F1008" s="8"/>
+    </row>
+    <row r="1009" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1009" s="2">
         <v>46296</v>
       </c>
-      <c r="B1009" s="14">
+      <c r="B1009" s="10">
         <v>0.60416666666666663</v>
       </c>
-      <c r="C1009" s="15" t="s">
+      <c r="C1009" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D1009" s="18" t="s">
+      <c r="D1009" s="8" t="s">
         <v>426</v>
       </c>
-      <c r="E1009" s="18"/>
-      <c r="F1009" s="18"/>
-      <c r="G1009" s="17"/>
-      <c r="H1009" s="17"/>
-    </row>
-    <row r="1010" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E1009" s="8"/>
+      <c r="F1009" s="8"/>
+    </row>
+    <row r="1010" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1010" s="13">
         <v>46296</v>
       </c>
@@ -16046,15 +16015,13 @@
       <c r="C1010" s="15" t="s">
         <v>416</v>
       </c>
-      <c r="D1010" s="18" t="s">
+      <c r="D1010" s="16" t="s">
         <v>394</v>
       </c>
-      <c r="E1010" s="18"/>
-      <c r="F1010" s="18"/>
-      <c r="G1010" s="17"/>
-      <c r="H1010" s="17"/>
-    </row>
-    <row r="1011" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E1010" s="16"/>
+      <c r="F1010" s="16"/>
+    </row>
+    <row r="1011" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1011" s="13">
         <v>46296</v>
       </c>
@@ -16064,15 +16031,13 @@
       <c r="C1011" s="15" t="s">
         <v>416</v>
       </c>
-      <c r="D1011" s="18" t="s">
+      <c r="D1011" s="16" t="s">
         <v>379</v>
       </c>
-      <c r="E1011" s="18"/>
-      <c r="F1011" s="18"/>
-      <c r="G1011" s="17"/>
-      <c r="H1011" s="17"/>
-    </row>
-    <row r="1012" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E1011" s="16"/>
+      <c r="F1011" s="16"/>
+    </row>
+    <row r="1012" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1012" s="13">
         <v>46296</v>
       </c>
@@ -16080,36 +16045,254 @@
       <c r="C1012" s="15" t="s">
         <v>416</v>
       </c>
-      <c r="D1012" s="18" t="s">
+      <c r="D1012" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="E1012" s="18"/>
-      <c r="F1012" s="18"/>
-      <c r="G1012" s="17"/>
-      <c r="H1012" s="17"/>
-    </row>
-    <row r="1013" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1013" s="15"/>
-      <c r="B1013" s="15"/>
-      <c r="C1013" s="15"/>
-      <c r="D1013" s="15"/>
-      <c r="E1013" s="15"/>
-      <c r="F1013" s="15"/>
-      <c r="G1013" s="17"/>
-      <c r="H1013" s="17"/>
-    </row>
-    <row r="1014" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1014" s="15"/>
-      <c r="B1014" s="15"/>
-      <c r="C1014" s="15"/>
-      <c r="D1014" s="15"/>
-      <c r="E1014" s="15"/>
-      <c r="F1014" s="15"/>
-      <c r="G1014" s="17"/>
-      <c r="H1014" s="17"/>
+      <c r="E1012" s="16"/>
+      <c r="F1012" s="16"/>
+    </row>
+    <row r="1013" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1013" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B1013" s="14">
+        <v>0.2638888888888889</v>
+      </c>
+      <c r="C1013" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1013" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="E1013" s="16"/>
+      <c r="F1013" s="16"/>
+    </row>
+    <row r="1014" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1014" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B1014" s="14">
+        <v>0.33888888888888891</v>
+      </c>
+      <c r="C1014" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1014" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="E1014" s="16"/>
+      <c r="F1014" s="16"/>
+    </row>
+    <row r="1015" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1015" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B1015" s="14">
+        <v>0.34722222222222221</v>
+      </c>
+      <c r="C1015" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1015" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="E1015" s="16"/>
+      <c r="F1015" s="16"/>
+    </row>
+    <row r="1016" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1016" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B1016" s="14"/>
+      <c r="C1016" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1016" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="E1016" s="16"/>
+      <c r="F1016" s="16"/>
+    </row>
+    <row r="1017" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1017" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B1017" s="14">
+        <v>0.35208333333333336</v>
+      </c>
+      <c r="C1017" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1017" s="16" t="s">
+        <v>394</v>
+      </c>
+      <c r="E1017" s="16"/>
+      <c r="F1017" s="16"/>
+    </row>
+    <row r="1018" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1018" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B1018" s="14">
+        <v>0.44097222222222221</v>
+      </c>
+      <c r="C1018" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1018" s="16" t="s">
+        <v>379</v>
+      </c>
+      <c r="E1018" s="16"/>
+      <c r="F1018" s="16"/>
+    </row>
+    <row r="1019" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1019" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B1019" s="14"/>
+      <c r="C1019" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1019" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1019" s="16"/>
+      <c r="F1019" s="16"/>
+    </row>
+    <row r="1020" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1020" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B1020" s="14">
+        <v>0.2638888888888889</v>
+      </c>
+      <c r="C1020" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1020" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="E1020" s="16"/>
+      <c r="F1020" s="16"/>
+    </row>
+    <row r="1021" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1021" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B1021" s="14">
+        <v>0.33888888888888891</v>
+      </c>
+      <c r="C1021" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1021" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="E1021" s="16"/>
+      <c r="F1021" s="16"/>
+    </row>
+    <row r="1022" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1022" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B1022" s="14">
+        <v>0.34722222222222221</v>
+      </c>
+      <c r="C1022" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1022" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="E1022" s="16"/>
+      <c r="F1022" s="16"/>
+    </row>
+    <row r="1023" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1023" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B1023" s="14"/>
+      <c r="C1023" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1023" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="E1023" s="16"/>
+      <c r="F1023" s="16"/>
+    </row>
+    <row r="1024" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1024" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B1024" s="14">
+        <v>0.35208333333333336</v>
+      </c>
+      <c r="C1024" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1024" s="16" t="s">
+        <v>394</v>
+      </c>
+      <c r="E1024" s="16"/>
+      <c r="F1024" s="16"/>
+    </row>
+    <row r="1025" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1025" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B1025" s="14">
+        <v>0.44097222222222221</v>
+      </c>
+      <c r="C1025" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1025" s="16" t="s">
+        <v>379</v>
+      </c>
+      <c r="E1025" s="16"/>
+      <c r="F1025" s="16"/>
+    </row>
+    <row r="1026" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1026" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B1026" s="14"/>
+      <c r="C1026" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1026" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1026" s="16"/>
+      <c r="F1026" s="16"/>
+    </row>
+    <row r="1027" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1027" s="15"/>
+      <c r="B1027" s="15"/>
+      <c r="C1027" s="15"/>
+      <c r="D1027" s="15"/>
+      <c r="E1027" s="15"/>
+      <c r="F1027" s="15"/>
+    </row>
+    <row r="1028" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1028" s="15"/>
+      <c r="B1028" s="15"/>
+      <c r="C1028" s="15"/>
+      <c r="D1028" s="15"/>
+      <c r="E1028" s="15"/>
+      <c r="F1028" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="D987:F987"/>
+    <mergeCell ref="D988:F988"/>
+    <mergeCell ref="D981:F981"/>
+    <mergeCell ref="D982:F982"/>
+    <mergeCell ref="D983:F983"/>
+    <mergeCell ref="D984:F984"/>
+    <mergeCell ref="D985:F985"/>
+    <mergeCell ref="D986:F986"/>
     <mergeCell ref="D965:F965"/>
     <mergeCell ref="D966:F966"/>
     <mergeCell ref="D967:F967"/>
@@ -16126,14 +16309,6 @@
     <mergeCell ref="D977:F977"/>
     <mergeCell ref="D978:F978"/>
     <mergeCell ref="D979:F979"/>
-    <mergeCell ref="D987:F987"/>
-    <mergeCell ref="D988:F988"/>
-    <mergeCell ref="D981:F981"/>
-    <mergeCell ref="D982:F982"/>
-    <mergeCell ref="D983:F983"/>
-    <mergeCell ref="D984:F984"/>
-    <mergeCell ref="D985:F985"/>
-    <mergeCell ref="D986:F986"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E645D7E2-55AF-4873-8082-AE2A52FACBD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C777164-EA05-497A-B1FB-C00B56CF1387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2054" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2070" uniqueCount="432">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1765,7 +1765,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1807,6 +1807,7 @@
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal 2" xfId="1" xr:uid="{71AF191C-2467-4F76-8A53-CA6D53E4DF10}"/>
@@ -2088,7 +2089,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1028"/>
+  <dimension ref="A1:G1040"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.69921875" style="1" bestFit="1" customWidth="1"/>
@@ -15989,7 +15990,7 @@
       <c r="E1008" s="8"/>
       <c r="F1008" s="8"/>
     </row>
-    <row r="1009" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1009" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1009" s="2">
         <v>46296</v>
       </c>
@@ -16005,209 +16006,209 @@
       <c r="E1009" s="8"/>
       <c r="F1009" s="8"/>
     </row>
-    <row r="1010" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1010" s="13">
+    <row r="1010" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1010" s="2">
         <v>46296</v>
       </c>
-      <c r="B1010" s="14">
+      <c r="B1010" s="10">
         <v>0.61458333333333337</v>
       </c>
-      <c r="C1010" s="15" t="s">
+      <c r="C1010" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D1010" s="16" t="s">
+      <c r="D1010" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="E1010" s="16"/>
-      <c r="F1010" s="16"/>
-    </row>
-    <row r="1011" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1011" s="13">
+      <c r="E1010" s="8"/>
+      <c r="F1010" s="8"/>
+    </row>
+    <row r="1011" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1011" s="2">
         <v>46296</v>
       </c>
-      <c r="B1011" s="14">
+      <c r="B1011" s="10">
         <v>0.70138888888888884</v>
       </c>
-      <c r="C1011" s="15" t="s">
+      <c r="C1011" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D1011" s="16" t="s">
+      <c r="D1011" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="E1011" s="16"/>
-      <c r="F1011" s="16"/>
-    </row>
-    <row r="1012" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1012" s="13">
+      <c r="E1011" s="8"/>
+      <c r="F1011" s="8"/>
+    </row>
+    <row r="1012" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1012" s="2">
         <v>46296</v>
       </c>
-      <c r="B1012" s="14"/>
-      <c r="C1012" s="15" t="s">
+      <c r="B1012" s="10"/>
+      <c r="C1012" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D1012" s="16" t="s">
+      <c r="D1012" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E1012" s="16"/>
-      <c r="F1012" s="16"/>
-    </row>
-    <row r="1013" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1013" s="13">
+      <c r="E1012" s="8"/>
+      <c r="F1012" s="8"/>
+    </row>
+    <row r="1013" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1013" s="2">
         <v>46297</v>
       </c>
-      <c r="B1013" s="14">
+      <c r="B1013" s="10">
         <v>0.2638888888888889</v>
       </c>
-      <c r="C1013" s="15" t="s">
+      <c r="C1013" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1013" s="16" t="s">
+      <c r="D1013" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="E1013" s="16"/>
-      <c r="F1013" s="16"/>
-    </row>
-    <row r="1014" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1014" s="13">
+      <c r="E1013" s="8"/>
+      <c r="F1013" s="8"/>
+    </row>
+    <row r="1014" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1014" s="2">
         <v>46297</v>
       </c>
-      <c r="B1014" s="14">
+      <c r="B1014" s="10">
         <v>0.33888888888888891</v>
       </c>
-      <c r="C1014" s="15" t="s">
+      <c r="C1014" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1014" s="16" t="s">
+      <c r="D1014" s="8" t="s">
         <v>428</v>
       </c>
-      <c r="E1014" s="16"/>
-      <c r="F1014" s="16"/>
-    </row>
-    <row r="1015" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1015" s="13">
+      <c r="E1014" s="8"/>
+      <c r="F1014" s="8"/>
+    </row>
+    <row r="1015" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1015" s="2">
         <v>46297</v>
       </c>
-      <c r="B1015" s="14">
+      <c r="B1015" s="10">
         <v>0.34722222222222221</v>
       </c>
-      <c r="C1015" s="15" t="s">
+      <c r="C1015" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1015" s="16" t="s">
+      <c r="D1015" s="8" t="s">
         <v>429</v>
       </c>
-      <c r="E1015" s="16"/>
-      <c r="F1015" s="16"/>
-    </row>
-    <row r="1016" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1016" s="13">
+      <c r="E1015" s="8"/>
+      <c r="F1015" s="8"/>
+    </row>
+    <row r="1016" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1016" s="2">
         <v>46297</v>
       </c>
-      <c r="B1016" s="14"/>
-      <c r="C1016" s="15" t="s">
+      <c r="B1016" s="10"/>
+      <c r="C1016" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1016" s="16" t="s">
+      <c r="D1016" s="8" t="s">
         <v>430</v>
       </c>
-      <c r="E1016" s="16"/>
-      <c r="F1016" s="16"/>
-    </row>
-    <row r="1017" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1017" s="13">
+      <c r="E1016" s="8"/>
+      <c r="F1016" s="8"/>
+    </row>
+    <row r="1017" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1017" s="2">
         <v>46297</v>
       </c>
-      <c r="B1017" s="14">
+      <c r="B1017" s="10">
         <v>0.35208333333333336</v>
       </c>
-      <c r="C1017" s="15" t="s">
+      <c r="C1017" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1017" s="16" t="s">
+      <c r="D1017" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="E1017" s="16"/>
-      <c r="F1017" s="16"/>
-    </row>
-    <row r="1018" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1018" s="13">
+      <c r="E1017" s="8"/>
+      <c r="F1017" s="8"/>
+    </row>
+    <row r="1018" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1018" s="2">
         <v>46297</v>
       </c>
-      <c r="B1018" s="14">
+      <c r="B1018" s="10">
         <v>0.44097222222222221</v>
       </c>
-      <c r="C1018" s="15" t="s">
+      <c r="C1018" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1018" s="16" t="s">
+      <c r="D1018" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="E1018" s="16"/>
-      <c r="F1018" s="16"/>
-    </row>
-    <row r="1019" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1019" s="13">
+      <c r="E1018" s="8"/>
+      <c r="F1018" s="8"/>
+    </row>
+    <row r="1019" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1019" s="2">
         <v>46297</v>
       </c>
-      <c r="B1019" s="14"/>
-      <c r="C1019" s="15" t="s">
+      <c r="B1019" s="10"/>
+      <c r="C1019" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1019" s="16" t="s">
+      <c r="D1019" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E1019" s="16"/>
-      <c r="F1019" s="16"/>
-    </row>
-    <row r="1020" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1020" s="13">
+      <c r="E1019" s="8"/>
+      <c r="F1019" s="8"/>
+    </row>
+    <row r="1020" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1020" s="2">
         <v>46297</v>
       </c>
-      <c r="B1020" s="14">
+      <c r="B1020" s="10">
         <v>0.2638888888888889</v>
       </c>
-      <c r="C1020" s="15" t="s">
+      <c r="C1020" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1020" s="16" t="s">
+      <c r="D1020" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="E1020" s="16"/>
-      <c r="F1020" s="16"/>
-    </row>
-    <row r="1021" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1021" s="13">
+      <c r="E1020" s="8"/>
+      <c r="F1020" s="8"/>
+    </row>
+    <row r="1021" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1021" s="2">
         <v>46297</v>
       </c>
-      <c r="B1021" s="14">
+      <c r="B1021" s="10">
         <v>0.33888888888888891</v>
       </c>
-      <c r="C1021" s="15" t="s">
+      <c r="C1021" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1021" s="16" t="s">
+      <c r="D1021" s="8" t="s">
         <v>428</v>
       </c>
-      <c r="E1021" s="16"/>
-      <c r="F1021" s="16"/>
-    </row>
-    <row r="1022" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1022" s="13">
+      <c r="E1021" s="8"/>
+      <c r="F1021" s="8"/>
+    </row>
+    <row r="1022" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1022" s="2">
         <v>46297</v>
       </c>
-      <c r="B1022" s="14">
+      <c r="B1022" s="10">
         <v>0.34722222222222221</v>
       </c>
-      <c r="C1022" s="15" t="s">
+      <c r="C1022" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1022" s="16" t="s">
+      <c r="D1022" s="8" t="s">
         <v>429</v>
       </c>
-      <c r="E1022" s="16"/>
-      <c r="F1022" s="16"/>
-    </row>
-    <row r="1023" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E1022" s="8"/>
+      <c r="F1022" s="8"/>
+    </row>
+    <row r="1023" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1023" s="13">
         <v>46297</v>
       </c>
@@ -16220,8 +16221,9 @@
       </c>
       <c r="E1023" s="16"/>
       <c r="F1023" s="16"/>
-    </row>
-    <row r="1024" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1023" s="17"/>
+    </row>
+    <row r="1024" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1024" s="13">
         <v>46297</v>
       </c>
@@ -16236,8 +16238,9 @@
       </c>
       <c r="E1024" s="16"/>
       <c r="F1024" s="16"/>
-    </row>
-    <row r="1025" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1024" s="17"/>
+    </row>
+    <row r="1025" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1025" s="13">
         <v>46297</v>
       </c>
@@ -16252,8 +16255,9 @@
       </c>
       <c r="E1025" s="16"/>
       <c r="F1025" s="16"/>
-    </row>
-    <row r="1026" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1025" s="17"/>
+    </row>
+    <row r="1026" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1026" s="13">
         <v>46297</v>
       </c>
@@ -16266,33 +16270,200 @@
       </c>
       <c r="E1026" s="16"/>
       <c r="F1026" s="16"/>
-    </row>
-    <row r="1027" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1027" s="15"/>
-      <c r="B1027" s="15"/>
-      <c r="C1027" s="15"/>
-      <c r="D1027" s="15"/>
-      <c r="E1027" s="15"/>
-      <c r="F1027" s="15"/>
-    </row>
-    <row r="1028" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1028" s="15"/>
-      <c r="B1028" s="15"/>
-      <c r="C1028" s="15"/>
-      <c r="D1028" s="15"/>
-      <c r="E1028" s="15"/>
-      <c r="F1028" s="15"/>
+      <c r="G1026" s="17"/>
+    </row>
+    <row r="1027" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1027" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B1027" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="C1027" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1027" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E1027" s="16"/>
+      <c r="F1027" s="16"/>
+      <c r="G1027" s="17"/>
+    </row>
+    <row r="1028" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1028" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B1028" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="C1028" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1028" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1028" s="16"/>
+      <c r="F1028" s="16"/>
+      <c r="G1028" s="17"/>
+    </row>
+    <row r="1029" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1029" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B1029" s="14">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1029" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1029" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E1029" s="16"/>
+      <c r="F1029" s="16"/>
+      <c r="G1029" s="17"/>
+    </row>
+    <row r="1030" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1030" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B1030" s="14">
+        <v>0.75</v>
+      </c>
+      <c r="C1030" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1030" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1030" s="16"/>
+      <c r="F1030" s="16"/>
+      <c r="G1030" s="17"/>
+    </row>
+    <row r="1031" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1031" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B1031" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="C1031" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1031" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E1031" s="16"/>
+      <c r="F1031" s="16"/>
+      <c r="G1031" s="17"/>
+    </row>
+    <row r="1032" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1032" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B1032" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="C1032" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1032" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1032" s="16"/>
+      <c r="F1032" s="16"/>
+      <c r="G1032" s="17"/>
+    </row>
+    <row r="1033" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1033" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B1033" s="14">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1033" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1033" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E1033" s="16"/>
+      <c r="F1033" s="16"/>
+      <c r="G1033" s="17"/>
+    </row>
+    <row r="1034" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1034" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B1034" s="14">
+        <v>0.75</v>
+      </c>
+      <c r="C1034" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1034" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1034" s="16"/>
+      <c r="F1034" s="16"/>
+      <c r="G1034" s="17"/>
+    </row>
+    <row r="1035" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1035" s="15"/>
+      <c r="B1035" s="15"/>
+      <c r="C1035" s="15"/>
+      <c r="D1035" s="15"/>
+      <c r="E1035" s="15"/>
+      <c r="F1035" s="15"/>
+      <c r="G1035" s="17"/>
+    </row>
+    <row r="1036" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1036" s="15"/>
+      <c r="B1036" s="15"/>
+      <c r="C1036" s="15"/>
+      <c r="D1036" s="15"/>
+      <c r="E1036" s="15"/>
+      <c r="F1036" s="15"/>
+      <c r="G1036" s="17"/>
+    </row>
+    <row r="1037" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1037" s="15"/>
+      <c r="B1037" s="15"/>
+      <c r="C1037" s="15"/>
+      <c r="D1037" s="15"/>
+      <c r="E1037" s="15"/>
+      <c r="F1037" s="15"/>
+      <c r="G1037" s="17"/>
+    </row>
+    <row r="1038" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1038" s="15"/>
+      <c r="B1038" s="15"/>
+      <c r="C1038" s="15"/>
+      <c r="D1038" s="15"/>
+      <c r="E1038" s="15"/>
+      <c r="F1038" s="15"/>
+      <c r="G1038" s="17"/>
+    </row>
+    <row r="1039" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1039" s="15"/>
+      <c r="B1039" s="15"/>
+      <c r="C1039" s="15"/>
+      <c r="D1039" s="15"/>
+      <c r="E1039" s="15"/>
+      <c r="F1039" s="15"/>
+      <c r="G1039" s="17"/>
+    </row>
+    <row r="1040" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1040" s="15"/>
+      <c r="B1040" s="15"/>
+      <c r="C1040" s="15"/>
+      <c r="D1040" s="15"/>
+      <c r="E1040" s="15"/>
+      <c r="F1040" s="15"/>
+      <c r="G1040" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="D987:F987"/>
-    <mergeCell ref="D988:F988"/>
-    <mergeCell ref="D981:F981"/>
-    <mergeCell ref="D982:F982"/>
-    <mergeCell ref="D983:F983"/>
-    <mergeCell ref="D984:F984"/>
-    <mergeCell ref="D985:F985"/>
-    <mergeCell ref="D986:F986"/>
     <mergeCell ref="D965:F965"/>
     <mergeCell ref="D966:F966"/>
     <mergeCell ref="D967:F967"/>
@@ -16309,6 +16480,14 @@
     <mergeCell ref="D977:F977"/>
     <mergeCell ref="D978:F978"/>
     <mergeCell ref="D979:F979"/>
+    <mergeCell ref="D987:F987"/>
+    <mergeCell ref="D988:F988"/>
+    <mergeCell ref="D981:F981"/>
+    <mergeCell ref="D982:F982"/>
+    <mergeCell ref="D983:F983"/>
+    <mergeCell ref="D984:F984"/>
+    <mergeCell ref="D985:F985"/>
+    <mergeCell ref="D986:F986"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C777164-EA05-497A-B1FB-C00B56CF1387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A2297F2-7132-43B4-A71F-4B0E5F1D9A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2070" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2062" uniqueCount="432">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1765,7 +1765,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1799,15 +1799,6 @@
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal 2" xfId="1" xr:uid="{71AF191C-2467-4F76-8A53-CA6D53E4DF10}"/>
@@ -2089,7 +2080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1040"/>
+  <dimension ref="A1:F1034"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.69921875" style="1" bestFit="1" customWidth="1"/>
@@ -15990,7 +15981,7 @@
       <c r="E1008" s="8"/>
       <c r="F1008" s="8"/>
     </row>
-    <row r="1009" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1009" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1009" s="2">
         <v>46296</v>
       </c>
@@ -16006,7 +15997,7 @@
       <c r="E1009" s="8"/>
       <c r="F1009" s="8"/>
     </row>
-    <row r="1010" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1010" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1010" s="2">
         <v>46296</v>
       </c>
@@ -16022,7 +16013,7 @@
       <c r="E1010" s="8"/>
       <c r="F1010" s="8"/>
     </row>
-    <row r="1011" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1011" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1011" s="2">
         <v>46296</v>
       </c>
@@ -16038,7 +16029,7 @@
       <c r="E1011" s="8"/>
       <c r="F1011" s="8"/>
     </row>
-    <row r="1012" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1012" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1012" s="2">
         <v>46296</v>
       </c>
@@ -16052,7 +16043,7 @@
       <c r="E1012" s="8"/>
       <c r="F1012" s="8"/>
     </row>
-    <row r="1013" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1013" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1013" s="2">
         <v>46297</v>
       </c>
@@ -16068,7 +16059,7 @@
       <c r="E1013" s="8"/>
       <c r="F1013" s="8"/>
     </row>
-    <row r="1014" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1014" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1014" s="2">
         <v>46297</v>
       </c>
@@ -16084,7 +16075,7 @@
       <c r="E1014" s="8"/>
       <c r="F1014" s="8"/>
     </row>
-    <row r="1015" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1015" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1015" s="2">
         <v>46297</v>
       </c>
@@ -16100,7 +16091,7 @@
       <c r="E1015" s="8"/>
       <c r="F1015" s="8"/>
     </row>
-    <row r="1016" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1016" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1016" s="2">
         <v>46297</v>
       </c>
@@ -16114,7 +16105,7 @@
       <c r="E1016" s="8"/>
       <c r="F1016" s="8"/>
     </row>
-    <row r="1017" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1017" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1017" s="2">
         <v>46297</v>
       </c>
@@ -16130,7 +16121,7 @@
       <c r="E1017" s="8"/>
       <c r="F1017" s="8"/>
     </row>
-    <row r="1018" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1018" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1018" s="2">
         <v>46297</v>
       </c>
@@ -16146,7 +16137,7 @@
       <c r="E1018" s="8"/>
       <c r="F1018" s="8"/>
     </row>
-    <row r="1019" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1019" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1019" s="2">
         <v>46297</v>
       </c>
@@ -16160,7 +16151,7 @@
       <c r="E1019" s="8"/>
       <c r="F1019" s="8"/>
     </row>
-    <row r="1020" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1020" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1020" s="2">
         <v>46297</v>
       </c>
@@ -16176,7 +16167,7 @@
       <c r="E1020" s="8"/>
       <c r="F1020" s="8"/>
     </row>
-    <row r="1021" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1021" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1021" s="2">
         <v>46297</v>
       </c>
@@ -16192,7 +16183,7 @@
       <c r="E1021" s="8"/>
       <c r="F1021" s="8"/>
     </row>
-    <row r="1022" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1022" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1022" s="2">
         <v>46297</v>
       </c>
@@ -16208,262 +16199,168 @@
       <c r="E1022" s="8"/>
       <c r="F1022" s="8"/>
     </row>
-    <row r="1023" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1023" s="13">
+    <row r="1023" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1023" s="2">
         <v>46297</v>
       </c>
-      <c r="B1023" s="14"/>
-      <c r="C1023" s="15" t="s">
+      <c r="B1023" s="10"/>
+      <c r="C1023" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1023" s="16" t="s">
+      <c r="D1023" s="8" t="s">
         <v>430</v>
       </c>
-      <c r="E1023" s="16"/>
-      <c r="F1023" s="16"/>
-      <c r="G1023" s="17"/>
-    </row>
-    <row r="1024" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1024" s="13">
+      <c r="E1023" s="8"/>
+      <c r="F1023" s="8"/>
+    </row>
+    <row r="1024" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1024" s="2">
         <v>46297</v>
       </c>
-      <c r="B1024" s="14">
+      <c r="B1024" s="10">
         <v>0.35208333333333336</v>
       </c>
-      <c r="C1024" s="15" t="s">
+      <c r="C1024" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1024" s="16" t="s">
+      <c r="D1024" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="E1024" s="16"/>
-      <c r="F1024" s="16"/>
-      <c r="G1024" s="17"/>
-    </row>
-    <row r="1025" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1025" s="13">
+      <c r="E1024" s="8"/>
+      <c r="F1024" s="8"/>
+    </row>
+    <row r="1025" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1025" s="2">
         <v>46297</v>
       </c>
-      <c r="B1025" s="14">
+      <c r="B1025" s="10">
         <v>0.44097222222222221</v>
       </c>
-      <c r="C1025" s="15" t="s">
+      <c r="C1025" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1025" s="16" t="s">
+      <c r="D1025" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="E1025" s="16"/>
-      <c r="F1025" s="16"/>
-      <c r="G1025" s="17"/>
-    </row>
-    <row r="1026" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1026" s="13">
+      <c r="E1025" s="8"/>
+      <c r="F1025" s="8"/>
+    </row>
+    <row r="1026" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1026" s="2">
         <v>46297</v>
       </c>
-      <c r="B1026" s="14"/>
-      <c r="C1026" s="15" t="s">
+      <c r="B1026" s="10"/>
+      <c r="C1026" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1026" s="16" t="s">
+      <c r="D1026" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E1026" s="16"/>
-      <c r="F1026" s="16"/>
-      <c r="G1026" s="17"/>
-    </row>
-    <row r="1027" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1027" s="13">
+      <c r="E1026" s="8"/>
+      <c r="F1026" s="8"/>
+    </row>
+    <row r="1027" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1027" s="2">
         <v>46298</v>
       </c>
-      <c r="B1027" s="14">
+      <c r="B1027" s="10">
         <v>0.375</v>
       </c>
-      <c r="C1027" s="15" t="s">
-        <v>427</v>
-      </c>
-      <c r="D1027" s="16" t="s">
+      <c r="C1027" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1027" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="E1027" s="16"/>
-      <c r="F1027" s="16"/>
-      <c r="G1027" s="17"/>
-    </row>
-    <row r="1028" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1028" s="13">
+      <c r="E1027" s="8"/>
+      <c r="F1027" s="8"/>
+    </row>
+    <row r="1028" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1028" s="2">
         <v>46298</v>
       </c>
-      <c r="B1028" s="14">
+      <c r="B1028" s="10">
         <v>0.5</v>
       </c>
-      <c r="C1028" s="15" t="s">
-        <v>427</v>
-      </c>
-      <c r="D1028" s="16" t="s">
+      <c r="C1028" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1028" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="E1028" s="16"/>
-      <c r="F1028" s="16"/>
-      <c r="G1028" s="17"/>
-    </row>
-    <row r="1029" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1029" s="13">
+      <c r="E1028" s="8"/>
+      <c r="F1028" s="8"/>
+    </row>
+    <row r="1029" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1029" s="2">
         <v>46298</v>
       </c>
-      <c r="B1029" s="14">
+      <c r="B1029" s="10">
         <v>0.54166666666666663</v>
       </c>
-      <c r="C1029" s="15" t="s">
-        <v>427</v>
-      </c>
-      <c r="D1029" s="16" t="s">
+      <c r="C1029" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1029" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="E1029" s="16"/>
-      <c r="F1029" s="16"/>
-      <c r="G1029" s="17"/>
-    </row>
-    <row r="1030" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1030" s="13">
+      <c r="E1029" s="8"/>
+      <c r="F1029" s="8"/>
+    </row>
+    <row r="1030" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1030" s="2">
         <v>46298</v>
       </c>
-      <c r="B1030" s="14">
+      <c r="B1030" s="10">
         <v>0.75</v>
       </c>
-      <c r="C1030" s="15" t="s">
-        <v>427</v>
-      </c>
-      <c r="D1030" s="16" t="s">
+      <c r="C1030" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1030" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="E1030" s="16"/>
-      <c r="F1030" s="16"/>
-      <c r="G1030" s="17"/>
-    </row>
-    <row r="1031" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1031" s="13">
-        <v>46298</v>
-      </c>
-      <c r="B1031" s="14">
-        <v>0.375</v>
-      </c>
-      <c r="C1031" s="15" t="s">
-        <v>431</v>
-      </c>
-      <c r="D1031" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="E1031" s="16"/>
-      <c r="F1031" s="16"/>
-      <c r="G1031" s="17"/>
-    </row>
-    <row r="1032" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1032" s="13">
-        <v>46298</v>
-      </c>
-      <c r="B1032" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="C1032" s="15" t="s">
-        <v>431</v>
-      </c>
-      <c r="D1032" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1032" s="16"/>
-      <c r="F1032" s="16"/>
-      <c r="G1032" s="17"/>
-    </row>
-    <row r="1033" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1033" s="13">
-        <v>46298</v>
-      </c>
-      <c r="B1033" s="14">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="C1033" s="15" t="s">
-        <v>431</v>
-      </c>
-      <c r="D1033" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="E1033" s="16"/>
-      <c r="F1033" s="16"/>
-      <c r="G1033" s="17"/>
-    </row>
-    <row r="1034" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1034" s="13">
-        <v>46298</v>
-      </c>
-      <c r="B1034" s="14">
-        <v>0.75</v>
-      </c>
-      <c r="C1034" s="15" t="s">
-        <v>431</v>
-      </c>
-      <c r="D1034" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="E1034" s="16"/>
-      <c r="F1034" s="16"/>
-      <c r="G1034" s="17"/>
-    </row>
-    <row r="1035" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1035" s="15"/>
-      <c r="B1035" s="15"/>
-      <c r="C1035" s="15"/>
-      <c r="D1035" s="15"/>
-      <c r="E1035" s="15"/>
-      <c r="F1035" s="15"/>
-      <c r="G1035" s="17"/>
-    </row>
-    <row r="1036" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1036" s="15"/>
-      <c r="B1036" s="15"/>
-      <c r="C1036" s="15"/>
-      <c r="D1036" s="15"/>
-      <c r="E1036" s="15"/>
-      <c r="F1036" s="15"/>
-      <c r="G1036" s="17"/>
-    </row>
-    <row r="1037" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1037" s="15"/>
-      <c r="B1037" s="15"/>
-      <c r="C1037" s="15"/>
-      <c r="D1037" s="15"/>
-      <c r="E1037" s="15"/>
-      <c r="F1037" s="15"/>
-      <c r="G1037" s="17"/>
-    </row>
-    <row r="1038" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1038" s="15"/>
-      <c r="B1038" s="15"/>
-      <c r="C1038" s="15"/>
-      <c r="D1038" s="15"/>
-      <c r="E1038" s="15"/>
-      <c r="F1038" s="15"/>
-      <c r="G1038" s="17"/>
-    </row>
-    <row r="1039" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1039" s="15"/>
-      <c r="B1039" s="15"/>
-      <c r="C1039" s="15"/>
-      <c r="D1039" s="15"/>
-      <c r="E1039" s="15"/>
-      <c r="F1039" s="15"/>
-      <c r="G1039" s="17"/>
-    </row>
-    <row r="1040" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1040" s="15"/>
-      <c r="B1040" s="15"/>
-      <c r="C1040" s="15"/>
-      <c r="D1040" s="15"/>
-      <c r="E1040" s="15"/>
-      <c r="F1040" s="15"/>
-      <c r="G1040" s="17"/>
+      <c r="E1030" s="8"/>
+      <c r="F1030" s="8"/>
+    </row>
+    <row r="1031" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1031" s="2"/>
+      <c r="B1031" s="10"/>
+      <c r="D1031" s="8"/>
+      <c r="E1031" s="8"/>
+      <c r="F1031" s="8"/>
+    </row>
+    <row r="1032" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1032" s="2"/>
+      <c r="B1032" s="10"/>
+      <c r="D1032" s="8"/>
+      <c r="E1032" s="8"/>
+      <c r="F1032" s="8"/>
+    </row>
+    <row r="1033" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1033" s="2"/>
+      <c r="B1033" s="10"/>
+      <c r="D1033" s="8"/>
+      <c r="E1033" s="8"/>
+      <c r="F1033" s="8"/>
+    </row>
+    <row r="1034" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1034" s="2"/>
+      <c r="B1034" s="10"/>
+      <c r="D1034" s="8"/>
+      <c r="E1034" s="8"/>
+      <c r="F1034" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="D987:F987"/>
+    <mergeCell ref="D988:F988"/>
+    <mergeCell ref="D981:F981"/>
+    <mergeCell ref="D982:F982"/>
+    <mergeCell ref="D983:F983"/>
+    <mergeCell ref="D984:F984"/>
+    <mergeCell ref="D985:F985"/>
+    <mergeCell ref="D986:F986"/>
     <mergeCell ref="D965:F965"/>
     <mergeCell ref="D966:F966"/>
     <mergeCell ref="D967:F967"/>
@@ -16480,14 +16377,6 @@
     <mergeCell ref="D977:F977"/>
     <mergeCell ref="D978:F978"/>
     <mergeCell ref="D979:F979"/>
-    <mergeCell ref="D987:F987"/>
-    <mergeCell ref="D988:F988"/>
-    <mergeCell ref="D981:F981"/>
-    <mergeCell ref="D982:F982"/>
-    <mergeCell ref="D983:F983"/>
-    <mergeCell ref="D984:F984"/>
-    <mergeCell ref="D985:F985"/>
-    <mergeCell ref="D986:F986"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A2297F2-7132-43B4-A71F-4B0E5F1D9A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24AE0ED4-E840-4004-8F6D-BE8DF0CF5B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2062" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2086" uniqueCount="432">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2080,7 +2080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1034"/>
+  <dimension ref="A1:F1042"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.69921875" style="1" bestFit="1" customWidth="1"/>
@@ -16324,43 +16324,183 @@
       <c r="F1030" s="8"/>
     </row>
     <row r="1031" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1031" s="2"/>
-      <c r="B1031" s="10"/>
-      <c r="D1031" s="8"/>
+      <c r="A1031" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B1031" s="10">
+        <v>0.375</v>
+      </c>
+      <c r="C1031" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1031" s="8" t="s">
+        <v>110</v>
+      </c>
       <c r="E1031" s="8"/>
       <c r="F1031" s="8"/>
     </row>
     <row r="1032" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1032" s="2"/>
-      <c r="B1032" s="10"/>
-      <c r="D1032" s="8"/>
+      <c r="A1032" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B1032" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="C1032" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1032" s="8" t="s">
+        <v>108</v>
+      </c>
       <c r="E1032" s="8"/>
       <c r="F1032" s="8"/>
     </row>
     <row r="1033" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1033" s="2"/>
-      <c r="B1033" s="10"/>
-      <c r="D1033" s="8"/>
+      <c r="A1033" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B1033" s="10">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1033" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1033" s="8" t="s">
+        <v>110</v>
+      </c>
       <c r="E1033" s="8"/>
       <c r="F1033" s="8"/>
     </row>
     <row r="1034" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1034" s="2"/>
-      <c r="B1034" s="10"/>
-      <c r="D1034" s="8"/>
+      <c r="A1034" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B1034" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="C1034" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1034" s="8" t="s">
+        <v>109</v>
+      </c>
       <c r="E1034" s="8"/>
       <c r="F1034" s="8"/>
     </row>
+    <row r="1035" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1035" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B1035" s="10">
+        <v>0.375</v>
+      </c>
+      <c r="C1035" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1035" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1036" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B1036" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="C1036" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1036" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1037" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B1037" s="10">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1037" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1037" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1038" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B1038" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="C1038" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1038" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1039" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B1039" s="10">
+        <v>0.375</v>
+      </c>
+      <c r="C1039" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1039" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1040" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B1040" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="C1040" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1040" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1041" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B1041" s="10">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1041" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1041" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1042" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B1042" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="C1042" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1042" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="D987:F987"/>
-    <mergeCell ref="D988:F988"/>
-    <mergeCell ref="D981:F981"/>
-    <mergeCell ref="D982:F982"/>
-    <mergeCell ref="D983:F983"/>
-    <mergeCell ref="D984:F984"/>
-    <mergeCell ref="D985:F985"/>
-    <mergeCell ref="D986:F986"/>
     <mergeCell ref="D965:F965"/>
     <mergeCell ref="D966:F966"/>
     <mergeCell ref="D967:F967"/>
@@ -16377,6 +16517,14 @@
     <mergeCell ref="D977:F977"/>
     <mergeCell ref="D978:F978"/>
     <mergeCell ref="D979:F979"/>
+    <mergeCell ref="D987:F987"/>
+    <mergeCell ref="D988:F988"/>
+    <mergeCell ref="D981:F981"/>
+    <mergeCell ref="D982:F982"/>
+    <mergeCell ref="D983:F983"/>
+    <mergeCell ref="D984:F984"/>
+    <mergeCell ref="D985:F985"/>
+    <mergeCell ref="D986:F986"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24AE0ED4-E840-4004-8F6D-BE8DF0CF5B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDFC482D-E17D-41CA-91CB-ED85C0521EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2086" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2094" uniqueCount="432">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2080,7 +2080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1042"/>
+  <dimension ref="A1:F1046"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.69921875" style="1" bestFit="1" customWidth="1"/>
@@ -16499,8 +16499,72 @@
         <v>109</v>
       </c>
     </row>
+    <row r="1043" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1043" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B1043" s="10">
+        <v>0.375</v>
+      </c>
+      <c r="C1043" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1043" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1044" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B1044" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="C1044" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1044" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1045" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B1045" s="10">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1045" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1045" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1046" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B1046" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="C1046" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1046" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="D987:F987"/>
+    <mergeCell ref="D988:F988"/>
+    <mergeCell ref="D981:F981"/>
+    <mergeCell ref="D982:F982"/>
+    <mergeCell ref="D983:F983"/>
+    <mergeCell ref="D984:F984"/>
+    <mergeCell ref="D985:F985"/>
+    <mergeCell ref="D986:F986"/>
     <mergeCell ref="D965:F965"/>
     <mergeCell ref="D966:F966"/>
     <mergeCell ref="D967:F967"/>
@@ -16517,14 +16581,6 @@
     <mergeCell ref="D977:F977"/>
     <mergeCell ref="D978:F978"/>
     <mergeCell ref="D979:F979"/>
-    <mergeCell ref="D987:F987"/>
-    <mergeCell ref="D988:F988"/>
-    <mergeCell ref="D981:F981"/>
-    <mergeCell ref="D982:F982"/>
-    <mergeCell ref="D983:F983"/>
-    <mergeCell ref="D984:F984"/>
-    <mergeCell ref="D985:F985"/>
-    <mergeCell ref="D986:F986"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDFC482D-E17D-41CA-91CB-ED85C0521EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9B5514-4FA6-4A61-9151-48D7A55FE9BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2094" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2124" uniqueCount="440">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1685,6 +1685,38 @@
   </si>
   <si>
     <t>D08</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>push on D12</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>climb D12</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>launch AIB-009</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>leg-A MGM</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">recovery </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>climb down D12</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sail to D08</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait D08 team</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1765,7 +1797,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1799,6 +1831,15 @@
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal 2" xfId="1" xr:uid="{71AF191C-2467-4F76-8A53-CA6D53E4DF10}"/>
@@ -2080,10 +2121,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1046"/>
+  <dimension ref="A1:G1064"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.296875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.8984375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.09765625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="54.8984375" style="1" bestFit="1" customWidth="1"/>
@@ -16471,7 +16512,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="1041" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1041" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1041" s="2">
         <v>46301</v>
       </c>
@@ -16485,7 +16526,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="1042" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1042" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1042" s="2">
         <v>46301</v>
       </c>
@@ -16499,7 +16540,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="1043" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1043" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1043" s="2">
         <v>46302</v>
       </c>
@@ -16513,7 +16554,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="1044" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1044" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1044" s="2">
         <v>46302</v>
       </c>
@@ -16527,7 +16568,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="1045" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1045" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1045" s="2">
         <v>46302</v>
       </c>
@@ -16541,7 +16582,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="1046" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1046" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1046" s="2">
         <v>46302</v>
       </c>
@@ -16555,16 +16596,296 @@
         <v>109</v>
       </c>
     </row>
+    <row r="1047" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1047" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1047" s="14">
+        <v>0.24861111111111112</v>
+      </c>
+      <c r="C1047" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1047" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="E1047" s="16"/>
+      <c r="F1047" s="16"/>
+      <c r="G1047" s="17"/>
+    </row>
+    <row r="1048" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1048" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1048" s="14">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="C1048" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1048" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="E1048" s="16"/>
+      <c r="F1048" s="16"/>
+      <c r="G1048" s="17"/>
+    </row>
+    <row r="1049" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1049" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1049" s="14"/>
+      <c r="C1049" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1049" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="E1049" s="16"/>
+      <c r="F1049" s="16"/>
+      <c r="G1049" s="17"/>
+    </row>
+    <row r="1050" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1050" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1050" s="14">
+        <v>0.34583333333333333</v>
+      </c>
+      <c r="C1050" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1050" s="16" t="s">
+        <v>398</v>
+      </c>
+      <c r="E1050" s="16"/>
+      <c r="F1050" s="16"/>
+      <c r="G1050" s="17"/>
+    </row>
+    <row r="1051" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1051" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1051" s="14">
+        <v>0.36249999999999999</v>
+      </c>
+      <c r="C1051" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1051" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1051" s="16"/>
+      <c r="F1051" s="16"/>
+      <c r="G1051" s="17"/>
+    </row>
+    <row r="1052" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1052" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1052" s="14"/>
+      <c r="C1052" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1052" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="E1052" s="16"/>
+      <c r="F1052" s="16"/>
+      <c r="G1052" s="17"/>
+    </row>
+    <row r="1053" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1053" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1053" s="14">
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="C1053" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1053" s="16" t="s">
+        <v>436</v>
+      </c>
+      <c r="E1053" s="16"/>
+      <c r="F1053" s="16"/>
+      <c r="G1053" s="17"/>
+    </row>
+    <row r="1054" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1054" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1054" s="14"/>
+      <c r="C1054" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1054" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="E1054" s="16"/>
+      <c r="F1054" s="16"/>
+      <c r="G1054" s="17"/>
+    </row>
+    <row r="1055" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1055" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1055" s="14"/>
+      <c r="C1055" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1055" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1055" s="16"/>
+      <c r="F1055" s="16"/>
+      <c r="G1055" s="17"/>
+    </row>
+    <row r="1056" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1056" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1056" s="14">
+        <v>0.46527777777777779</v>
+      </c>
+      <c r="C1056" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1056" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="E1056" s="16"/>
+      <c r="F1056" s="16"/>
+      <c r="G1056" s="17"/>
+    </row>
+    <row r="1057" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1057" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1057" s="14">
+        <v>0.47222222222222221</v>
+      </c>
+      <c r="C1057" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1057" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="E1057" s="16"/>
+      <c r="F1057" s="16"/>
+      <c r="G1057" s="17"/>
+    </row>
+    <row r="1058" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1058" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1058" s="14">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C1058" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1058" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="E1058" s="16"/>
+      <c r="F1058" s="16"/>
+      <c r="G1058" s="17"/>
+    </row>
+    <row r="1059" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1059" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1059" s="14">
+        <v>0.49305555555555558</v>
+      </c>
+      <c r="C1059" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1059" s="16" t="s">
+        <v>394</v>
+      </c>
+      <c r="E1059" s="16"/>
+      <c r="F1059" s="16"/>
+      <c r="G1059" s="17"/>
+    </row>
+    <row r="1060" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1060" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1060" s="14">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="C1060" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1060" s="16" t="s">
+        <v>379</v>
+      </c>
+      <c r="E1060" s="16"/>
+      <c r="F1060" s="16"/>
+      <c r="G1060" s="17"/>
+    </row>
+    <row r="1061" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1061" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1061" s="14"/>
+      <c r="C1061" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1061" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1061" s="16"/>
+      <c r="F1061" s="16"/>
+      <c r="G1061" s="17"/>
+    </row>
+    <row r="1062" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1062" s="15"/>
+      <c r="B1062" s="15"/>
+      <c r="C1062" s="15"/>
+      <c r="D1062" s="16"/>
+      <c r="E1062" s="16"/>
+      <c r="F1062" s="16"/>
+      <c r="G1062" s="17"/>
+    </row>
+    <row r="1063" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1063" s="15"/>
+      <c r="B1063" s="15"/>
+      <c r="C1063" s="15"/>
+      <c r="D1063" s="15"/>
+      <c r="E1063" s="15"/>
+      <c r="F1063" s="15"/>
+      <c r="G1063" s="17"/>
+    </row>
+    <row r="1064" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1064" s="15"/>
+      <c r="B1064" s="15"/>
+      <c r="C1064" s="15"/>
+      <c r="D1064" s="15"/>
+      <c r="E1064" s="15"/>
+      <c r="F1064" s="15"/>
+      <c r="G1064" s="17"/>
+    </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="D987:F987"/>
-    <mergeCell ref="D988:F988"/>
-    <mergeCell ref="D981:F981"/>
-    <mergeCell ref="D982:F982"/>
-    <mergeCell ref="D983:F983"/>
-    <mergeCell ref="D984:F984"/>
-    <mergeCell ref="D985:F985"/>
-    <mergeCell ref="D986:F986"/>
+  <mergeCells count="40">
+    <mergeCell ref="D1062:F1062"/>
+    <mergeCell ref="D1057:F1057"/>
+    <mergeCell ref="D1058:F1058"/>
+    <mergeCell ref="D1059:F1059"/>
+    <mergeCell ref="D1060:F1060"/>
+    <mergeCell ref="D1061:F1061"/>
+    <mergeCell ref="D1052:F1052"/>
+    <mergeCell ref="D1053:F1053"/>
+    <mergeCell ref="D1054:F1054"/>
+    <mergeCell ref="D1055:F1055"/>
+    <mergeCell ref="D1056:F1056"/>
+    <mergeCell ref="D1047:F1047"/>
+    <mergeCell ref="D1048:F1048"/>
+    <mergeCell ref="D1049:F1049"/>
+    <mergeCell ref="D1050:F1050"/>
+    <mergeCell ref="D1051:F1051"/>
     <mergeCell ref="D965:F965"/>
     <mergeCell ref="D966:F966"/>
     <mergeCell ref="D967:F967"/>
@@ -16581,6 +16902,14 @@
     <mergeCell ref="D977:F977"/>
     <mergeCell ref="D978:F978"/>
     <mergeCell ref="D979:F979"/>
+    <mergeCell ref="D987:F987"/>
+    <mergeCell ref="D988:F988"/>
+    <mergeCell ref="D981:F981"/>
+    <mergeCell ref="D982:F982"/>
+    <mergeCell ref="D983:F983"/>
+    <mergeCell ref="D984:F984"/>
+    <mergeCell ref="D985:F985"/>
+    <mergeCell ref="D986:F986"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9B5514-4FA6-4A61-9151-48D7A55FE9BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B509E05E-024F-480D-8817-AD8D47418495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2124" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2158" uniqueCount="452">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1718,13 +1718,49 @@
   <si>
     <t>wait D08 team</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>push on D12</t>
+  </si>
+  <si>
+    <t>push off D12</t>
+  </si>
+  <si>
+    <t>push on D08</t>
+  </si>
+  <si>
+    <t>climb up D08</t>
+  </si>
+  <si>
+    <t>lift bags</t>
+  </si>
+  <si>
+    <t>setup</t>
+  </si>
+  <si>
+    <t>leg A inspection</t>
+  </si>
+  <si>
+    <t>recovery</t>
+  </si>
+  <si>
+    <t>data transfer</t>
+  </si>
+  <si>
+    <t>washdown</t>
+  </si>
+  <si>
+    <t>housekeep</t>
+  </si>
+  <si>
+    <t>climb down</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1775,6 +1811,13 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1793,9 +1836,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1839,11 +1888,17 @@
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="6">
     <cellStyle name="Normal 2" xfId="1" xr:uid="{71AF191C-2467-4F76-8A53-CA6D53E4DF10}"/>
+    <cellStyle name="Normal 3" xfId="3" xr:uid="{8515996D-D0CD-4334-9C8D-B68B8CB97685}"/>
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="一般 2" xfId="4" xr:uid="{A374185A-BC77-41A8-B0CC-625AACE658C9}"/>
+    <cellStyle name="一般 3" xfId="2" xr:uid="{DC8E441D-4A1C-4CC7-8BA8-9559B8E2851C}"/>
+    <cellStyle name="百分比 2" xfId="5" xr:uid="{185B8069-6B49-42E9-A89A-88A74642D22B}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2121,7 +2176,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1064"/>
+  <dimension ref="A1:F1081"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.296875" style="1" bestFit="1" customWidth="1"/>
@@ -16512,7 +16567,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="1041" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1041" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1041" s="2">
         <v>46301</v>
       </c>
@@ -16526,7 +16581,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="1042" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1042" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1042" s="2">
         <v>46301</v>
       </c>
@@ -16540,7 +16595,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="1043" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1043" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1043" s="2">
         <v>46302</v>
       </c>
@@ -16554,7 +16609,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="1044" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1044" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1044" s="2">
         <v>46302</v>
       </c>
@@ -16568,7 +16623,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="1045" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1045" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1045" s="2">
         <v>46302</v>
       </c>
@@ -16582,7 +16637,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="1046" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1046" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1046" s="2">
         <v>46302</v>
       </c>
@@ -16596,237 +16651,223 @@
         <v>109</v>
       </c>
     </row>
-    <row r="1047" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1047" s="13">
+    <row r="1047" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1047" s="2">
         <v>46308</v>
       </c>
-      <c r="B1047" s="14">
+      <c r="B1047" s="10">
         <v>0.24861111111111112</v>
       </c>
-      <c r="C1047" s="15" t="s">
+      <c r="C1047" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1047" s="16" t="s">
+      <c r="D1047" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="E1047" s="16"/>
-      <c r="F1047" s="16"/>
-      <c r="G1047" s="17"/>
-    </row>
-    <row r="1048" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1048" s="13">
+      <c r="E1047" s="12"/>
+      <c r="F1047" s="12"/>
+    </row>
+    <row r="1048" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1048" s="2">
         <v>46308</v>
       </c>
-      <c r="B1048" s="14">
+      <c r="B1048" s="10">
         <v>0.32500000000000001</v>
       </c>
-      <c r="C1048" s="15" t="s">
+      <c r="C1048" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1048" s="16" t="s">
+      <c r="D1048" s="12" t="s">
         <v>432</v>
       </c>
-      <c r="E1048" s="16"/>
-      <c r="F1048" s="16"/>
-      <c r="G1048" s="17"/>
-    </row>
-    <row r="1049" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1049" s="13">
+      <c r="E1048" s="12"/>
+      <c r="F1048" s="12"/>
+    </row>
+    <row r="1049" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1049" s="2">
         <v>46308</v>
       </c>
-      <c r="B1049" s="14"/>
-      <c r="C1049" s="15" t="s">
+      <c r="B1049" s="10"/>
+      <c r="C1049" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1049" s="16" t="s">
+      <c r="D1049" s="12" t="s">
         <v>433</v>
       </c>
-      <c r="E1049" s="16"/>
-      <c r="F1049" s="16"/>
-      <c r="G1049" s="17"/>
-    </row>
-    <row r="1050" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1050" s="13">
+      <c r="E1049" s="12"/>
+      <c r="F1049" s="12"/>
+    </row>
+    <row r="1050" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1050" s="2">
         <v>46308</v>
       </c>
-      <c r="B1050" s="14">
+      <c r="B1050" s="10">
         <v>0.34583333333333333</v>
       </c>
-      <c r="C1050" s="15" t="s">
+      <c r="C1050" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1050" s="16" t="s">
+      <c r="D1050" s="12" t="s">
         <v>398</v>
       </c>
-      <c r="E1050" s="16"/>
-      <c r="F1050" s="16"/>
-      <c r="G1050" s="17"/>
-    </row>
-    <row r="1051" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1051" s="13">
+      <c r="E1050" s="12"/>
+      <c r="F1050" s="12"/>
+    </row>
+    <row r="1051" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1051" s="2">
         <v>46308</v>
       </c>
-      <c r="B1051" s="14">
+      <c r="B1051" s="10">
         <v>0.36249999999999999</v>
       </c>
-      <c r="C1051" s="15" t="s">
+      <c r="C1051" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1051" s="16" t="s">
+      <c r="D1051" s="12" t="s">
         <v>434</v>
       </c>
-      <c r="E1051" s="16"/>
-      <c r="F1051" s="16"/>
-      <c r="G1051" s="17"/>
-    </row>
-    <row r="1052" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1052" s="13">
+      <c r="E1051" s="12"/>
+      <c r="F1051" s="12"/>
+    </row>
+    <row r="1052" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1052" s="2">
         <v>46308</v>
       </c>
-      <c r="B1052" s="14"/>
-      <c r="C1052" s="15" t="s">
+      <c r="B1052" s="10"/>
+      <c r="C1052" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1052" s="16" t="s">
+      <c r="D1052" s="12" t="s">
         <v>435</v>
       </c>
-      <c r="E1052" s="16"/>
-      <c r="F1052" s="16"/>
-      <c r="G1052" s="17"/>
-    </row>
-    <row r="1053" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1053" s="13">
+      <c r="E1052" s="12"/>
+      <c r="F1052" s="12"/>
+    </row>
+    <row r="1053" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1053" s="2">
         <v>46308</v>
       </c>
-      <c r="B1053" s="14">
+      <c r="B1053" s="10">
         <v>0.40972222222222221</v>
       </c>
-      <c r="C1053" s="15" t="s">
+      <c r="C1053" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1053" s="16" t="s">
+      <c r="D1053" s="12" t="s">
         <v>436</v>
       </c>
-      <c r="E1053" s="16"/>
-      <c r="F1053" s="16"/>
-      <c r="G1053" s="17"/>
-    </row>
-    <row r="1054" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1054" s="13">
+      <c r="E1053" s="12"/>
+      <c r="F1053" s="12"/>
+    </row>
+    <row r="1054" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1054" s="2">
         <v>46308</v>
       </c>
-      <c r="B1054" s="14"/>
-      <c r="C1054" s="15" t="s">
+      <c r="B1054" s="10"/>
+      <c r="C1054" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1054" s="16" t="s">
+      <c r="D1054" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="E1054" s="16"/>
-      <c r="F1054" s="16"/>
-      <c r="G1054" s="17"/>
-    </row>
-    <row r="1055" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1055" s="13">
+      <c r="E1054" s="12"/>
+      <c r="F1054" s="12"/>
+    </row>
+    <row r="1055" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1055" s="2">
         <v>46308</v>
       </c>
-      <c r="B1055" s="14"/>
-      <c r="C1055" s="15" t="s">
+      <c r="B1055" s="10"/>
+      <c r="C1055" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1055" s="16" t="s">
+      <c r="D1055" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="E1055" s="16"/>
-      <c r="F1055" s="16"/>
-      <c r="G1055" s="17"/>
-    </row>
-    <row r="1056" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1056" s="13">
+      <c r="E1055" s="12"/>
+      <c r="F1055" s="12"/>
+    </row>
+    <row r="1056" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1056" s="2">
         <v>46308</v>
       </c>
-      <c r="B1056" s="14">
+      <c r="B1056" s="10">
         <v>0.46527777777777779</v>
       </c>
-      <c r="C1056" s="15" t="s">
+      <c r="C1056" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1056" s="16" t="s">
+      <c r="D1056" s="12" t="s">
         <v>437</v>
       </c>
-      <c r="E1056" s="16"/>
-      <c r="F1056" s="16"/>
-      <c r="G1056" s="17"/>
-    </row>
-    <row r="1057" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1057" s="13">
+      <c r="E1056" s="12"/>
+      <c r="F1056" s="12"/>
+    </row>
+    <row r="1057" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1057" s="2">
         <v>46308</v>
       </c>
-      <c r="B1057" s="14">
+      <c r="B1057" s="10">
         <v>0.47222222222222221</v>
       </c>
-      <c r="C1057" s="15" t="s">
+      <c r="C1057" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1057" s="16" t="s">
+      <c r="D1057" s="12" t="s">
         <v>438</v>
       </c>
-      <c r="E1057" s="16"/>
-      <c r="F1057" s="16"/>
-      <c r="G1057" s="17"/>
-    </row>
-    <row r="1058" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1058" s="13">
+      <c r="E1057" s="12"/>
+      <c r="F1057" s="12"/>
+    </row>
+    <row r="1058" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1058" s="2">
         <v>46308</v>
       </c>
-      <c r="B1058" s="14">
+      <c r="B1058" s="10">
         <v>0.47916666666666669</v>
       </c>
-      <c r="C1058" s="15" t="s">
+      <c r="C1058" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1058" s="16" t="s">
+      <c r="D1058" s="12" t="s">
         <v>439</v>
       </c>
-      <c r="E1058" s="16"/>
-      <c r="F1058" s="16"/>
-      <c r="G1058" s="17"/>
-    </row>
-    <row r="1059" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1059" s="13">
+      <c r="E1058" s="12"/>
+      <c r="F1058" s="12"/>
+    </row>
+    <row r="1059" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1059" s="2">
         <v>46308</v>
       </c>
-      <c r="B1059" s="14">
+      <c r="B1059" s="10">
         <v>0.49305555555555558</v>
       </c>
-      <c r="C1059" s="15" t="s">
+      <c r="C1059" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1059" s="16" t="s">
+      <c r="D1059" s="12" t="s">
         <v>394</v>
       </c>
-      <c r="E1059" s="16"/>
-      <c r="F1059" s="16"/>
-      <c r="G1059" s="17"/>
-    </row>
-    <row r="1060" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1060" s="13">
+      <c r="E1059" s="12"/>
+      <c r="F1059" s="12"/>
+    </row>
+    <row r="1060" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1060" s="2">
         <v>46308</v>
       </c>
-      <c r="B1060" s="14">
+      <c r="B1060" s="10">
         <v>0.57638888888888884</v>
       </c>
-      <c r="C1060" s="15" t="s">
+      <c r="C1060" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1060" s="16" t="s">
+      <c r="D1060" s="12" t="s">
         <v>379</v>
       </c>
-      <c r="E1060" s="16"/>
-      <c r="F1060" s="16"/>
-      <c r="G1060" s="17"/>
-    </row>
-    <row r="1061" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E1060" s="12"/>
+      <c r="F1060" s="12"/>
+    </row>
+    <row r="1061" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1061" s="13">
         <v>46308</v>
       </c>
@@ -16839,53 +16880,302 @@
       </c>
       <c r="E1061" s="16"/>
       <c r="F1061" s="16"/>
-      <c r="G1061" s="17"/>
-    </row>
-    <row r="1062" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1062" s="15"/>
-      <c r="B1062" s="15"/>
-      <c r="C1062" s="15"/>
-      <c r="D1062" s="16"/>
+    </row>
+    <row r="1062" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1062" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1062" s="14">
+        <v>0.24861111111111112</v>
+      </c>
+      <c r="C1062" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1062" s="16" t="s">
+        <v>371</v>
+      </c>
       <c r="E1062" s="16"/>
       <c r="F1062" s="16"/>
-      <c r="G1062" s="17"/>
-    </row>
-    <row r="1063" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1063" s="15"/>
-      <c r="B1063" s="15"/>
-      <c r="C1063" s="15"/>
-      <c r="D1063" s="15"/>
-      <c r="E1063" s="15"/>
-      <c r="F1063" s="15"/>
-      <c r="G1063" s="17"/>
-    </row>
-    <row r="1064" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1064" s="15"/>
-      <c r="B1064" s="15"/>
-      <c r="C1064" s="15"/>
-      <c r="D1064" s="15"/>
-      <c r="E1064" s="15"/>
-      <c r="F1064" s="15"/>
-      <c r="G1064" s="17"/>
+    </row>
+    <row r="1063" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1063" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1063" s="14">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="C1063" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1063" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="E1063" s="16"/>
+      <c r="F1063" s="16"/>
+    </row>
+    <row r="1064" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1064" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1064" s="14">
+        <v>0.34027777777777779</v>
+      </c>
+      <c r="C1064" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1064" s="16" t="s">
+        <v>441</v>
+      </c>
+      <c r="E1064" s="16"/>
+      <c r="F1064" s="16"/>
+    </row>
+    <row r="1065" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1065" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1065" s="14">
+        <v>0.34722222222222221</v>
+      </c>
+      <c r="C1065" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1065" s="16" t="s">
+        <v>442</v>
+      </c>
+      <c r="E1065" s="16"/>
+      <c r="F1065" s="16"/>
+    </row>
+    <row r="1066" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1066" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1066" s="14">
+        <v>0.35138888888888886</v>
+      </c>
+      <c r="C1066" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1066" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="E1066" s="16"/>
+      <c r="F1066" s="16"/>
+    </row>
+    <row r="1067" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1067" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1067" s="14"/>
+      <c r="C1067" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1067" s="16" t="s">
+        <v>444</v>
+      </c>
+      <c r="E1067" s="16"/>
+      <c r="F1067" s="16"/>
+    </row>
+    <row r="1068" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1068" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1068" s="14"/>
+      <c r="C1068" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1068" s="16" t="s">
+        <v>445</v>
+      </c>
+      <c r="E1068" s="16"/>
+      <c r="F1068" s="16"/>
+    </row>
+    <row r="1069" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1069" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1069" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="C1069" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1069" s="16" t="s">
+        <v>405</v>
+      </c>
+      <c r="E1069" s="16"/>
+      <c r="F1069" s="16"/>
+    </row>
+    <row r="1070" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1070" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1070" s="14"/>
+      <c r="C1070" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1070" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="E1070" s="16"/>
+      <c r="F1070" s="16"/>
+    </row>
+    <row r="1071" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1071" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1071" s="14">
+        <v>0.43819444444444444</v>
+      </c>
+      <c r="C1071" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1071" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="E1071" s="16"/>
+      <c r="F1071" s="16"/>
+    </row>
+    <row r="1072" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1072" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1072" s="14"/>
+      <c r="C1072" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1072" s="16" t="s">
+        <v>448</v>
+      </c>
+      <c r="E1072" s="16"/>
+      <c r="F1072" s="16"/>
+    </row>
+    <row r="1073" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1073" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1073" s="14"/>
+      <c r="C1073" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1073" s="17" t="s">
+        <v>449</v>
+      </c>
+      <c r="E1073" s="17"/>
+      <c r="F1073" s="17"/>
+    </row>
+    <row r="1074" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1074" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1074" s="14"/>
+      <c r="C1074" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1074" s="16" t="s">
+        <v>450</v>
+      </c>
+      <c r="E1074" s="16"/>
+      <c r="F1074" s="16"/>
+    </row>
+    <row r="1075" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1075" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1075" s="14">
+        <v>0.4909722222222222</v>
+      </c>
+      <c r="C1075" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1075" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="E1075" s="16"/>
+      <c r="F1075" s="16"/>
+    </row>
+    <row r="1076" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1076" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1076" s="14">
+        <v>0.49305555555555558</v>
+      </c>
+      <c r="C1076" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1076" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="E1076" s="16"/>
+      <c r="F1076" s="16"/>
+    </row>
+    <row r="1077" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1077" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1077" s="14">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="C1077" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1077" s="16" t="s">
+        <v>379</v>
+      </c>
+      <c r="E1077" s="16"/>
+      <c r="F1077" s="16"/>
+    </row>
+    <row r="1078" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1078" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B1078" s="14"/>
+      <c r="C1078" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1078" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1078" s="16"/>
+      <c r="F1078" s="16"/>
+    </row>
+    <row r="1079" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1079" s="15"/>
+      <c r="B1079" s="15"/>
+      <c r="C1079" s="15"/>
+      <c r="D1079" s="15"/>
+      <c r="E1079" s="15"/>
+      <c r="F1079" s="15"/>
+    </row>
+    <row r="1080" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1080" s="15"/>
+      <c r="B1080" s="15"/>
+      <c r="C1080" s="15"/>
+      <c r="D1080" s="15"/>
+      <c r="E1080" s="15"/>
+      <c r="F1080" s="15"/>
+    </row>
+    <row r="1081" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1081" s="15"/>
+      <c r="B1081" s="15"/>
+      <c r="C1081" s="15"/>
+      <c r="D1081" s="15"/>
+      <c r="E1081" s="15"/>
+      <c r="F1081" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="55">
+    <mergeCell ref="D987:F987"/>
+    <mergeCell ref="D988:F988"/>
+    <mergeCell ref="D981:F981"/>
+    <mergeCell ref="D982:F982"/>
+    <mergeCell ref="D983:F983"/>
+    <mergeCell ref="D984:F984"/>
+    <mergeCell ref="D985:F985"/>
+    <mergeCell ref="D986:F986"/>
+    <mergeCell ref="D1064:F1064"/>
     <mergeCell ref="D1062:F1062"/>
-    <mergeCell ref="D1057:F1057"/>
-    <mergeCell ref="D1058:F1058"/>
-    <mergeCell ref="D1059:F1059"/>
-    <mergeCell ref="D1060:F1060"/>
-    <mergeCell ref="D1061:F1061"/>
-    <mergeCell ref="D1052:F1052"/>
-    <mergeCell ref="D1053:F1053"/>
-    <mergeCell ref="D1054:F1054"/>
-    <mergeCell ref="D1055:F1055"/>
-    <mergeCell ref="D1056:F1056"/>
-    <mergeCell ref="D1047:F1047"/>
-    <mergeCell ref="D1048:F1048"/>
-    <mergeCell ref="D1049:F1049"/>
-    <mergeCell ref="D1050:F1050"/>
-    <mergeCell ref="D1051:F1051"/>
+    <mergeCell ref="D1063:F1063"/>
     <mergeCell ref="D965:F965"/>
     <mergeCell ref="D966:F966"/>
     <mergeCell ref="D967:F967"/>
@@ -16902,14 +17192,34 @@
     <mergeCell ref="D977:F977"/>
     <mergeCell ref="D978:F978"/>
     <mergeCell ref="D979:F979"/>
-    <mergeCell ref="D987:F987"/>
-    <mergeCell ref="D988:F988"/>
-    <mergeCell ref="D981:F981"/>
-    <mergeCell ref="D982:F982"/>
-    <mergeCell ref="D983:F983"/>
-    <mergeCell ref="D984:F984"/>
-    <mergeCell ref="D985:F985"/>
-    <mergeCell ref="D986:F986"/>
+    <mergeCell ref="D1047:F1047"/>
+    <mergeCell ref="D1048:F1048"/>
+    <mergeCell ref="D1049:F1049"/>
+    <mergeCell ref="D1050:F1050"/>
+    <mergeCell ref="D1051:F1051"/>
+    <mergeCell ref="D1065:F1065"/>
+    <mergeCell ref="D1068:F1068"/>
+    <mergeCell ref="D1069:F1069"/>
+    <mergeCell ref="D1066:F1066"/>
+    <mergeCell ref="D1067:F1067"/>
+    <mergeCell ref="D1052:F1052"/>
+    <mergeCell ref="D1053:F1053"/>
+    <mergeCell ref="D1054:F1054"/>
+    <mergeCell ref="D1055:F1055"/>
+    <mergeCell ref="D1056:F1056"/>
+    <mergeCell ref="D1072:F1072"/>
+    <mergeCell ref="D1070:F1070"/>
+    <mergeCell ref="D1071:F1071"/>
+    <mergeCell ref="D1077:F1077"/>
+    <mergeCell ref="D1074:F1074"/>
+    <mergeCell ref="D1075:F1075"/>
+    <mergeCell ref="D1076:F1076"/>
+    <mergeCell ref="D1057:F1057"/>
+    <mergeCell ref="D1058:F1058"/>
+    <mergeCell ref="D1059:F1059"/>
+    <mergeCell ref="D1060:F1060"/>
+    <mergeCell ref="D1061:F1061"/>
+    <mergeCell ref="D1078:F1078"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B509E05E-024F-480D-8817-AD8D47418495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD059BA-5836-43CD-B6EC-E5090BB6497C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2158" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2174" uniqueCount="452">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1846,7 +1846,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1878,17 +1878,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2176,7 +2165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1081"/>
+  <dimension ref="A1:F1086"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.296875" style="1" bestFit="1" customWidth="1"/>
@@ -16868,311 +16857,422 @@
       <c r="F1060" s="12"/>
     </row>
     <row r="1061" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1061" s="13">
+      <c r="A1061" s="2">
         <v>46308</v>
       </c>
-      <c r="B1061" s="14"/>
-      <c r="C1061" s="15" t="s">
+      <c r="B1061" s="10"/>
+      <c r="C1061" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1061" s="16" t="s">
+      <c r="D1061" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="E1061" s="16"/>
-      <c r="F1061" s="16"/>
+      <c r="E1061" s="12"/>
+      <c r="F1061" s="12"/>
     </row>
     <row r="1062" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1062" s="13">
+      <c r="A1062" s="2">
         <v>46308</v>
       </c>
-      <c r="B1062" s="14">
+      <c r="B1062" s="10">
         <v>0.24861111111111112</v>
       </c>
-      <c r="C1062" s="15" t="s">
+      <c r="C1062" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1062" s="16" t="s">
+      <c r="D1062" s="12" t="s">
         <v>371</v>
       </c>
-      <c r="E1062" s="16"/>
-      <c r="F1062" s="16"/>
+      <c r="E1062" s="12"/>
+      <c r="F1062" s="12"/>
     </row>
     <row r="1063" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1063" s="13">
+      <c r="A1063" s="2">
         <v>46308</v>
       </c>
-      <c r="B1063" s="14">
+      <c r="B1063" s="10">
         <v>0.32500000000000001</v>
       </c>
-      <c r="C1063" s="15" t="s">
+      <c r="C1063" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1063" s="16" t="s">
+      <c r="D1063" s="12" t="s">
         <v>440</v>
       </c>
-      <c r="E1063" s="16"/>
-      <c r="F1063" s="16"/>
+      <c r="E1063" s="12"/>
+      <c r="F1063" s="12"/>
     </row>
     <row r="1064" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1064" s="13">
+      <c r="A1064" s="2">
         <v>46308</v>
       </c>
-      <c r="B1064" s="14">
+      <c r="B1064" s="10">
         <v>0.34027777777777779</v>
       </c>
-      <c r="C1064" s="15" t="s">
+      <c r="C1064" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1064" s="16" t="s">
+      <c r="D1064" s="12" t="s">
         <v>441</v>
       </c>
-      <c r="E1064" s="16"/>
-      <c r="F1064" s="16"/>
+      <c r="E1064" s="12"/>
+      <c r="F1064" s="12"/>
     </row>
     <row r="1065" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1065" s="13">
+      <c r="A1065" s="2">
         <v>46308</v>
       </c>
-      <c r="B1065" s="14">
+      <c r="B1065" s="10">
         <v>0.34722222222222221</v>
       </c>
-      <c r="C1065" s="15" t="s">
+      <c r="C1065" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1065" s="16" t="s">
+      <c r="D1065" s="12" t="s">
         <v>442</v>
       </c>
-      <c r="E1065" s="16"/>
-      <c r="F1065" s="16"/>
+      <c r="E1065" s="12"/>
+      <c r="F1065" s="12"/>
     </row>
     <row r="1066" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1066" s="13">
+      <c r="A1066" s="2">
         <v>46308</v>
       </c>
-      <c r="B1066" s="14">
+      <c r="B1066" s="10">
         <v>0.35138888888888886</v>
       </c>
-      <c r="C1066" s="15" t="s">
+      <c r="C1066" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1066" s="16" t="s">
+      <c r="D1066" s="12" t="s">
         <v>443</v>
       </c>
-      <c r="E1066" s="16"/>
-      <c r="F1066" s="16"/>
+      <c r="E1066" s="12"/>
+      <c r="F1066" s="12"/>
     </row>
     <row r="1067" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1067" s="13">
+      <c r="A1067" s="2">
         <v>46308</v>
       </c>
-      <c r="B1067" s="14"/>
-      <c r="C1067" s="15" t="s">
+      <c r="B1067" s="10"/>
+      <c r="C1067" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1067" s="16" t="s">
+      <c r="D1067" s="12" t="s">
         <v>444</v>
       </c>
-      <c r="E1067" s="16"/>
-      <c r="F1067" s="16"/>
+      <c r="E1067" s="12"/>
+      <c r="F1067" s="12"/>
     </row>
     <row r="1068" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1068" s="13">
+      <c r="A1068" s="2">
         <v>46308</v>
       </c>
-      <c r="B1068" s="14"/>
-      <c r="C1068" s="15" t="s">
+      <c r="B1068" s="10"/>
+      <c r="C1068" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1068" s="16" t="s">
+      <c r="D1068" s="12" t="s">
         <v>445</v>
       </c>
-      <c r="E1068" s="16"/>
-      <c r="F1068" s="16"/>
+      <c r="E1068" s="12"/>
+      <c r="F1068" s="12"/>
     </row>
     <row r="1069" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1069" s="13">
+      <c r="A1069" s="2">
         <v>46308</v>
       </c>
-      <c r="B1069" s="14">
+      <c r="B1069" s="10">
         <v>0.375</v>
       </c>
-      <c r="C1069" s="15" t="s">
+      <c r="C1069" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1069" s="16" t="s">
+      <c r="D1069" s="12" t="s">
         <v>405</v>
       </c>
-      <c r="E1069" s="16"/>
-      <c r="F1069" s="16"/>
+      <c r="E1069" s="12"/>
+      <c r="F1069" s="12"/>
     </row>
     <row r="1070" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1070" s="13">
+      <c r="A1070" s="2">
         <v>46308</v>
       </c>
-      <c r="B1070" s="14"/>
-      <c r="C1070" s="15" t="s">
+      <c r="B1070" s="10"/>
+      <c r="C1070" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1070" s="16" t="s">
+      <c r="D1070" s="12" t="s">
         <v>446</v>
       </c>
-      <c r="E1070" s="16"/>
-      <c r="F1070" s="16"/>
+      <c r="E1070" s="12"/>
+      <c r="F1070" s="12"/>
     </row>
     <row r="1071" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1071" s="13">
+      <c r="A1071" s="2">
         <v>46308</v>
       </c>
-      <c r="B1071" s="14">
+      <c r="B1071" s="10">
         <v>0.43819444444444444</v>
       </c>
-      <c r="C1071" s="15" t="s">
+      <c r="C1071" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1071" s="16" t="s">
+      <c r="D1071" s="12" t="s">
         <v>447</v>
       </c>
-      <c r="E1071" s="16"/>
-      <c r="F1071" s="16"/>
+      <c r="E1071" s="12"/>
+      <c r="F1071" s="12"/>
     </row>
     <row r="1072" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1072" s="13">
+      <c r="A1072" s="2">
         <v>46308</v>
       </c>
-      <c r="B1072" s="14"/>
-      <c r="C1072" s="15" t="s">
+      <c r="B1072" s="10"/>
+      <c r="C1072" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1072" s="16" t="s">
+      <c r="D1072" s="12" t="s">
         <v>448</v>
       </c>
-      <c r="E1072" s="16"/>
-      <c r="F1072" s="16"/>
+      <c r="E1072" s="12"/>
+      <c r="F1072" s="12"/>
     </row>
     <row r="1073" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1073" s="13">
+      <c r="A1073" s="2">
         <v>46308</v>
       </c>
-      <c r="B1073" s="14"/>
-      <c r="C1073" s="15" t="s">
+      <c r="B1073" s="10"/>
+      <c r="C1073" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1073" s="17" t="s">
+      <c r="D1073" s="11" t="s">
         <v>449</v>
       </c>
-      <c r="E1073" s="17"/>
-      <c r="F1073" s="17"/>
+      <c r="E1073" s="11"/>
+      <c r="F1073" s="11"/>
     </row>
     <row r="1074" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1074" s="13">
+      <c r="A1074" s="2">
         <v>46308</v>
       </c>
-      <c r="B1074" s="14"/>
-      <c r="C1074" s="15" t="s">
+      <c r="B1074" s="10"/>
+      <c r="C1074" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1074" s="16" t="s">
+      <c r="D1074" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="E1074" s="16"/>
-      <c r="F1074" s="16"/>
+      <c r="E1074" s="12"/>
+      <c r="F1074" s="12"/>
     </row>
     <row r="1075" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1075" s="13">
+      <c r="A1075" s="2">
         <v>46308</v>
       </c>
-      <c r="B1075" s="14">
+      <c r="B1075" s="10">
         <v>0.4909722222222222</v>
       </c>
-      <c r="C1075" s="15" t="s">
+      <c r="C1075" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1075" s="16" t="s">
+      <c r="D1075" s="12" t="s">
         <v>451</v>
       </c>
-      <c r="E1075" s="16"/>
-      <c r="F1075" s="16"/>
+      <c r="E1075" s="12"/>
+      <c r="F1075" s="12"/>
     </row>
     <row r="1076" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1076" s="13">
+      <c r="A1076" s="2">
         <v>46308</v>
       </c>
-      <c r="B1076" s="14">
+      <c r="B1076" s="10">
         <v>0.49305555555555558</v>
       </c>
-      <c r="C1076" s="15" t="s">
+      <c r="C1076" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1076" s="16" t="s">
+      <c r="D1076" s="12" t="s">
         <v>362</v>
       </c>
-      <c r="E1076" s="16"/>
-      <c r="F1076" s="16"/>
+      <c r="E1076" s="12"/>
+      <c r="F1076" s="12"/>
     </row>
     <row r="1077" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1077" s="13">
+      <c r="A1077" s="2">
         <v>46308</v>
       </c>
-      <c r="B1077" s="14">
+      <c r="B1077" s="10">
         <v>0.57638888888888884</v>
       </c>
-      <c r="C1077" s="15" t="s">
+      <c r="C1077" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1077" s="16" t="s">
+      <c r="D1077" s="12" t="s">
         <v>379</v>
       </c>
-      <c r="E1077" s="16"/>
-      <c r="F1077" s="16"/>
+      <c r="E1077" s="12"/>
+      <c r="F1077" s="12"/>
     </row>
     <row r="1078" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1078" s="13">
+      <c r="A1078" s="2">
         <v>46308</v>
       </c>
-      <c r="B1078" s="14"/>
-      <c r="C1078" s="15" t="s">
+      <c r="B1078" s="10"/>
+      <c r="C1078" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1078" s="16" t="s">
+      <c r="D1078" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="E1078" s="16"/>
-      <c r="F1078" s="16"/>
+      <c r="E1078" s="12"/>
+      <c r="F1078" s="12"/>
     </row>
     <row r="1079" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1079" s="15"/>
-      <c r="B1079" s="15"/>
-      <c r="C1079" s="15"/>
-      <c r="D1079" s="15"/>
-      <c r="E1079" s="15"/>
-      <c r="F1079" s="15"/>
+      <c r="A1079" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1079" s="10">
+        <v>0.375</v>
+      </c>
+      <c r="C1079" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1079" s="8" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="1080" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1080" s="15"/>
-      <c r="B1080" s="15"/>
-      <c r="C1080" s="15"/>
-      <c r="D1080" s="15"/>
-      <c r="E1080" s="15"/>
-      <c r="F1080" s="15"/>
+      <c r="A1080" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1080" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="C1080" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1080" s="8" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="1081" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1081" s="15"/>
-      <c r="B1081" s="15"/>
-      <c r="C1081" s="15"/>
-      <c r="D1081" s="15"/>
-      <c r="E1081" s="15"/>
-      <c r="F1081" s="15"/>
+      <c r="A1081" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1081" s="10">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1081" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1081" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1082" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1082" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="C1082" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1082" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1083" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1083" s="10">
+        <v>0.375</v>
+      </c>
+      <c r="C1083" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1083" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1084" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1084" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="C1084" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1084" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1085" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1085" s="10">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1085" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1085" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1086" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1086" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="C1086" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1086" s="8" t="s">
+        <v>109</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="D987:F987"/>
-    <mergeCell ref="D988:F988"/>
-    <mergeCell ref="D981:F981"/>
-    <mergeCell ref="D982:F982"/>
-    <mergeCell ref="D983:F983"/>
-    <mergeCell ref="D984:F984"/>
-    <mergeCell ref="D985:F985"/>
-    <mergeCell ref="D986:F986"/>
+    <mergeCell ref="D1078:F1078"/>
+    <mergeCell ref="D1072:F1072"/>
+    <mergeCell ref="D1070:F1070"/>
+    <mergeCell ref="D1071:F1071"/>
+    <mergeCell ref="D1077:F1077"/>
+    <mergeCell ref="D1074:F1074"/>
+    <mergeCell ref="D1075:F1075"/>
+    <mergeCell ref="D1076:F1076"/>
+    <mergeCell ref="D1069:F1069"/>
+    <mergeCell ref="D1066:F1066"/>
+    <mergeCell ref="D1067:F1067"/>
+    <mergeCell ref="D1052:F1052"/>
+    <mergeCell ref="D1053:F1053"/>
+    <mergeCell ref="D1054:F1054"/>
+    <mergeCell ref="D1055:F1055"/>
+    <mergeCell ref="D1056:F1056"/>
+    <mergeCell ref="D1057:F1057"/>
+    <mergeCell ref="D1058:F1058"/>
+    <mergeCell ref="D1059:F1059"/>
+    <mergeCell ref="D1060:F1060"/>
+    <mergeCell ref="D1061:F1061"/>
+    <mergeCell ref="D1049:F1049"/>
+    <mergeCell ref="D1050:F1050"/>
+    <mergeCell ref="D1051:F1051"/>
+    <mergeCell ref="D1065:F1065"/>
+    <mergeCell ref="D1068:F1068"/>
+    <mergeCell ref="D977:F977"/>
+    <mergeCell ref="D978:F978"/>
+    <mergeCell ref="D979:F979"/>
+    <mergeCell ref="D1047:F1047"/>
+    <mergeCell ref="D1048:F1048"/>
     <mergeCell ref="D1064:F1064"/>
     <mergeCell ref="D1062:F1062"/>
     <mergeCell ref="D1063:F1063"/>
@@ -17189,37 +17289,14 @@
     <mergeCell ref="D974:F974"/>
     <mergeCell ref="D975:F975"/>
     <mergeCell ref="D976:F976"/>
-    <mergeCell ref="D977:F977"/>
-    <mergeCell ref="D978:F978"/>
-    <mergeCell ref="D979:F979"/>
-    <mergeCell ref="D1047:F1047"/>
-    <mergeCell ref="D1048:F1048"/>
-    <mergeCell ref="D1049:F1049"/>
-    <mergeCell ref="D1050:F1050"/>
-    <mergeCell ref="D1051:F1051"/>
-    <mergeCell ref="D1065:F1065"/>
-    <mergeCell ref="D1068:F1068"/>
-    <mergeCell ref="D1069:F1069"/>
-    <mergeCell ref="D1066:F1066"/>
-    <mergeCell ref="D1067:F1067"/>
-    <mergeCell ref="D1052:F1052"/>
-    <mergeCell ref="D1053:F1053"/>
-    <mergeCell ref="D1054:F1054"/>
-    <mergeCell ref="D1055:F1055"/>
-    <mergeCell ref="D1056:F1056"/>
-    <mergeCell ref="D1072:F1072"/>
-    <mergeCell ref="D1070:F1070"/>
-    <mergeCell ref="D1071:F1071"/>
-    <mergeCell ref="D1077:F1077"/>
-    <mergeCell ref="D1074:F1074"/>
-    <mergeCell ref="D1075:F1075"/>
-    <mergeCell ref="D1076:F1076"/>
-    <mergeCell ref="D1057:F1057"/>
-    <mergeCell ref="D1058:F1058"/>
-    <mergeCell ref="D1059:F1059"/>
-    <mergeCell ref="D1060:F1060"/>
-    <mergeCell ref="D1061:F1061"/>
-    <mergeCell ref="D1078:F1078"/>
+    <mergeCell ref="D987:F987"/>
+    <mergeCell ref="D988:F988"/>
+    <mergeCell ref="D981:F981"/>
+    <mergeCell ref="D982:F982"/>
+    <mergeCell ref="D983:F983"/>
+    <mergeCell ref="D984:F984"/>
+    <mergeCell ref="D985:F985"/>
+    <mergeCell ref="D986:F986"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD059BA-5836-43CD-B6EC-E5090BB6497C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{928B58FD-BC95-4C41-8869-9D2CDDFEC8F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2174" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2196" uniqueCount="458">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1754,6 +1754,30 @@
   </si>
   <si>
     <t>climb down</t>
+  </si>
+  <si>
+    <t>push on C01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait C01 team</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sail to A06</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>push on A06</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>climb down</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A06</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1846,7 +1870,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1880,6 +1904,15 @@
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal 2" xfId="1" xr:uid="{71AF191C-2467-4F76-8A53-CA6D53E4DF10}"/>
@@ -2165,7 +2198,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1086"/>
+  <dimension ref="A1:I1098"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.296875" style="1" bestFit="1" customWidth="1"/>
@@ -17038,7 +17071,7 @@
       <c r="E1072" s="12"/>
       <c r="F1072" s="12"/>
     </row>
-    <row r="1073" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1073" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1073" s="2">
         <v>46308</v>
       </c>
@@ -17052,7 +17085,7 @@
       <c r="E1073" s="11"/>
       <c r="F1073" s="11"/>
     </row>
-    <row r="1074" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1074" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1074" s="2">
         <v>46308</v>
       </c>
@@ -17066,7 +17099,7 @@
       <c r="E1074" s="12"/>
       <c r="F1074" s="12"/>
     </row>
-    <row r="1075" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1075" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1075" s="2">
         <v>46308</v>
       </c>
@@ -17082,7 +17115,7 @@
       <c r="E1075" s="12"/>
       <c r="F1075" s="12"/>
     </row>
-    <row r="1076" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1076" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1076" s="2">
         <v>46308</v>
       </c>
@@ -17098,7 +17131,7 @@
       <c r="E1076" s="12"/>
       <c r="F1076" s="12"/>
     </row>
-    <row r="1077" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1077" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1077" s="2">
         <v>46308</v>
       </c>
@@ -17114,7 +17147,7 @@
       <c r="E1077" s="12"/>
       <c r="F1077" s="12"/>
     </row>
-    <row r="1078" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1078" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1078" s="2">
         <v>46308</v>
       </c>
@@ -17128,7 +17161,7 @@
       <c r="E1078" s="12"/>
       <c r="F1078" s="12"/>
     </row>
-    <row r="1079" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1079" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1079" s="2">
         <v>46309</v>
       </c>
@@ -17142,7 +17175,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="1080" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1080" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1080" s="2">
         <v>46309</v>
       </c>
@@ -17156,100 +17189,368 @@
         <v>108</v>
       </c>
     </row>
-    <row r="1081" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1081" s="2">
+    <row r="1081" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1081" s="13">
         <v>46309</v>
       </c>
-      <c r="B1081" s="10">
+      <c r="B1081" s="14">
         <v>0.54166666666666663</v>
       </c>
-      <c r="C1081" s="1" t="s">
+      <c r="C1081" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="D1081" s="8" t="s">
+      <c r="D1081" s="16" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="1082" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1082" s="2">
+      <c r="E1081" s="15"/>
+      <c r="F1081" s="15"/>
+      <c r="G1081" s="17"/>
+      <c r="H1081" s="17"/>
+      <c r="I1081" s="17"/>
+    </row>
+    <row r="1082" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1082" s="13">
         <v>46309</v>
       </c>
-      <c r="B1082" s="10">
+      <c r="B1082" s="14">
         <v>0.75</v>
       </c>
-      <c r="C1082" s="1" t="s">
+      <c r="C1082" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="D1082" s="8" t="s">
+      <c r="D1082" s="16" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="1083" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1083" s="2">
+      <c r="E1082" s="15"/>
+      <c r="F1082" s="15"/>
+      <c r="G1082" s="17"/>
+      <c r="H1082" s="17"/>
+      <c r="I1082" s="17"/>
+    </row>
+    <row r="1083" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1083" s="13">
         <v>46310</v>
       </c>
-      <c r="B1083" s="10">
+      <c r="B1083" s="14">
         <v>0.375</v>
       </c>
-      <c r="C1083" s="1" t="s">
+      <c r="C1083" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="D1083" s="8" t="s">
+      <c r="D1083" s="16" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="1084" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1084" s="2">
+      <c r="E1083" s="15"/>
+      <c r="F1083" s="15"/>
+      <c r="G1083" s="17"/>
+      <c r="H1083" s="17"/>
+      <c r="I1083" s="17"/>
+    </row>
+    <row r="1084" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1084" s="13">
         <v>46310</v>
       </c>
-      <c r="B1084" s="10">
+      <c r="B1084" s="14">
         <v>0.5</v>
       </c>
-      <c r="C1084" s="1" t="s">
+      <c r="C1084" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="D1084" s="8" t="s">
+      <c r="D1084" s="16" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="1085" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1085" s="2">
+      <c r="E1084" s="15"/>
+      <c r="F1084" s="15"/>
+      <c r="G1084" s="17"/>
+      <c r="H1084" s="17"/>
+      <c r="I1084" s="17"/>
+    </row>
+    <row r="1085" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1085" s="13">
         <v>46310</v>
       </c>
-      <c r="B1085" s="10">
+      <c r="B1085" s="14">
         <v>0.54166666666666663</v>
       </c>
-      <c r="C1085" s="1" t="s">
+      <c r="C1085" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="D1085" s="8" t="s">
+      <c r="D1085" s="16" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="1086" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1086" s="2">
+      <c r="E1085" s="15"/>
+      <c r="F1085" s="15"/>
+      <c r="G1085" s="17"/>
+      <c r="H1085" s="17"/>
+      <c r="I1085" s="17"/>
+    </row>
+    <row r="1086" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1086" s="13">
         <v>46310</v>
       </c>
-      <c r="B1086" s="10">
+      <c r="B1086" s="14">
         <v>0.75</v>
       </c>
-      <c r="C1086" s="1" t="s">
+      <c r="C1086" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="D1086" s="8" t="s">
+      <c r="D1086" s="16" t="s">
         <v>109</v>
       </c>
+      <c r="E1086" s="15"/>
+      <c r="F1086" s="15"/>
+      <c r="G1086" s="17"/>
+      <c r="H1086" s="17"/>
+      <c r="I1086" s="17"/>
+    </row>
+    <row r="1087" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1087" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1087" s="14">
+        <v>0.2590277777777778</v>
+      </c>
+      <c r="C1087" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="D1087" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="E1087" s="16"/>
+      <c r="F1087" s="16"/>
+      <c r="G1087" s="17"/>
+      <c r="H1087" s="17"/>
+      <c r="I1087" s="17"/>
+    </row>
+    <row r="1088" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1088" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1088" s="14">
+        <v>0.35694444444444445</v>
+      </c>
+      <c r="C1088" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="D1088" s="16" t="s">
+        <v>452</v>
+      </c>
+      <c r="E1088" s="16"/>
+      <c r="F1088" s="16"/>
+      <c r="G1088" s="17"/>
+      <c r="H1088" s="17"/>
+      <c r="I1088" s="17"/>
+    </row>
+    <row r="1089" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1089" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1089" s="14"/>
+      <c r="C1089" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="D1089" s="16" t="s">
+        <v>453</v>
+      </c>
+      <c r="E1089" s="16"/>
+      <c r="F1089" s="16"/>
+      <c r="G1089" s="17"/>
+      <c r="H1089" s="17"/>
+      <c r="I1089" s="17"/>
+    </row>
+    <row r="1090" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1090" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1090" s="14">
+        <v>0.37847222222222221</v>
+      </c>
+      <c r="C1090" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="D1090" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="E1090" s="16"/>
+      <c r="F1090" s="16"/>
+      <c r="G1090" s="17"/>
+      <c r="H1090" s="17"/>
+      <c r="I1090" s="17"/>
+    </row>
+    <row r="1091" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1091" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1091" s="14">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="C1091" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="D1091" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="E1091" s="16"/>
+      <c r="F1091" s="16"/>
+      <c r="G1091" s="17"/>
+      <c r="H1091" s="17"/>
+      <c r="I1091" s="17"/>
+    </row>
+    <row r="1092" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1092" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1092" s="14"/>
+      <c r="C1092" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="D1092" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="E1092" s="16"/>
+      <c r="F1092" s="16"/>
+      <c r="G1092" s="17"/>
+      <c r="H1092" s="17"/>
+      <c r="I1092" s="17"/>
+    </row>
+    <row r="1093" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1093" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1093" s="14"/>
+      <c r="C1093" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="D1093" s="16" t="s">
+        <v>456</v>
+      </c>
+      <c r="E1093" s="16"/>
+      <c r="F1093" s="16"/>
+      <c r="G1093" s="17"/>
+      <c r="H1093" s="17"/>
+      <c r="I1093" s="17"/>
+    </row>
+    <row r="1094" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1094" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1094" s="14">
+        <v>0.4201388888888889</v>
+      </c>
+      <c r="C1094" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="D1094" s="16" t="s">
+        <v>453</v>
+      </c>
+      <c r="E1094" s="16"/>
+      <c r="F1094" s="16"/>
+      <c r="G1094" s="17"/>
+      <c r="H1094" s="17"/>
+      <c r="I1094" s="17"/>
+    </row>
+    <row r="1095" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1095" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1095" s="14">
+        <v>0.49305555555555558</v>
+      </c>
+      <c r="C1095" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="D1095" s="16" t="s">
+        <v>394</v>
+      </c>
+      <c r="E1095" s="16"/>
+      <c r="F1095" s="16"/>
+      <c r="G1095" s="17"/>
+      <c r="H1095" s="17"/>
+      <c r="I1095" s="17"/>
+    </row>
+    <row r="1096" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1096" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1096" s="14">
+        <v>0.59375</v>
+      </c>
+      <c r="C1096" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="D1096" s="16" t="s">
+        <v>379</v>
+      </c>
+      <c r="E1096" s="16"/>
+      <c r="F1096" s="16"/>
+      <c r="G1096" s="17"/>
+      <c r="H1096" s="17"/>
+      <c r="I1096" s="17"/>
+    </row>
+    <row r="1097" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1097" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1097" s="14"/>
+      <c r="C1097" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="D1097" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1097" s="16"/>
+      <c r="F1097" s="16"/>
+      <c r="G1097" s="17"/>
+      <c r="H1097" s="17"/>
+      <c r="I1097" s="17"/>
+    </row>
+    <row r="1098" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1098" s="15"/>
+      <c r="B1098" s="15"/>
+      <c r="C1098" s="15"/>
+      <c r="D1098" s="15"/>
+      <c r="E1098" s="15"/>
+      <c r="F1098" s="15"/>
+      <c r="G1098" s="17"/>
+      <c r="H1098" s="17"/>
+      <c r="I1098" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="D1078:F1078"/>
-    <mergeCell ref="D1072:F1072"/>
-    <mergeCell ref="D1070:F1070"/>
-    <mergeCell ref="D1071:F1071"/>
-    <mergeCell ref="D1077:F1077"/>
-    <mergeCell ref="D1074:F1074"/>
-    <mergeCell ref="D1075:F1075"/>
-    <mergeCell ref="D1076:F1076"/>
+    <mergeCell ref="D965:F965"/>
+    <mergeCell ref="D966:F966"/>
+    <mergeCell ref="D967:F967"/>
+    <mergeCell ref="D968:F968"/>
+    <mergeCell ref="D980:F980"/>
+    <mergeCell ref="D969:F969"/>
+    <mergeCell ref="D970:F970"/>
+    <mergeCell ref="D971:F971"/>
+    <mergeCell ref="D972:F972"/>
+    <mergeCell ref="D973:F973"/>
+    <mergeCell ref="D974:F974"/>
+    <mergeCell ref="D975:F975"/>
+    <mergeCell ref="D976:F976"/>
+    <mergeCell ref="D977:F977"/>
+    <mergeCell ref="D978:F978"/>
+    <mergeCell ref="D979:F979"/>
+    <mergeCell ref="D1047:F1047"/>
+    <mergeCell ref="D1048:F1048"/>
+    <mergeCell ref="D987:F987"/>
+    <mergeCell ref="D988:F988"/>
+    <mergeCell ref="D981:F981"/>
+    <mergeCell ref="D982:F982"/>
+    <mergeCell ref="D983:F983"/>
+    <mergeCell ref="D984:F984"/>
+    <mergeCell ref="D985:F985"/>
+    <mergeCell ref="D986:F986"/>
+    <mergeCell ref="D1049:F1049"/>
+    <mergeCell ref="D1050:F1050"/>
+    <mergeCell ref="D1051:F1051"/>
+    <mergeCell ref="D1065:F1065"/>
+    <mergeCell ref="D1068:F1068"/>
+    <mergeCell ref="D1064:F1064"/>
+    <mergeCell ref="D1062:F1062"/>
+    <mergeCell ref="D1063:F1063"/>
     <mergeCell ref="D1069:F1069"/>
     <mergeCell ref="D1066:F1066"/>
     <mergeCell ref="D1067:F1067"/>
@@ -17263,40 +17564,14 @@
     <mergeCell ref="D1059:F1059"/>
     <mergeCell ref="D1060:F1060"/>
     <mergeCell ref="D1061:F1061"/>
-    <mergeCell ref="D1049:F1049"/>
-    <mergeCell ref="D1050:F1050"/>
-    <mergeCell ref="D1051:F1051"/>
-    <mergeCell ref="D1065:F1065"/>
-    <mergeCell ref="D1068:F1068"/>
-    <mergeCell ref="D977:F977"/>
-    <mergeCell ref="D978:F978"/>
-    <mergeCell ref="D979:F979"/>
-    <mergeCell ref="D1047:F1047"/>
-    <mergeCell ref="D1048:F1048"/>
-    <mergeCell ref="D1064:F1064"/>
-    <mergeCell ref="D1062:F1062"/>
-    <mergeCell ref="D1063:F1063"/>
-    <mergeCell ref="D965:F965"/>
-    <mergeCell ref="D966:F966"/>
-    <mergeCell ref="D967:F967"/>
-    <mergeCell ref="D968:F968"/>
-    <mergeCell ref="D980:F980"/>
-    <mergeCell ref="D969:F969"/>
-    <mergeCell ref="D970:F970"/>
-    <mergeCell ref="D971:F971"/>
-    <mergeCell ref="D972:F972"/>
-    <mergeCell ref="D973:F973"/>
-    <mergeCell ref="D974:F974"/>
-    <mergeCell ref="D975:F975"/>
-    <mergeCell ref="D976:F976"/>
-    <mergeCell ref="D987:F987"/>
-    <mergeCell ref="D988:F988"/>
-    <mergeCell ref="D981:F981"/>
-    <mergeCell ref="D982:F982"/>
-    <mergeCell ref="D983:F983"/>
-    <mergeCell ref="D984:F984"/>
-    <mergeCell ref="D985:F985"/>
-    <mergeCell ref="D986:F986"/>
+    <mergeCell ref="D1078:F1078"/>
+    <mergeCell ref="D1072:F1072"/>
+    <mergeCell ref="D1070:F1070"/>
+    <mergeCell ref="D1071:F1071"/>
+    <mergeCell ref="D1077:F1077"/>
+    <mergeCell ref="D1074:F1074"/>
+    <mergeCell ref="D1075:F1075"/>
+    <mergeCell ref="D1076:F1076"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{928B58FD-BC95-4C41-8869-9D2CDDFEC8F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{471E2059-1334-4656-9894-0EE881BC83D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2196" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2262" uniqueCount="484">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1777,6 +1777,93 @@
   </si>
   <si>
     <t>A06</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>C01</t>
+  </si>
+  <si>
+    <t>TBT</t>
+  </si>
+  <si>
+    <t>Port departure</t>
+  </si>
+  <si>
+    <t>to F2</t>
+  </si>
+  <si>
+    <t>First push on</t>
+  </si>
+  <si>
+    <t>C01 push-on and climb up</t>
+  </si>
+  <si>
+    <t>Climb up</t>
+  </si>
+  <si>
+    <t>Lifting bags</t>
+  </si>
+  <si>
+    <t>Settting up</t>
+  </si>
+  <si>
+    <t>Leg B: MGM, CPM</t>
+  </si>
+  <si>
+    <t>Recovery</t>
+  </si>
+  <si>
+    <t>Data transfer, Washdown, Housekeep</t>
+  </si>
+  <si>
+    <t>Climb down</t>
+  </si>
+  <si>
+    <t>C01 Climb down and push-off</t>
+  </si>
+  <si>
+    <t>Last push off</t>
+  </si>
+  <si>
+    <t>to TC port</t>
+  </si>
+  <si>
+    <t>Port arrival</t>
+  </si>
+  <si>
+    <t>push on D04</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait D04 team/Unable to climb the tower due to an SRL issue.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sail to D06</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>set up AIB-009/ current meter</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>no power supply on TP</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>strong current, wait on weather</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>climb down D06</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sail to A01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait A01 team(Michael)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2198,7 +2285,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1098"/>
+  <dimension ref="A1:I1132"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.296875" style="1" bestFit="1" customWidth="1"/>
@@ -17071,7 +17158,7 @@
       <c r="E1072" s="12"/>
       <c r="F1072" s="12"/>
     </row>
-    <row r="1073" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1073" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1073" s="2">
         <v>46308</v>
       </c>
@@ -17085,7 +17172,7 @@
       <c r="E1073" s="11"/>
       <c r="F1073" s="11"/>
     </row>
-    <row r="1074" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1074" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1074" s="2">
         <v>46308</v>
       </c>
@@ -17099,7 +17186,7 @@
       <c r="E1074" s="12"/>
       <c r="F1074" s="12"/>
     </row>
-    <row r="1075" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1075" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1075" s="2">
         <v>46308</v>
       </c>
@@ -17115,7 +17202,7 @@
       <c r="E1075" s="12"/>
       <c r="F1075" s="12"/>
     </row>
-    <row r="1076" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1076" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1076" s="2">
         <v>46308</v>
       </c>
@@ -17131,7 +17218,7 @@
       <c r="E1076" s="12"/>
       <c r="F1076" s="12"/>
     </row>
-    <row r="1077" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1077" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1077" s="2">
         <v>46308</v>
       </c>
@@ -17147,7 +17234,7 @@
       <c r="E1077" s="12"/>
       <c r="F1077" s="12"/>
     </row>
-    <row r="1078" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1078" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1078" s="2">
         <v>46308</v>
       </c>
@@ -17161,7 +17248,7 @@
       <c r="E1078" s="12"/>
       <c r="F1078" s="12"/>
     </row>
-    <row r="1079" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1079" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1079" s="2">
         <v>46309</v>
       </c>
@@ -17175,7 +17262,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="1080" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1080" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1080" s="2">
         <v>46309</v>
       </c>
@@ -17189,303 +17276,243 @@
         <v>108</v>
       </c>
     </row>
-    <row r="1081" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1081" s="13">
+    <row r="1081" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1081" s="2">
         <v>46309</v>
       </c>
-      <c r="B1081" s="14">
+      <c r="B1081" s="10">
         <v>0.54166666666666663</v>
       </c>
-      <c r="C1081" s="15" t="s">
+      <c r="C1081" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D1081" s="16" t="s">
+      <c r="D1081" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="E1081" s="15"/>
-      <c r="F1081" s="15"/>
-      <c r="G1081" s="17"/>
-      <c r="H1081" s="17"/>
-      <c r="I1081" s="17"/>
-    </row>
-    <row r="1082" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1082" s="13">
+    </row>
+    <row r="1082" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1082" s="2">
         <v>46309</v>
       </c>
-      <c r="B1082" s="14">
+      <c r="B1082" s="10">
         <v>0.75</v>
       </c>
-      <c r="C1082" s="15" t="s">
+      <c r="C1082" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D1082" s="16" t="s">
+      <c r="D1082" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="E1082" s="15"/>
-      <c r="F1082" s="15"/>
-      <c r="G1082" s="17"/>
-      <c r="H1082" s="17"/>
-      <c r="I1082" s="17"/>
-    </row>
-    <row r="1083" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1083" s="13">
+    </row>
+    <row r="1083" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1083" s="2">
         <v>46310</v>
       </c>
-      <c r="B1083" s="14">
+      <c r="B1083" s="10">
         <v>0.375</v>
       </c>
-      <c r="C1083" s="15" t="s">
+      <c r="C1083" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D1083" s="16" t="s">
+      <c r="D1083" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="E1083" s="15"/>
-      <c r="F1083" s="15"/>
-      <c r="G1083" s="17"/>
-      <c r="H1083" s="17"/>
-      <c r="I1083" s="17"/>
-    </row>
-    <row r="1084" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1084" s="13">
+    </row>
+    <row r="1084" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1084" s="2">
         <v>46310</v>
       </c>
-      <c r="B1084" s="14">
+      <c r="B1084" s="10">
         <v>0.5</v>
       </c>
-      <c r="C1084" s="15" t="s">
+      <c r="C1084" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D1084" s="16" t="s">
+      <c r="D1084" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="E1084" s="15"/>
-      <c r="F1084" s="15"/>
-      <c r="G1084" s="17"/>
-      <c r="H1084" s="17"/>
-      <c r="I1084" s="17"/>
-    </row>
-    <row r="1085" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1085" s="13">
+    </row>
+    <row r="1085" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1085" s="2">
         <v>46310</v>
       </c>
-      <c r="B1085" s="14">
+      <c r="B1085" s="10">
         <v>0.54166666666666663</v>
       </c>
-      <c r="C1085" s="15" t="s">
+      <c r="C1085" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D1085" s="16" t="s">
+      <c r="D1085" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="E1085" s="15"/>
-      <c r="F1085" s="15"/>
-      <c r="G1085" s="17"/>
-      <c r="H1085" s="17"/>
-      <c r="I1085" s="17"/>
-    </row>
-    <row r="1086" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1086" s="13">
+    </row>
+    <row r="1086" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1086" s="2">
         <v>46310</v>
       </c>
-      <c r="B1086" s="14">
+      <c r="B1086" s="10">
         <v>0.75</v>
       </c>
-      <c r="C1086" s="15" t="s">
+      <c r="C1086" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D1086" s="16" t="s">
+      <c r="D1086" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="E1086" s="15"/>
-      <c r="F1086" s="15"/>
-      <c r="G1086" s="17"/>
-      <c r="H1086" s="17"/>
-      <c r="I1086" s="17"/>
-    </row>
-    <row r="1087" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1087" s="13">
+    </row>
+    <row r="1087" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1087" s="2">
         <v>46311</v>
       </c>
-      <c r="B1087" s="14">
+      <c r="B1087" s="10">
         <v>0.2590277777777778</v>
       </c>
-      <c r="C1087" s="15" t="s">
+      <c r="C1087" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="D1087" s="16" t="s">
+      <c r="D1087" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="E1087" s="16"/>
-      <c r="F1087" s="16"/>
-      <c r="G1087" s="17"/>
-      <c r="H1087" s="17"/>
-      <c r="I1087" s="17"/>
-    </row>
-    <row r="1088" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1088" s="13">
+      <c r="E1087" s="8"/>
+      <c r="F1087" s="8"/>
+    </row>
+    <row r="1088" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1088" s="2">
         <v>46311</v>
       </c>
-      <c r="B1088" s="14">
+      <c r="B1088" s="10">
         <v>0.35694444444444445</v>
       </c>
-      <c r="C1088" s="15" t="s">
+      <c r="C1088" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="D1088" s="16" t="s">
+      <c r="D1088" s="8" t="s">
         <v>452</v>
       </c>
-      <c r="E1088" s="16"/>
-      <c r="F1088" s="16"/>
-      <c r="G1088" s="17"/>
-      <c r="H1088" s="17"/>
-      <c r="I1088" s="17"/>
+      <c r="E1088" s="8"/>
+      <c r="F1088" s="8"/>
     </row>
     <row r="1089" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1089" s="13">
+      <c r="A1089" s="2">
         <v>46311</v>
       </c>
-      <c r="B1089" s="14"/>
-      <c r="C1089" s="15" t="s">
+      <c r="B1089" s="10"/>
+      <c r="C1089" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="D1089" s="16" t="s">
+      <c r="D1089" s="8" t="s">
         <v>453</v>
       </c>
-      <c r="E1089" s="16"/>
-      <c r="F1089" s="16"/>
-      <c r="G1089" s="17"/>
-      <c r="H1089" s="17"/>
-      <c r="I1089" s="17"/>
+      <c r="E1089" s="8"/>
+      <c r="F1089" s="8"/>
     </row>
     <row r="1090" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1090" s="13">
+      <c r="A1090" s="2">
         <v>46311</v>
       </c>
-      <c r="B1090" s="14">
+      <c r="B1090" s="10">
         <v>0.37847222222222221</v>
       </c>
-      <c r="C1090" s="15" t="s">
+      <c r="C1090" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="D1090" s="16" t="s">
+      <c r="D1090" s="8" t="s">
         <v>454</v>
       </c>
-      <c r="E1090" s="16"/>
-      <c r="F1090" s="16"/>
-      <c r="G1090" s="17"/>
-      <c r="H1090" s="17"/>
-      <c r="I1090" s="17"/>
+      <c r="E1090" s="8"/>
+      <c r="F1090" s="8"/>
     </row>
     <row r="1091" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1091" s="13">
+      <c r="A1091" s="2">
         <v>46311</v>
       </c>
-      <c r="B1091" s="14">
+      <c r="B1091" s="10">
         <v>0.3923611111111111</v>
       </c>
-      <c r="C1091" s="15" t="s">
+      <c r="C1091" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="D1091" s="16" t="s">
+      <c r="D1091" s="8" t="s">
         <v>455</v>
       </c>
-      <c r="E1091" s="16"/>
-      <c r="F1091" s="16"/>
-      <c r="G1091" s="17"/>
-      <c r="H1091" s="17"/>
-      <c r="I1091" s="17"/>
+      <c r="E1091" s="8"/>
+      <c r="F1091" s="8"/>
     </row>
     <row r="1092" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1092" s="13">
+      <c r="A1092" s="2">
         <v>46311</v>
       </c>
-      <c r="B1092" s="14"/>
-      <c r="C1092" s="15" t="s">
+      <c r="B1092" s="10"/>
+      <c r="C1092" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="D1092" s="16" t="s">
+      <c r="D1092" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="E1092" s="16"/>
-      <c r="F1092" s="16"/>
-      <c r="G1092" s="17"/>
-      <c r="H1092" s="17"/>
-      <c r="I1092" s="17"/>
+      <c r="E1092" s="8"/>
+      <c r="F1092" s="8"/>
     </row>
     <row r="1093" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1093" s="13">
+      <c r="A1093" s="2">
         <v>46311</v>
       </c>
-      <c r="B1093" s="14"/>
-      <c r="C1093" s="15" t="s">
+      <c r="B1093" s="10"/>
+      <c r="C1093" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="D1093" s="16" t="s">
+      <c r="D1093" s="8" t="s">
         <v>456</v>
       </c>
-      <c r="E1093" s="16"/>
-      <c r="F1093" s="16"/>
-      <c r="G1093" s="17"/>
-      <c r="H1093" s="17"/>
-      <c r="I1093" s="17"/>
+      <c r="E1093" s="8"/>
+      <c r="F1093" s="8"/>
     </row>
     <row r="1094" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1094" s="13">
+      <c r="A1094" s="2">
         <v>46311</v>
       </c>
-      <c r="B1094" s="14">
+      <c r="B1094" s="10">
         <v>0.4201388888888889</v>
       </c>
-      <c r="C1094" s="15" t="s">
+      <c r="C1094" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="D1094" s="16" t="s">
+      <c r="D1094" s="8" t="s">
         <v>453</v>
       </c>
-      <c r="E1094" s="16"/>
-      <c r="F1094" s="16"/>
-      <c r="G1094" s="17"/>
-      <c r="H1094" s="17"/>
-      <c r="I1094" s="17"/>
+      <c r="E1094" s="8"/>
+      <c r="F1094" s="8"/>
     </row>
     <row r="1095" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1095" s="13">
+      <c r="A1095" s="2">
         <v>46311</v>
       </c>
-      <c r="B1095" s="14">
+      <c r="B1095" s="10">
         <v>0.49305555555555558</v>
       </c>
-      <c r="C1095" s="15" t="s">
+      <c r="C1095" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="D1095" s="16" t="s">
+      <c r="D1095" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="E1095" s="16"/>
-      <c r="F1095" s="16"/>
-      <c r="G1095" s="17"/>
-      <c r="H1095" s="17"/>
-      <c r="I1095" s="17"/>
+      <c r="E1095" s="8"/>
+      <c r="F1095" s="8"/>
     </row>
     <row r="1096" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1096" s="13">
+      <c r="A1096" s="2">
         <v>46311</v>
       </c>
-      <c r="B1096" s="14">
+      <c r="B1096" s="10">
         <v>0.59375</v>
       </c>
-      <c r="C1096" s="15" t="s">
+      <c r="C1096" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="D1096" s="16" t="s">
+      <c r="D1096" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="E1096" s="16"/>
-      <c r="F1096" s="16"/>
-      <c r="G1096" s="17"/>
-      <c r="H1096" s="17"/>
-      <c r="I1096" s="17"/>
+      <c r="E1096" s="8"/>
+      <c r="F1096" s="8"/>
     </row>
     <row r="1097" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1097" s="13">
@@ -17505,18 +17532,671 @@
       <c r="I1097" s="17"/>
     </row>
     <row r="1098" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1098" s="15"/>
-      <c r="B1098" s="15"/>
-      <c r="C1098" s="15"/>
-      <c r="D1098" s="15"/>
+      <c r="A1098" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1098" s="14">
+        <v>0.25</v>
+      </c>
+      <c r="C1098" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="D1098" s="16" t="s">
+        <v>459</v>
+      </c>
       <c r="E1098" s="15"/>
       <c r="F1098" s="15"/>
       <c r="G1098" s="17"/>
       <c r="H1098" s="17"/>
       <c r="I1098" s="17"/>
     </row>
+    <row r="1099" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1099" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1099" s="14">
+        <v>0.2590277777777778</v>
+      </c>
+      <c r="C1099" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="D1099" s="16" t="s">
+        <v>460</v>
+      </c>
+      <c r="E1099" s="15"/>
+      <c r="F1099" s="15"/>
+      <c r="G1099" s="17"/>
+      <c r="H1099" s="17"/>
+      <c r="I1099" s="17"/>
+    </row>
+    <row r="1100" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1100" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1100" s="14"/>
+      <c r="C1100" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="D1100" s="16" t="s">
+        <v>461</v>
+      </c>
+      <c r="E1100" s="15"/>
+      <c r="F1100" s="15"/>
+      <c r="G1100" s="17"/>
+      <c r="H1100" s="17"/>
+      <c r="I1100" s="17"/>
+    </row>
+    <row r="1101" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1101" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1101" s="14">
+        <v>0.35694444444444445</v>
+      </c>
+      <c r="C1101" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="D1101" s="16" t="s">
+        <v>462</v>
+      </c>
+      <c r="E1101" s="15"/>
+      <c r="F1101" s="15"/>
+      <c r="G1101" s="17"/>
+      <c r="H1101" s="17"/>
+      <c r="I1101" s="17"/>
+    </row>
+    <row r="1102" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1102" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1102" s="14"/>
+      <c r="C1102" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="D1102" s="16" t="s">
+        <v>463</v>
+      </c>
+      <c r="E1102" s="15"/>
+      <c r="F1102" s="15"/>
+      <c r="G1102" s="17"/>
+      <c r="H1102" s="17"/>
+      <c r="I1102" s="17"/>
+    </row>
+    <row r="1103" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1103" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1103" s="14">
+        <v>0.3659722222222222</v>
+      </c>
+      <c r="C1103" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="D1103" s="16" t="s">
+        <v>464</v>
+      </c>
+      <c r="E1103" s="15"/>
+      <c r="F1103" s="15"/>
+      <c r="G1103" s="17"/>
+      <c r="H1103" s="17"/>
+      <c r="I1103" s="17"/>
+    </row>
+    <row r="1104" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1104" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1104" s="14">
+        <v>0.36875000000000002</v>
+      </c>
+      <c r="C1104" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="D1104" s="16" t="s">
+        <v>465</v>
+      </c>
+      <c r="E1104" s="15"/>
+      <c r="F1104" s="15"/>
+      <c r="G1104" s="17"/>
+      <c r="H1104" s="17"/>
+      <c r="I1104" s="17"/>
+    </row>
+    <row r="1105" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1105" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1105" s="14">
+        <v>0.37916666666666665</v>
+      </c>
+      <c r="C1105" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="D1105" s="16" t="s">
+        <v>466</v>
+      </c>
+      <c r="E1105" s="15"/>
+      <c r="F1105" s="15"/>
+      <c r="G1105" s="17"/>
+      <c r="H1105" s="17"/>
+      <c r="I1105" s="17"/>
+    </row>
+    <row r="1106" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1106" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1106" s="14">
+        <v>0.3972222222222222</v>
+      </c>
+      <c r="C1106" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="D1106" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1106" s="15"/>
+      <c r="F1106" s="15"/>
+      <c r="G1106" s="17"/>
+      <c r="H1106" s="17"/>
+      <c r="I1106" s="17"/>
+    </row>
+    <row r="1107" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1107" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1107" s="14"/>
+      <c r="C1107" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="D1107" s="16" t="s">
+        <v>467</v>
+      </c>
+      <c r="E1107" s="15"/>
+      <c r="F1107" s="15"/>
+      <c r="G1107" s="17"/>
+      <c r="H1107" s="17"/>
+      <c r="I1107" s="17"/>
+    </row>
+    <row r="1108" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1108" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1108" s="14">
+        <v>0.44166666666666665</v>
+      </c>
+      <c r="C1108" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="D1108" s="16" t="s">
+        <v>468</v>
+      </c>
+      <c r="E1108" s="15"/>
+      <c r="F1108" s="15"/>
+      <c r="G1108" s="17"/>
+      <c r="H1108" s="17"/>
+      <c r="I1108" s="17"/>
+    </row>
+    <row r="1109" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1109" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1109" s="14"/>
+      <c r="C1109" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="D1109" s="16" t="s">
+        <v>469</v>
+      </c>
+      <c r="E1109" s="15"/>
+      <c r="F1109" s="15"/>
+      <c r="G1109" s="17"/>
+      <c r="H1109" s="17"/>
+      <c r="I1109" s="17"/>
+    </row>
+    <row r="1110" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1110" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1110" s="14">
+        <v>0.48819444444444443</v>
+      </c>
+      <c r="C1110" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="D1110" s="16" t="s">
+        <v>470</v>
+      </c>
+      <c r="E1110" s="15"/>
+      <c r="F1110" s="15"/>
+      <c r="G1110" s="17"/>
+      <c r="H1110" s="17"/>
+      <c r="I1110" s="17"/>
+    </row>
+    <row r="1111" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1111" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1111" s="14"/>
+      <c r="C1111" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="D1111" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="E1111" s="15"/>
+      <c r="F1111" s="15"/>
+      <c r="G1111" s="17"/>
+      <c r="H1111" s="17"/>
+      <c r="I1111" s="17"/>
+    </row>
+    <row r="1112" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1112" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1112" s="14">
+        <v>0.49305555555555558</v>
+      </c>
+      <c r="C1112" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="D1112" s="16" t="s">
+        <v>472</v>
+      </c>
+      <c r="E1112" s="15"/>
+      <c r="F1112" s="15"/>
+      <c r="G1112" s="17"/>
+      <c r="H1112" s="17"/>
+      <c r="I1112" s="17"/>
+    </row>
+    <row r="1113" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1113" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1113" s="14"/>
+      <c r="C1113" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="D1113" s="16" t="s">
+        <v>473</v>
+      </c>
+      <c r="E1113" s="15"/>
+      <c r="F1113" s="15"/>
+      <c r="G1113" s="17"/>
+      <c r="H1113" s="17"/>
+      <c r="I1113" s="17"/>
+    </row>
+    <row r="1114" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1114" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1114" s="14">
+        <v>0.59375</v>
+      </c>
+      <c r="C1114" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="D1114" s="16" t="s">
+        <v>474</v>
+      </c>
+      <c r="E1114" s="15"/>
+      <c r="F1114" s="15"/>
+      <c r="G1114" s="17"/>
+      <c r="H1114" s="17"/>
+      <c r="I1114" s="17"/>
+    </row>
+    <row r="1115" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1115" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B1115" s="14"/>
+      <c r="C1115" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="D1115" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1115" s="15"/>
+      <c r="F1115" s="15"/>
+      <c r="G1115" s="17"/>
+      <c r="H1115" s="17"/>
+      <c r="I1115" s="17"/>
+    </row>
+    <row r="1116" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1116" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1116" s="14">
+        <v>0.28472222222222221</v>
+      </c>
+      <c r="C1116" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1116" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="E1116" s="16"/>
+      <c r="F1116" s="16"/>
+      <c r="G1116" s="17"/>
+      <c r="H1116" s="17"/>
+      <c r="I1116" s="17"/>
+    </row>
+    <row r="1117" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1117" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1117" s="14">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="C1117" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1117" s="16" t="s">
+        <v>475</v>
+      </c>
+      <c r="E1117" s="16"/>
+      <c r="F1117" s="16"/>
+      <c r="G1117" s="17"/>
+      <c r="H1117" s="17"/>
+      <c r="I1117" s="17"/>
+    </row>
+    <row r="1118" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1118" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1118" s="14"/>
+      <c r="C1118" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1118" s="16" t="s">
+        <v>476</v>
+      </c>
+      <c r="E1118" s="16"/>
+      <c r="F1118" s="16"/>
+      <c r="G1118" s="17"/>
+      <c r="H1118" s="17"/>
+      <c r="I1118" s="17"/>
+    </row>
+    <row r="1119" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1119" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1119" s="14">
+        <v>0.37361111111111112</v>
+      </c>
+      <c r="C1119" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1119" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="E1119" s="16"/>
+      <c r="F1119" s="16"/>
+      <c r="G1119" s="17"/>
+      <c r="H1119" s="17"/>
+      <c r="I1119" s="17"/>
+    </row>
+    <row r="1120" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1120" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1120" s="14">
+        <v>0.38055555555555554</v>
+      </c>
+      <c r="C1120" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1120" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="E1120" s="16"/>
+      <c r="F1120" s="16"/>
+      <c r="G1120" s="17"/>
+      <c r="H1120" s="17"/>
+      <c r="I1120" s="17"/>
+    </row>
+    <row r="1121" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1121" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1121" s="14"/>
+      <c r="C1121" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1121" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="E1121" s="16"/>
+      <c r="F1121" s="16"/>
+      <c r="G1121" s="17"/>
+      <c r="H1121" s="17"/>
+      <c r="I1121" s="17"/>
+    </row>
+    <row r="1122" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1122" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1122" s="14"/>
+      <c r="C1122" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1122" s="16" t="s">
+        <v>479</v>
+      </c>
+      <c r="E1122" s="16"/>
+      <c r="F1122" s="16"/>
+      <c r="G1122" s="17"/>
+      <c r="H1122" s="17"/>
+      <c r="I1122" s="17"/>
+    </row>
+    <row r="1123" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1123" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1123" s="14">
+        <v>0.44097222222222221</v>
+      </c>
+      <c r="C1123" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1123" s="16" t="s">
+        <v>480</v>
+      </c>
+      <c r="E1123" s="16"/>
+      <c r="F1123" s="16"/>
+      <c r="G1123" s="17"/>
+      <c r="H1123" s="17"/>
+      <c r="I1123" s="17"/>
+    </row>
+    <row r="1124" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1124" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1124" s="14">
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="C1124" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1124" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1124" s="16"/>
+      <c r="F1124" s="16"/>
+      <c r="G1124" s="17"/>
+      <c r="H1124" s="17"/>
+      <c r="I1124" s="17"/>
+    </row>
+    <row r="1125" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1125" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1125" s="14"/>
+      <c r="C1125" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1125" s="16" t="s">
+        <v>481</v>
+      </c>
+      <c r="E1125" s="16"/>
+      <c r="F1125" s="16"/>
+      <c r="G1125" s="17"/>
+      <c r="H1125" s="17"/>
+      <c r="I1125" s="17"/>
+    </row>
+    <row r="1126" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1126" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1126" s="14">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="C1126" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1126" s="16" t="s">
+        <v>482</v>
+      </c>
+      <c r="E1126" s="16"/>
+      <c r="F1126" s="16"/>
+      <c r="G1126" s="17"/>
+      <c r="H1126" s="17"/>
+      <c r="I1126" s="17"/>
+    </row>
+    <row r="1127" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1127" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1127" s="14">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="C1127" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1127" s="16" t="s">
+        <v>483</v>
+      </c>
+      <c r="E1127" s="16"/>
+      <c r="F1127" s="16"/>
+      <c r="G1127" s="17"/>
+      <c r="H1127" s="17"/>
+      <c r="I1127" s="17"/>
+    </row>
+    <row r="1128" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1128" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1128" s="14">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="C1128" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1128" s="16" t="s">
+        <v>394</v>
+      </c>
+      <c r="E1128" s="16"/>
+      <c r="F1128" s="16"/>
+      <c r="G1128" s="17"/>
+      <c r="H1128" s="17"/>
+      <c r="I1128" s="17"/>
+    </row>
+    <row r="1129" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1129" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1129" s="14">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="C1129" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1129" s="16" t="s">
+        <v>379</v>
+      </c>
+      <c r="E1129" s="16"/>
+      <c r="F1129" s="16"/>
+      <c r="G1129" s="17"/>
+      <c r="H1129" s="17"/>
+      <c r="I1129" s="17"/>
+    </row>
+    <row r="1130" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1130" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1130" s="14"/>
+      <c r="C1130" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1130" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1130" s="16"/>
+      <c r="F1130" s="16"/>
+      <c r="G1130" s="17"/>
+      <c r="H1130" s="17"/>
+      <c r="I1130" s="17"/>
+    </row>
+    <row r="1131" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1131" s="15"/>
+      <c r="B1131" s="15"/>
+      <c r="C1131" s="15"/>
+      <c r="D1131" s="15"/>
+      <c r="E1131" s="15"/>
+      <c r="F1131" s="15"/>
+      <c r="G1131" s="17"/>
+      <c r="H1131" s="17"/>
+      <c r="I1131" s="17"/>
+    </row>
+    <row r="1132" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1132" s="15"/>
+      <c r="B1132" s="15"/>
+      <c r="C1132" s="15"/>
+      <c r="D1132" s="15"/>
+      <c r="E1132" s="15"/>
+      <c r="F1132" s="15"/>
+      <c r="G1132" s="17"/>
+      <c r="H1132" s="17"/>
+      <c r="I1132" s="17"/>
+    </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="D1078:F1078"/>
+    <mergeCell ref="D1072:F1072"/>
+    <mergeCell ref="D1070:F1070"/>
+    <mergeCell ref="D1071:F1071"/>
+    <mergeCell ref="D1077:F1077"/>
+    <mergeCell ref="D1074:F1074"/>
+    <mergeCell ref="D1075:F1075"/>
+    <mergeCell ref="D1076:F1076"/>
+    <mergeCell ref="D1069:F1069"/>
+    <mergeCell ref="D1066:F1066"/>
+    <mergeCell ref="D1067:F1067"/>
+    <mergeCell ref="D1052:F1052"/>
+    <mergeCell ref="D1053:F1053"/>
+    <mergeCell ref="D1054:F1054"/>
+    <mergeCell ref="D1055:F1055"/>
+    <mergeCell ref="D1056:F1056"/>
+    <mergeCell ref="D1057:F1057"/>
+    <mergeCell ref="D1058:F1058"/>
+    <mergeCell ref="D1059:F1059"/>
+    <mergeCell ref="D1060:F1060"/>
+    <mergeCell ref="D1061:F1061"/>
+    <mergeCell ref="D1049:F1049"/>
+    <mergeCell ref="D1050:F1050"/>
+    <mergeCell ref="D1051:F1051"/>
+    <mergeCell ref="D1065:F1065"/>
+    <mergeCell ref="D1068:F1068"/>
+    <mergeCell ref="D1064:F1064"/>
+    <mergeCell ref="D1062:F1062"/>
+    <mergeCell ref="D1063:F1063"/>
+    <mergeCell ref="D1047:F1047"/>
+    <mergeCell ref="D1048:F1048"/>
+    <mergeCell ref="D987:F987"/>
+    <mergeCell ref="D988:F988"/>
+    <mergeCell ref="D981:F981"/>
+    <mergeCell ref="D982:F982"/>
+    <mergeCell ref="D983:F983"/>
+    <mergeCell ref="D984:F984"/>
+    <mergeCell ref="D985:F985"/>
+    <mergeCell ref="D986:F986"/>
     <mergeCell ref="D965:F965"/>
     <mergeCell ref="D966:F966"/>
     <mergeCell ref="D967:F967"/>
@@ -17533,45 +18213,6 @@
     <mergeCell ref="D977:F977"/>
     <mergeCell ref="D978:F978"/>
     <mergeCell ref="D979:F979"/>
-    <mergeCell ref="D1047:F1047"/>
-    <mergeCell ref="D1048:F1048"/>
-    <mergeCell ref="D987:F987"/>
-    <mergeCell ref="D988:F988"/>
-    <mergeCell ref="D981:F981"/>
-    <mergeCell ref="D982:F982"/>
-    <mergeCell ref="D983:F983"/>
-    <mergeCell ref="D984:F984"/>
-    <mergeCell ref="D985:F985"/>
-    <mergeCell ref="D986:F986"/>
-    <mergeCell ref="D1049:F1049"/>
-    <mergeCell ref="D1050:F1050"/>
-    <mergeCell ref="D1051:F1051"/>
-    <mergeCell ref="D1065:F1065"/>
-    <mergeCell ref="D1068:F1068"/>
-    <mergeCell ref="D1064:F1064"/>
-    <mergeCell ref="D1062:F1062"/>
-    <mergeCell ref="D1063:F1063"/>
-    <mergeCell ref="D1069:F1069"/>
-    <mergeCell ref="D1066:F1066"/>
-    <mergeCell ref="D1067:F1067"/>
-    <mergeCell ref="D1052:F1052"/>
-    <mergeCell ref="D1053:F1053"/>
-    <mergeCell ref="D1054:F1054"/>
-    <mergeCell ref="D1055:F1055"/>
-    <mergeCell ref="D1056:F1056"/>
-    <mergeCell ref="D1057:F1057"/>
-    <mergeCell ref="D1058:F1058"/>
-    <mergeCell ref="D1059:F1059"/>
-    <mergeCell ref="D1060:F1060"/>
-    <mergeCell ref="D1061:F1061"/>
-    <mergeCell ref="D1078:F1078"/>
-    <mergeCell ref="D1072:F1072"/>
-    <mergeCell ref="D1070:F1070"/>
-    <mergeCell ref="D1071:F1071"/>
-    <mergeCell ref="D1077:F1077"/>
-    <mergeCell ref="D1074:F1074"/>
-    <mergeCell ref="D1075:F1075"/>
-    <mergeCell ref="D1076:F1076"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{471E2059-1334-4656-9894-0EE881BC83D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{681C5606-2CC6-4DFE-BA31-99B0DC1CA665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2262" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2358" uniqueCount="500">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1864,6 +1864,57 @@
   </si>
   <si>
     <t>wait A01 team(Michael)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Climbing canceled due to SRL issue</t>
+  </si>
+  <si>
+    <t>Push off D04</t>
+  </si>
+  <si>
+    <t>to D06</t>
+  </si>
+  <si>
+    <t>Push on D06</t>
+  </si>
+  <si>
+    <t>wait for D06 team</t>
+  </si>
+  <si>
+    <t>push off D06</t>
+  </si>
+  <si>
+    <t>to D01</t>
+  </si>
+  <si>
+    <t>Push on D01</t>
+  </si>
+  <si>
+    <t>Climb up D01</t>
+  </si>
+  <si>
+    <t>Setup</t>
+  </si>
+  <si>
+    <t>AIB-006</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wait on current</t>
+  </si>
+  <si>
+    <t>Housekeep</t>
+  </si>
+  <si>
+    <t>Push on D04</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D04</t>
+  </si>
+  <si>
+    <t>D01</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1999,7 +2050,9 @@
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal 2" xfId="1" xr:uid="{71AF191C-2467-4F76-8A53-CA6D53E4DF10}"/>
@@ -2285,7 +2338,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1132"/>
+  <dimension ref="A1:F1178"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.296875" style="1" bestFit="1" customWidth="1"/>
@@ -17392,7 +17445,7 @@
       <c r="E1088" s="8"/>
       <c r="F1088" s="8"/>
     </row>
-    <row r="1089" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1089" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1089" s="2">
         <v>46311</v>
       </c>
@@ -17406,7 +17459,7 @@
       <c r="E1089" s="8"/>
       <c r="F1089" s="8"/>
     </row>
-    <row r="1090" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1090" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1090" s="2">
         <v>46311</v>
       </c>
@@ -17422,7 +17475,7 @@
       <c r="E1090" s="8"/>
       <c r="F1090" s="8"/>
     </row>
-    <row r="1091" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1091" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1091" s="2">
         <v>46311</v>
       </c>
@@ -17438,7 +17491,7 @@
       <c r="E1091" s="8"/>
       <c r="F1091" s="8"/>
     </row>
-    <row r="1092" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1092" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1092" s="2">
         <v>46311</v>
       </c>
@@ -17452,7 +17505,7 @@
       <c r="E1092" s="8"/>
       <c r="F1092" s="8"/>
     </row>
-    <row r="1093" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1093" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1093" s="2">
         <v>46311</v>
       </c>
@@ -17466,7 +17519,7 @@
       <c r="E1093" s="8"/>
       <c r="F1093" s="8"/>
     </row>
-    <row r="1094" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1094" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1094" s="2">
         <v>46311</v>
       </c>
@@ -17482,7 +17535,7 @@
       <c r="E1094" s="8"/>
       <c r="F1094" s="8"/>
     </row>
-    <row r="1095" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1095" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1095" s="2">
         <v>46311</v>
       </c>
@@ -17498,7 +17551,7 @@
       <c r="E1095" s="8"/>
       <c r="F1095" s="8"/>
     </row>
-    <row r="1096" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1096" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1096" s="2">
         <v>46311</v>
       </c>
@@ -17514,610 +17567,475 @@
       <c r="E1096" s="8"/>
       <c r="F1096" s="8"/>
     </row>
-    <row r="1097" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1097" s="13">
+    <row r="1097" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1097" s="2">
         <v>46311</v>
       </c>
-      <c r="B1097" s="14"/>
-      <c r="C1097" s="15" t="s">
+      <c r="B1097" s="10"/>
+      <c r="C1097" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="D1097" s="16" t="s">
+      <c r="D1097" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E1097" s="16"/>
-      <c r="F1097" s="16"/>
-      <c r="G1097" s="17"/>
-      <c r="H1097" s="17"/>
-      <c r="I1097" s="17"/>
-    </row>
-    <row r="1098" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1098" s="13">
+      <c r="E1097" s="8"/>
+      <c r="F1097" s="8"/>
+    </row>
+    <row r="1098" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1098" s="2">
         <v>46311</v>
       </c>
-      <c r="B1098" s="14">
+      <c r="B1098" s="10">
         <v>0.25</v>
       </c>
-      <c r="C1098" s="15" t="s">
+      <c r="C1098" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="D1098" s="16" t="s">
+      <c r="D1098" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="E1098" s="15"/>
-      <c r="F1098" s="15"/>
-      <c r="G1098" s="17"/>
-      <c r="H1098" s="17"/>
-      <c r="I1098" s="17"/>
-    </row>
-    <row r="1099" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1099" s="13">
+    </row>
+    <row r="1099" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1099" s="2">
         <v>46311</v>
       </c>
-      <c r="B1099" s="14">
+      <c r="B1099" s="10">
         <v>0.2590277777777778</v>
       </c>
-      <c r="C1099" s="15" t="s">
+      <c r="C1099" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="D1099" s="16" t="s">
+      <c r="D1099" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="E1099" s="15"/>
-      <c r="F1099" s="15"/>
-      <c r="G1099" s="17"/>
-      <c r="H1099" s="17"/>
-      <c r="I1099" s="17"/>
-    </row>
-    <row r="1100" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1100" s="13">
+    </row>
+    <row r="1100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1100" s="2">
         <v>46311</v>
       </c>
-      <c r="B1100" s="14"/>
-      <c r="C1100" s="15" t="s">
+      <c r="B1100" s="10"/>
+      <c r="C1100" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="D1100" s="16" t="s">
+      <c r="D1100" s="8" t="s">
         <v>461</v>
       </c>
-      <c r="E1100" s="15"/>
-      <c r="F1100" s="15"/>
-      <c r="G1100" s="17"/>
-      <c r="H1100" s="17"/>
-      <c r="I1100" s="17"/>
-    </row>
-    <row r="1101" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1101" s="13">
+    </row>
+    <row r="1101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1101" s="2">
         <v>46311</v>
       </c>
-      <c r="B1101" s="14">
+      <c r="B1101" s="10">
         <v>0.35694444444444445</v>
       </c>
-      <c r="C1101" s="15" t="s">
+      <c r="C1101" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="D1101" s="16" t="s">
+      <c r="D1101" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="E1101" s="15"/>
-      <c r="F1101" s="15"/>
-      <c r="G1101" s="17"/>
-      <c r="H1101" s="17"/>
-      <c r="I1101" s="17"/>
-    </row>
-    <row r="1102" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1102" s="13">
+    </row>
+    <row r="1102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1102" s="2">
         <v>46311</v>
       </c>
-      <c r="B1102" s="14"/>
-      <c r="C1102" s="15" t="s">
+      <c r="B1102" s="10"/>
+      <c r="C1102" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="D1102" s="16" t="s">
+      <c r="D1102" s="8" t="s">
         <v>463</v>
       </c>
-      <c r="E1102" s="15"/>
-      <c r="F1102" s="15"/>
-      <c r="G1102" s="17"/>
-      <c r="H1102" s="17"/>
-      <c r="I1102" s="17"/>
-    </row>
-    <row r="1103" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1103" s="13">
+    </row>
+    <row r="1103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1103" s="2">
         <v>46311</v>
       </c>
-      <c r="B1103" s="14">
+      <c r="B1103" s="10">
         <v>0.3659722222222222</v>
       </c>
-      <c r="C1103" s="15" t="s">
+      <c r="C1103" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="D1103" s="16" t="s">
+      <c r="D1103" s="8" t="s">
         <v>464</v>
       </c>
-      <c r="E1103" s="15"/>
-      <c r="F1103" s="15"/>
-      <c r="G1103" s="17"/>
-      <c r="H1103" s="17"/>
-      <c r="I1103" s="17"/>
-    </row>
-    <row r="1104" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1104" s="13">
+    </row>
+    <row r="1104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1104" s="2">
         <v>46311</v>
       </c>
-      <c r="B1104" s="14">
+      <c r="B1104" s="10">
         <v>0.36875000000000002</v>
       </c>
-      <c r="C1104" s="15" t="s">
+      <c r="C1104" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="D1104" s="16" t="s">
+      <c r="D1104" s="8" t="s">
         <v>465</v>
       </c>
-      <c r="E1104" s="15"/>
-      <c r="F1104" s="15"/>
-      <c r="G1104" s="17"/>
-      <c r="H1104" s="17"/>
-      <c r="I1104" s="17"/>
-    </row>
-    <row r="1105" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1105" s="13">
+    </row>
+    <row r="1105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1105" s="2">
         <v>46311</v>
       </c>
-      <c r="B1105" s="14">
+      <c r="B1105" s="10">
         <v>0.37916666666666665</v>
       </c>
-      <c r="C1105" s="15" t="s">
+      <c r="C1105" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="D1105" s="16" t="s">
+      <c r="D1105" s="8" t="s">
         <v>466</v>
       </c>
-      <c r="E1105" s="15"/>
-      <c r="F1105" s="15"/>
-      <c r="G1105" s="17"/>
-      <c r="H1105" s="17"/>
-      <c r="I1105" s="17"/>
-    </row>
-    <row r="1106" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1106" s="13">
+    </row>
+    <row r="1106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1106" s="2">
         <v>46311</v>
       </c>
-      <c r="B1106" s="14">
+      <c r="B1106" s="10">
         <v>0.3972222222222222</v>
       </c>
-      <c r="C1106" s="15" t="s">
+      <c r="C1106" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="D1106" s="16" t="s">
+      <c r="D1106" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="E1106" s="15"/>
-      <c r="F1106" s="15"/>
-      <c r="G1106" s="17"/>
-      <c r="H1106" s="17"/>
-      <c r="I1106" s="17"/>
-    </row>
-    <row r="1107" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1107" s="13">
+    </row>
+    <row r="1107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1107" s="2">
         <v>46311</v>
       </c>
-      <c r="B1107" s="14"/>
-      <c r="C1107" s="15" t="s">
+      <c r="B1107" s="10"/>
+      <c r="C1107" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="D1107" s="16" t="s">
+      <c r="D1107" s="8" t="s">
         <v>467</v>
       </c>
-      <c r="E1107" s="15"/>
-      <c r="F1107" s="15"/>
-      <c r="G1107" s="17"/>
-      <c r="H1107" s="17"/>
-      <c r="I1107" s="17"/>
-    </row>
-    <row r="1108" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1108" s="13">
+    </row>
+    <row r="1108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1108" s="2">
         <v>46311</v>
       </c>
-      <c r="B1108" s="14">
+      <c r="B1108" s="10">
         <v>0.44166666666666665</v>
       </c>
-      <c r="C1108" s="15" t="s">
+      <c r="C1108" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="D1108" s="16" t="s">
+      <c r="D1108" s="8" t="s">
         <v>468</v>
       </c>
-      <c r="E1108" s="15"/>
-      <c r="F1108" s="15"/>
-      <c r="G1108" s="17"/>
-      <c r="H1108" s="17"/>
-      <c r="I1108" s="17"/>
-    </row>
-    <row r="1109" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1109" s="13">
+    </row>
+    <row r="1109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1109" s="2">
         <v>46311</v>
       </c>
-      <c r="B1109" s="14"/>
-      <c r="C1109" s="15" t="s">
+      <c r="B1109" s="10"/>
+      <c r="C1109" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="D1109" s="16" t="s">
+      <c r="D1109" s="8" t="s">
         <v>469</v>
       </c>
-      <c r="E1109" s="15"/>
-      <c r="F1109" s="15"/>
-      <c r="G1109" s="17"/>
-      <c r="H1109" s="17"/>
-      <c r="I1109" s="17"/>
-    </row>
-    <row r="1110" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1110" s="13">
+    </row>
+    <row r="1110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1110" s="2">
         <v>46311</v>
       </c>
-      <c r="B1110" s="14">
+      <c r="B1110" s="10">
         <v>0.48819444444444443</v>
       </c>
-      <c r="C1110" s="15" t="s">
+      <c r="C1110" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="D1110" s="16" t="s">
+      <c r="D1110" s="8" t="s">
         <v>470</v>
       </c>
-      <c r="E1110" s="15"/>
-      <c r="F1110" s="15"/>
-      <c r="G1110" s="17"/>
-      <c r="H1110" s="17"/>
-      <c r="I1110" s="17"/>
-    </row>
-    <row r="1111" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1111" s="13">
+    </row>
+    <row r="1111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1111" s="2">
         <v>46311</v>
       </c>
-      <c r="B1111" s="14"/>
-      <c r="C1111" s="15" t="s">
+      <c r="B1111" s="10"/>
+      <c r="C1111" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="D1111" s="16" t="s">
+      <c r="D1111" s="8" t="s">
         <v>471</v>
       </c>
-      <c r="E1111" s="15"/>
-      <c r="F1111" s="15"/>
-      <c r="G1111" s="17"/>
-      <c r="H1111" s="17"/>
-      <c r="I1111" s="17"/>
-    </row>
-    <row r="1112" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1112" s="13">
+    </row>
+    <row r="1112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1112" s="2">
         <v>46311</v>
       </c>
-      <c r="B1112" s="14">
+      <c r="B1112" s="10">
         <v>0.49305555555555558</v>
       </c>
-      <c r="C1112" s="15" t="s">
+      <c r="C1112" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="D1112" s="16" t="s">
+      <c r="D1112" s="8" t="s">
         <v>472</v>
       </c>
-      <c r="E1112" s="15"/>
-      <c r="F1112" s="15"/>
-      <c r="G1112" s="17"/>
-      <c r="H1112" s="17"/>
-      <c r="I1112" s="17"/>
-    </row>
-    <row r="1113" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1113" s="13">
+    </row>
+    <row r="1113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1113" s="2">
         <v>46311</v>
       </c>
-      <c r="B1113" s="14"/>
-      <c r="C1113" s="15" t="s">
+      <c r="B1113" s="10"/>
+      <c r="C1113" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="D1113" s="16" t="s">
+      <c r="D1113" s="8" t="s">
         <v>473</v>
       </c>
-      <c r="E1113" s="15"/>
-      <c r="F1113" s="15"/>
-      <c r="G1113" s="17"/>
-      <c r="H1113" s="17"/>
-      <c r="I1113" s="17"/>
-    </row>
-    <row r="1114" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1114" s="13">
+    </row>
+    <row r="1114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1114" s="2">
         <v>46311</v>
       </c>
-      <c r="B1114" s="14">
+      <c r="B1114" s="10">
         <v>0.59375</v>
       </c>
-      <c r="C1114" s="15" t="s">
+      <c r="C1114" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="D1114" s="16" t="s">
+      <c r="D1114" s="8" t="s">
         <v>474</v>
       </c>
-      <c r="E1114" s="15"/>
-      <c r="F1114" s="15"/>
-      <c r="G1114" s="17"/>
-      <c r="H1114" s="17"/>
-      <c r="I1114" s="17"/>
-    </row>
-    <row r="1115" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1115" s="13">
+    </row>
+    <row r="1115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1115" s="2">
         <v>46311</v>
       </c>
-      <c r="B1115" s="14"/>
-      <c r="C1115" s="15" t="s">
+      <c r="B1115" s="10"/>
+      <c r="C1115" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="D1115" s="16" t="s">
+      <c r="D1115" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E1115" s="15"/>
-      <c r="F1115" s="15"/>
-      <c r="G1115" s="17"/>
-      <c r="H1115" s="17"/>
-      <c r="I1115" s="17"/>
-    </row>
-    <row r="1116" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1116" s="13">
+    </row>
+    <row r="1116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1116" s="2">
         <v>46312</v>
       </c>
-      <c r="B1116" s="14">
+      <c r="B1116" s="10">
         <v>0.28472222222222221</v>
       </c>
-      <c r="C1116" s="15" t="s">
+      <c r="C1116" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D1116" s="16" t="s">
+      <c r="D1116" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="E1116" s="16"/>
-      <c r="F1116" s="16"/>
-      <c r="G1116" s="17"/>
-      <c r="H1116" s="17"/>
-      <c r="I1116" s="17"/>
-    </row>
-    <row r="1117" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1117" s="13">
+      <c r="E1116" s="8"/>
+      <c r="F1116" s="8"/>
+    </row>
+    <row r="1117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1117" s="2">
         <v>46312</v>
       </c>
-      <c r="B1117" s="14">
+      <c r="B1117" s="10">
         <v>0.36458333333333331</v>
       </c>
-      <c r="C1117" s="15" t="s">
+      <c r="C1117" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D1117" s="16" t="s">
+      <c r="D1117" s="8" t="s">
         <v>475</v>
       </c>
-      <c r="E1117" s="16"/>
-      <c r="F1117" s="16"/>
-      <c r="G1117" s="17"/>
-      <c r="H1117" s="17"/>
-      <c r="I1117" s="17"/>
-    </row>
-    <row r="1118" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1118" s="13">
+      <c r="E1117" s="8"/>
+      <c r="F1117" s="8"/>
+    </row>
+    <row r="1118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1118" s="2">
         <v>46312</v>
       </c>
-      <c r="B1118" s="14"/>
-      <c r="C1118" s="15" t="s">
+      <c r="B1118" s="10"/>
+      <c r="C1118" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D1118" s="16" t="s">
+      <c r="D1118" s="8" t="s">
         <v>476</v>
       </c>
-      <c r="E1118" s="16"/>
-      <c r="F1118" s="16"/>
-      <c r="G1118" s="17"/>
-      <c r="H1118" s="17"/>
-      <c r="I1118" s="17"/>
-    </row>
-    <row r="1119" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1119" s="13">
+      <c r="E1118" s="8"/>
+      <c r="F1118" s="8"/>
+    </row>
+    <row r="1119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1119" s="2">
         <v>46312</v>
       </c>
-      <c r="B1119" s="14">
+      <c r="B1119" s="10">
         <v>0.37361111111111112</v>
       </c>
-      <c r="C1119" s="15" t="s">
+      <c r="C1119" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D1119" s="16" t="s">
+      <c r="D1119" s="8" t="s">
         <v>477</v>
       </c>
-      <c r="E1119" s="16"/>
-      <c r="F1119" s="16"/>
-      <c r="G1119" s="17"/>
-      <c r="H1119" s="17"/>
-      <c r="I1119" s="17"/>
-    </row>
-    <row r="1120" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1120" s="13">
+      <c r="E1119" s="8"/>
+      <c r="F1119" s="8"/>
+    </row>
+    <row r="1120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1120" s="2">
         <v>46312</v>
       </c>
-      <c r="B1120" s="14">
+      <c r="B1120" s="10">
         <v>0.38055555555555554</v>
       </c>
-      <c r="C1120" s="15" t="s">
+      <c r="C1120" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D1120" s="16" t="s">
+      <c r="D1120" s="8" t="s">
         <v>455</v>
       </c>
-      <c r="E1120" s="16"/>
-      <c r="F1120" s="16"/>
-      <c r="G1120" s="17"/>
-      <c r="H1120" s="17"/>
-      <c r="I1120" s="17"/>
-    </row>
-    <row r="1121" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1121" s="13">
+      <c r="E1120" s="8"/>
+      <c r="F1120" s="8"/>
+    </row>
+    <row r="1121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1121" s="2">
         <v>46312</v>
       </c>
-      <c r="B1121" s="14"/>
-      <c r="C1121" s="15" t="s">
+      <c r="B1121" s="10"/>
+      <c r="C1121" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D1121" s="16" t="s">
+      <c r="D1121" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="E1121" s="16"/>
-      <c r="F1121" s="16"/>
-      <c r="G1121" s="17"/>
-      <c r="H1121" s="17"/>
-      <c r="I1121" s="17"/>
-    </row>
-    <row r="1122" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1122" s="13">
+      <c r="E1121" s="8"/>
+      <c r="F1121" s="8"/>
+    </row>
+    <row r="1122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1122" s="2">
         <v>46312</v>
       </c>
-      <c r="B1122" s="14"/>
-      <c r="C1122" s="15" t="s">
+      <c r="B1122" s="10"/>
+      <c r="C1122" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D1122" s="16" t="s">
+      <c r="D1122" s="8" t="s">
         <v>479</v>
       </c>
-      <c r="E1122" s="16"/>
-      <c r="F1122" s="16"/>
-      <c r="G1122" s="17"/>
-      <c r="H1122" s="17"/>
-      <c r="I1122" s="17"/>
-    </row>
-    <row r="1123" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1123" s="13">
+      <c r="E1122" s="8"/>
+      <c r="F1122" s="8"/>
+    </row>
+    <row r="1123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1123" s="2">
         <v>46312</v>
       </c>
-      <c r="B1123" s="14">
+      <c r="B1123" s="10">
         <v>0.44097222222222221</v>
       </c>
-      <c r="C1123" s="15" t="s">
+      <c r="C1123" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D1123" s="16" t="s">
+      <c r="D1123" s="8" t="s">
         <v>480</v>
       </c>
-      <c r="E1123" s="16"/>
-      <c r="F1123" s="16"/>
-      <c r="G1123" s="17"/>
-      <c r="H1123" s="17"/>
-      <c r="I1123" s="17"/>
-    </row>
-    <row r="1124" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1124" s="13">
+      <c r="E1123" s="8"/>
+      <c r="F1123" s="8"/>
+    </row>
+    <row r="1124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1124" s="2">
         <v>46312</v>
       </c>
-      <c r="B1124" s="14">
+      <c r="B1124" s="10">
         <v>0.50694444444444442</v>
       </c>
-      <c r="C1124" s="15" t="s">
+      <c r="C1124" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D1124" s="16" t="s">
+      <c r="D1124" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="E1124" s="16"/>
-      <c r="F1124" s="16"/>
-      <c r="G1124" s="17"/>
-      <c r="H1124" s="17"/>
-      <c r="I1124" s="17"/>
-    </row>
-    <row r="1125" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1125" s="13">
+      <c r="E1124" s="8"/>
+      <c r="F1124" s="8"/>
+    </row>
+    <row r="1125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1125" s="2">
         <v>46312</v>
       </c>
-      <c r="B1125" s="14"/>
-      <c r="C1125" s="15" t="s">
+      <c r="B1125" s="10"/>
+      <c r="C1125" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D1125" s="16" t="s">
+      <c r="D1125" s="8" t="s">
         <v>481</v>
       </c>
-      <c r="E1125" s="16"/>
-      <c r="F1125" s="16"/>
-      <c r="G1125" s="17"/>
-      <c r="H1125" s="17"/>
-      <c r="I1125" s="17"/>
-    </row>
-    <row r="1126" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1126" s="13">
+      <c r="E1125" s="8"/>
+      <c r="F1125" s="8"/>
+    </row>
+    <row r="1126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1126" s="2">
         <v>46312</v>
       </c>
-      <c r="B1126" s="14">
+      <c r="B1126" s="10">
         <v>0.54861111111111116</v>
       </c>
-      <c r="C1126" s="15" t="s">
+      <c r="C1126" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D1126" s="16" t="s">
+      <c r="D1126" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="E1126" s="16"/>
-      <c r="F1126" s="16"/>
-      <c r="G1126" s="17"/>
-      <c r="H1126" s="17"/>
-      <c r="I1126" s="17"/>
-    </row>
-    <row r="1127" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1127" s="13">
+      <c r="E1126" s="8"/>
+      <c r="F1126" s="8"/>
+    </row>
+    <row r="1127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1127" s="2">
         <v>46312</v>
       </c>
-      <c r="B1127" s="14">
+      <c r="B1127" s="10">
         <v>0.55555555555555558</v>
       </c>
-      <c r="C1127" s="15" t="s">
+      <c r="C1127" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D1127" s="16" t="s">
+      <c r="D1127" s="8" t="s">
         <v>483</v>
       </c>
-      <c r="E1127" s="16"/>
-      <c r="F1127" s="16"/>
-      <c r="G1127" s="17"/>
-      <c r="H1127" s="17"/>
-      <c r="I1127" s="17"/>
-    </row>
-    <row r="1128" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1128" s="13">
+      <c r="E1127" s="8"/>
+      <c r="F1127" s="8"/>
+    </row>
+    <row r="1128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1128" s="2">
         <v>46312</v>
       </c>
-      <c r="B1128" s="14">
+      <c r="B1128" s="10">
         <v>0.57638888888888884</v>
       </c>
-      <c r="C1128" s="15" t="s">
+      <c r="C1128" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D1128" s="16" t="s">
+      <c r="D1128" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="E1128" s="16"/>
-      <c r="F1128" s="16"/>
-      <c r="G1128" s="17"/>
-      <c r="H1128" s="17"/>
-      <c r="I1128" s="17"/>
-    </row>
-    <row r="1129" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1129" s="13">
+      <c r="E1128" s="8"/>
+      <c r="F1128" s="8"/>
+    </row>
+    <row r="1129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1129" s="2">
         <v>46312</v>
       </c>
-      <c r="B1129" s="14">
+      <c r="B1129" s="10">
         <v>0.67708333333333337</v>
       </c>
-      <c r="C1129" s="15" t="s">
+      <c r="C1129" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D1129" s="16" t="s">
+      <c r="D1129" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="E1129" s="16"/>
-      <c r="F1129" s="16"/>
-      <c r="G1129" s="17"/>
-      <c r="H1129" s="17"/>
-      <c r="I1129" s="17"/>
-    </row>
-    <row r="1130" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E1129" s="8"/>
+      <c r="F1129" s="8"/>
+    </row>
+    <row r="1130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1130" s="13">
         <v>46312</v>
       </c>
@@ -18128,75 +18046,639 @@
       <c r="D1130" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="E1130" s="16"/>
-      <c r="F1130" s="16"/>
-      <c r="G1130" s="17"/>
-      <c r="H1130" s="17"/>
-      <c r="I1130" s="17"/>
-    </row>
-    <row r="1131" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1131" s="15"/>
-      <c r="B1131" s="15"/>
-      <c r="C1131" s="15"/>
-      <c r="D1131" s="15"/>
-      <c r="E1131" s="15"/>
-      <c r="F1131" s="15"/>
-      <c r="G1131" s="17"/>
-      <c r="H1131" s="17"/>
-      <c r="I1131" s="17"/>
-    </row>
-    <row r="1132" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1132" s="15"/>
-      <c r="B1132" s="15"/>
-      <c r="C1132" s="15"/>
-      <c r="D1132" s="15"/>
-      <c r="E1132" s="15"/>
-      <c r="F1132" s="15"/>
-      <c r="G1132" s="17"/>
-      <c r="H1132" s="17"/>
-      <c r="I1132" s="17"/>
+      <c r="E1130" s="8"/>
+      <c r="F1130" s="8"/>
+    </row>
+    <row r="1131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1131" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1131" s="14">
+        <v>0.25</v>
+      </c>
+      <c r="C1131" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="D1131" s="16" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1132" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1132" s="14">
+        <v>0.28472222222222221</v>
+      </c>
+      <c r="C1132" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="D1132" s="16" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1133" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1133" s="14"/>
+      <c r="C1133" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="D1133" s="16" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1134" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1134" s="14">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="C1134" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="D1134" s="16" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1135" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1135" s="14"/>
+      <c r="C1135" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="D1135" s="16" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1136" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1136" s="14"/>
+      <c r="C1136" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="D1136" s="17" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1137" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1137" s="14">
+        <v>0.37291666666666667</v>
+      </c>
+      <c r="C1137" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="D1137" s="16" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1138" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1138" s="14"/>
+      <c r="C1138" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="D1138" s="16" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1139" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1139" s="14">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="C1139" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="D1139" s="16" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1140" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1140" s="14"/>
+      <c r="C1140" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="D1140" s="16" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1141" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1141" s="14">
+        <v>0.39791666666666664</v>
+      </c>
+      <c r="C1141" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="D1141" s="16" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1142" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1142" s="14"/>
+      <c r="C1142" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="D1142" s="16" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1143" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1143" s="14">
+        <v>0.42222222222222222</v>
+      </c>
+      <c r="C1143" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="D1143" s="16" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1144" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1144" s="14"/>
+      <c r="C1144" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="D1144" s="16" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1145" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1145" s="14"/>
+      <c r="C1145" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="D1145" s="16" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1146" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1146" s="14">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="C1146" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="D1146" s="16" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1147" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1147" s="14"/>
+      <c r="C1147" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="D1147" s="16" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1148" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1148" s="14">
+        <v>0.45208333333333334</v>
+      </c>
+      <c r="C1148" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="D1148" s="16" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1149" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1149" s="14">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="C1149" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="D1149" s="16" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1150" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1150" s="14">
+        <v>0.57430555555555551</v>
+      </c>
+      <c r="C1150" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="D1150" s="16" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1151" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1151" s="14">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="C1151" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="D1151" s="16" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1152" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1152" s="14"/>
+      <c r="C1152" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="D1152" s="16" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1153" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1153" s="14">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="C1153" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="D1153" s="16" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1154" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1154" s="15"/>
+      <c r="C1154" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="D1154" s="16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1155" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1155" s="14">
+        <v>0.25</v>
+      </c>
+      <c r="C1155" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1155" s="16" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1156" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1156" s="14">
+        <v>0.28472222222222221</v>
+      </c>
+      <c r="C1156" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1156" s="16" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1157" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1157" s="14"/>
+      <c r="C1157" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1157" s="16" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1158" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1158" s="14">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="C1158" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1158" s="16" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1159" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1159" s="14"/>
+      <c r="C1159" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1159" s="16" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1160" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1160" s="14"/>
+      <c r="C1160" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1160" s="17" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1161" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1161" s="14">
+        <v>0.37291666666666667</v>
+      </c>
+      <c r="C1161" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1161" s="16" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1162" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1162" s="14"/>
+      <c r="C1162" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1162" s="16" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1163" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1163" s="14">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="C1163" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1163" s="16" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1164" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1164" s="14"/>
+      <c r="C1164" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1164" s="16" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1165" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1165" s="14">
+        <v>0.39791666666666664</v>
+      </c>
+      <c r="C1165" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1165" s="16" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1166" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1166" s="14"/>
+      <c r="C1166" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1166" s="16" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1167" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1167" s="14">
+        <v>0.42222222222222222</v>
+      </c>
+      <c r="C1167" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1167" s="16" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1168" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1168" s="14"/>
+      <c r="C1168" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1168" s="16" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1169" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1169" s="14"/>
+      <c r="C1169" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1169" s="16" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1170" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1170" s="14">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="C1170" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1170" s="16" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1171" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1171" s="14"/>
+      <c r="C1171" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1171" s="16" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1172" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1172" s="14">
+        <v>0.45208333333333334</v>
+      </c>
+      <c r="C1172" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1172" s="16" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1173" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1173" s="14">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="C1173" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1173" s="16" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1174" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1174" s="14">
+        <v>0.57430555555555551</v>
+      </c>
+      <c r="C1174" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1174" s="16" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1175" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1175" s="14">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="C1175" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1175" s="16" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1176" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1176" s="14"/>
+      <c r="C1176" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1176" s="16" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1177" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1177" s="14">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="C1177" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1177" s="16" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1178" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B1178" s="15"/>
+      <c r="C1178" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1178" s="16" t="s">
+        <v>55</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="D1078:F1078"/>
-    <mergeCell ref="D1072:F1072"/>
-    <mergeCell ref="D1070:F1070"/>
-    <mergeCell ref="D1071:F1071"/>
-    <mergeCell ref="D1077:F1077"/>
-    <mergeCell ref="D1074:F1074"/>
-    <mergeCell ref="D1075:F1075"/>
-    <mergeCell ref="D1076:F1076"/>
-    <mergeCell ref="D1069:F1069"/>
-    <mergeCell ref="D1066:F1066"/>
-    <mergeCell ref="D1067:F1067"/>
-    <mergeCell ref="D1052:F1052"/>
-    <mergeCell ref="D1053:F1053"/>
-    <mergeCell ref="D1054:F1054"/>
-    <mergeCell ref="D1055:F1055"/>
-    <mergeCell ref="D1056:F1056"/>
-    <mergeCell ref="D1057:F1057"/>
-    <mergeCell ref="D1058:F1058"/>
-    <mergeCell ref="D1059:F1059"/>
-    <mergeCell ref="D1060:F1060"/>
-    <mergeCell ref="D1061:F1061"/>
-    <mergeCell ref="D1049:F1049"/>
-    <mergeCell ref="D1050:F1050"/>
-    <mergeCell ref="D1051:F1051"/>
-    <mergeCell ref="D1065:F1065"/>
-    <mergeCell ref="D1068:F1068"/>
-    <mergeCell ref="D1064:F1064"/>
-    <mergeCell ref="D1062:F1062"/>
-    <mergeCell ref="D1063:F1063"/>
-    <mergeCell ref="D1047:F1047"/>
-    <mergeCell ref="D1048:F1048"/>
-    <mergeCell ref="D987:F987"/>
-    <mergeCell ref="D988:F988"/>
-    <mergeCell ref="D981:F981"/>
-    <mergeCell ref="D982:F982"/>
-    <mergeCell ref="D983:F983"/>
-    <mergeCell ref="D984:F984"/>
-    <mergeCell ref="D985:F985"/>
-    <mergeCell ref="D986:F986"/>
     <mergeCell ref="D965:F965"/>
     <mergeCell ref="D966:F966"/>
     <mergeCell ref="D967:F967"/>
@@ -18213,6 +18695,45 @@
     <mergeCell ref="D977:F977"/>
     <mergeCell ref="D978:F978"/>
     <mergeCell ref="D979:F979"/>
+    <mergeCell ref="D1047:F1047"/>
+    <mergeCell ref="D1048:F1048"/>
+    <mergeCell ref="D987:F987"/>
+    <mergeCell ref="D988:F988"/>
+    <mergeCell ref="D981:F981"/>
+    <mergeCell ref="D982:F982"/>
+    <mergeCell ref="D983:F983"/>
+    <mergeCell ref="D984:F984"/>
+    <mergeCell ref="D985:F985"/>
+    <mergeCell ref="D986:F986"/>
+    <mergeCell ref="D1049:F1049"/>
+    <mergeCell ref="D1050:F1050"/>
+    <mergeCell ref="D1051:F1051"/>
+    <mergeCell ref="D1065:F1065"/>
+    <mergeCell ref="D1068:F1068"/>
+    <mergeCell ref="D1064:F1064"/>
+    <mergeCell ref="D1062:F1062"/>
+    <mergeCell ref="D1063:F1063"/>
+    <mergeCell ref="D1069:F1069"/>
+    <mergeCell ref="D1066:F1066"/>
+    <mergeCell ref="D1067:F1067"/>
+    <mergeCell ref="D1052:F1052"/>
+    <mergeCell ref="D1053:F1053"/>
+    <mergeCell ref="D1054:F1054"/>
+    <mergeCell ref="D1055:F1055"/>
+    <mergeCell ref="D1056:F1056"/>
+    <mergeCell ref="D1057:F1057"/>
+    <mergeCell ref="D1058:F1058"/>
+    <mergeCell ref="D1059:F1059"/>
+    <mergeCell ref="D1060:F1060"/>
+    <mergeCell ref="D1061:F1061"/>
+    <mergeCell ref="D1078:F1078"/>
+    <mergeCell ref="D1072:F1072"/>
+    <mergeCell ref="D1070:F1070"/>
+    <mergeCell ref="D1071:F1071"/>
+    <mergeCell ref="D1077:F1077"/>
+    <mergeCell ref="D1074:F1074"/>
+    <mergeCell ref="D1075:F1075"/>
+    <mergeCell ref="D1076:F1076"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{681C5606-2CC6-4DFE-BA31-99B0DC1CA665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C898BE7-962E-4EBC-9C7C-7F22035B4D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2358" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2442" uniqueCount="512">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1916,6 +1916,54 @@
   <si>
     <t>D01</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>push on D01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait D01 team(BeeX&amp;Michael)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sail to C10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>push on C10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SRL issue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assisted Siemens technicians with SRL replacement 
+during work at height.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sail to D01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait D01 team(Michael)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sail to</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait A01 team(F2 &amp; Siemens)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>C10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Push on D04</t>
   </si>
 </sst>
 </file>
@@ -2008,7 +2056,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2050,6 +2098,7 @@
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2338,7 +2387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1178"/>
+  <dimension ref="A1:H1222"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.296875" style="1" bestFit="1" customWidth="1"/>
@@ -17897,7 +17946,7 @@
       <c r="E1120" s="8"/>
       <c r="F1120" s="8"/>
     </row>
-    <row r="1121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1121" s="2">
         <v>46312</v>
       </c>
@@ -17911,7 +17960,7 @@
       <c r="E1121" s="8"/>
       <c r="F1121" s="8"/>
     </row>
-    <row r="1122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1122" s="2">
         <v>46312</v>
       </c>
@@ -17925,7 +17974,7 @@
       <c r="E1122" s="8"/>
       <c r="F1122" s="8"/>
     </row>
-    <row r="1123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1123" s="2">
         <v>46312</v>
       </c>
@@ -17941,7 +17990,7 @@
       <c r="E1123" s="8"/>
       <c r="F1123" s="8"/>
     </row>
-    <row r="1124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1124" s="2">
         <v>46312</v>
       </c>
@@ -17957,7 +18006,7 @@
       <c r="E1124" s="8"/>
       <c r="F1124" s="8"/>
     </row>
-    <row r="1125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1125" s="2">
         <v>46312</v>
       </c>
@@ -17971,7 +18020,7 @@
       <c r="E1125" s="8"/>
       <c r="F1125" s="8"/>
     </row>
-    <row r="1126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1126" s="2">
         <v>46312</v>
       </c>
@@ -17987,55 +18036,61 @@
       <c r="E1126" s="8"/>
       <c r="F1126" s="8"/>
     </row>
-    <row r="1127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1127" s="2">
+    <row r="1127" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1127" s="13">
         <v>46312</v>
       </c>
-      <c r="B1127" s="10">
+      <c r="B1127" s="14">
         <v>0.55555555555555558</v>
       </c>
-      <c r="C1127" s="1" t="s">
+      <c r="C1127" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="D1127" s="8" t="s">
+      <c r="D1127" s="16" t="s">
         <v>483</v>
       </c>
-      <c r="E1127" s="8"/>
-      <c r="F1127" s="8"/>
-    </row>
-    <row r="1128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1128" s="2">
+      <c r="E1127" s="16"/>
+      <c r="F1127" s="16"/>
+      <c r="G1127" s="17"/>
+      <c r="H1127" s="17"/>
+    </row>
+    <row r="1128" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1128" s="13">
         <v>46312</v>
       </c>
-      <c r="B1128" s="10">
+      <c r="B1128" s="14">
         <v>0.57638888888888884</v>
       </c>
-      <c r="C1128" s="1" t="s">
+      <c r="C1128" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="D1128" s="8" t="s">
+      <c r="D1128" s="16" t="s">
         <v>394</v>
       </c>
-      <c r="E1128" s="8"/>
-      <c r="F1128" s="8"/>
-    </row>
-    <row r="1129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1129" s="2">
+      <c r="E1128" s="16"/>
+      <c r="F1128" s="16"/>
+      <c r="G1128" s="17"/>
+      <c r="H1128" s="17"/>
+    </row>
+    <row r="1129" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1129" s="13">
         <v>46312</v>
       </c>
-      <c r="B1129" s="10">
+      <c r="B1129" s="14">
         <v>0.67708333333333337</v>
       </c>
-      <c r="C1129" s="1" t="s">
+      <c r="C1129" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="D1129" s="8" t="s">
+      <c r="D1129" s="16" t="s">
         <v>379</v>
       </c>
-      <c r="E1129" s="8"/>
-      <c r="F1129" s="8"/>
-    </row>
-    <row r="1130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E1129" s="16"/>
+      <c r="F1129" s="16"/>
+      <c r="G1129" s="17"/>
+      <c r="H1129" s="17"/>
+    </row>
+    <row r="1130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1130" s="13">
         <v>46312</v>
       </c>
@@ -18046,10 +18101,12 @@
       <c r="D1130" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="E1130" s="8"/>
-      <c r="F1130" s="8"/>
-    </row>
-    <row r="1131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E1130" s="16"/>
+      <c r="F1130" s="16"/>
+      <c r="G1130" s="17"/>
+      <c r="H1130" s="17"/>
+    </row>
+    <row r="1131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1131" s="13">
         <v>46312</v>
       </c>
@@ -18062,8 +18119,12 @@
       <c r="D1131" s="16" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="1132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E1131" s="15"/>
+      <c r="F1131" s="15"/>
+      <c r="G1131" s="17"/>
+      <c r="H1131" s="17"/>
+    </row>
+    <row r="1132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1132" s="13">
         <v>46312</v>
       </c>
@@ -18076,8 +18137,12 @@
       <c r="D1132" s="16" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="1133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E1132" s="15"/>
+      <c r="F1132" s="15"/>
+      <c r="G1132" s="17"/>
+      <c r="H1132" s="17"/>
+    </row>
+    <row r="1133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1133" s="13">
         <v>46312</v>
       </c>
@@ -18088,8 +18153,12 @@
       <c r="D1133" s="16" t="s">
         <v>461</v>
       </c>
-    </row>
-    <row r="1134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E1133" s="15"/>
+      <c r="F1133" s="15"/>
+      <c r="G1133" s="17"/>
+      <c r="H1133" s="17"/>
+    </row>
+    <row r="1134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1134" s="13">
         <v>46312</v>
       </c>
@@ -18102,8 +18171,12 @@
       <c r="D1134" s="16" t="s">
         <v>462</v>
       </c>
-    </row>
-    <row r="1135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E1134" s="15"/>
+      <c r="F1134" s="15"/>
+      <c r="G1134" s="17"/>
+      <c r="H1134" s="17"/>
+    </row>
+    <row r="1135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1135" s="13">
         <v>46312</v>
       </c>
@@ -18114,8 +18187,12 @@
       <c r="D1135" s="16" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="1136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E1135" s="15"/>
+      <c r="F1135" s="15"/>
+      <c r="G1135" s="17"/>
+      <c r="H1135" s="17"/>
+    </row>
+    <row r="1136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1136" s="13">
         <v>46312</v>
       </c>
@@ -18123,11 +18200,15 @@
       <c r="C1136" s="15" t="s">
         <v>498</v>
       </c>
-      <c r="D1136" s="17" t="s">
+      <c r="D1136" s="18" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="1137" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1136" s="15"/>
+      <c r="F1136" s="15"/>
+      <c r="G1136" s="17"/>
+      <c r="H1136" s="17"/>
+    </row>
+    <row r="1137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1137" s="13">
         <v>46312</v>
       </c>
@@ -18140,8 +18221,12 @@
       <c r="D1137" s="16" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="1138" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1137" s="15"/>
+      <c r="F1137" s="15"/>
+      <c r="G1137" s="17"/>
+      <c r="H1137" s="17"/>
+    </row>
+    <row r="1138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1138" s="13">
         <v>46312</v>
       </c>
@@ -18152,8 +18237,12 @@
       <c r="D1138" s="16" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="1139" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1138" s="15"/>
+      <c r="F1138" s="15"/>
+      <c r="G1138" s="17"/>
+      <c r="H1138" s="17"/>
+    </row>
+    <row r="1139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1139" s="13">
         <v>46312</v>
       </c>
@@ -18166,8 +18255,12 @@
       <c r="D1139" s="16" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="1140" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1139" s="15"/>
+      <c r="F1139" s="15"/>
+      <c r="G1139" s="17"/>
+      <c r="H1139" s="17"/>
+    </row>
+    <row r="1140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1140" s="13">
         <v>46312</v>
       </c>
@@ -18178,8 +18271,12 @@
       <c r="D1140" s="16" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="1141" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1140" s="15"/>
+      <c r="F1140" s="15"/>
+      <c r="G1140" s="17"/>
+      <c r="H1140" s="17"/>
+    </row>
+    <row r="1141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1141" s="13">
         <v>46312</v>
       </c>
@@ -18192,8 +18289,12 @@
       <c r="D1141" s="16" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="1142" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1141" s="15"/>
+      <c r="F1141" s="15"/>
+      <c r="G1141" s="17"/>
+      <c r="H1141" s="17"/>
+    </row>
+    <row r="1142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1142" s="13">
         <v>46312</v>
       </c>
@@ -18204,8 +18305,12 @@
       <c r="D1142" s="16" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="1143" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1142" s="15"/>
+      <c r="F1142" s="15"/>
+      <c r="G1142" s="17"/>
+      <c r="H1142" s="17"/>
+    </row>
+    <row r="1143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1143" s="13">
         <v>46312</v>
       </c>
@@ -18218,8 +18323,12 @@
       <c r="D1143" s="16" t="s">
         <v>464</v>
       </c>
-    </row>
-    <row r="1144" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1143" s="15"/>
+      <c r="F1143" s="15"/>
+      <c r="G1143" s="17"/>
+      <c r="H1143" s="17"/>
+    </row>
+    <row r="1144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1144" s="13">
         <v>46312</v>
       </c>
@@ -18230,8 +18339,12 @@
       <c r="D1144" s="16" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="1145" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1144" s="15"/>
+      <c r="F1144" s="15"/>
+      <c r="G1144" s="17"/>
+      <c r="H1144" s="17"/>
+    </row>
+    <row r="1145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1145" s="13">
         <v>46312</v>
       </c>
@@ -18242,8 +18355,12 @@
       <c r="D1145" s="16" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="1146" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1145" s="15"/>
+      <c r="F1145" s="15"/>
+      <c r="G1145" s="17"/>
+      <c r="H1145" s="17"/>
+    </row>
+    <row r="1146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1146" s="13">
         <v>46312</v>
       </c>
@@ -18256,8 +18373,12 @@
       <c r="D1146" s="16" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="1147" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1146" s="15"/>
+      <c r="F1146" s="15"/>
+      <c r="G1146" s="17"/>
+      <c r="H1146" s="17"/>
+    </row>
+    <row r="1147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1147" s="13">
         <v>46312</v>
       </c>
@@ -18268,8 +18389,12 @@
       <c r="D1147" s="16" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="1148" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1147" s="15"/>
+      <c r="F1147" s="15"/>
+      <c r="G1147" s="17"/>
+      <c r="H1147" s="17"/>
+    </row>
+    <row r="1148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1148" s="13">
         <v>46312</v>
       </c>
@@ -18282,8 +18407,12 @@
       <c r="D1148" s="16" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="1149" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1148" s="15"/>
+      <c r="F1148" s="15"/>
+      <c r="G1148" s="17"/>
+      <c r="H1148" s="17"/>
+    </row>
+    <row r="1149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1149" s="13">
         <v>46312</v>
       </c>
@@ -18296,8 +18425,12 @@
       <c r="D1149" s="16" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="1150" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1149" s="15"/>
+      <c r="F1149" s="15"/>
+      <c r="G1149" s="17"/>
+      <c r="H1149" s="17"/>
+    </row>
+    <row r="1150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1150" s="13">
         <v>46312</v>
       </c>
@@ -18310,8 +18443,12 @@
       <c r="D1150" s="16" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="1151" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1150" s="15"/>
+      <c r="F1150" s="15"/>
+      <c r="G1150" s="17"/>
+      <c r="H1150" s="17"/>
+    </row>
+    <row r="1151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1151" s="13">
         <v>46312</v>
       </c>
@@ -18324,8 +18461,12 @@
       <c r="D1151" s="16" t="s">
         <v>472</v>
       </c>
-    </row>
-    <row r="1152" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1151" s="15"/>
+      <c r="F1151" s="15"/>
+      <c r="G1151" s="17"/>
+      <c r="H1151" s="17"/>
+    </row>
+    <row r="1152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1152" s="13">
         <v>46312</v>
       </c>
@@ -18336,8 +18477,12 @@
       <c r="D1152" s="16" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="1153" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1152" s="15"/>
+      <c r="F1152" s="15"/>
+      <c r="G1152" s="17"/>
+      <c r="H1152" s="17"/>
+    </row>
+    <row r="1153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1153" s="13">
         <v>46312</v>
       </c>
@@ -18350,8 +18495,12 @@
       <c r="D1153" s="16" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="1154" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1153" s="15"/>
+      <c r="F1153" s="15"/>
+      <c r="G1153" s="17"/>
+      <c r="H1153" s="17"/>
+    </row>
+    <row r="1154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1154" s="13">
         <v>46312</v>
       </c>
@@ -18362,8 +18511,12 @@
       <c r="D1154" s="16" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="1155" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1154" s="15"/>
+      <c r="F1154" s="15"/>
+      <c r="G1154" s="17"/>
+      <c r="H1154" s="17"/>
+    </row>
+    <row r="1155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1155" s="13">
         <v>46312</v>
       </c>
@@ -18376,8 +18529,12 @@
       <c r="D1155" s="16" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="1156" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1155" s="15"/>
+      <c r="F1155" s="15"/>
+      <c r="G1155" s="17"/>
+      <c r="H1155" s="17"/>
+    </row>
+    <row r="1156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1156" s="13">
         <v>46312</v>
       </c>
@@ -18390,8 +18547,12 @@
       <c r="D1156" s="16" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="1157" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1156" s="15"/>
+      <c r="F1156" s="15"/>
+      <c r="G1156" s="17"/>
+      <c r="H1156" s="17"/>
+    </row>
+    <row r="1157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1157" s="13">
         <v>46312</v>
       </c>
@@ -18402,8 +18563,12 @@
       <c r="D1157" s="16" t="s">
         <v>461</v>
       </c>
-    </row>
-    <row r="1158" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1157" s="15"/>
+      <c r="F1157" s="15"/>
+      <c r="G1157" s="17"/>
+      <c r="H1157" s="17"/>
+    </row>
+    <row r="1158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1158" s="13">
         <v>46312</v>
       </c>
@@ -18416,8 +18581,12 @@
       <c r="D1158" s="16" t="s">
         <v>462</v>
       </c>
-    </row>
-    <row r="1159" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1158" s="15"/>
+      <c r="F1158" s="15"/>
+      <c r="G1158" s="17"/>
+      <c r="H1158" s="17"/>
+    </row>
+    <row r="1159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1159" s="13">
         <v>46312</v>
       </c>
@@ -18428,8 +18597,12 @@
       <c r="D1159" s="16" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="1160" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1159" s="15"/>
+      <c r="F1159" s="15"/>
+      <c r="G1159" s="17"/>
+      <c r="H1159" s="17"/>
+    </row>
+    <row r="1160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1160" s="13">
         <v>46312</v>
       </c>
@@ -18437,11 +18610,15 @@
       <c r="C1160" s="15" t="s">
         <v>499</v>
       </c>
-      <c r="D1160" s="17" t="s">
+      <c r="D1160" s="18" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="1161" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1160" s="15"/>
+      <c r="F1160" s="15"/>
+      <c r="G1160" s="17"/>
+      <c r="H1160" s="17"/>
+    </row>
+    <row r="1161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1161" s="13">
         <v>46312</v>
       </c>
@@ -18454,8 +18631,12 @@
       <c r="D1161" s="16" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="1162" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1161" s="15"/>
+      <c r="F1161" s="15"/>
+      <c r="G1161" s="17"/>
+      <c r="H1161" s="17"/>
+    </row>
+    <row r="1162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1162" s="13">
         <v>46312</v>
       </c>
@@ -18466,8 +18647,12 @@
       <c r="D1162" s="16" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="1163" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1162" s="15"/>
+      <c r="F1162" s="15"/>
+      <c r="G1162" s="17"/>
+      <c r="H1162" s="17"/>
+    </row>
+    <row r="1163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1163" s="13">
         <v>46312</v>
       </c>
@@ -18480,8 +18665,12 @@
       <c r="D1163" s="16" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="1164" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1163" s="15"/>
+      <c r="F1163" s="15"/>
+      <c r="G1163" s="17"/>
+      <c r="H1163" s="17"/>
+    </row>
+    <row r="1164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1164" s="13">
         <v>46312</v>
       </c>
@@ -18492,8 +18681,12 @@
       <c r="D1164" s="16" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="1165" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1164" s="15"/>
+      <c r="F1164" s="15"/>
+      <c r="G1164" s="17"/>
+      <c r="H1164" s="17"/>
+    </row>
+    <row r="1165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1165" s="13">
         <v>46312</v>
       </c>
@@ -18506,8 +18699,12 @@
       <c r="D1165" s="16" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="1166" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1165" s="15"/>
+      <c r="F1165" s="15"/>
+      <c r="G1165" s="17"/>
+      <c r="H1165" s="17"/>
+    </row>
+    <row r="1166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1166" s="13">
         <v>46312</v>
       </c>
@@ -18518,8 +18715,12 @@
       <c r="D1166" s="16" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="1167" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1166" s="15"/>
+      <c r="F1166" s="15"/>
+      <c r="G1166" s="17"/>
+      <c r="H1166" s="17"/>
+    </row>
+    <row r="1167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1167" s="13">
         <v>46312</v>
       </c>
@@ -18532,8 +18733,12 @@
       <c r="D1167" s="16" t="s">
         <v>464</v>
       </c>
-    </row>
-    <row r="1168" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1167" s="15"/>
+      <c r="F1167" s="15"/>
+      <c r="G1167" s="17"/>
+      <c r="H1167" s="17"/>
+    </row>
+    <row r="1168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1168" s="13">
         <v>46312</v>
       </c>
@@ -18544,8 +18749,12 @@
       <c r="D1168" s="16" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="1169" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1168" s="15"/>
+      <c r="F1168" s="15"/>
+      <c r="G1168" s="17"/>
+      <c r="H1168" s="17"/>
+    </row>
+    <row r="1169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1169" s="13">
         <v>46312</v>
       </c>
@@ -18556,8 +18765,12 @@
       <c r="D1169" s="16" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="1170" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1169" s="15"/>
+      <c r="F1169" s="15"/>
+      <c r="G1169" s="17"/>
+      <c r="H1169" s="17"/>
+    </row>
+    <row r="1170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1170" s="13">
         <v>46312</v>
       </c>
@@ -18570,8 +18783,12 @@
       <c r="D1170" s="16" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="1171" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1170" s="15"/>
+      <c r="F1170" s="15"/>
+      <c r="G1170" s="17"/>
+      <c r="H1170" s="17"/>
+    </row>
+    <row r="1171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1171" s="13">
         <v>46312</v>
       </c>
@@ -18582,8 +18799,12 @@
       <c r="D1171" s="16" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="1172" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1171" s="15"/>
+      <c r="F1171" s="15"/>
+      <c r="G1171" s="17"/>
+      <c r="H1171" s="17"/>
+    </row>
+    <row r="1172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1172" s="13">
         <v>46312</v>
       </c>
@@ -18596,8 +18817,12 @@
       <c r="D1172" s="16" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="1173" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1172" s="15"/>
+      <c r="F1172" s="15"/>
+      <c r="G1172" s="17"/>
+      <c r="H1172" s="17"/>
+    </row>
+    <row r="1173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1173" s="13">
         <v>46312</v>
       </c>
@@ -18610,8 +18835,12 @@
       <c r="D1173" s="16" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="1174" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1173" s="15"/>
+      <c r="F1173" s="15"/>
+      <c r="G1173" s="17"/>
+      <c r="H1173" s="17"/>
+    </row>
+    <row r="1174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1174" s="13">
         <v>46312</v>
       </c>
@@ -18624,8 +18853,12 @@
       <c r="D1174" s="16" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="1175" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1174" s="15"/>
+      <c r="F1174" s="15"/>
+      <c r="G1174" s="17"/>
+      <c r="H1174" s="17"/>
+    </row>
+    <row r="1175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1175" s="13">
         <v>46312</v>
       </c>
@@ -18638,8 +18871,12 @@
       <c r="D1175" s="16" t="s">
         <v>472</v>
       </c>
-    </row>
-    <row r="1176" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1175" s="15"/>
+      <c r="F1175" s="15"/>
+      <c r="G1175" s="17"/>
+      <c r="H1175" s="17"/>
+    </row>
+    <row r="1176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1176" s="13">
         <v>46312</v>
       </c>
@@ -18650,8 +18887,12 @@
       <c r="D1176" s="16" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="1177" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1176" s="15"/>
+      <c r="F1176" s="15"/>
+      <c r="G1176" s="17"/>
+      <c r="H1176" s="17"/>
+    </row>
+    <row r="1177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1177" s="13">
         <v>46312</v>
       </c>
@@ -18664,8 +18905,12 @@
       <c r="D1177" s="16" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="1178" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1177" s="15"/>
+      <c r="F1177" s="15"/>
+      <c r="G1177" s="17"/>
+      <c r="H1177" s="17"/>
+    </row>
+    <row r="1178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1178" s="13">
         <v>46312</v>
       </c>
@@ -18676,9 +18921,796 @@
       <c r="D1178" s="16" t="s">
         <v>55</v>
       </c>
+      <c r="E1178" s="15"/>
+      <c r="F1178" s="15"/>
+      <c r="G1178" s="17"/>
+      <c r="H1178" s="17"/>
+    </row>
+    <row r="1179" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1179" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1179" s="14">
+        <v>0.2638888888888889</v>
+      </c>
+      <c r="C1179" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="D1179" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="E1179" s="16"/>
+      <c r="F1179" s="16"/>
+      <c r="G1179" s="17"/>
+      <c r="H1179" s="17"/>
+    </row>
+    <row r="1180" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1180" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1180" s="14">
+        <v>0.34722222222222221</v>
+      </c>
+      <c r="C1180" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="D1180" s="16" t="s">
+        <v>500</v>
+      </c>
+      <c r="E1180" s="16"/>
+      <c r="F1180" s="16"/>
+      <c r="G1180" s="17"/>
+      <c r="H1180" s="17"/>
+    </row>
+    <row r="1181" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1181" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1181" s="14"/>
+      <c r="C1181" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="D1181" s="16" t="s">
+        <v>501</v>
+      </c>
+      <c r="E1181" s="16"/>
+      <c r="F1181" s="16"/>
+      <c r="G1181" s="17"/>
+      <c r="H1181" s="17"/>
+    </row>
+    <row r="1182" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1182" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1182" s="14">
+        <v>0.36319444444444443</v>
+      </c>
+      <c r="C1182" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="D1182" s="16" t="s">
+        <v>502</v>
+      </c>
+      <c r="E1182" s="16"/>
+      <c r="F1182" s="16"/>
+      <c r="G1182" s="17"/>
+      <c r="H1182" s="17"/>
+    </row>
+    <row r="1183" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1183" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1183" s="14">
+        <v>0.37152777777777779</v>
+      </c>
+      <c r="C1183" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="D1183" s="16" t="s">
+        <v>503</v>
+      </c>
+      <c r="E1183" s="16"/>
+      <c r="F1183" s="16"/>
+      <c r="G1183" s="17"/>
+      <c r="H1183" s="17"/>
+    </row>
+    <row r="1184" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1184" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1184" s="14">
+        <v>0.37847222222222221</v>
+      </c>
+      <c r="C1184" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="D1184" s="16" t="s">
+        <v>504</v>
+      </c>
+      <c r="E1184" s="16"/>
+      <c r="F1184" s="16"/>
+      <c r="G1184" s="17"/>
+      <c r="H1184" s="17"/>
+    </row>
+    <row r="1185" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1185" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1185" s="14"/>
+      <c r="C1185" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="D1185" s="16" t="s">
+        <v>505</v>
+      </c>
+      <c r="E1185" s="16"/>
+      <c r="F1185" s="16"/>
+      <c r="G1185" s="17"/>
+      <c r="H1185" s="17"/>
+    </row>
+    <row r="1186" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1186" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1186" s="14">
+        <v>0.41388888888888886</v>
+      </c>
+      <c r="C1186" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="D1186" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="E1186" s="16"/>
+      <c r="F1186" s="16"/>
+      <c r="G1186" s="17"/>
+      <c r="H1186" s="17"/>
+    </row>
+    <row r="1187" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1187" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1187" s="14">
+        <v>0.43402777777777779</v>
+      </c>
+      <c r="C1187" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="D1187" s="16" t="s">
+        <v>480</v>
+      </c>
+      <c r="E1187" s="16"/>
+      <c r="F1187" s="16"/>
+      <c r="G1187" s="17"/>
+      <c r="H1187" s="17"/>
+    </row>
+    <row r="1188" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1188" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1188" s="14"/>
+      <c r="C1188" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="D1188" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1188" s="16"/>
+      <c r="F1188" s="16"/>
+      <c r="G1188" s="17"/>
+      <c r="H1188" s="17"/>
+    </row>
+    <row r="1189" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1189" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1189" s="14">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="C1189" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="D1189" s="16" t="s">
+        <v>481</v>
+      </c>
+      <c r="E1189" s="16"/>
+      <c r="F1189" s="16"/>
+      <c r="G1189" s="17"/>
+      <c r="H1189" s="17"/>
+    </row>
+    <row r="1190" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1190" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1190" s="14">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="C1190" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="D1190" s="16" t="s">
+        <v>506</v>
+      </c>
+      <c r="E1190" s="16"/>
+      <c r="F1190" s="16"/>
+      <c r="G1190" s="17"/>
+      <c r="H1190" s="17"/>
+    </row>
+    <row r="1191" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1191" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1191" s="14">
+        <v>0.55694444444444446</v>
+      </c>
+      <c r="C1191" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="D1191" s="16" t="s">
+        <v>507</v>
+      </c>
+      <c r="E1191" s="16"/>
+      <c r="F1191" s="16"/>
+      <c r="G1191" s="17"/>
+      <c r="H1191" s="17"/>
+    </row>
+    <row r="1192" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1192" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1192" s="14">
+        <v>0.56944444444444442</v>
+      </c>
+      <c r="C1192" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="D1192" s="16" t="s">
+        <v>508</v>
+      </c>
+      <c r="E1192" s="16"/>
+      <c r="F1192" s="16"/>
+      <c r="G1192" s="17"/>
+      <c r="H1192" s="17"/>
+    </row>
+    <row r="1193" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1193" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1193" s="14">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C1193" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="D1193" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="E1193" s="16"/>
+      <c r="F1193" s="16"/>
+      <c r="G1193" s="17"/>
+      <c r="H1193" s="17"/>
+    </row>
+    <row r="1194" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1194" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1194" s="14">
+        <v>0.65277777777777779</v>
+      </c>
+      <c r="C1194" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="D1194" s="16" t="s">
+        <v>394</v>
+      </c>
+      <c r="E1194" s="16"/>
+      <c r="F1194" s="16"/>
+      <c r="G1194" s="17"/>
+      <c r="H1194" s="17"/>
+    </row>
+    <row r="1195" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1195" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1195" s="14"/>
+      <c r="C1195" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="D1195" s="16" t="s">
+        <v>379</v>
+      </c>
+      <c r="E1195" s="16"/>
+      <c r="F1195" s="16"/>
+      <c r="G1195" s="17"/>
+      <c r="H1195" s="17"/>
+    </row>
+    <row r="1196" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1196" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1196" s="14"/>
+      <c r="C1196" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="D1196" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1196" s="16"/>
+      <c r="F1196" s="16"/>
+      <c r="G1196" s="17"/>
+      <c r="H1196" s="17"/>
+    </row>
+    <row r="1197" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1197" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1197" s="14">
+        <v>0.25</v>
+      </c>
+      <c r="C1197" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1197" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="E1197" s="15"/>
+      <c r="F1197" s="15"/>
+      <c r="G1197" s="17"/>
+      <c r="H1197" s="17"/>
+    </row>
+    <row r="1198" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1198" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1198" s="14">
+        <v>0.28472222222222221</v>
+      </c>
+      <c r="C1198" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1198" s="16" t="s">
+        <v>460</v>
+      </c>
+      <c r="E1198" s="15"/>
+      <c r="F1198" s="15"/>
+      <c r="G1198" s="17"/>
+      <c r="H1198" s="17"/>
+    </row>
+    <row r="1199" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1199" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1199" s="14"/>
+      <c r="C1199" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1199" s="16" t="s">
+        <v>461</v>
+      </c>
+      <c r="E1199" s="15"/>
+      <c r="F1199" s="15"/>
+      <c r="G1199" s="17"/>
+      <c r="H1199" s="17"/>
+    </row>
+    <row r="1200" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1200" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1200" s="14">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="C1200" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1200" s="16" t="s">
+        <v>462</v>
+      </c>
+      <c r="E1200" s="15"/>
+      <c r="F1200" s="15"/>
+      <c r="G1200" s="17"/>
+      <c r="H1200" s="17"/>
+    </row>
+    <row r="1201" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1201" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1201" s="14"/>
+      <c r="C1201" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1201" s="16" t="s">
+        <v>511</v>
+      </c>
+      <c r="E1201" s="15"/>
+      <c r="F1201" s="15"/>
+      <c r="G1201" s="17"/>
+      <c r="H1201" s="17"/>
+    </row>
+    <row r="1202" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1202" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1202" s="14"/>
+      <c r="C1202" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1202" s="18" t="s">
+        <v>484</v>
+      </c>
+      <c r="E1202" s="15"/>
+      <c r="F1202" s="15"/>
+      <c r="G1202" s="17"/>
+      <c r="H1202" s="17"/>
+    </row>
+    <row r="1203" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1203" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1203" s="14">
+        <v>0.37291666666666667</v>
+      </c>
+      <c r="C1203" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1203" s="16" t="s">
+        <v>485</v>
+      </c>
+      <c r="E1203" s="15"/>
+      <c r="F1203" s="15"/>
+      <c r="G1203" s="17"/>
+      <c r="H1203" s="17"/>
+    </row>
+    <row r="1204" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1204" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1204" s="14"/>
+      <c r="C1204" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1204" s="16" t="s">
+        <v>486</v>
+      </c>
+      <c r="E1204" s="15"/>
+      <c r="F1204" s="15"/>
+      <c r="G1204" s="17"/>
+      <c r="H1204" s="17"/>
+    </row>
+    <row r="1205" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1205" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1205" s="14">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="C1205" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1205" s="16" t="s">
+        <v>487</v>
+      </c>
+      <c r="E1205" s="15"/>
+      <c r="F1205" s="15"/>
+      <c r="G1205" s="17"/>
+      <c r="H1205" s="17"/>
+    </row>
+    <row r="1206" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1206" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1206" s="14"/>
+      <c r="C1206" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1206" s="16" t="s">
+        <v>488</v>
+      </c>
+      <c r="E1206" s="15"/>
+      <c r="F1206" s="15"/>
+      <c r="G1206" s="17"/>
+      <c r="H1206" s="17"/>
+    </row>
+    <row r="1207" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1207" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1207" s="14">
+        <v>0.39791666666666664</v>
+      </c>
+      <c r="C1207" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1207" s="16" t="s">
+        <v>489</v>
+      </c>
+      <c r="E1207" s="15"/>
+      <c r="F1207" s="15"/>
+      <c r="G1207" s="17"/>
+      <c r="H1207" s="17"/>
+    </row>
+    <row r="1208" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1208" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1208" s="14"/>
+      <c r="C1208" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1208" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="E1208" s="15"/>
+      <c r="F1208" s="15"/>
+      <c r="G1208" s="17"/>
+      <c r="H1208" s="17"/>
+    </row>
+    <row r="1209" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1209" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1209" s="14">
+        <v>0.42222222222222222</v>
+      </c>
+      <c r="C1209" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1209" s="16" t="s">
+        <v>464</v>
+      </c>
+      <c r="E1209" s="15"/>
+      <c r="F1209" s="15"/>
+      <c r="G1209" s="17"/>
+      <c r="H1209" s="17"/>
+    </row>
+    <row r="1210" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1210" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1210" s="14"/>
+      <c r="C1210" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1210" s="16" t="s">
+        <v>491</v>
+      </c>
+      <c r="E1210" s="15"/>
+      <c r="F1210" s="15"/>
+      <c r="G1210" s="17"/>
+      <c r="H1210" s="17"/>
+    </row>
+    <row r="1211" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1211" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1211" s="14"/>
+      <c r="C1211" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1211" s="16" t="s">
+        <v>492</v>
+      </c>
+      <c r="E1211" s="15"/>
+      <c r="F1211" s="15"/>
+      <c r="G1211" s="17"/>
+      <c r="H1211" s="17"/>
+    </row>
+    <row r="1212" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1212" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1212" s="14">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="C1212" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1212" s="16" t="s">
+        <v>493</v>
+      </c>
+      <c r="E1212" s="15"/>
+      <c r="F1212" s="15"/>
+      <c r="G1212" s="17"/>
+      <c r="H1212" s="17"/>
+    </row>
+    <row r="1213" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1213" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1213" s="14"/>
+      <c r="C1213" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1213" s="16" t="s">
+        <v>494</v>
+      </c>
+      <c r="E1213" s="15"/>
+      <c r="F1213" s="15"/>
+      <c r="G1213" s="17"/>
+      <c r="H1213" s="17"/>
+    </row>
+    <row r="1214" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1214" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1214" s="14">
+        <v>0.45208333333333334</v>
+      </c>
+      <c r="C1214" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1214" s="16" t="s">
+        <v>495</v>
+      </c>
+      <c r="E1214" s="15"/>
+      <c r="F1214" s="15"/>
+      <c r="G1214" s="17"/>
+      <c r="H1214" s="17"/>
+    </row>
+    <row r="1215" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1215" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1215" s="14">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="C1215" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1215" s="16" t="s">
+        <v>496</v>
+      </c>
+      <c r="E1215" s="15"/>
+      <c r="F1215" s="15"/>
+      <c r="G1215" s="17"/>
+      <c r="H1215" s="17"/>
+    </row>
+    <row r="1216" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1216" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1216" s="14">
+        <v>0.57430555555555551</v>
+      </c>
+      <c r="C1216" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1216" s="16" t="s">
+        <v>470</v>
+      </c>
+      <c r="E1216" s="15"/>
+      <c r="F1216" s="15"/>
+      <c r="G1216" s="17"/>
+      <c r="H1216" s="17"/>
+    </row>
+    <row r="1217" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1217" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1217" s="14">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="C1217" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1217" s="16" t="s">
+        <v>472</v>
+      </c>
+      <c r="E1217" s="15"/>
+      <c r="F1217" s="15"/>
+      <c r="G1217" s="17"/>
+      <c r="H1217" s="17"/>
+    </row>
+    <row r="1218" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1218" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1218" s="14"/>
+      <c r="C1218" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1218" s="16" t="s">
+        <v>473</v>
+      </c>
+      <c r="E1218" s="15"/>
+      <c r="F1218" s="15"/>
+      <c r="G1218" s="17"/>
+      <c r="H1218" s="17"/>
+    </row>
+    <row r="1219" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1219" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1219" s="14">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="C1219" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1219" s="16" t="s">
+        <v>474</v>
+      </c>
+      <c r="E1219" s="15"/>
+      <c r="F1219" s="15"/>
+      <c r="G1219" s="17"/>
+      <c r="H1219" s="17"/>
+    </row>
+    <row r="1220" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1220" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B1220" s="14"/>
+      <c r="C1220" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1220" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1220" s="15"/>
+      <c r="F1220" s="15"/>
+      <c r="G1220" s="17"/>
+      <c r="H1220" s="17"/>
+    </row>
+    <row r="1221" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1221" s="15"/>
+      <c r="B1221" s="15"/>
+      <c r="C1221" s="15"/>
+      <c r="D1221" s="15"/>
+      <c r="E1221" s="15"/>
+      <c r="F1221" s="15"/>
+      <c r="G1221" s="17"/>
+      <c r="H1221" s="17"/>
+    </row>
+    <row r="1222" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1222" s="15"/>
+      <c r="B1222" s="15"/>
+      <c r="C1222" s="15"/>
+      <c r="D1222" s="15"/>
+      <c r="E1222" s="15"/>
+      <c r="F1222" s="15"/>
+      <c r="G1222" s="17"/>
+      <c r="H1222" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="D1078:F1078"/>
+    <mergeCell ref="D1072:F1072"/>
+    <mergeCell ref="D1070:F1070"/>
+    <mergeCell ref="D1071:F1071"/>
+    <mergeCell ref="D1077:F1077"/>
+    <mergeCell ref="D1074:F1074"/>
+    <mergeCell ref="D1075:F1075"/>
+    <mergeCell ref="D1076:F1076"/>
+    <mergeCell ref="D1069:F1069"/>
+    <mergeCell ref="D1066:F1066"/>
+    <mergeCell ref="D1067:F1067"/>
+    <mergeCell ref="D1052:F1052"/>
+    <mergeCell ref="D1053:F1053"/>
+    <mergeCell ref="D1054:F1054"/>
+    <mergeCell ref="D1055:F1055"/>
+    <mergeCell ref="D1056:F1056"/>
+    <mergeCell ref="D1057:F1057"/>
+    <mergeCell ref="D1058:F1058"/>
+    <mergeCell ref="D1059:F1059"/>
+    <mergeCell ref="D1060:F1060"/>
+    <mergeCell ref="D1061:F1061"/>
+    <mergeCell ref="D1049:F1049"/>
+    <mergeCell ref="D1050:F1050"/>
+    <mergeCell ref="D1051:F1051"/>
+    <mergeCell ref="D1065:F1065"/>
+    <mergeCell ref="D1068:F1068"/>
+    <mergeCell ref="D1064:F1064"/>
+    <mergeCell ref="D1062:F1062"/>
+    <mergeCell ref="D1063:F1063"/>
+    <mergeCell ref="D1047:F1047"/>
+    <mergeCell ref="D1048:F1048"/>
+    <mergeCell ref="D987:F987"/>
+    <mergeCell ref="D988:F988"/>
+    <mergeCell ref="D981:F981"/>
+    <mergeCell ref="D982:F982"/>
+    <mergeCell ref="D983:F983"/>
+    <mergeCell ref="D984:F984"/>
+    <mergeCell ref="D985:F985"/>
+    <mergeCell ref="D986:F986"/>
     <mergeCell ref="D965:F965"/>
     <mergeCell ref="D966:F966"/>
     <mergeCell ref="D967:F967"/>
@@ -18695,45 +19727,6 @@
     <mergeCell ref="D977:F977"/>
     <mergeCell ref="D978:F978"/>
     <mergeCell ref="D979:F979"/>
-    <mergeCell ref="D1047:F1047"/>
-    <mergeCell ref="D1048:F1048"/>
-    <mergeCell ref="D987:F987"/>
-    <mergeCell ref="D988:F988"/>
-    <mergeCell ref="D981:F981"/>
-    <mergeCell ref="D982:F982"/>
-    <mergeCell ref="D983:F983"/>
-    <mergeCell ref="D984:F984"/>
-    <mergeCell ref="D985:F985"/>
-    <mergeCell ref="D986:F986"/>
-    <mergeCell ref="D1049:F1049"/>
-    <mergeCell ref="D1050:F1050"/>
-    <mergeCell ref="D1051:F1051"/>
-    <mergeCell ref="D1065:F1065"/>
-    <mergeCell ref="D1068:F1068"/>
-    <mergeCell ref="D1064:F1064"/>
-    <mergeCell ref="D1062:F1062"/>
-    <mergeCell ref="D1063:F1063"/>
-    <mergeCell ref="D1069:F1069"/>
-    <mergeCell ref="D1066:F1066"/>
-    <mergeCell ref="D1067:F1067"/>
-    <mergeCell ref="D1052:F1052"/>
-    <mergeCell ref="D1053:F1053"/>
-    <mergeCell ref="D1054:F1054"/>
-    <mergeCell ref="D1055:F1055"/>
-    <mergeCell ref="D1056:F1056"/>
-    <mergeCell ref="D1057:F1057"/>
-    <mergeCell ref="D1058:F1058"/>
-    <mergeCell ref="D1059:F1059"/>
-    <mergeCell ref="D1060:F1060"/>
-    <mergeCell ref="D1061:F1061"/>
-    <mergeCell ref="D1078:F1078"/>
-    <mergeCell ref="D1072:F1072"/>
-    <mergeCell ref="D1070:F1070"/>
-    <mergeCell ref="D1071:F1071"/>
-    <mergeCell ref="D1077:F1077"/>
-    <mergeCell ref="D1074:F1074"/>
-    <mergeCell ref="D1075:F1075"/>
-    <mergeCell ref="D1076:F1076"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C898BE7-962E-4EBC-9C7C-7F22035B4D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28ACABF2-263B-413F-A618-8179B86B5837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2442" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2442" uniqueCount="511">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1948,10 +1948,6 @@
   </si>
   <si>
     <t>wait D01 team(Michael)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>sail to</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2056,7 +2052,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2088,19 +2084,10 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2387,7 +2374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1222"/>
+  <dimension ref="A1:F1220"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.296875" style="1" bestFit="1" customWidth="1"/>
@@ -15636,11 +15623,11 @@
       <c r="C965" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D965" s="12" t="s">
+      <c r="D965" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="E965" s="12"/>
-      <c r="F965" s="12"/>
+      <c r="E965" s="13"/>
+      <c r="F965" s="13"/>
     </row>
     <row r="966" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A966" s="2">
@@ -15652,11 +15639,11 @@
       <c r="C966" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D966" s="12" t="s">
+      <c r="D966" s="13" t="s">
         <v>409</v>
       </c>
-      <c r="E966" s="12"/>
-      <c r="F966" s="12"/>
+      <c r="E966" s="13"/>
+      <c r="F966" s="13"/>
     </row>
     <row r="967" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A967" s="2">
@@ -15666,11 +15653,11 @@
       <c r="C967" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D967" s="12" t="s">
+      <c r="D967" s="13" t="s">
         <v>410</v>
       </c>
-      <c r="E967" s="12"/>
-      <c r="F967" s="12"/>
+      <c r="E967" s="13"/>
+      <c r="F967" s="13"/>
     </row>
     <row r="968" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A968" s="2">
@@ -15682,11 +15669,11 @@
       <c r="C968" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D968" s="12" t="s">
+      <c r="D968" s="13" t="s">
         <v>382</v>
       </c>
-      <c r="E968" s="12"/>
-      <c r="F968" s="12"/>
+      <c r="E968" s="13"/>
+      <c r="F968" s="13"/>
     </row>
     <row r="969" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A969" s="2">
@@ -15698,11 +15685,11 @@
       <c r="C969" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D969" s="12" t="s">
+      <c r="D969" s="13" t="s">
         <v>383</v>
       </c>
-      <c r="E969" s="12"/>
-      <c r="F969" s="12"/>
+      <c r="E969" s="13"/>
+      <c r="F969" s="13"/>
     </row>
     <row r="970" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A970" s="2">
@@ -15712,11 +15699,11 @@
       <c r="C970" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D970" s="12" t="s">
+      <c r="D970" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="E970" s="12"/>
-      <c r="F970" s="12"/>
+      <c r="E970" s="13"/>
+      <c r="F970" s="13"/>
     </row>
     <row r="971" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A971" s="2">
@@ -15728,11 +15715,11 @@
       <c r="C971" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D971" s="12" t="s">
+      <c r="D971" s="13" t="s">
         <v>398</v>
       </c>
-      <c r="E971" s="12"/>
-      <c r="F971" s="12"/>
+      <c r="E971" s="13"/>
+      <c r="F971" s="13"/>
     </row>
     <row r="972" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A972" s="2">
@@ -15744,11 +15731,11 @@
       <c r="C972" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D972" s="12" t="s">
+      <c r="D972" s="13" t="s">
         <v>386</v>
       </c>
-      <c r="E972" s="12"/>
-      <c r="F972" s="12"/>
+      <c r="E972" s="13"/>
+      <c r="F972" s="13"/>
     </row>
     <row r="973" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A973" s="2">
@@ -15758,11 +15745,11 @@
       <c r="C973" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D973" s="12" t="s">
+      <c r="D973" s="13" t="s">
         <v>411</v>
       </c>
-      <c r="E973" s="12"/>
-      <c r="F973" s="12"/>
+      <c r="E973" s="13"/>
+      <c r="F973" s="13"/>
     </row>
     <row r="974" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A974" s="2">
@@ -15772,11 +15759,11 @@
       <c r="C974" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D974" s="12" t="s">
+      <c r="D974" s="13" t="s">
         <v>412</v>
       </c>
-      <c r="E974" s="12"/>
-      <c r="F974" s="12"/>
+      <c r="E974" s="13"/>
+      <c r="F974" s="13"/>
     </row>
     <row r="975" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A975" s="2">
@@ -15786,11 +15773,11 @@
       <c r="C975" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D975" s="12" t="s">
+      <c r="D975" s="13" t="s">
         <v>413</v>
       </c>
-      <c r="E975" s="12"/>
-      <c r="F975" s="12"/>
+      <c r="E975" s="13"/>
+      <c r="F975" s="13"/>
     </row>
     <row r="976" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A976" s="2">
@@ -15800,11 +15787,11 @@
       <c r="C976" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D976" s="12" t="s">
+      <c r="D976" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="E976" s="12"/>
-      <c r="F976" s="12"/>
+      <c r="E976" s="13"/>
+      <c r="F976" s="13"/>
     </row>
     <row r="977" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A977" s="2">
@@ -15816,11 +15803,11 @@
       <c r="C977" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D977" s="12" t="s">
+      <c r="D977" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E977" s="12"/>
-      <c r="F977" s="12"/>
+      <c r="E977" s="13"/>
+      <c r="F977" s="13"/>
     </row>
     <row r="978" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A978" s="2">
@@ -15830,11 +15817,11 @@
       <c r="C978" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D978" s="12" t="s">
+      <c r="D978" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="E978" s="12"/>
-      <c r="F978" s="12"/>
+      <c r="E978" s="13"/>
+      <c r="F978" s="13"/>
     </row>
     <row r="979" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A979" s="2">
@@ -15846,11 +15833,11 @@
       <c r="C979" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D979" s="12" t="s">
+      <c r="D979" s="13" t="s">
         <v>386</v>
       </c>
-      <c r="E979" s="12"/>
-      <c r="F979" s="12"/>
+      <c r="E979" s="13"/>
+      <c r="F979" s="13"/>
     </row>
     <row r="980" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A980" s="2">
@@ -15860,11 +15847,11 @@
       <c r="C980" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D980" s="12" t="s">
+      <c r="D980" s="13" t="s">
         <v>414</v>
       </c>
-      <c r="E980" s="12"/>
-      <c r="F980" s="12"/>
+      <c r="E980" s="13"/>
+      <c r="F980" s="13"/>
     </row>
     <row r="981" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A981" s="2">
@@ -15874,11 +15861,11 @@
       <c r="C981" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D981" s="12" t="s">
+      <c r="D981" s="13" t="s">
         <v>415</v>
       </c>
-      <c r="E981" s="12"/>
-      <c r="F981" s="12"/>
+      <c r="E981" s="13"/>
+      <c r="F981" s="13"/>
     </row>
     <row r="982" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A982" s="2">
@@ -15890,11 +15877,11 @@
       <c r="C982" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D982" s="12" t="s">
+      <c r="D982" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E982" s="12"/>
-      <c r="F982" s="12"/>
+      <c r="E982" s="13"/>
+      <c r="F982" s="13"/>
     </row>
     <row r="983" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A983" s="2">
@@ -15904,11 +15891,11 @@
       <c r="C983" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D983" s="12" t="s">
+      <c r="D983" s="13" t="s">
         <v>390</v>
       </c>
-      <c r="E983" s="12"/>
-      <c r="F983" s="12"/>
+      <c r="E983" s="13"/>
+      <c r="F983" s="13"/>
     </row>
     <row r="984" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A984" s="2">
@@ -15918,11 +15905,11 @@
       <c r="C984" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D984" s="12" t="s">
+      <c r="D984" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="E984" s="12"/>
-      <c r="F984" s="12"/>
+      <c r="E984" s="13"/>
+      <c r="F984" s="13"/>
     </row>
     <row r="985" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A985" s="2">
@@ -15934,11 +15921,11 @@
       <c r="C985" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D985" s="12" t="s">
+      <c r="D985" s="13" t="s">
         <v>391</v>
       </c>
-      <c r="E985" s="12"/>
-      <c r="F985" s="12"/>
+      <c r="E985" s="13"/>
+      <c r="F985" s="13"/>
     </row>
     <row r="986" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A986" s="2">
@@ -15950,11 +15937,11 @@
       <c r="C986" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D986" s="12" t="s">
+      <c r="D986" s="13" t="s">
         <v>394</v>
       </c>
-      <c r="E986" s="12"/>
-      <c r="F986" s="12"/>
+      <c r="E986" s="13"/>
+      <c r="F986" s="13"/>
     </row>
     <row r="987" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A987" s="2">
@@ -15966,11 +15953,11 @@
       <c r="C987" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D987" s="12" t="s">
+      <c r="D987" s="13" t="s">
         <v>379</v>
       </c>
-      <c r="E987" s="12"/>
-      <c r="F987" s="12"/>
+      <c r="E987" s="13"/>
+      <c r="F987" s="13"/>
     </row>
     <row r="988" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A988" s="2">
@@ -15980,11 +15967,11 @@
       <c r="C988" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D988" s="12" t="s">
+      <c r="D988" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="E988" s="12"/>
-      <c r="F988" s="12"/>
+      <c r="E988" s="13"/>
+      <c r="F988" s="13"/>
     </row>
     <row r="989" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A989" s="2">
@@ -16872,11 +16859,11 @@
       <c r="C1047" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1047" s="12" t="s">
+      <c r="D1047" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="E1047" s="12"/>
-      <c r="F1047" s="12"/>
+      <c r="E1047" s="13"/>
+      <c r="F1047" s="13"/>
     </row>
     <row r="1048" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1048" s="2">
@@ -16888,11 +16875,11 @@
       <c r="C1048" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1048" s="12" t="s">
+      <c r="D1048" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="E1048" s="12"/>
-      <c r="F1048" s="12"/>
+      <c r="E1048" s="13"/>
+      <c r="F1048" s="13"/>
     </row>
     <row r="1049" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1049" s="2">
@@ -16902,11 +16889,11 @@
       <c r="C1049" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1049" s="12" t="s">
+      <c r="D1049" s="13" t="s">
         <v>433</v>
       </c>
-      <c r="E1049" s="12"/>
-      <c r="F1049" s="12"/>
+      <c r="E1049" s="13"/>
+      <c r="F1049" s="13"/>
     </row>
     <row r="1050" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1050" s="2">
@@ -16918,11 +16905,11 @@
       <c r="C1050" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1050" s="12" t="s">
+      <c r="D1050" s="13" t="s">
         <v>398</v>
       </c>
-      <c r="E1050" s="12"/>
-      <c r="F1050" s="12"/>
+      <c r="E1050" s="13"/>
+      <c r="F1050" s="13"/>
     </row>
     <row r="1051" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1051" s="2">
@@ -16934,11 +16921,11 @@
       <c r="C1051" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1051" s="12" t="s">
+      <c r="D1051" s="13" t="s">
         <v>434</v>
       </c>
-      <c r="E1051" s="12"/>
-      <c r="F1051" s="12"/>
+      <c r="E1051" s="13"/>
+      <c r="F1051" s="13"/>
     </row>
     <row r="1052" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1052" s="2">
@@ -16948,11 +16935,11 @@
       <c r="C1052" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1052" s="12" t="s">
+      <c r="D1052" s="13" t="s">
         <v>435</v>
       </c>
-      <c r="E1052" s="12"/>
-      <c r="F1052" s="12"/>
+      <c r="E1052" s="13"/>
+      <c r="F1052" s="13"/>
     </row>
     <row r="1053" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1053" s="2">
@@ -16964,11 +16951,11 @@
       <c r="C1053" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1053" s="12" t="s">
+      <c r="D1053" s="13" t="s">
         <v>436</v>
       </c>
-      <c r="E1053" s="12"/>
-      <c r="F1053" s="12"/>
+      <c r="E1053" s="13"/>
+      <c r="F1053" s="13"/>
     </row>
     <row r="1054" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1054" s="2">
@@ -16978,11 +16965,11 @@
       <c r="C1054" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1054" s="12" t="s">
+      <c r="D1054" s="13" t="s">
         <v>390</v>
       </c>
-      <c r="E1054" s="12"/>
-      <c r="F1054" s="12"/>
+      <c r="E1054" s="13"/>
+      <c r="F1054" s="13"/>
     </row>
     <row r="1055" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1055" s="2">
@@ -16992,11 +16979,11 @@
       <c r="C1055" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1055" s="12" t="s">
+      <c r="D1055" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="E1055" s="12"/>
-      <c r="F1055" s="12"/>
+      <c r="E1055" s="13"/>
+      <c r="F1055" s="13"/>
     </row>
     <row r="1056" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1056" s="2">
@@ -17008,11 +16995,11 @@
       <c r="C1056" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1056" s="12" t="s">
+      <c r="D1056" s="13" t="s">
         <v>437</v>
       </c>
-      <c r="E1056" s="12"/>
-      <c r="F1056" s="12"/>
+      <c r="E1056" s="13"/>
+      <c r="F1056" s="13"/>
     </row>
     <row r="1057" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1057" s="2">
@@ -17024,11 +17011,11 @@
       <c r="C1057" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1057" s="12" t="s">
+      <c r="D1057" s="13" t="s">
         <v>438</v>
       </c>
-      <c r="E1057" s="12"/>
-      <c r="F1057" s="12"/>
+      <c r="E1057" s="13"/>
+      <c r="F1057" s="13"/>
     </row>
     <row r="1058" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1058" s="2">
@@ -17040,11 +17027,11 @@
       <c r="C1058" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1058" s="12" t="s">
+      <c r="D1058" s="13" t="s">
         <v>439</v>
       </c>
-      <c r="E1058" s="12"/>
-      <c r="F1058" s="12"/>
+      <c r="E1058" s="13"/>
+      <c r="F1058" s="13"/>
     </row>
     <row r="1059" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1059" s="2">
@@ -17056,11 +17043,11 @@
       <c r="C1059" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1059" s="12" t="s">
+      <c r="D1059" s="13" t="s">
         <v>394</v>
       </c>
-      <c r="E1059" s="12"/>
-      <c r="F1059" s="12"/>
+      <c r="E1059" s="13"/>
+      <c r="F1059" s="13"/>
     </row>
     <row r="1060" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1060" s="2">
@@ -17072,11 +17059,11 @@
       <c r="C1060" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1060" s="12" t="s">
+      <c r="D1060" s="13" t="s">
         <v>379</v>
       </c>
-      <c r="E1060" s="12"/>
-      <c r="F1060" s="12"/>
+      <c r="E1060" s="13"/>
+      <c r="F1060" s="13"/>
     </row>
     <row r="1061" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1061" s="2">
@@ -17086,11 +17073,11 @@
       <c r="C1061" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1061" s="12" t="s">
+      <c r="D1061" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="E1061" s="12"/>
-      <c r="F1061" s="12"/>
+      <c r="E1061" s="13"/>
+      <c r="F1061" s="13"/>
     </row>
     <row r="1062" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1062" s="2">
@@ -17102,11 +17089,11 @@
       <c r="C1062" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1062" s="12" t="s">
+      <c r="D1062" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="E1062" s="12"/>
-      <c r="F1062" s="12"/>
+      <c r="E1062" s="13"/>
+      <c r="F1062" s="13"/>
     </row>
     <row r="1063" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1063" s="2">
@@ -17118,11 +17105,11 @@
       <c r="C1063" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1063" s="12" t="s">
+      <c r="D1063" s="13" t="s">
         <v>440</v>
       </c>
-      <c r="E1063" s="12"/>
-      <c r="F1063" s="12"/>
+      <c r="E1063" s="13"/>
+      <c r="F1063" s="13"/>
     </row>
     <row r="1064" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1064" s="2">
@@ -17134,11 +17121,11 @@
       <c r="C1064" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1064" s="12" t="s">
+      <c r="D1064" s="13" t="s">
         <v>441</v>
       </c>
-      <c r="E1064" s="12"/>
-      <c r="F1064" s="12"/>
+      <c r="E1064" s="13"/>
+      <c r="F1064" s="13"/>
     </row>
     <row r="1065" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1065" s="2">
@@ -17150,11 +17137,11 @@
       <c r="C1065" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1065" s="12" t="s">
+      <c r="D1065" s="13" t="s">
         <v>442</v>
       </c>
-      <c r="E1065" s="12"/>
-      <c r="F1065" s="12"/>
+      <c r="E1065" s="13"/>
+      <c r="F1065" s="13"/>
     </row>
     <row r="1066" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1066" s="2">
@@ -17166,11 +17153,11 @@
       <c r="C1066" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1066" s="12" t="s">
+      <c r="D1066" s="13" t="s">
         <v>443</v>
       </c>
-      <c r="E1066" s="12"/>
-      <c r="F1066" s="12"/>
+      <c r="E1066" s="13"/>
+      <c r="F1066" s="13"/>
     </row>
     <row r="1067" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1067" s="2">
@@ -17180,11 +17167,11 @@
       <c r="C1067" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1067" s="12" t="s">
+      <c r="D1067" s="13" t="s">
         <v>444</v>
       </c>
-      <c r="E1067" s="12"/>
-      <c r="F1067" s="12"/>
+      <c r="E1067" s="13"/>
+      <c r="F1067" s="13"/>
     </row>
     <row r="1068" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1068" s="2">
@@ -17194,11 +17181,11 @@
       <c r="C1068" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1068" s="12" t="s">
+      <c r="D1068" s="13" t="s">
         <v>445</v>
       </c>
-      <c r="E1068" s="12"/>
-      <c r="F1068" s="12"/>
+      <c r="E1068" s="13"/>
+      <c r="F1068" s="13"/>
     </row>
     <row r="1069" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1069" s="2">
@@ -17210,11 +17197,11 @@
       <c r="C1069" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1069" s="12" t="s">
+      <c r="D1069" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="E1069" s="12"/>
-      <c r="F1069" s="12"/>
+      <c r="E1069" s="13"/>
+      <c r="F1069" s="13"/>
     </row>
     <row r="1070" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1070" s="2">
@@ -17224,11 +17211,11 @@
       <c r="C1070" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1070" s="12" t="s">
+      <c r="D1070" s="13" t="s">
         <v>446</v>
       </c>
-      <c r="E1070" s="12"/>
-      <c r="F1070" s="12"/>
+      <c r="E1070" s="13"/>
+      <c r="F1070" s="13"/>
     </row>
     <row r="1071" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1071" s="2">
@@ -17240,11 +17227,11 @@
       <c r="C1071" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1071" s="12" t="s">
+      <c r="D1071" s="13" t="s">
         <v>447</v>
       </c>
-      <c r="E1071" s="12"/>
-      <c r="F1071" s="12"/>
+      <c r="E1071" s="13"/>
+      <c r="F1071" s="13"/>
     </row>
     <row r="1072" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1072" s="2">
@@ -17254,11 +17241,11 @@
       <c r="C1072" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1072" s="12" t="s">
+      <c r="D1072" s="13" t="s">
         <v>448</v>
       </c>
-      <c r="E1072" s="12"/>
-      <c r="F1072" s="12"/>
+      <c r="E1072" s="13"/>
+      <c r="F1072" s="13"/>
     </row>
     <row r="1073" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1073" s="2">
@@ -17282,11 +17269,11 @@
       <c r="C1074" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1074" s="12" t="s">
+      <c r="D1074" s="13" t="s">
         <v>450</v>
       </c>
-      <c r="E1074" s="12"/>
-      <c r="F1074" s="12"/>
+      <c r="E1074" s="13"/>
+      <c r="F1074" s="13"/>
     </row>
     <row r="1075" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1075" s="2">
@@ -17298,11 +17285,11 @@
       <c r="C1075" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1075" s="12" t="s">
+      <c r="D1075" s="13" t="s">
         <v>451</v>
       </c>
-      <c r="E1075" s="12"/>
-      <c r="F1075" s="12"/>
+      <c r="E1075" s="13"/>
+      <c r="F1075" s="13"/>
     </row>
     <row r="1076" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1076" s="2">
@@ -17314,11 +17301,11 @@
       <c r="C1076" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1076" s="12" t="s">
+      <c r="D1076" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="E1076" s="12"/>
-      <c r="F1076" s="12"/>
+      <c r="E1076" s="13"/>
+      <c r="F1076" s="13"/>
     </row>
     <row r="1077" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1077" s="2">
@@ -17330,11 +17317,11 @@
       <c r="C1077" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1077" s="12" t="s">
+      <c r="D1077" s="13" t="s">
         <v>379</v>
       </c>
-      <c r="E1077" s="12"/>
-      <c r="F1077" s="12"/>
+      <c r="E1077" s="13"/>
+      <c r="F1077" s="13"/>
     </row>
     <row r="1078" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1078" s="2">
@@ -17344,11 +17331,11 @@
       <c r="C1078" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D1078" s="12" t="s">
+      <c r="D1078" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="E1078" s="12"/>
-      <c r="F1078" s="12"/>
+      <c r="E1078" s="13"/>
+      <c r="F1078" s="13"/>
     </row>
     <row r="1079" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1079" s="2">
@@ -17946,7 +17933,7 @@
       <c r="E1120" s="8"/>
       <c r="F1120" s="8"/>
     </row>
-    <row r="1121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1121" s="2">
         <v>46312</v>
       </c>
@@ -17960,7 +17947,7 @@
       <c r="E1121" s="8"/>
       <c r="F1121" s="8"/>
     </row>
-    <row r="1122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1122" s="2">
         <v>46312</v>
       </c>
@@ -17974,7 +17961,7 @@
       <c r="E1122" s="8"/>
       <c r="F1122" s="8"/>
     </row>
-    <row r="1123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1123" s="2">
         <v>46312</v>
       </c>
@@ -17990,7 +17977,7 @@
       <c r="E1123" s="8"/>
       <c r="F1123" s="8"/>
     </row>
-    <row r="1124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1124" s="2">
         <v>46312</v>
       </c>
@@ -18006,7 +17993,7 @@
       <c r="E1124" s="8"/>
       <c r="F1124" s="8"/>
     </row>
-    <row r="1125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1125" s="2">
         <v>46312</v>
       </c>
@@ -18020,7 +18007,7 @@
       <c r="E1125" s="8"/>
       <c r="F1125" s="8"/>
     </row>
-    <row r="1126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1126" s="2">
         <v>46312</v>
       </c>
@@ -18036,1681 +18023,1288 @@
       <c r="E1126" s="8"/>
       <c r="F1126" s="8"/>
     </row>
-    <row r="1127" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1127" s="13">
+    <row r="1127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1127" s="2">
         <v>46312</v>
       </c>
-      <c r="B1127" s="14">
+      <c r="B1127" s="10">
         <v>0.55555555555555558</v>
       </c>
-      <c r="C1127" s="15" t="s">
+      <c r="C1127" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D1127" s="16" t="s">
+      <c r="D1127" s="8" t="s">
         <v>483</v>
       </c>
-      <c r="E1127" s="16"/>
-      <c r="F1127" s="16"/>
-      <c r="G1127" s="17"/>
-      <c r="H1127" s="17"/>
-    </row>
-    <row r="1128" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1128" s="13">
+      <c r="E1127" s="8"/>
+      <c r="F1127" s="8"/>
+    </row>
+    <row r="1128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1128" s="2">
         <v>46312</v>
       </c>
-      <c r="B1128" s="14">
+      <c r="B1128" s="10">
         <v>0.57638888888888884</v>
       </c>
-      <c r="C1128" s="15" t="s">
+      <c r="C1128" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D1128" s="16" t="s">
+      <c r="D1128" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="E1128" s="16"/>
-      <c r="F1128" s="16"/>
-      <c r="G1128" s="17"/>
-      <c r="H1128" s="17"/>
-    </row>
-    <row r="1129" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1129" s="13">
+      <c r="E1128" s="8"/>
+      <c r="F1128" s="8"/>
+    </row>
+    <row r="1129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1129" s="2">
         <v>46312</v>
       </c>
-      <c r="B1129" s="14">
+      <c r="B1129" s="10">
         <v>0.67708333333333337</v>
       </c>
-      <c r="C1129" s="15" t="s">
+      <c r="C1129" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D1129" s="16" t="s">
+      <c r="D1129" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="E1129" s="16"/>
-      <c r="F1129" s="16"/>
-      <c r="G1129" s="17"/>
-      <c r="H1129" s="17"/>
-    </row>
-    <row r="1130" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1130" s="13">
+      <c r="E1129" s="8"/>
+      <c r="F1129" s="8"/>
+    </row>
+    <row r="1130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1130" s="2">
         <v>46312</v>
       </c>
-      <c r="B1130" s="14"/>
-      <c r="C1130" s="15" t="s">
+      <c r="B1130" s="10"/>
+      <c r="C1130" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D1130" s="16" t="s">
+      <c r="D1130" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E1130" s="16"/>
-      <c r="F1130" s="16"/>
-      <c r="G1130" s="17"/>
-      <c r="H1130" s="17"/>
-    </row>
-    <row r="1131" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1131" s="13">
+      <c r="E1130" s="8"/>
+      <c r="F1130" s="8"/>
+    </row>
+    <row r="1131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1131" s="2">
         <v>46312</v>
       </c>
-      <c r="B1131" s="14">
+      <c r="B1131" s="10">
         <v>0.25</v>
       </c>
-      <c r="C1131" s="15" t="s">
+      <c r="C1131" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="D1131" s="16" t="s">
+      <c r="D1131" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="E1131" s="15"/>
-      <c r="F1131" s="15"/>
-      <c r="G1131" s="17"/>
-      <c r="H1131" s="17"/>
-    </row>
-    <row r="1132" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1132" s="13">
+    </row>
+    <row r="1132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1132" s="2">
         <v>46312</v>
       </c>
-      <c r="B1132" s="14">
+      <c r="B1132" s="10">
         <v>0.28472222222222221</v>
       </c>
-      <c r="C1132" s="15" t="s">
+      <c r="C1132" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="D1132" s="16" t="s">
+      <c r="D1132" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="E1132" s="15"/>
-      <c r="F1132" s="15"/>
-      <c r="G1132" s="17"/>
-      <c r="H1132" s="17"/>
-    </row>
-    <row r="1133" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1133" s="13">
+    </row>
+    <row r="1133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1133" s="2">
         <v>46312</v>
       </c>
-      <c r="B1133" s="14"/>
-      <c r="C1133" s="15" t="s">
+      <c r="B1133" s="10"/>
+      <c r="C1133" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="D1133" s="16" t="s">
+      <c r="D1133" s="8" t="s">
         <v>461</v>
       </c>
-      <c r="E1133" s="15"/>
-      <c r="F1133" s="15"/>
-      <c r="G1133" s="17"/>
-      <c r="H1133" s="17"/>
-    </row>
-    <row r="1134" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1134" s="13">
+    </row>
+    <row r="1134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1134" s="2">
         <v>46312</v>
       </c>
-      <c r="B1134" s="14">
+      <c r="B1134" s="10">
         <v>0.36458333333333331</v>
       </c>
-      <c r="C1134" s="15" t="s">
+      <c r="C1134" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="D1134" s="16" t="s">
+      <c r="D1134" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="E1134" s="15"/>
-      <c r="F1134" s="15"/>
-      <c r="G1134" s="17"/>
-      <c r="H1134" s="17"/>
-    </row>
-    <row r="1135" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1135" s="13">
+    </row>
+    <row r="1135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1135" s="2">
         <v>46312</v>
       </c>
-      <c r="B1135" s="14"/>
-      <c r="C1135" s="15" t="s">
+      <c r="B1135" s="10"/>
+      <c r="C1135" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="D1135" s="16" t="s">
+      <c r="D1135" s="8" t="s">
         <v>497</v>
       </c>
-      <c r="E1135" s="15"/>
-      <c r="F1135" s="15"/>
-      <c r="G1135" s="17"/>
-      <c r="H1135" s="17"/>
-    </row>
-    <row r="1136" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1136" s="13">
+    </row>
+    <row r="1136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1136" s="2">
         <v>46312</v>
       </c>
-      <c r="B1136" s="14"/>
-      <c r="C1136" s="15" t="s">
+      <c r="B1136" s="10"/>
+      <c r="C1136" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="D1136" s="18" t="s">
+      <c r="D1136" s="12" t="s">
         <v>484</v>
       </c>
-      <c r="E1136" s="15"/>
-      <c r="F1136" s="15"/>
-      <c r="G1136" s="17"/>
-      <c r="H1136" s="17"/>
-    </row>
-    <row r="1137" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1137" s="13">
+    </row>
+    <row r="1137" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1137" s="2">
         <v>46312</v>
       </c>
-      <c r="B1137" s="14">
+      <c r="B1137" s="10">
         <v>0.37291666666666667</v>
       </c>
-      <c r="C1137" s="15" t="s">
+      <c r="C1137" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="D1137" s="16" t="s">
+      <c r="D1137" s="8" t="s">
         <v>485</v>
       </c>
-      <c r="E1137" s="15"/>
-      <c r="F1137" s="15"/>
-      <c r="G1137" s="17"/>
-      <c r="H1137" s="17"/>
-    </row>
-    <row r="1138" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1138" s="13">
+    </row>
+    <row r="1138" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1138" s="2">
         <v>46312</v>
       </c>
-      <c r="B1138" s="14"/>
-      <c r="C1138" s="15" t="s">
+      <c r="B1138" s="10"/>
+      <c r="C1138" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="D1138" s="16" t="s">
+      <c r="D1138" s="8" t="s">
         <v>486</v>
       </c>
-      <c r="E1138" s="15"/>
-      <c r="F1138" s="15"/>
-      <c r="G1138" s="17"/>
-      <c r="H1138" s="17"/>
-    </row>
-    <row r="1139" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1139" s="13">
+    </row>
+    <row r="1139" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1139" s="2">
         <v>46312</v>
       </c>
-      <c r="B1139" s="14">
+      <c r="B1139" s="10">
         <v>0.38194444444444442</v>
       </c>
-      <c r="C1139" s="15" t="s">
+      <c r="C1139" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="D1139" s="16" t="s">
+      <c r="D1139" s="8" t="s">
         <v>487</v>
       </c>
-      <c r="E1139" s="15"/>
-      <c r="F1139" s="15"/>
-      <c r="G1139" s="17"/>
-      <c r="H1139" s="17"/>
-    </row>
-    <row r="1140" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1140" s="13">
+    </row>
+    <row r="1140" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1140" s="2">
         <v>46312</v>
       </c>
-      <c r="B1140" s="14"/>
-      <c r="C1140" s="15" t="s">
+      <c r="B1140" s="10"/>
+      <c r="C1140" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="D1140" s="16" t="s">
+      <c r="D1140" s="8" t="s">
         <v>488</v>
       </c>
-      <c r="E1140" s="15"/>
-      <c r="F1140" s="15"/>
-      <c r="G1140" s="17"/>
-      <c r="H1140" s="17"/>
-    </row>
-    <row r="1141" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1141" s="13">
+    </row>
+    <row r="1141" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1141" s="2">
         <v>46312</v>
       </c>
-      <c r="B1141" s="14">
+      <c r="B1141" s="10">
         <v>0.39791666666666664</v>
       </c>
-      <c r="C1141" s="15" t="s">
+      <c r="C1141" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="D1141" s="16" t="s">
+      <c r="D1141" s="8" t="s">
         <v>489</v>
       </c>
-      <c r="E1141" s="15"/>
-      <c r="F1141" s="15"/>
-      <c r="G1141" s="17"/>
-      <c r="H1141" s="17"/>
-    </row>
-    <row r="1142" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1142" s="13">
+    </row>
+    <row r="1142" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1142" s="2">
         <v>46312</v>
       </c>
-      <c r="B1142" s="14"/>
-      <c r="C1142" s="15" t="s">
+      <c r="B1142" s="10"/>
+      <c r="C1142" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="D1142" s="16" t="s">
+      <c r="D1142" s="8" t="s">
         <v>490</v>
       </c>
-      <c r="E1142" s="15"/>
-      <c r="F1142" s="15"/>
-      <c r="G1142" s="17"/>
-      <c r="H1142" s="17"/>
-    </row>
-    <row r="1143" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1143" s="13">
+    </row>
+    <row r="1143" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1143" s="2">
         <v>46312</v>
       </c>
-      <c r="B1143" s="14">
+      <c r="B1143" s="10">
         <v>0.42222222222222222</v>
       </c>
-      <c r="C1143" s="15" t="s">
+      <c r="C1143" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="D1143" s="16" t="s">
+      <c r="D1143" s="8" t="s">
         <v>464</v>
       </c>
-      <c r="E1143" s="15"/>
-      <c r="F1143" s="15"/>
-      <c r="G1143" s="17"/>
-      <c r="H1143" s="17"/>
-    </row>
-    <row r="1144" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1144" s="13">
+    </row>
+    <row r="1144" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1144" s="2">
         <v>46312</v>
       </c>
-      <c r="B1144" s="14"/>
-      <c r="C1144" s="15" t="s">
+      <c r="B1144" s="10"/>
+      <c r="C1144" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="D1144" s="16" t="s">
+      <c r="D1144" s="8" t="s">
         <v>491</v>
       </c>
-      <c r="E1144" s="15"/>
-      <c r="F1144" s="15"/>
-      <c r="G1144" s="17"/>
-      <c r="H1144" s="17"/>
-    </row>
-    <row r="1145" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1145" s="13">
+    </row>
+    <row r="1145" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1145" s="2">
         <v>46312</v>
       </c>
-      <c r="B1145" s="14"/>
-      <c r="C1145" s="15" t="s">
+      <c r="B1145" s="10"/>
+      <c r="C1145" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="D1145" s="16" t="s">
+      <c r="D1145" s="8" t="s">
         <v>492</v>
       </c>
-      <c r="E1145" s="15"/>
-      <c r="F1145" s="15"/>
-      <c r="G1145" s="17"/>
-      <c r="H1145" s="17"/>
-    </row>
-    <row r="1146" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1146" s="13">
+    </row>
+    <row r="1146" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1146" s="2">
         <v>46312</v>
       </c>
-      <c r="B1146" s="14">
+      <c r="B1146" s="10">
         <v>0.42708333333333331</v>
       </c>
-      <c r="C1146" s="15" t="s">
+      <c r="C1146" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="D1146" s="16" t="s">
+      <c r="D1146" s="8" t="s">
         <v>493</v>
       </c>
-      <c r="E1146" s="15"/>
-      <c r="F1146" s="15"/>
-      <c r="G1146" s="17"/>
-      <c r="H1146" s="17"/>
-    </row>
-    <row r="1147" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1147" s="13">
+    </row>
+    <row r="1147" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1147" s="2">
         <v>46312</v>
       </c>
-      <c r="B1147" s="14"/>
-      <c r="C1147" s="15" t="s">
+      <c r="B1147" s="10"/>
+      <c r="C1147" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="D1147" s="16" t="s">
+      <c r="D1147" s="8" t="s">
         <v>494</v>
       </c>
-      <c r="E1147" s="15"/>
-      <c r="F1147" s="15"/>
-      <c r="G1147" s="17"/>
-      <c r="H1147" s="17"/>
-    </row>
-    <row r="1148" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1148" s="13">
+    </row>
+    <row r="1148" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1148" s="2">
         <v>46312</v>
       </c>
-      <c r="B1148" s="14">
+      <c r="B1148" s="10">
         <v>0.45208333333333334</v>
       </c>
-      <c r="C1148" s="15" t="s">
+      <c r="C1148" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="D1148" s="16" t="s">
+      <c r="D1148" s="8" t="s">
         <v>495</v>
       </c>
-      <c r="E1148" s="15"/>
-      <c r="F1148" s="15"/>
-      <c r="G1148" s="17"/>
-      <c r="H1148" s="17"/>
-    </row>
-    <row r="1149" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1149" s="13">
+    </row>
+    <row r="1149" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1149" s="2">
         <v>46312</v>
       </c>
-      <c r="B1149" s="14">
+      <c r="B1149" s="10">
         <v>0.52916666666666667</v>
       </c>
-      <c r="C1149" s="15" t="s">
+      <c r="C1149" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="D1149" s="16" t="s">
+      <c r="D1149" s="8" t="s">
         <v>496</v>
       </c>
-      <c r="E1149" s="15"/>
-      <c r="F1149" s="15"/>
-      <c r="G1149" s="17"/>
-      <c r="H1149" s="17"/>
-    </row>
-    <row r="1150" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1150" s="13">
+    </row>
+    <row r="1150" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1150" s="2">
         <v>46312</v>
       </c>
-      <c r="B1150" s="14">
+      <c r="B1150" s="10">
         <v>0.57430555555555551</v>
       </c>
-      <c r="C1150" s="15" t="s">
+      <c r="C1150" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="D1150" s="16" t="s">
+      <c r="D1150" s="8" t="s">
         <v>470</v>
       </c>
-      <c r="E1150" s="15"/>
-      <c r="F1150" s="15"/>
-      <c r="G1150" s="17"/>
-      <c r="H1150" s="17"/>
-    </row>
-    <row r="1151" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1151" s="13">
+    </row>
+    <row r="1151" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1151" s="2">
         <v>46312</v>
       </c>
-      <c r="B1151" s="14">
+      <c r="B1151" s="10">
         <v>0.57638888888888884</v>
       </c>
-      <c r="C1151" s="15" t="s">
+      <c r="C1151" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="D1151" s="16" t="s">
+      <c r="D1151" s="8" t="s">
         <v>472</v>
       </c>
-      <c r="E1151" s="15"/>
-      <c r="F1151" s="15"/>
-      <c r="G1151" s="17"/>
-      <c r="H1151" s="17"/>
-    </row>
-    <row r="1152" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1152" s="13">
+    </row>
+    <row r="1152" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1152" s="2">
         <v>46312</v>
       </c>
-      <c r="B1152" s="14"/>
-      <c r="C1152" s="15" t="s">
+      <c r="B1152" s="10"/>
+      <c r="C1152" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="D1152" s="16" t="s">
+      <c r="D1152" s="8" t="s">
         <v>473</v>
       </c>
-      <c r="E1152" s="15"/>
-      <c r="F1152" s="15"/>
-      <c r="G1152" s="17"/>
-      <c r="H1152" s="17"/>
-    </row>
-    <row r="1153" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1153" s="13">
+    </row>
+    <row r="1153" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1153" s="2">
         <v>46312</v>
       </c>
-      <c r="B1153" s="14">
+      <c r="B1153" s="10">
         <v>0.67708333333333337</v>
       </c>
-      <c r="C1153" s="15" t="s">
+      <c r="C1153" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="D1153" s="16" t="s">
+      <c r="D1153" s="8" t="s">
         <v>474</v>
       </c>
-      <c r="E1153" s="15"/>
-      <c r="F1153" s="15"/>
-      <c r="G1153" s="17"/>
-      <c r="H1153" s="17"/>
-    </row>
-    <row r="1154" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1154" s="13">
+    </row>
+    <row r="1154" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1154" s="2">
         <v>46312</v>
       </c>
-      <c r="B1154" s="15"/>
-      <c r="C1154" s="15" t="s">
+      <c r="C1154" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="D1154" s="16" t="s">
+      <c r="D1154" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E1154" s="15"/>
-      <c r="F1154" s="15"/>
-      <c r="G1154" s="17"/>
-      <c r="H1154" s="17"/>
-    </row>
-    <row r="1155" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1155" s="13">
+    </row>
+    <row r="1155" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1155" s="2">
         <v>46312</v>
       </c>
-      <c r="B1155" s="14">
+      <c r="B1155" s="10">
         <v>0.25</v>
       </c>
-      <c r="C1155" s="15" t="s">
+      <c r="C1155" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1155" s="16" t="s">
+      <c r="D1155" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="E1155" s="15"/>
-      <c r="F1155" s="15"/>
-      <c r="G1155" s="17"/>
-      <c r="H1155" s="17"/>
-    </row>
-    <row r="1156" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1156" s="13">
+    </row>
+    <row r="1156" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1156" s="2">
         <v>46312</v>
       </c>
-      <c r="B1156" s="14">
+      <c r="B1156" s="10">
         <v>0.28472222222222221</v>
       </c>
-      <c r="C1156" s="15" t="s">
+      <c r="C1156" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1156" s="16" t="s">
+      <c r="D1156" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="E1156" s="15"/>
-      <c r="F1156" s="15"/>
-      <c r="G1156" s="17"/>
-      <c r="H1156" s="17"/>
-    </row>
-    <row r="1157" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1157" s="13">
+    </row>
+    <row r="1157" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1157" s="2">
         <v>46312</v>
       </c>
-      <c r="B1157" s="14"/>
-      <c r="C1157" s="15" t="s">
+      <c r="B1157" s="10"/>
+      <c r="C1157" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1157" s="16" t="s">
+      <c r="D1157" s="8" t="s">
         <v>461</v>
       </c>
-      <c r="E1157" s="15"/>
-      <c r="F1157" s="15"/>
-      <c r="G1157" s="17"/>
-      <c r="H1157" s="17"/>
-    </row>
-    <row r="1158" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1158" s="13">
+    </row>
+    <row r="1158" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1158" s="2">
         <v>46312</v>
       </c>
-      <c r="B1158" s="14">
+      <c r="B1158" s="10">
         <v>0.36458333333333331</v>
       </c>
-      <c r="C1158" s="15" t="s">
+      <c r="C1158" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1158" s="16" t="s">
+      <c r="D1158" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="E1158" s="15"/>
-      <c r="F1158" s="15"/>
-      <c r="G1158" s="17"/>
-      <c r="H1158" s="17"/>
-    </row>
-    <row r="1159" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1159" s="13">
+    </row>
+    <row r="1159" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1159" s="2">
         <v>46312</v>
       </c>
-      <c r="B1159" s="14"/>
-      <c r="C1159" s="15" t="s">
+      <c r="B1159" s="10"/>
+      <c r="C1159" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1159" s="16" t="s">
+      <c r="D1159" s="8" t="s">
         <v>497</v>
       </c>
-      <c r="E1159" s="15"/>
-      <c r="F1159" s="15"/>
-      <c r="G1159" s="17"/>
-      <c r="H1159" s="17"/>
-    </row>
-    <row r="1160" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1160" s="13">
+    </row>
+    <row r="1160" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1160" s="2">
         <v>46312</v>
       </c>
-      <c r="B1160" s="14"/>
-      <c r="C1160" s="15" t="s">
+      <c r="B1160" s="10"/>
+      <c r="C1160" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1160" s="18" t="s">
+      <c r="D1160" s="12" t="s">
         <v>484</v>
       </c>
-      <c r="E1160" s="15"/>
-      <c r="F1160" s="15"/>
-      <c r="G1160" s="17"/>
-      <c r="H1160" s="17"/>
-    </row>
-    <row r="1161" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1161" s="13">
+    </row>
+    <row r="1161" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1161" s="2">
         <v>46312</v>
       </c>
-      <c r="B1161" s="14">
+      <c r="B1161" s="10">
         <v>0.37291666666666667</v>
       </c>
-      <c r="C1161" s="15" t="s">
+      <c r="C1161" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1161" s="16" t="s">
+      <c r="D1161" s="8" t="s">
         <v>485</v>
       </c>
-      <c r="E1161" s="15"/>
-      <c r="F1161" s="15"/>
-      <c r="G1161" s="17"/>
-      <c r="H1161" s="17"/>
-    </row>
-    <row r="1162" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1162" s="13">
+    </row>
+    <row r="1162" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1162" s="2">
         <v>46312</v>
       </c>
-      <c r="B1162" s="14"/>
-      <c r="C1162" s="15" t="s">
+      <c r="B1162" s="10"/>
+      <c r="C1162" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1162" s="16" t="s">
+      <c r="D1162" s="8" t="s">
         <v>486</v>
       </c>
-      <c r="E1162" s="15"/>
-      <c r="F1162" s="15"/>
-      <c r="G1162" s="17"/>
-      <c r="H1162" s="17"/>
-    </row>
-    <row r="1163" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1163" s="13">
+    </row>
+    <row r="1163" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1163" s="2">
         <v>46312</v>
       </c>
-      <c r="B1163" s="14">
+      <c r="B1163" s="10">
         <v>0.38194444444444442</v>
       </c>
-      <c r="C1163" s="15" t="s">
+      <c r="C1163" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1163" s="16" t="s">
+      <c r="D1163" s="8" t="s">
         <v>487</v>
       </c>
-      <c r="E1163" s="15"/>
-      <c r="F1163" s="15"/>
-      <c r="G1163" s="17"/>
-      <c r="H1163" s="17"/>
-    </row>
-    <row r="1164" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1164" s="13">
+    </row>
+    <row r="1164" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1164" s="2">
         <v>46312</v>
       </c>
-      <c r="B1164" s="14"/>
-      <c r="C1164" s="15" t="s">
+      <c r="B1164" s="10"/>
+      <c r="C1164" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1164" s="16" t="s">
+      <c r="D1164" s="8" t="s">
         <v>488</v>
       </c>
-      <c r="E1164" s="15"/>
-      <c r="F1164" s="15"/>
-      <c r="G1164" s="17"/>
-      <c r="H1164" s="17"/>
-    </row>
-    <row r="1165" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1165" s="13">
+    </row>
+    <row r="1165" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1165" s="2">
         <v>46312</v>
       </c>
-      <c r="B1165" s="14">
+      <c r="B1165" s="10">
         <v>0.39791666666666664</v>
       </c>
-      <c r="C1165" s="15" t="s">
+      <c r="C1165" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1165" s="16" t="s">
+      <c r="D1165" s="8" t="s">
         <v>489</v>
       </c>
-      <c r="E1165" s="15"/>
-      <c r="F1165" s="15"/>
-      <c r="G1165" s="17"/>
-      <c r="H1165" s="17"/>
-    </row>
-    <row r="1166" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1166" s="13">
+    </row>
+    <row r="1166" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1166" s="2">
         <v>46312</v>
       </c>
-      <c r="B1166" s="14"/>
-      <c r="C1166" s="15" t="s">
+      <c r="B1166" s="10"/>
+      <c r="C1166" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1166" s="16" t="s">
+      <c r="D1166" s="8" t="s">
         <v>490</v>
       </c>
-      <c r="E1166" s="15"/>
-      <c r="F1166" s="15"/>
-      <c r="G1166" s="17"/>
-      <c r="H1166" s="17"/>
-    </row>
-    <row r="1167" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1167" s="13">
+    </row>
+    <row r="1167" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1167" s="2">
         <v>46312</v>
       </c>
-      <c r="B1167" s="14">
+      <c r="B1167" s="10">
         <v>0.42222222222222222</v>
       </c>
-      <c r="C1167" s="15" t="s">
+      <c r="C1167" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1167" s="16" t="s">
+      <c r="D1167" s="8" t="s">
         <v>464</v>
       </c>
-      <c r="E1167" s="15"/>
-      <c r="F1167" s="15"/>
-      <c r="G1167" s="17"/>
-      <c r="H1167" s="17"/>
-    </row>
-    <row r="1168" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1168" s="13">
+    </row>
+    <row r="1168" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1168" s="2">
         <v>46312</v>
       </c>
-      <c r="B1168" s="14"/>
-      <c r="C1168" s="15" t="s">
+      <c r="B1168" s="10"/>
+      <c r="C1168" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1168" s="16" t="s">
+      <c r="D1168" s="8" t="s">
         <v>491</v>
       </c>
-      <c r="E1168" s="15"/>
-      <c r="F1168" s="15"/>
-      <c r="G1168" s="17"/>
-      <c r="H1168" s="17"/>
-    </row>
-    <row r="1169" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1169" s="13">
+    </row>
+    <row r="1169" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1169" s="2">
         <v>46312</v>
       </c>
-      <c r="B1169" s="14"/>
-      <c r="C1169" s="15" t="s">
+      <c r="B1169" s="10"/>
+      <c r="C1169" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1169" s="16" t="s">
+      <c r="D1169" s="8" t="s">
         <v>492</v>
       </c>
-      <c r="E1169" s="15"/>
-      <c r="F1169" s="15"/>
-      <c r="G1169" s="17"/>
-      <c r="H1169" s="17"/>
-    </row>
-    <row r="1170" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1170" s="13">
+    </row>
+    <row r="1170" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1170" s="2">
         <v>46312</v>
       </c>
-      <c r="B1170" s="14">
+      <c r="B1170" s="10">
         <v>0.42708333333333331</v>
       </c>
-      <c r="C1170" s="15" t="s">
+      <c r="C1170" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1170" s="16" t="s">
+      <c r="D1170" s="8" t="s">
         <v>493</v>
       </c>
-      <c r="E1170" s="15"/>
-      <c r="F1170" s="15"/>
-      <c r="G1170" s="17"/>
-      <c r="H1170" s="17"/>
-    </row>
-    <row r="1171" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1171" s="13">
+    </row>
+    <row r="1171" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1171" s="2">
         <v>46312</v>
       </c>
-      <c r="B1171" s="14"/>
-      <c r="C1171" s="15" t="s">
+      <c r="B1171" s="10"/>
+      <c r="C1171" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1171" s="16" t="s">
+      <c r="D1171" s="8" t="s">
         <v>494</v>
       </c>
-      <c r="E1171" s="15"/>
-      <c r="F1171" s="15"/>
-      <c r="G1171" s="17"/>
-      <c r="H1171" s="17"/>
-    </row>
-    <row r="1172" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1172" s="13">
+    </row>
+    <row r="1172" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1172" s="2">
         <v>46312</v>
       </c>
-      <c r="B1172" s="14">
+      <c r="B1172" s="10">
         <v>0.45208333333333334</v>
       </c>
-      <c r="C1172" s="15" t="s">
+      <c r="C1172" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1172" s="16" t="s">
+      <c r="D1172" s="8" t="s">
         <v>495</v>
       </c>
-      <c r="E1172" s="15"/>
-      <c r="F1172" s="15"/>
-      <c r="G1172" s="17"/>
-      <c r="H1172" s="17"/>
-    </row>
-    <row r="1173" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1173" s="13">
+    </row>
+    <row r="1173" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1173" s="2">
         <v>46312</v>
       </c>
-      <c r="B1173" s="14">
+      <c r="B1173" s="10">
         <v>0.52916666666666667</v>
       </c>
-      <c r="C1173" s="15" t="s">
+      <c r="C1173" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1173" s="16" t="s">
+      <c r="D1173" s="8" t="s">
         <v>496</v>
       </c>
-      <c r="E1173" s="15"/>
-      <c r="F1173" s="15"/>
-      <c r="G1173" s="17"/>
-      <c r="H1173" s="17"/>
-    </row>
-    <row r="1174" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1174" s="13">
+    </row>
+    <row r="1174" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1174" s="2">
         <v>46312</v>
       </c>
-      <c r="B1174" s="14">
+      <c r="B1174" s="10">
         <v>0.57430555555555551</v>
       </c>
-      <c r="C1174" s="15" t="s">
+      <c r="C1174" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1174" s="16" t="s">
+      <c r="D1174" s="8" t="s">
         <v>470</v>
       </c>
-      <c r="E1174" s="15"/>
-      <c r="F1174" s="15"/>
-      <c r="G1174" s="17"/>
-      <c r="H1174" s="17"/>
-    </row>
-    <row r="1175" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1175" s="13">
+    </row>
+    <row r="1175" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1175" s="2">
         <v>46312</v>
       </c>
-      <c r="B1175" s="14">
+      <c r="B1175" s="10">
         <v>0.57638888888888884</v>
       </c>
-      <c r="C1175" s="15" t="s">
+      <c r="C1175" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1175" s="16" t="s">
+      <c r="D1175" s="8" t="s">
         <v>472</v>
       </c>
-      <c r="E1175" s="15"/>
-      <c r="F1175" s="15"/>
-      <c r="G1175" s="17"/>
-      <c r="H1175" s="17"/>
-    </row>
-    <row r="1176" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1176" s="13">
+    </row>
+    <row r="1176" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1176" s="2">
         <v>46312</v>
       </c>
-      <c r="B1176" s="14"/>
-      <c r="C1176" s="15" t="s">
+      <c r="B1176" s="10"/>
+      <c r="C1176" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1176" s="16" t="s">
+      <c r="D1176" s="8" t="s">
         <v>473</v>
       </c>
-      <c r="E1176" s="15"/>
-      <c r="F1176" s="15"/>
-      <c r="G1176" s="17"/>
-      <c r="H1176" s="17"/>
-    </row>
-    <row r="1177" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1177" s="13">
+    </row>
+    <row r="1177" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1177" s="2">
         <v>46312</v>
       </c>
-      <c r="B1177" s="14">
+      <c r="B1177" s="10">
         <v>0.67708333333333337</v>
       </c>
-      <c r="C1177" s="15" t="s">
+      <c r="C1177" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1177" s="16" t="s">
+      <c r="D1177" s="8" t="s">
         <v>474</v>
       </c>
-      <c r="E1177" s="15"/>
-      <c r="F1177" s="15"/>
-      <c r="G1177" s="17"/>
-      <c r="H1177" s="17"/>
-    </row>
-    <row r="1178" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1178" s="13">
+    </row>
+    <row r="1178" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1178" s="2">
         <v>46312</v>
       </c>
-      <c r="B1178" s="15"/>
-      <c r="C1178" s="15" t="s">
+      <c r="C1178" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1178" s="16" t="s">
+      <c r="D1178" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E1178" s="15"/>
-      <c r="F1178" s="15"/>
-      <c r="G1178" s="17"/>
-      <c r="H1178" s="17"/>
-    </row>
-    <row r="1179" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1179" s="13">
+    </row>
+    <row r="1179" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1179" s="2">
         <v>46313</v>
       </c>
-      <c r="B1179" s="14">
+      <c r="B1179" s="10">
         <v>0.2638888888888889</v>
       </c>
-      <c r="C1179" s="15" t="s">
+      <c r="C1179" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1179" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="E1179" s="8"/>
+      <c r="F1179" s="8"/>
+    </row>
+    <row r="1180" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1180" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1180" s="10">
+        <v>0.34722222222222221</v>
+      </c>
+      <c r="C1180" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1180" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="E1180" s="8"/>
+      <c r="F1180" s="8"/>
+    </row>
+    <row r="1181" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1181" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1181" s="10"/>
+      <c r="C1181" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1181" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="E1181" s="8"/>
+      <c r="F1181" s="8"/>
+    </row>
+    <row r="1182" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1182" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1182" s="10">
+        <v>0.36319444444444443</v>
+      </c>
+      <c r="C1182" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1182" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="E1182" s="8"/>
+      <c r="F1182" s="8"/>
+    </row>
+    <row r="1183" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1183" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1183" s="10">
+        <v>0.37152777777777779</v>
+      </c>
+      <c r="C1183" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1183" s="8" t="s">
+        <v>503</v>
+      </c>
+      <c r="E1183" s="8"/>
+      <c r="F1183" s="8"/>
+    </row>
+    <row r="1184" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1184" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1184" s="10">
+        <v>0.37847222222222221</v>
+      </c>
+      <c r="C1184" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1184" s="8" t="s">
+        <v>504</v>
+      </c>
+      <c r="E1184" s="8"/>
+      <c r="F1184" s="8"/>
+    </row>
+    <row r="1185" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1185" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1185" s="10"/>
+      <c r="C1185" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1185" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="E1185" s="8"/>
+      <c r="F1185" s="8"/>
+    </row>
+    <row r="1186" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1186" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1186" s="10">
+        <v>0.41388888888888886</v>
+      </c>
+      <c r="C1186" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1186" s="8" t="s">
+        <v>478</v>
+      </c>
+      <c r="E1186" s="8"/>
+      <c r="F1186" s="8"/>
+    </row>
+    <row r="1187" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1187" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1187" s="10">
+        <v>0.43402777777777779</v>
+      </c>
+      <c r="C1187" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1187" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="E1187" s="8"/>
+      <c r="F1187" s="8"/>
+    </row>
+    <row r="1188" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1188" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1188" s="10"/>
+      <c r="C1188" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1188" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1188" s="8"/>
+      <c r="F1188" s="8"/>
+    </row>
+    <row r="1189" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1189" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1189" s="10">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="C1189" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1189" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="E1189" s="8"/>
+      <c r="F1189" s="8"/>
+    </row>
+    <row r="1190" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1190" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1190" s="10">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="C1190" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1190" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="E1190" s="8"/>
+      <c r="F1190" s="8"/>
+    </row>
+    <row r="1191" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1191" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1191" s="10">
+        <v>0.55694444444444446</v>
+      </c>
+      <c r="C1191" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1191" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="E1191" s="8"/>
+      <c r="F1191" s="8"/>
+    </row>
+    <row r="1192" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1192" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1192" s="10">
+        <v>0.56944444444444442</v>
+      </c>
+      <c r="C1192" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1192" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="E1192" s="8"/>
+      <c r="F1192" s="8"/>
+    </row>
+    <row r="1193" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1193" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1193" s="10">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C1193" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1193" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="E1193" s="8"/>
+      <c r="F1193" s="8"/>
+    </row>
+    <row r="1194" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1194" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1194" s="10">
+        <v>0.65277777777777779</v>
+      </c>
+      <c r="C1194" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1194" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="E1194" s="8"/>
+      <c r="F1194" s="8"/>
+    </row>
+    <row r="1195" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1195" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1195" s="10"/>
+      <c r="C1195" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1195" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="E1195" s="8"/>
+      <c r="F1195" s="8"/>
+    </row>
+    <row r="1196" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1196" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1196" s="10"/>
+      <c r="C1196" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1196" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1196" s="8"/>
+      <c r="F1196" s="8"/>
+    </row>
+    <row r="1197" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1197" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1197" s="10">
+        <v>0.25</v>
+      </c>
+      <c r="C1197" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1197" s="8" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1198" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1198" s="10">
+        <v>0.28472222222222221</v>
+      </c>
+      <c r="C1198" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1198" s="8" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1199" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1199" s="10"/>
+      <c r="C1199" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1199" s="8" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1200" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1200" s="10">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="C1200" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1200" s="8" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1201" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1201" s="10"/>
+      <c r="C1201" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1201" s="8" t="s">
         <v>510</v>
       </c>
-      <c r="D1179" s="16" t="s">
-        <v>282</v>
-      </c>
-      <c r="E1179" s="16"/>
-      <c r="F1179" s="16"/>
-      <c r="G1179" s="17"/>
-      <c r="H1179" s="17"/>
-    </row>
-    <row r="1180" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1180" s="13">
+    </row>
+    <row r="1202" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1202" s="2">
         <v>46313</v>
       </c>
-      <c r="B1180" s="14">
-        <v>0.34722222222222221</v>
-      </c>
-      <c r="C1180" s="15" t="s">
-        <v>510</v>
-      </c>
-      <c r="D1180" s="16" t="s">
-        <v>500</v>
-      </c>
-      <c r="E1180" s="16"/>
-      <c r="F1180" s="16"/>
-      <c r="G1180" s="17"/>
-      <c r="H1180" s="17"/>
-    </row>
-    <row r="1181" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1181" s="13">
+      <c r="B1202" s="10"/>
+      <c r="C1202" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1202" s="12" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1203" s="2">
         <v>46313</v>
       </c>
-      <c r="B1181" s="14"/>
-      <c r="C1181" s="15" t="s">
-        <v>510</v>
-      </c>
-      <c r="D1181" s="16" t="s">
-        <v>501</v>
-      </c>
-      <c r="E1181" s="16"/>
-      <c r="F1181" s="16"/>
-      <c r="G1181" s="17"/>
-      <c r="H1181" s="17"/>
-    </row>
-    <row r="1182" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1182" s="13">
+      <c r="B1203" s="10">
+        <v>0.37291666666666667</v>
+      </c>
+      <c r="C1203" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1203" s="8" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1204" s="2">
         <v>46313</v>
       </c>
-      <c r="B1182" s="14">
-        <v>0.36319444444444443</v>
-      </c>
-      <c r="C1182" s="15" t="s">
-        <v>510</v>
-      </c>
-      <c r="D1182" s="16" t="s">
-        <v>502</v>
-      </c>
-      <c r="E1182" s="16"/>
-      <c r="F1182" s="16"/>
-      <c r="G1182" s="17"/>
-      <c r="H1182" s="17"/>
-    </row>
-    <row r="1183" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1183" s="13">
+      <c r="B1204" s="10"/>
+      <c r="C1204" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1204" s="8" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1205" s="2">
         <v>46313</v>
       </c>
-      <c r="B1183" s="14">
-        <v>0.37152777777777779</v>
-      </c>
-      <c r="C1183" s="15" t="s">
-        <v>510</v>
-      </c>
-      <c r="D1183" s="16" t="s">
-        <v>503</v>
-      </c>
-      <c r="E1183" s="16"/>
-      <c r="F1183" s="16"/>
-      <c r="G1183" s="17"/>
-      <c r="H1183" s="17"/>
-    </row>
-    <row r="1184" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1184" s="13">
+      <c r="B1205" s="10">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="C1205" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1205" s="8" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1206" s="2">
         <v>46313</v>
       </c>
-      <c r="B1184" s="14">
-        <v>0.37847222222222221</v>
-      </c>
-      <c r="C1184" s="15" t="s">
-        <v>510</v>
-      </c>
-      <c r="D1184" s="16" t="s">
-        <v>504</v>
-      </c>
-      <c r="E1184" s="16"/>
-      <c r="F1184" s="16"/>
-      <c r="G1184" s="17"/>
-      <c r="H1184" s="17"/>
-    </row>
-    <row r="1185" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1185" s="13">
+      <c r="B1206" s="10"/>
+      <c r="C1206" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1206" s="8" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1207" s="2">
         <v>46313</v>
       </c>
-      <c r="B1185" s="14"/>
-      <c r="C1185" s="15" t="s">
-        <v>510</v>
-      </c>
-      <c r="D1185" s="16" t="s">
-        <v>505</v>
-      </c>
-      <c r="E1185" s="16"/>
-      <c r="F1185" s="16"/>
-      <c r="G1185" s="17"/>
-      <c r="H1185" s="17"/>
-    </row>
-    <row r="1186" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1186" s="13">
+      <c r="B1207" s="10">
+        <v>0.39791666666666664</v>
+      </c>
+      <c r="C1207" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1207" s="8" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1208" s="2">
         <v>46313</v>
       </c>
-      <c r="B1186" s="14">
-        <v>0.41388888888888886</v>
-      </c>
-      <c r="C1186" s="15" t="s">
-        <v>510</v>
-      </c>
-      <c r="D1186" s="16" t="s">
-        <v>478</v>
-      </c>
-      <c r="E1186" s="16"/>
-      <c r="F1186" s="16"/>
-      <c r="G1186" s="17"/>
-      <c r="H1186" s="17"/>
-    </row>
-    <row r="1187" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1187" s="13">
+      <c r="B1208" s="10"/>
+      <c r="C1208" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1208" s="8" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1209" s="2">
         <v>46313</v>
       </c>
-      <c r="B1187" s="14">
-        <v>0.43402777777777779</v>
-      </c>
-      <c r="C1187" s="15" t="s">
-        <v>510</v>
-      </c>
-      <c r="D1187" s="16" t="s">
-        <v>480</v>
-      </c>
-      <c r="E1187" s="16"/>
-      <c r="F1187" s="16"/>
-      <c r="G1187" s="17"/>
-      <c r="H1187" s="17"/>
-    </row>
-    <row r="1188" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1188" s="13">
+      <c r="B1209" s="10">
+        <v>0.42222222222222222</v>
+      </c>
+      <c r="C1209" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1209" s="8" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1210" s="2">
         <v>46313</v>
       </c>
-      <c r="B1188" s="14"/>
-      <c r="C1188" s="15" t="s">
-        <v>510</v>
-      </c>
-      <c r="D1188" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="E1188" s="16"/>
-      <c r="F1188" s="16"/>
-      <c r="G1188" s="17"/>
-      <c r="H1188" s="17"/>
-    </row>
-    <row r="1189" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1189" s="13">
+      <c r="B1210" s="10"/>
+      <c r="C1210" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1210" s="8" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1211" s="2">
         <v>46313</v>
       </c>
-      <c r="B1189" s="14">
-        <v>0.53472222222222221</v>
-      </c>
-      <c r="C1189" s="15" t="s">
-        <v>510</v>
-      </c>
-      <c r="D1189" s="16" t="s">
-        <v>481</v>
-      </c>
-      <c r="E1189" s="16"/>
-      <c r="F1189" s="16"/>
-      <c r="G1189" s="17"/>
-      <c r="H1189" s="17"/>
-    </row>
-    <row r="1190" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1190" s="13">
+      <c r="B1211" s="10"/>
+      <c r="C1211" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1211" s="8" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1212" s="2">
         <v>46313</v>
       </c>
-      <c r="B1190" s="14">
-        <v>0.54861111111111116</v>
-      </c>
-      <c r="C1190" s="15" t="s">
-        <v>510</v>
-      </c>
-      <c r="D1190" s="16" t="s">
-        <v>506</v>
-      </c>
-      <c r="E1190" s="16"/>
-      <c r="F1190" s="16"/>
-      <c r="G1190" s="17"/>
-      <c r="H1190" s="17"/>
-    </row>
-    <row r="1191" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1191" s="13">
+      <c r="B1212" s="10">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="C1212" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1212" s="8" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1213" s="2">
         <v>46313</v>
       </c>
-      <c r="B1191" s="14">
-        <v>0.55694444444444446</v>
-      </c>
-      <c r="C1191" s="15" t="s">
-        <v>510</v>
-      </c>
-      <c r="D1191" s="16" t="s">
-        <v>507</v>
-      </c>
-      <c r="E1191" s="16"/>
-      <c r="F1191" s="16"/>
-      <c r="G1191" s="17"/>
-      <c r="H1191" s="17"/>
-    </row>
-    <row r="1192" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1192" s="13">
+      <c r="B1213" s="10"/>
+      <c r="C1213" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1213" s="8" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1214" s="2">
         <v>46313</v>
       </c>
-      <c r="B1192" s="14">
-        <v>0.56944444444444442</v>
-      </c>
-      <c r="C1192" s="15" t="s">
-        <v>510</v>
-      </c>
-      <c r="D1192" s="16" t="s">
-        <v>508</v>
-      </c>
-      <c r="E1192" s="16"/>
-      <c r="F1192" s="16"/>
-      <c r="G1192" s="17"/>
-      <c r="H1192" s="17"/>
-    </row>
-    <row r="1193" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1193" s="13">
+      <c r="B1214" s="10">
+        <v>0.45208333333333334</v>
+      </c>
+      <c r="C1214" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1214" s="8" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1215" s="2">
         <v>46313</v>
       </c>
-      <c r="B1193" s="14">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="C1193" s="15" t="s">
-        <v>510</v>
-      </c>
-      <c r="D1193" s="16" t="s">
-        <v>509</v>
-      </c>
-      <c r="E1193" s="16"/>
-      <c r="F1193" s="16"/>
-      <c r="G1193" s="17"/>
-      <c r="H1193" s="17"/>
-    </row>
-    <row r="1194" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1194" s="13">
+      <c r="B1215" s="10">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="C1215" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1215" s="8" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1216" s="2">
         <v>46313</v>
       </c>
-      <c r="B1194" s="14">
-        <v>0.65277777777777779</v>
-      </c>
-      <c r="C1194" s="15" t="s">
-        <v>510</v>
-      </c>
-      <c r="D1194" s="16" t="s">
-        <v>394</v>
-      </c>
-      <c r="E1194" s="16"/>
-      <c r="F1194" s="16"/>
-      <c r="G1194" s="17"/>
-      <c r="H1194" s="17"/>
-    </row>
-    <row r="1195" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1195" s="13">
+      <c r="B1216" s="10">
+        <v>0.57430555555555551</v>
+      </c>
+      <c r="C1216" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1216" s="8" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1217" s="2">
         <v>46313</v>
       </c>
-      <c r="B1195" s="14"/>
-      <c r="C1195" s="15" t="s">
-        <v>510</v>
-      </c>
-      <c r="D1195" s="16" t="s">
-        <v>379</v>
-      </c>
-      <c r="E1195" s="16"/>
-      <c r="F1195" s="16"/>
-      <c r="G1195" s="17"/>
-      <c r="H1195" s="17"/>
-    </row>
-    <row r="1196" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1196" s="13">
+      <c r="B1217" s="10">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="C1217" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1217" s="8" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1218" s="2">
         <v>46313</v>
       </c>
-      <c r="B1196" s="14"/>
-      <c r="C1196" s="15" t="s">
-        <v>510</v>
-      </c>
-      <c r="D1196" s="16" t="s">
+      <c r="B1218" s="10"/>
+      <c r="C1218" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1218" s="8" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1219" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1219" s="10">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="C1219" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1219" s="8" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1220" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1220" s="10"/>
+      <c r="C1220" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1220" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E1196" s="16"/>
-      <c r="F1196" s="16"/>
-      <c r="G1196" s="17"/>
-      <c r="H1196" s="17"/>
-    </row>
-    <row r="1197" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1197" s="13">
-        <v>46313</v>
-      </c>
-      <c r="B1197" s="14">
-        <v>0.25</v>
-      </c>
-      <c r="C1197" s="15" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1197" s="16" t="s">
-        <v>459</v>
-      </c>
-      <c r="E1197" s="15"/>
-      <c r="F1197" s="15"/>
-      <c r="G1197" s="17"/>
-      <c r="H1197" s="17"/>
-    </row>
-    <row r="1198" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1198" s="13">
-        <v>46313</v>
-      </c>
-      <c r="B1198" s="14">
-        <v>0.28472222222222221</v>
-      </c>
-      <c r="C1198" s="15" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1198" s="16" t="s">
-        <v>460</v>
-      </c>
-      <c r="E1198" s="15"/>
-      <c r="F1198" s="15"/>
-      <c r="G1198" s="17"/>
-      <c r="H1198" s="17"/>
-    </row>
-    <row r="1199" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1199" s="13">
-        <v>46313</v>
-      </c>
-      <c r="B1199" s="14"/>
-      <c r="C1199" s="15" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1199" s="16" t="s">
-        <v>461</v>
-      </c>
-      <c r="E1199" s="15"/>
-      <c r="F1199" s="15"/>
-      <c r="G1199" s="17"/>
-      <c r="H1199" s="17"/>
-    </row>
-    <row r="1200" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1200" s="13">
-        <v>46313</v>
-      </c>
-      <c r="B1200" s="14">
-        <v>0.36458333333333331</v>
-      </c>
-      <c r="C1200" s="15" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1200" s="16" t="s">
-        <v>462</v>
-      </c>
-      <c r="E1200" s="15"/>
-      <c r="F1200" s="15"/>
-      <c r="G1200" s="17"/>
-      <c r="H1200" s="17"/>
-    </row>
-    <row r="1201" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1201" s="13">
-        <v>46313</v>
-      </c>
-      <c r="B1201" s="14"/>
-      <c r="C1201" s="15" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1201" s="16" t="s">
-        <v>511</v>
-      </c>
-      <c r="E1201" s="15"/>
-      <c r="F1201" s="15"/>
-      <c r="G1201" s="17"/>
-      <c r="H1201" s="17"/>
-    </row>
-    <row r="1202" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1202" s="13">
-        <v>46313</v>
-      </c>
-      <c r="B1202" s="14"/>
-      <c r="C1202" s="15" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1202" s="18" t="s">
-        <v>484</v>
-      </c>
-      <c r="E1202" s="15"/>
-      <c r="F1202" s="15"/>
-      <c r="G1202" s="17"/>
-      <c r="H1202" s="17"/>
-    </row>
-    <row r="1203" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1203" s="13">
-        <v>46313</v>
-      </c>
-      <c r="B1203" s="14">
-        <v>0.37291666666666667</v>
-      </c>
-      <c r="C1203" s="15" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1203" s="16" t="s">
-        <v>485</v>
-      </c>
-      <c r="E1203" s="15"/>
-      <c r="F1203" s="15"/>
-      <c r="G1203" s="17"/>
-      <c r="H1203" s="17"/>
-    </row>
-    <row r="1204" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1204" s="13">
-        <v>46313</v>
-      </c>
-      <c r="B1204" s="14"/>
-      <c r="C1204" s="15" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1204" s="16" t="s">
-        <v>486</v>
-      </c>
-      <c r="E1204" s="15"/>
-      <c r="F1204" s="15"/>
-      <c r="G1204" s="17"/>
-      <c r="H1204" s="17"/>
-    </row>
-    <row r="1205" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1205" s="13">
-        <v>46313</v>
-      </c>
-      <c r="B1205" s="14">
-        <v>0.38194444444444442</v>
-      </c>
-      <c r="C1205" s="15" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1205" s="16" t="s">
-        <v>487</v>
-      </c>
-      <c r="E1205" s="15"/>
-      <c r="F1205" s="15"/>
-      <c r="G1205" s="17"/>
-      <c r="H1205" s="17"/>
-    </row>
-    <row r="1206" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1206" s="13">
-        <v>46313</v>
-      </c>
-      <c r="B1206" s="14"/>
-      <c r="C1206" s="15" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1206" s="16" t="s">
-        <v>488</v>
-      </c>
-      <c r="E1206" s="15"/>
-      <c r="F1206" s="15"/>
-      <c r="G1206" s="17"/>
-      <c r="H1206" s="17"/>
-    </row>
-    <row r="1207" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1207" s="13">
-        <v>46313</v>
-      </c>
-      <c r="B1207" s="14">
-        <v>0.39791666666666664</v>
-      </c>
-      <c r="C1207" s="15" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1207" s="16" t="s">
-        <v>489</v>
-      </c>
-      <c r="E1207" s="15"/>
-      <c r="F1207" s="15"/>
-      <c r="G1207" s="17"/>
-      <c r="H1207" s="17"/>
-    </row>
-    <row r="1208" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1208" s="13">
-        <v>46313</v>
-      </c>
-      <c r="B1208" s="14"/>
-      <c r="C1208" s="15" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1208" s="16" t="s">
-        <v>490</v>
-      </c>
-      <c r="E1208" s="15"/>
-      <c r="F1208" s="15"/>
-      <c r="G1208" s="17"/>
-      <c r="H1208" s="17"/>
-    </row>
-    <row r="1209" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1209" s="13">
-        <v>46313</v>
-      </c>
-      <c r="B1209" s="14">
-        <v>0.42222222222222222</v>
-      </c>
-      <c r="C1209" s="15" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1209" s="16" t="s">
-        <v>464</v>
-      </c>
-      <c r="E1209" s="15"/>
-      <c r="F1209" s="15"/>
-      <c r="G1209" s="17"/>
-      <c r="H1209" s="17"/>
-    </row>
-    <row r="1210" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1210" s="13">
-        <v>46313</v>
-      </c>
-      <c r="B1210" s="14"/>
-      <c r="C1210" s="15" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1210" s="16" t="s">
-        <v>491</v>
-      </c>
-      <c r="E1210" s="15"/>
-      <c r="F1210" s="15"/>
-      <c r="G1210" s="17"/>
-      <c r="H1210" s="17"/>
-    </row>
-    <row r="1211" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1211" s="13">
-        <v>46313</v>
-      </c>
-      <c r="B1211" s="14"/>
-      <c r="C1211" s="15" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1211" s="16" t="s">
-        <v>492</v>
-      </c>
-      <c r="E1211" s="15"/>
-      <c r="F1211" s="15"/>
-      <c r="G1211" s="17"/>
-      <c r="H1211" s="17"/>
-    </row>
-    <row r="1212" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1212" s="13">
-        <v>46313</v>
-      </c>
-      <c r="B1212" s="14">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="C1212" s="15" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1212" s="16" t="s">
-        <v>493</v>
-      </c>
-      <c r="E1212" s="15"/>
-      <c r="F1212" s="15"/>
-      <c r="G1212" s="17"/>
-      <c r="H1212" s="17"/>
-    </row>
-    <row r="1213" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1213" s="13">
-        <v>46313</v>
-      </c>
-      <c r="B1213" s="14"/>
-      <c r="C1213" s="15" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1213" s="16" t="s">
-        <v>494</v>
-      </c>
-      <c r="E1213" s="15"/>
-      <c r="F1213" s="15"/>
-      <c r="G1213" s="17"/>
-      <c r="H1213" s="17"/>
-    </row>
-    <row r="1214" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1214" s="13">
-        <v>46313</v>
-      </c>
-      <c r="B1214" s="14">
-        <v>0.45208333333333334</v>
-      </c>
-      <c r="C1214" s="15" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1214" s="16" t="s">
-        <v>495</v>
-      </c>
-      <c r="E1214" s="15"/>
-      <c r="F1214" s="15"/>
-      <c r="G1214" s="17"/>
-      <c r="H1214" s="17"/>
-    </row>
-    <row r="1215" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1215" s="13">
-        <v>46313</v>
-      </c>
-      <c r="B1215" s="14">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="C1215" s="15" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1215" s="16" t="s">
-        <v>496</v>
-      </c>
-      <c r="E1215" s="15"/>
-      <c r="F1215" s="15"/>
-      <c r="G1215" s="17"/>
-      <c r="H1215" s="17"/>
-    </row>
-    <row r="1216" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1216" s="13">
-        <v>46313</v>
-      </c>
-      <c r="B1216" s="14">
-        <v>0.57430555555555551</v>
-      </c>
-      <c r="C1216" s="15" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1216" s="16" t="s">
-        <v>470</v>
-      </c>
-      <c r="E1216" s="15"/>
-      <c r="F1216" s="15"/>
-      <c r="G1216" s="17"/>
-      <c r="H1216" s="17"/>
-    </row>
-    <row r="1217" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1217" s="13">
-        <v>46313</v>
-      </c>
-      <c r="B1217" s="14">
-        <v>0.57638888888888884</v>
-      </c>
-      <c r="C1217" s="15" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1217" s="16" t="s">
-        <v>472</v>
-      </c>
-      <c r="E1217" s="15"/>
-      <c r="F1217" s="15"/>
-      <c r="G1217" s="17"/>
-      <c r="H1217" s="17"/>
-    </row>
-    <row r="1218" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1218" s="13">
-        <v>46313</v>
-      </c>
-      <c r="B1218" s="14"/>
-      <c r="C1218" s="15" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1218" s="16" t="s">
-        <v>473</v>
-      </c>
-      <c r="E1218" s="15"/>
-      <c r="F1218" s="15"/>
-      <c r="G1218" s="17"/>
-      <c r="H1218" s="17"/>
-    </row>
-    <row r="1219" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1219" s="13">
-        <v>46313</v>
-      </c>
-      <c r="B1219" s="14">
-        <v>0.67708333333333337</v>
-      </c>
-      <c r="C1219" s="15" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1219" s="16" t="s">
-        <v>474</v>
-      </c>
-      <c r="E1219" s="15"/>
-      <c r="F1219" s="15"/>
-      <c r="G1219" s="17"/>
-      <c r="H1219" s="17"/>
-    </row>
-    <row r="1220" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1220" s="13">
-        <v>46313</v>
-      </c>
-      <c r="B1220" s="14"/>
-      <c r="C1220" s="15" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1220" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1220" s="15"/>
-      <c r="F1220" s="15"/>
-      <c r="G1220" s="17"/>
-      <c r="H1220" s="17"/>
-    </row>
-    <row r="1221" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1221" s="15"/>
-      <c r="B1221" s="15"/>
-      <c r="C1221" s="15"/>
-      <c r="D1221" s="15"/>
-      <c r="E1221" s="15"/>
-      <c r="F1221" s="15"/>
-      <c r="G1221" s="17"/>
-      <c r="H1221" s="17"/>
-    </row>
-    <row r="1222" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1222" s="15"/>
-      <c r="B1222" s="15"/>
-      <c r="C1222" s="15"/>
-      <c r="D1222" s="15"/>
-      <c r="E1222" s="15"/>
-      <c r="F1222" s="15"/>
-      <c r="G1222" s="17"/>
-      <c r="H1222" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="D1078:F1078"/>
-    <mergeCell ref="D1072:F1072"/>
-    <mergeCell ref="D1070:F1070"/>
-    <mergeCell ref="D1071:F1071"/>
-    <mergeCell ref="D1077:F1077"/>
-    <mergeCell ref="D1074:F1074"/>
-    <mergeCell ref="D1075:F1075"/>
-    <mergeCell ref="D1076:F1076"/>
-    <mergeCell ref="D1069:F1069"/>
-    <mergeCell ref="D1066:F1066"/>
-    <mergeCell ref="D1067:F1067"/>
-    <mergeCell ref="D1052:F1052"/>
-    <mergeCell ref="D1053:F1053"/>
-    <mergeCell ref="D1054:F1054"/>
-    <mergeCell ref="D1055:F1055"/>
-    <mergeCell ref="D1056:F1056"/>
-    <mergeCell ref="D1057:F1057"/>
-    <mergeCell ref="D1058:F1058"/>
-    <mergeCell ref="D1059:F1059"/>
-    <mergeCell ref="D1060:F1060"/>
-    <mergeCell ref="D1061:F1061"/>
-    <mergeCell ref="D1049:F1049"/>
-    <mergeCell ref="D1050:F1050"/>
-    <mergeCell ref="D1051:F1051"/>
-    <mergeCell ref="D1065:F1065"/>
-    <mergeCell ref="D1068:F1068"/>
-    <mergeCell ref="D1064:F1064"/>
-    <mergeCell ref="D1062:F1062"/>
-    <mergeCell ref="D1063:F1063"/>
-    <mergeCell ref="D1047:F1047"/>
-    <mergeCell ref="D1048:F1048"/>
-    <mergeCell ref="D987:F987"/>
-    <mergeCell ref="D988:F988"/>
-    <mergeCell ref="D981:F981"/>
-    <mergeCell ref="D982:F982"/>
-    <mergeCell ref="D983:F983"/>
-    <mergeCell ref="D984:F984"/>
-    <mergeCell ref="D985:F985"/>
-    <mergeCell ref="D986:F986"/>
     <mergeCell ref="D965:F965"/>
     <mergeCell ref="D966:F966"/>
     <mergeCell ref="D967:F967"/>
@@ -19727,6 +19321,45 @@
     <mergeCell ref="D977:F977"/>
     <mergeCell ref="D978:F978"/>
     <mergeCell ref="D979:F979"/>
+    <mergeCell ref="D1047:F1047"/>
+    <mergeCell ref="D1048:F1048"/>
+    <mergeCell ref="D987:F987"/>
+    <mergeCell ref="D988:F988"/>
+    <mergeCell ref="D981:F981"/>
+    <mergeCell ref="D982:F982"/>
+    <mergeCell ref="D983:F983"/>
+    <mergeCell ref="D984:F984"/>
+    <mergeCell ref="D985:F985"/>
+    <mergeCell ref="D986:F986"/>
+    <mergeCell ref="D1049:F1049"/>
+    <mergeCell ref="D1050:F1050"/>
+    <mergeCell ref="D1051:F1051"/>
+    <mergeCell ref="D1065:F1065"/>
+    <mergeCell ref="D1068:F1068"/>
+    <mergeCell ref="D1064:F1064"/>
+    <mergeCell ref="D1062:F1062"/>
+    <mergeCell ref="D1063:F1063"/>
+    <mergeCell ref="D1069:F1069"/>
+    <mergeCell ref="D1066:F1066"/>
+    <mergeCell ref="D1067:F1067"/>
+    <mergeCell ref="D1052:F1052"/>
+    <mergeCell ref="D1053:F1053"/>
+    <mergeCell ref="D1054:F1054"/>
+    <mergeCell ref="D1055:F1055"/>
+    <mergeCell ref="D1056:F1056"/>
+    <mergeCell ref="D1057:F1057"/>
+    <mergeCell ref="D1058:F1058"/>
+    <mergeCell ref="D1059:F1059"/>
+    <mergeCell ref="D1060:F1060"/>
+    <mergeCell ref="D1061:F1061"/>
+    <mergeCell ref="D1078:F1078"/>
+    <mergeCell ref="D1072:F1072"/>
+    <mergeCell ref="D1070:F1070"/>
+    <mergeCell ref="D1071:F1071"/>
+    <mergeCell ref="D1077:F1077"/>
+    <mergeCell ref="D1074:F1074"/>
+    <mergeCell ref="D1075:F1075"/>
+    <mergeCell ref="D1076:F1076"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28ACABF2-263B-413F-A618-8179B86B5837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63431D88-0E91-4C77-9D63-9C550DEDBAF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2442" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2426" uniqueCount="516">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1959,7 +1959,25 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Push on D04</t>
+    <t>First push on (D01)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mob</t>
+  </si>
+  <si>
+    <t>Ready to deploy AIB-006</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wait on current (0.9~1.1 knots)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D01 push off</t>
+  </si>
+  <si>
+    <t>A01 push off (SRL repairing team)</t>
   </si>
 </sst>
 </file>
@@ -2052,7 +2070,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2088,6 +2106,17 @@
     </xf>
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -18965,7 +18994,9 @@
       <c r="A1195" s="2">
         <v>46313</v>
       </c>
-      <c r="B1195" s="10"/>
+      <c r="B1195" s="10">
+        <v>0.76041666666666663</v>
+      </c>
       <c r="C1195" s="1" t="s">
         <v>509</v>
       </c>
@@ -18976,335 +19007,356 @@
       <c r="F1195" s="8"/>
     </row>
     <row r="1196" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1196" s="2">
+      <c r="A1196" s="14">
         <v>46313</v>
       </c>
-      <c r="B1196" s="10"/>
-      <c r="C1196" s="1" t="s">
+      <c r="B1196" s="15"/>
+      <c r="C1196" s="16" t="s">
         <v>509</v>
       </c>
-      <c r="D1196" s="8" t="s">
+      <c r="D1196" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="E1196" s="8"/>
-      <c r="F1196" s="8"/>
+      <c r="E1196" s="17"/>
+      <c r="F1196" s="17"/>
     </row>
     <row r="1197" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1197" s="2">
+      <c r="A1197" s="14">
         <v>46313</v>
       </c>
-      <c r="B1197" s="10">
+      <c r="B1197" s="15">
         <v>0.25</v>
       </c>
-      <c r="C1197" s="1" t="s">
+      <c r="C1197" s="16" t="s">
         <v>499</v>
       </c>
-      <c r="D1197" s="8" t="s">
+      <c r="D1197" s="18" t="s">
         <v>459</v>
       </c>
+      <c r="E1197" s="16"/>
+      <c r="F1197" s="16"/>
     </row>
     <row r="1198" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1198" s="2">
+      <c r="A1198" s="14">
         <v>46313</v>
       </c>
-      <c r="B1198" s="10">
-        <v>0.28472222222222221</v>
-      </c>
-      <c r="C1198" s="1" t="s">
+      <c r="B1198" s="15">
+        <v>0.2638888888888889</v>
+      </c>
+      <c r="C1198" s="16" t="s">
         <v>499</v>
       </c>
-      <c r="D1198" s="8" t="s">
+      <c r="D1198" s="18" t="s">
         <v>460</v>
       </c>
+      <c r="E1198" s="16"/>
+      <c r="F1198" s="16"/>
     </row>
     <row r="1199" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1199" s="2">
+      <c r="A1199" s="14">
         <v>46313</v>
       </c>
-      <c r="B1199" s="10"/>
-      <c r="C1199" s="1" t="s">
+      <c r="B1199" s="15"/>
+      <c r="C1199" s="16" t="s">
         <v>499</v>
       </c>
-      <c r="D1199" s="8" t="s">
+      <c r="D1199" s="18" t="s">
         <v>461</v>
       </c>
+      <c r="E1199" s="16"/>
+      <c r="F1199" s="16"/>
     </row>
     <row r="1200" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1200" s="2">
+      <c r="A1200" s="14">
         <v>46313</v>
       </c>
-      <c r="B1200" s="10">
-        <v>0.36458333333333331</v>
-      </c>
-      <c r="C1200" s="1" t="s">
+      <c r="B1200" s="15">
+        <v>0.34722222222222221</v>
+      </c>
+      <c r="C1200" s="16" t="s">
         <v>499</v>
       </c>
-      <c r="D1200" s="8" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="1201" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1201" s="2">
+      <c r="D1200" s="18" t="s">
+        <v>510</v>
+      </c>
+      <c r="E1200" s="16"/>
+      <c r="F1200" s="16"/>
+    </row>
+    <row r="1201" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1201" s="14">
         <v>46313</v>
       </c>
-      <c r="B1201" s="10"/>
-      <c r="C1201" s="1" t="s">
+      <c r="B1201" s="15">
+        <v>0.3576388888888889</v>
+      </c>
+      <c r="C1201" s="16" t="s">
         <v>499</v>
       </c>
-      <c r="D1201" s="8" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="1202" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1202" s="2">
+      <c r="D1201" s="18" t="s">
+        <v>464</v>
+      </c>
+      <c r="E1201" s="16"/>
+      <c r="F1201" s="16"/>
+    </row>
+    <row r="1202" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1202" s="14">
         <v>46313</v>
       </c>
-      <c r="B1202" s="10"/>
-      <c r="C1202" s="1" t="s">
+      <c r="B1202" s="15"/>
+      <c r="C1202" s="16" t="s">
         <v>499</v>
       </c>
-      <c r="D1202" s="12" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="1203" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1203" s="2">
+      <c r="D1202" s="18" t="s">
+        <v>511</v>
+      </c>
+      <c r="E1202" s="16"/>
+      <c r="F1202" s="16"/>
+    </row>
+    <row r="1203" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1203" s="14">
         <v>46313</v>
       </c>
-      <c r="B1203" s="10">
-        <v>0.37291666666666667</v>
-      </c>
-      <c r="C1203" s="1" t="s">
+      <c r="B1203" s="15">
+        <v>0.36944444444444446</v>
+      </c>
+      <c r="C1203" s="16" t="s">
         <v>499</v>
       </c>
-      <c r="D1203" s="8" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="1204" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1204" s="2">
+      <c r="D1203" s="18" t="s">
+        <v>512</v>
+      </c>
+      <c r="E1203" s="16"/>
+      <c r="F1203" s="16"/>
+    </row>
+    <row r="1204" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1204" s="14">
         <v>46313</v>
       </c>
-      <c r="B1204" s="10"/>
-      <c r="C1204" s="1" t="s">
+      <c r="B1204" s="15"/>
+      <c r="C1204" s="16" t="s">
         <v>499</v>
       </c>
-      <c r="D1204" s="8" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="1205" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1205" s="2">
+      <c r="D1204" s="18" t="s">
+        <v>513</v>
+      </c>
+      <c r="E1204" s="16"/>
+      <c r="F1204" s="16"/>
+    </row>
+    <row r="1205" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1205" s="14">
         <v>46313</v>
       </c>
-      <c r="B1205" s="10">
-        <v>0.38194444444444442</v>
-      </c>
-      <c r="C1205" s="1" t="s">
+      <c r="B1205" s="15">
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="C1205" s="16" t="s">
         <v>499</v>
       </c>
-      <c r="D1205" s="8" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="1206" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1206" s="2">
+      <c r="D1205" s="18" t="s">
+        <v>496</v>
+      </c>
+      <c r="E1205" s="16"/>
+      <c r="F1205" s="16"/>
+    </row>
+    <row r="1206" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1206" s="14">
         <v>46313</v>
       </c>
-      <c r="B1206" s="10"/>
-      <c r="C1206" s="1" t="s">
+      <c r="B1206" s="15">
+        <v>0.56666666666666665</v>
+      </c>
+      <c r="C1206" s="16" t="s">
         <v>499</v>
       </c>
-      <c r="D1206" s="8" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="1207" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1207" s="2">
+      <c r="D1206" s="18" t="s">
+        <v>470</v>
+      </c>
+      <c r="E1206" s="16"/>
+      <c r="F1206" s="16"/>
+    </row>
+    <row r="1207" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1207" s="14">
         <v>46313</v>
       </c>
-      <c r="B1207" s="10">
-        <v>0.39791666666666664</v>
-      </c>
-      <c r="C1207" s="1" t="s">
+      <c r="B1207" s="15">
+        <v>0.56944444444444442</v>
+      </c>
+      <c r="C1207" s="16" t="s">
         <v>499</v>
       </c>
-      <c r="D1207" s="8" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="1208" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1208" s="2">
+      <c r="D1207" s="18" t="s">
+        <v>514</v>
+      </c>
+      <c r="E1207" s="16"/>
+      <c r="F1207" s="16"/>
+    </row>
+    <row r="1208" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1208" s="14">
         <v>46313</v>
       </c>
-      <c r="B1208" s="10"/>
-      <c r="C1208" s="1" t="s">
+      <c r="B1208" s="15">
+        <v>0.65277777777777779</v>
+      </c>
+      <c r="C1208" s="16" t="s">
         <v>499</v>
       </c>
-      <c r="D1208" s="8" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="1209" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1209" s="2">
+      <c r="D1208" s="18" t="s">
+        <v>472</v>
+      </c>
+      <c r="E1208" s="16"/>
+      <c r="F1208" s="16"/>
+    </row>
+    <row r="1209" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1209" s="14">
         <v>46313</v>
       </c>
-      <c r="B1209" s="10">
-        <v>0.42222222222222222</v>
-      </c>
-      <c r="C1209" s="1" t="s">
+      <c r="B1209" s="15"/>
+      <c r="C1209" s="16" t="s">
         <v>499</v>
       </c>
-      <c r="D1209" s="8" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="1210" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1210" s="2">
+      <c r="D1209" s="18" t="s">
+        <v>515</v>
+      </c>
+      <c r="E1209" s="16"/>
+      <c r="F1209" s="16"/>
+    </row>
+    <row r="1210" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1210" s="14">
         <v>46313</v>
       </c>
-      <c r="B1210" s="10"/>
-      <c r="C1210" s="1" t="s">
+      <c r="B1210" s="15"/>
+      <c r="C1210" s="16" t="s">
         <v>499</v>
       </c>
-      <c r="D1210" s="8" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="1211" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1211" s="2">
+      <c r="D1210" s="18" t="s">
+        <v>473</v>
+      </c>
+      <c r="E1210" s="16"/>
+      <c r="F1210" s="16"/>
+    </row>
+    <row r="1211" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1211" s="14">
         <v>46313</v>
       </c>
-      <c r="B1211" s="10"/>
-      <c r="C1211" s="1" t="s">
+      <c r="B1211" s="15">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="C1211" s="16" t="s">
         <v>499</v>
       </c>
-      <c r="D1211" s="8" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="1212" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1212" s="2">
+      <c r="D1211" s="18" t="s">
+        <v>474</v>
+      </c>
+      <c r="E1211" s="16"/>
+      <c r="F1211" s="16"/>
+    </row>
+    <row r="1212" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1212" s="14">
         <v>46313</v>
       </c>
-      <c r="B1212" s="10">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="C1212" s="1" t="s">
+      <c r="B1212" s="15"/>
+      <c r="C1212" s="16" t="s">
         <v>499</v>
       </c>
-      <c r="D1212" s="8" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="1213" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1213" s="2">
-        <v>46313</v>
-      </c>
-      <c r="B1213" s="10"/>
-      <c r="C1213" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1213" s="8" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="1214" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1214" s="2">
-        <v>46313</v>
-      </c>
-      <c r="B1214" s="10">
-        <v>0.45208333333333334</v>
-      </c>
-      <c r="C1214" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1214" s="8" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="1215" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1215" s="2">
-        <v>46313</v>
-      </c>
-      <c r="B1215" s="10">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="C1215" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1215" s="8" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="1216" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1216" s="2">
-        <v>46313</v>
-      </c>
-      <c r="B1216" s="10">
-        <v>0.57430555555555551</v>
-      </c>
-      <c r="C1216" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1216" s="8" t="s">
-        <v>470</v>
-      </c>
+      <c r="D1212" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1212" s="16"/>
+      <c r="F1212" s="16"/>
+    </row>
+    <row r="1213" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1213" s="14"/>
+      <c r="B1213" s="15"/>
+      <c r="C1213" s="16"/>
+      <c r="D1213" s="17"/>
+      <c r="E1213" s="16"/>
+      <c r="F1213" s="16"/>
+    </row>
+    <row r="1214" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1214" s="14"/>
+      <c r="B1214" s="15"/>
+      <c r="C1214" s="16"/>
+      <c r="D1214" s="17"/>
+      <c r="E1214" s="16"/>
+      <c r="F1214" s="16"/>
+    </row>
+    <row r="1215" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1215" s="14"/>
+      <c r="B1215" s="15"/>
+      <c r="C1215" s="16"/>
+      <c r="D1215" s="17"/>
+      <c r="E1215" s="16"/>
+      <c r="F1215" s="16"/>
+    </row>
+    <row r="1216" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1216" s="14"/>
+      <c r="B1216" s="15"/>
+      <c r="C1216" s="16"/>
+      <c r="D1216" s="17"/>
+      <c r="E1216" s="16"/>
+      <c r="F1216" s="16"/>
     </row>
     <row r="1217" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1217" s="2">
-        <v>46313</v>
-      </c>
-      <c r="B1217" s="10">
-        <v>0.57638888888888884</v>
-      </c>
-      <c r="C1217" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1217" s="8" t="s">
-        <v>472</v>
-      </c>
+      <c r="A1217" s="2"/>
+      <c r="B1217" s="10"/>
+      <c r="D1217" s="8"/>
     </row>
     <row r="1218" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1218" s="2">
-        <v>46313</v>
-      </c>
+      <c r="A1218" s="2"/>
       <c r="B1218" s="10"/>
-      <c r="C1218" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1218" s="8" t="s">
-        <v>473</v>
-      </c>
+      <c r="D1218" s="8"/>
     </row>
     <row r="1219" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1219" s="2">
-        <v>46313</v>
-      </c>
-      <c r="B1219" s="10">
-        <v>0.67708333333333337</v>
-      </c>
-      <c r="C1219" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1219" s="8" t="s">
-        <v>474</v>
-      </c>
+      <c r="A1219" s="2"/>
+      <c r="B1219" s="10"/>
+      <c r="D1219" s="8"/>
     </row>
     <row r="1220" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1220" s="2">
-        <v>46313</v>
-      </c>
+      <c r="A1220" s="2"/>
       <c r="B1220" s="10"/>
-      <c r="C1220" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1220" s="8" t="s">
-        <v>55</v>
-      </c>
+      <c r="D1220" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="D1078:F1078"/>
+    <mergeCell ref="D1072:F1072"/>
+    <mergeCell ref="D1070:F1070"/>
+    <mergeCell ref="D1071:F1071"/>
+    <mergeCell ref="D1077:F1077"/>
+    <mergeCell ref="D1074:F1074"/>
+    <mergeCell ref="D1075:F1075"/>
+    <mergeCell ref="D1076:F1076"/>
+    <mergeCell ref="D1069:F1069"/>
+    <mergeCell ref="D1066:F1066"/>
+    <mergeCell ref="D1067:F1067"/>
+    <mergeCell ref="D1052:F1052"/>
+    <mergeCell ref="D1053:F1053"/>
+    <mergeCell ref="D1054:F1054"/>
+    <mergeCell ref="D1055:F1055"/>
+    <mergeCell ref="D1056:F1056"/>
+    <mergeCell ref="D1057:F1057"/>
+    <mergeCell ref="D1058:F1058"/>
+    <mergeCell ref="D1059:F1059"/>
+    <mergeCell ref="D1060:F1060"/>
+    <mergeCell ref="D1061:F1061"/>
+    <mergeCell ref="D1049:F1049"/>
+    <mergeCell ref="D1050:F1050"/>
+    <mergeCell ref="D1051:F1051"/>
+    <mergeCell ref="D1065:F1065"/>
+    <mergeCell ref="D1068:F1068"/>
+    <mergeCell ref="D1064:F1064"/>
+    <mergeCell ref="D1062:F1062"/>
+    <mergeCell ref="D1063:F1063"/>
+    <mergeCell ref="D1047:F1047"/>
+    <mergeCell ref="D1048:F1048"/>
+    <mergeCell ref="D987:F987"/>
+    <mergeCell ref="D988:F988"/>
+    <mergeCell ref="D981:F981"/>
+    <mergeCell ref="D982:F982"/>
+    <mergeCell ref="D983:F983"/>
+    <mergeCell ref="D984:F984"/>
+    <mergeCell ref="D985:F985"/>
+    <mergeCell ref="D986:F986"/>
     <mergeCell ref="D965:F965"/>
     <mergeCell ref="D966:F966"/>
     <mergeCell ref="D967:F967"/>
@@ -19321,45 +19373,6 @@
     <mergeCell ref="D977:F977"/>
     <mergeCell ref="D978:F978"/>
     <mergeCell ref="D979:F979"/>
-    <mergeCell ref="D1047:F1047"/>
-    <mergeCell ref="D1048:F1048"/>
-    <mergeCell ref="D987:F987"/>
-    <mergeCell ref="D988:F988"/>
-    <mergeCell ref="D981:F981"/>
-    <mergeCell ref="D982:F982"/>
-    <mergeCell ref="D983:F983"/>
-    <mergeCell ref="D984:F984"/>
-    <mergeCell ref="D985:F985"/>
-    <mergeCell ref="D986:F986"/>
-    <mergeCell ref="D1049:F1049"/>
-    <mergeCell ref="D1050:F1050"/>
-    <mergeCell ref="D1051:F1051"/>
-    <mergeCell ref="D1065:F1065"/>
-    <mergeCell ref="D1068:F1068"/>
-    <mergeCell ref="D1064:F1064"/>
-    <mergeCell ref="D1062:F1062"/>
-    <mergeCell ref="D1063:F1063"/>
-    <mergeCell ref="D1069:F1069"/>
-    <mergeCell ref="D1066:F1066"/>
-    <mergeCell ref="D1067:F1067"/>
-    <mergeCell ref="D1052:F1052"/>
-    <mergeCell ref="D1053:F1053"/>
-    <mergeCell ref="D1054:F1054"/>
-    <mergeCell ref="D1055:F1055"/>
-    <mergeCell ref="D1056:F1056"/>
-    <mergeCell ref="D1057:F1057"/>
-    <mergeCell ref="D1058:F1058"/>
-    <mergeCell ref="D1059:F1059"/>
-    <mergeCell ref="D1060:F1060"/>
-    <mergeCell ref="D1061:F1061"/>
-    <mergeCell ref="D1078:F1078"/>
-    <mergeCell ref="D1072:F1072"/>
-    <mergeCell ref="D1070:F1070"/>
-    <mergeCell ref="D1071:F1071"/>
-    <mergeCell ref="D1077:F1077"/>
-    <mergeCell ref="D1074:F1074"/>
-    <mergeCell ref="D1075:F1075"/>
-    <mergeCell ref="D1076:F1076"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63431D88-0E91-4C77-9D63-9C550DEDBAF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D14692-52E7-4A9A-99E3-96B2AFF3DDA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2426" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2484" uniqueCount="523">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1978,6 +1978,29 @@
   </si>
   <si>
     <t>A01 push off (SRL repairing team)</t>
+  </si>
+  <si>
+    <t>AIB Maintenance (Thrusters and Tether)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sail toD01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>First push on (D01)</t>
+  </si>
+  <si>
+    <t>Wait for work permit</t>
+  </si>
+  <si>
+    <t>Ready to deploy AIB-006</t>
+  </si>
+  <si>
+    <t>Wait on current (0.8~1.0 knots)</t>
+  </si>
+  <si>
+    <t>Last push off (D01)</t>
   </si>
 </sst>
 </file>
@@ -2070,7 +2093,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2113,10 +2136,11 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2403,7 +2427,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1220"/>
+  <dimension ref="A1:G1243"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.296875" style="1" bestFit="1" customWidth="1"/>
@@ -19007,250 +19031,220 @@
       <c r="F1195" s="8"/>
     </row>
     <row r="1196" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1196" s="14">
+      <c r="A1196" s="2">
         <v>46313</v>
       </c>
-      <c r="B1196" s="15"/>
-      <c r="C1196" s="16" t="s">
+      <c r="B1196" s="10"/>
+      <c r="C1196" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="D1196" s="17" t="s">
+      <c r="D1196" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E1196" s="17"/>
-      <c r="F1196" s="17"/>
+      <c r="E1196" s="8"/>
+      <c r="F1196" s="8"/>
     </row>
     <row r="1197" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1197" s="14">
+      <c r="A1197" s="2">
         <v>46313</v>
       </c>
-      <c r="B1197" s="15">
+      <c r="B1197" s="10">
         <v>0.25</v>
       </c>
-      <c r="C1197" s="16" t="s">
+      <c r="C1197" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1197" s="18" t="s">
+      <c r="D1197" s="12" t="s">
         <v>459</v>
       </c>
-      <c r="E1197" s="16"/>
-      <c r="F1197" s="16"/>
     </row>
     <row r="1198" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1198" s="14">
+      <c r="A1198" s="2">
         <v>46313</v>
       </c>
-      <c r="B1198" s="15">
+      <c r="B1198" s="10">
         <v>0.2638888888888889</v>
       </c>
-      <c r="C1198" s="16" t="s">
+      <c r="C1198" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1198" s="18" t="s">
+      <c r="D1198" s="12" t="s">
         <v>460</v>
       </c>
-      <c r="E1198" s="16"/>
-      <c r="F1198" s="16"/>
     </row>
     <row r="1199" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1199" s="14">
+      <c r="A1199" s="2">
         <v>46313</v>
       </c>
-      <c r="B1199" s="15"/>
-      <c r="C1199" s="16" t="s">
+      <c r="B1199" s="10"/>
+      <c r="C1199" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1199" s="18" t="s">
+      <c r="D1199" s="12" t="s">
         <v>461</v>
       </c>
-      <c r="E1199" s="16"/>
-      <c r="F1199" s="16"/>
     </row>
     <row r="1200" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1200" s="14">
+      <c r="A1200" s="2">
         <v>46313</v>
       </c>
-      <c r="B1200" s="15">
+      <c r="B1200" s="10">
         <v>0.34722222222222221</v>
       </c>
-      <c r="C1200" s="16" t="s">
+      <c r="C1200" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1200" s="18" t="s">
+      <c r="D1200" s="12" t="s">
         <v>510</v>
       </c>
-      <c r="E1200" s="16"/>
-      <c r="F1200" s="16"/>
-    </row>
-    <row r="1201" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1201" s="14">
+    </row>
+    <row r="1201" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1201" s="2">
         <v>46313</v>
       </c>
-      <c r="B1201" s="15">
+      <c r="B1201" s="10">
         <v>0.3576388888888889</v>
       </c>
-      <c r="C1201" s="16" t="s">
+      <c r="C1201" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1201" s="18" t="s">
+      <c r="D1201" s="12" t="s">
         <v>464</v>
       </c>
-      <c r="E1201" s="16"/>
-      <c r="F1201" s="16"/>
-    </row>
-    <row r="1202" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1202" s="14">
+    </row>
+    <row r="1202" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1202" s="2">
         <v>46313</v>
       </c>
-      <c r="B1202" s="15"/>
-      <c r="C1202" s="16" t="s">
+      <c r="B1202" s="10"/>
+      <c r="C1202" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1202" s="18" t="s">
+      <c r="D1202" s="12" t="s">
         <v>511</v>
       </c>
-      <c r="E1202" s="16"/>
-      <c r="F1202" s="16"/>
-    </row>
-    <row r="1203" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1203" s="14">
+    </row>
+    <row r="1203" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1203" s="2">
         <v>46313</v>
       </c>
-      <c r="B1203" s="15">
+      <c r="B1203" s="10">
         <v>0.36944444444444446</v>
       </c>
-      <c r="C1203" s="16" t="s">
+      <c r="C1203" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1203" s="18" t="s">
+      <c r="D1203" s="12" t="s">
         <v>512</v>
       </c>
-      <c r="E1203" s="16"/>
-      <c r="F1203" s="16"/>
-    </row>
-    <row r="1204" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1204" s="14">
+    </row>
+    <row r="1204" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1204" s="2">
         <v>46313</v>
       </c>
-      <c r="B1204" s="15"/>
-      <c r="C1204" s="16" t="s">
+      <c r="B1204" s="10"/>
+      <c r="C1204" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1204" s="18" t="s">
+      <c r="D1204" s="12" t="s">
         <v>513</v>
       </c>
-      <c r="E1204" s="16"/>
-      <c r="F1204" s="16"/>
-    </row>
-    <row r="1205" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1205" s="14">
+    </row>
+    <row r="1205" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1205" s="2">
         <v>46313</v>
       </c>
-      <c r="B1205" s="15">
+      <c r="B1205" s="10">
         <v>0.53333333333333333</v>
       </c>
-      <c r="C1205" s="16" t="s">
+      <c r="C1205" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1205" s="18" t="s">
+      <c r="D1205" s="12" t="s">
         <v>496</v>
       </c>
-      <c r="E1205" s="16"/>
-      <c r="F1205" s="16"/>
-    </row>
-    <row r="1206" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1206" s="14">
+    </row>
+    <row r="1206" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1206" s="2">
         <v>46313</v>
       </c>
-      <c r="B1206" s="15">
+      <c r="B1206" s="10">
         <v>0.56666666666666665</v>
       </c>
-      <c r="C1206" s="16" t="s">
+      <c r="C1206" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1206" s="18" t="s">
+      <c r="D1206" s="12" t="s">
         <v>470</v>
       </c>
-      <c r="E1206" s="16"/>
-      <c r="F1206" s="16"/>
-    </row>
-    <row r="1207" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1207" s="14">
+    </row>
+    <row r="1207" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1207" s="2">
         <v>46313</v>
       </c>
-      <c r="B1207" s="15">
+      <c r="B1207" s="10">
         <v>0.56944444444444442</v>
       </c>
-      <c r="C1207" s="16" t="s">
+      <c r="C1207" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1207" s="18" t="s">
+      <c r="D1207" s="12" t="s">
         <v>514</v>
       </c>
-      <c r="E1207" s="16"/>
-      <c r="F1207" s="16"/>
-    </row>
-    <row r="1208" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1208" s="14">
+    </row>
+    <row r="1208" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1208" s="2">
         <v>46313</v>
       </c>
-      <c r="B1208" s="15">
+      <c r="B1208" s="10">
         <v>0.65277777777777779</v>
       </c>
-      <c r="C1208" s="16" t="s">
+      <c r="C1208" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1208" s="18" t="s">
+      <c r="D1208" s="12" t="s">
         <v>472</v>
       </c>
-      <c r="E1208" s="16"/>
-      <c r="F1208" s="16"/>
-    </row>
-    <row r="1209" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1209" s="14">
+    </row>
+    <row r="1209" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1209" s="2">
         <v>46313</v>
       </c>
-      <c r="B1209" s="15"/>
-      <c r="C1209" s="16" t="s">
+      <c r="B1209" s="10"/>
+      <c r="C1209" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1209" s="18" t="s">
+      <c r="D1209" s="12" t="s">
         <v>515</v>
       </c>
-      <c r="E1209" s="16"/>
-      <c r="F1209" s="16"/>
-    </row>
-    <row r="1210" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1210" s="14">
+    </row>
+    <row r="1210" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1210" s="2">
         <v>46313</v>
       </c>
-      <c r="B1210" s="15"/>
-      <c r="C1210" s="16" t="s">
+      <c r="B1210" s="10"/>
+      <c r="C1210" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1210" s="18" t="s">
+      <c r="D1210" s="12" t="s">
         <v>473</v>
       </c>
-      <c r="E1210" s="16"/>
-      <c r="F1210" s="16"/>
-    </row>
-    <row r="1211" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1211" s="14">
+    </row>
+    <row r="1211" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1211" s="2">
         <v>46313</v>
       </c>
-      <c r="B1211" s="15">
+      <c r="B1211" s="10">
         <v>0.76041666666666663</v>
       </c>
-      <c r="C1211" s="16" t="s">
+      <c r="C1211" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1211" s="18" t="s">
+      <c r="D1211" s="12" t="s">
         <v>474</v>
       </c>
-      <c r="E1211" s="16"/>
-      <c r="F1211" s="16"/>
-    </row>
-    <row r="1212" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1212" s="14">
         <v>46313</v>
       </c>
@@ -19258,105 +19252,504 @@
       <c r="C1212" s="16" t="s">
         <v>499</v>
       </c>
-      <c r="D1212" s="18" t="s">
+      <c r="D1212" s="17" t="s">
         <v>55</v>
       </c>
       <c r="E1212" s="16"/>
       <c r="F1212" s="16"/>
-    </row>
-    <row r="1213" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1213" s="14"/>
-      <c r="B1213" s="15"/>
-      <c r="C1213" s="16"/>
-      <c r="D1213" s="17"/>
-      <c r="E1213" s="16"/>
-      <c r="F1213" s="16"/>
-    </row>
-    <row r="1214" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1214" s="14"/>
-      <c r="B1214" s="15"/>
-      <c r="C1214" s="16"/>
-      <c r="D1214" s="17"/>
-      <c r="E1214" s="16"/>
-      <c r="F1214" s="16"/>
-    </row>
-    <row r="1215" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1215" s="14"/>
+      <c r="G1212" s="18"/>
+    </row>
+    <row r="1213" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1213" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B1213" s="15">
+        <v>0.25694444444444442</v>
+      </c>
+      <c r="C1213" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1213" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="E1213" s="19"/>
+      <c r="F1213" s="19"/>
+      <c r="G1213" s="18"/>
+    </row>
+    <row r="1214" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1214" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B1214" s="15">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C1214" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1214" s="19" t="s">
+        <v>500</v>
+      </c>
+      <c r="E1214" s="19"/>
+      <c r="F1214" s="19"/>
+      <c r="G1214" s="18"/>
+    </row>
+    <row r="1215" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1215" s="14">
+        <v>46314</v>
+      </c>
       <c r="B1215" s="15"/>
-      <c r="C1215" s="16"/>
-      <c r="D1215" s="17"/>
-      <c r="E1215" s="16"/>
-      <c r="F1215" s="16"/>
-    </row>
-    <row r="1216" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1216" s="14"/>
-      <c r="B1216" s="15"/>
-      <c r="C1216" s="16"/>
-      <c r="D1216" s="17"/>
-      <c r="E1216" s="16"/>
-      <c r="F1216" s="16"/>
-    </row>
-    <row r="1217" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1217" s="2"/>
-      <c r="B1217" s="10"/>
-      <c r="D1217" s="8"/>
-    </row>
-    <row r="1218" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1218" s="2"/>
-      <c r="B1218" s="10"/>
-      <c r="D1218" s="8"/>
-    </row>
-    <row r="1219" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1219" s="2"/>
-      <c r="B1219" s="10"/>
-      <c r="D1219" s="8"/>
-    </row>
-    <row r="1220" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1220" s="2"/>
-      <c r="B1220" s="10"/>
-      <c r="D1220" s="8"/>
+      <c r="C1215" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1215" s="19" t="s">
+        <v>501</v>
+      </c>
+      <c r="E1215" s="19"/>
+      <c r="F1215" s="19"/>
+      <c r="G1215" s="18"/>
+    </row>
+    <row r="1216" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1216" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B1216" s="15">
+        <v>0.35069444444444442</v>
+      </c>
+      <c r="C1216" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1216" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="E1216" s="19"/>
+      <c r="F1216" s="19"/>
+      <c r="G1216" s="18"/>
+    </row>
+    <row r="1217" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1217" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B1217" s="15">
+        <v>0.3576388888888889</v>
+      </c>
+      <c r="C1217" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1217" s="19" t="s">
+        <v>503</v>
+      </c>
+      <c r="E1217" s="19"/>
+      <c r="F1217" s="19"/>
+      <c r="G1217" s="18"/>
+    </row>
+    <row r="1218" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1218" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B1218" s="15">
+        <v>0.375</v>
+      </c>
+      <c r="C1218" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1218" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="E1218" s="19"/>
+      <c r="F1218" s="19"/>
+      <c r="G1218" s="18"/>
+    </row>
+    <row r="1219" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1219" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B1219" s="15"/>
+      <c r="C1219" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1219" s="19" t="s">
+        <v>480</v>
+      </c>
+      <c r="E1219" s="19"/>
+      <c r="F1219" s="19"/>
+      <c r="G1219" s="18"/>
+    </row>
+    <row r="1220" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1220" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B1220" s="15"/>
+      <c r="C1220" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1220" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="E1220" s="19"/>
+      <c r="F1220" s="19"/>
+      <c r="G1220" s="18"/>
+    </row>
+    <row r="1221" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1221" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B1221" s="15"/>
+      <c r="C1221" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1221" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1221" s="19"/>
+      <c r="F1221" s="19"/>
+      <c r="G1221" s="18"/>
+    </row>
+    <row r="1222" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1222" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B1222" s="15">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="C1222" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1222" s="19" t="s">
+        <v>481</v>
+      </c>
+      <c r="E1222" s="19"/>
+      <c r="F1222" s="19"/>
+      <c r="G1222" s="18"/>
+    </row>
+    <row r="1223" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1223" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B1223" s="15">
+        <v>0.55347222222222225</v>
+      </c>
+      <c r="C1223" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1223" s="19" t="s">
+        <v>517</v>
+      </c>
+      <c r="E1223" s="19"/>
+      <c r="F1223" s="19"/>
+      <c r="G1223" s="18"/>
+    </row>
+    <row r="1224" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1224" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B1224" s="15">
+        <v>0.5625</v>
+      </c>
+      <c r="C1224" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1224" s="19" t="s">
+        <v>507</v>
+      </c>
+      <c r="E1224" s="19"/>
+      <c r="F1224" s="19"/>
+      <c r="G1224" s="18"/>
+    </row>
+    <row r="1225" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1225" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B1225" s="15">
+        <v>0.57430555555555551</v>
+      </c>
+      <c r="C1225" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1225" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="E1225" s="19"/>
+      <c r="F1225" s="19"/>
+      <c r="G1225" s="18"/>
+    </row>
+    <row r="1226" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1226" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B1226" s="15">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C1226" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1226" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="E1226" s="19"/>
+      <c r="F1226" s="19"/>
+      <c r="G1226" s="18"/>
+    </row>
+    <row r="1227" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1227" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B1227" s="15"/>
+      <c r="C1227" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1227" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1227" s="19"/>
+      <c r="F1227" s="19"/>
+      <c r="G1227" s="18"/>
+    </row>
+    <row r="1228" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1228" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B1228" s="15">
+        <v>0.25694444444444442</v>
+      </c>
+      <c r="C1228" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1228" s="17" t="s">
+        <v>460</v>
+      </c>
+      <c r="E1228" s="16"/>
+      <c r="F1228" s="16"/>
+      <c r="G1228" s="18"/>
+    </row>
+    <row r="1229" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1229" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B1229" s="15"/>
+      <c r="C1229" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1229" s="17" t="s">
+        <v>461</v>
+      </c>
+      <c r="E1229" s="16"/>
+      <c r="F1229" s="16"/>
+      <c r="G1229" s="18"/>
+    </row>
+    <row r="1230" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1230" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B1230" s="15">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C1230" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1230" s="17" t="s">
+        <v>518</v>
+      </c>
+      <c r="E1230" s="16"/>
+      <c r="F1230" s="16"/>
+      <c r="G1230" s="18"/>
+    </row>
+    <row r="1231" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1231" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B1231" s="15">
+        <v>0.34375</v>
+      </c>
+      <c r="C1231" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1231" s="17" t="s">
+        <v>492</v>
+      </c>
+      <c r="E1231" s="16"/>
+      <c r="F1231" s="16"/>
+      <c r="G1231" s="18"/>
+    </row>
+    <row r="1232" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1232" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B1232" s="15"/>
+      <c r="C1232" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1232" s="17" t="s">
+        <v>519</v>
+      </c>
+      <c r="E1232" s="16"/>
+      <c r="F1232" s="16"/>
+      <c r="G1232" s="18"/>
+    </row>
+    <row r="1233" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1233" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B1233" s="15"/>
+      <c r="C1233" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1233" s="17" t="s">
+        <v>511</v>
+      </c>
+      <c r="E1233" s="16"/>
+      <c r="F1233" s="16"/>
+      <c r="G1233" s="18"/>
+    </row>
+    <row r="1234" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1234" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B1234" s="15">
+        <v>0.36319444444444443</v>
+      </c>
+      <c r="C1234" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1234" s="17" t="s">
+        <v>520</v>
+      </c>
+      <c r="E1234" s="16"/>
+      <c r="F1234" s="16"/>
+      <c r="G1234" s="18"/>
+    </row>
+    <row r="1235" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1235" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B1235" s="15"/>
+      <c r="C1235" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1235" s="17" t="s">
+        <v>521</v>
+      </c>
+      <c r="E1235" s="16"/>
+      <c r="F1235" s="16"/>
+      <c r="G1235" s="18"/>
+    </row>
+    <row r="1236" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1236" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B1236" s="15">
+        <v>0.53680555555555554</v>
+      </c>
+      <c r="C1236" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1236" s="17" t="s">
+        <v>496</v>
+      </c>
+      <c r="E1236" s="16"/>
+      <c r="F1236" s="16"/>
+      <c r="G1236" s="18"/>
+    </row>
+    <row r="1237" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1237" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B1237" s="15">
+        <v>0.5708333333333333</v>
+      </c>
+      <c r="C1237" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1237" s="17" t="s">
+        <v>470</v>
+      </c>
+      <c r="E1237" s="16"/>
+      <c r="F1237" s="16"/>
+      <c r="G1237" s="18"/>
+    </row>
+    <row r="1238" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1238" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B1238" s="15">
+        <v>0.57430555555555551</v>
+      </c>
+      <c r="C1238" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1238" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="E1238" s="16"/>
+      <c r="F1238" s="16"/>
+      <c r="G1238" s="18"/>
+    </row>
+    <row r="1239" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1239" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B1239" s="15"/>
+      <c r="C1239" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1239" s="17" t="s">
+        <v>473</v>
+      </c>
+      <c r="E1239" s="16"/>
+      <c r="F1239" s="16"/>
+      <c r="G1239" s="18"/>
+    </row>
+    <row r="1240" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1240" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B1240" s="15">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C1240" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1240" s="17" t="s">
+        <v>474</v>
+      </c>
+      <c r="E1240" s="16"/>
+      <c r="F1240" s="16"/>
+      <c r="G1240" s="18"/>
+    </row>
+    <row r="1241" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1241" s="14">
+        <v>46314</v>
+      </c>
+      <c r="B1241" s="15"/>
+      <c r="C1241" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1241" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1241" s="16"/>
+      <c r="F1241" s="16"/>
+      <c r="G1241" s="18"/>
+    </row>
+    <row r="1242" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1242" s="16"/>
+      <c r="B1242" s="16"/>
+      <c r="C1242" s="16"/>
+      <c r="D1242" s="16"/>
+      <c r="E1242" s="16"/>
+      <c r="F1242" s="16"/>
+      <c r="G1242" s="18"/>
+    </row>
+    <row r="1243" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1243" s="16"/>
+      <c r="B1243" s="16"/>
+      <c r="C1243" s="16"/>
+      <c r="D1243" s="16"/>
+      <c r="E1243" s="16"/>
+      <c r="F1243" s="16"/>
+      <c r="G1243" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="D1078:F1078"/>
-    <mergeCell ref="D1072:F1072"/>
-    <mergeCell ref="D1070:F1070"/>
-    <mergeCell ref="D1071:F1071"/>
-    <mergeCell ref="D1077:F1077"/>
-    <mergeCell ref="D1074:F1074"/>
-    <mergeCell ref="D1075:F1075"/>
-    <mergeCell ref="D1076:F1076"/>
-    <mergeCell ref="D1069:F1069"/>
-    <mergeCell ref="D1066:F1066"/>
-    <mergeCell ref="D1067:F1067"/>
-    <mergeCell ref="D1052:F1052"/>
-    <mergeCell ref="D1053:F1053"/>
-    <mergeCell ref="D1054:F1054"/>
-    <mergeCell ref="D1055:F1055"/>
-    <mergeCell ref="D1056:F1056"/>
-    <mergeCell ref="D1057:F1057"/>
-    <mergeCell ref="D1058:F1058"/>
-    <mergeCell ref="D1059:F1059"/>
-    <mergeCell ref="D1060:F1060"/>
-    <mergeCell ref="D1061:F1061"/>
-    <mergeCell ref="D1049:F1049"/>
-    <mergeCell ref="D1050:F1050"/>
-    <mergeCell ref="D1051:F1051"/>
-    <mergeCell ref="D1065:F1065"/>
-    <mergeCell ref="D1068:F1068"/>
-    <mergeCell ref="D1064:F1064"/>
-    <mergeCell ref="D1062:F1062"/>
-    <mergeCell ref="D1063:F1063"/>
-    <mergeCell ref="D1047:F1047"/>
-    <mergeCell ref="D1048:F1048"/>
-    <mergeCell ref="D987:F987"/>
-    <mergeCell ref="D988:F988"/>
-    <mergeCell ref="D981:F981"/>
-    <mergeCell ref="D982:F982"/>
-    <mergeCell ref="D983:F983"/>
-    <mergeCell ref="D984:F984"/>
-    <mergeCell ref="D985:F985"/>
-    <mergeCell ref="D986:F986"/>
     <mergeCell ref="D965:F965"/>
     <mergeCell ref="D966:F966"/>
     <mergeCell ref="D967:F967"/>
@@ -19373,6 +19766,45 @@
     <mergeCell ref="D977:F977"/>
     <mergeCell ref="D978:F978"/>
     <mergeCell ref="D979:F979"/>
+    <mergeCell ref="D1047:F1047"/>
+    <mergeCell ref="D1048:F1048"/>
+    <mergeCell ref="D987:F987"/>
+    <mergeCell ref="D988:F988"/>
+    <mergeCell ref="D981:F981"/>
+    <mergeCell ref="D982:F982"/>
+    <mergeCell ref="D983:F983"/>
+    <mergeCell ref="D984:F984"/>
+    <mergeCell ref="D985:F985"/>
+    <mergeCell ref="D986:F986"/>
+    <mergeCell ref="D1049:F1049"/>
+    <mergeCell ref="D1050:F1050"/>
+    <mergeCell ref="D1051:F1051"/>
+    <mergeCell ref="D1065:F1065"/>
+    <mergeCell ref="D1068:F1068"/>
+    <mergeCell ref="D1064:F1064"/>
+    <mergeCell ref="D1062:F1062"/>
+    <mergeCell ref="D1063:F1063"/>
+    <mergeCell ref="D1069:F1069"/>
+    <mergeCell ref="D1066:F1066"/>
+    <mergeCell ref="D1067:F1067"/>
+    <mergeCell ref="D1052:F1052"/>
+    <mergeCell ref="D1053:F1053"/>
+    <mergeCell ref="D1054:F1054"/>
+    <mergeCell ref="D1055:F1055"/>
+    <mergeCell ref="D1056:F1056"/>
+    <mergeCell ref="D1057:F1057"/>
+    <mergeCell ref="D1058:F1058"/>
+    <mergeCell ref="D1059:F1059"/>
+    <mergeCell ref="D1060:F1060"/>
+    <mergeCell ref="D1061:F1061"/>
+    <mergeCell ref="D1078:F1078"/>
+    <mergeCell ref="D1072:F1072"/>
+    <mergeCell ref="D1070:F1070"/>
+    <mergeCell ref="D1071:F1071"/>
+    <mergeCell ref="D1077:F1077"/>
+    <mergeCell ref="D1074:F1074"/>
+    <mergeCell ref="D1075:F1075"/>
+    <mergeCell ref="D1076:F1076"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hourly.xlsx
+++ b/hourly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D14692-52E7-4A9A-99E3-96B2AFF3DDA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CDAB27B-F682-4B91-A008-EA5F38CC61CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2484" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2554" uniqueCount="528">
   <si>
     <t>Sailing to F2-C05</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2001,6 +2001,22 @@
   </si>
   <si>
     <t>Last push off (D01)</t>
+  </si>
+  <si>
+    <t>(D01)</t>
+  </si>
+  <si>
+    <t>Mob AIB-006</t>
+  </si>
+  <si>
+    <t>Wait on weather</t>
+  </si>
+  <si>
+    <t>0.9 m/s current</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Maintenance</t>
   </si>
 </sst>
 </file>
@@ -2427,7 +2443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1243"/>
+  <dimension ref="A1:I1276"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.296875" style="1" bestFit="1" customWidth="1"/>
@@ -19098,7 +19114,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="1201" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1201" s="2">
         <v>46313</v>
       </c>
@@ -19112,7 +19128,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="1202" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1202" s="2">
         <v>46313</v>
       </c>
@@ -19124,7 +19140,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="1203" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1203" s="2">
         <v>46313</v>
       </c>
@@ -19138,7 +19154,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="1204" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1204" s="2">
         <v>46313</v>
       </c>
@@ -19150,7 +19166,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="1205" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1205" s="2">
         <v>46313</v>
       </c>
@@ -19164,7 +19180,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="1206" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1206" s="2">
         <v>46313</v>
       </c>
@@ -19178,7 +19194,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="1207" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1207" s="2">
         <v>46313</v>
       </c>
@@ -19192,7 +19208,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="1208" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1208" s="2">
         <v>46313</v>
       </c>
@@ -19206,7 +19222,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="1209" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1209" s="2">
         <v>46313</v>
       </c>
@@ -19218,7 +19234,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="1210" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1210" s="2">
         <v>46313</v>
       </c>
@@ -19230,7 +19246,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="1211" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1211" s="2">
         <v>46313</v>
       </c>
@@ -19244,461 +19260,407 @@
         <v>474</v>
       </c>
     </row>
-    <row r="1212" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1212" s="14">
+    <row r="1212" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1212" s="2">
         <v>46313</v>
       </c>
-      <c r="B1212" s="15"/>
-      <c r="C1212" s="16" t="s">
+      <c r="B1212" s="10"/>
+      <c r="C1212" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1212" s="17" t="s">
+      <c r="D1212" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="E1212" s="16"/>
-      <c r="F1212" s="16"/>
-      <c r="G1212" s="18"/>
-    </row>
-    <row r="1213" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1213" s="14">
+    </row>
+    <row r="1213" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1213" s="2">
         <v>46314</v>
       </c>
-      <c r="B1213" s="15">
+      <c r="B1213" s="10">
         <v>0.25694444444444442</v>
       </c>
-      <c r="C1213" s="16" t="s">
+      <c r="C1213" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="D1213" s="19" t="s">
+      <c r="D1213" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="E1213" s="19"/>
-      <c r="F1213" s="19"/>
-      <c r="G1213" s="18"/>
-    </row>
-    <row r="1214" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1214" s="14">
+      <c r="E1213" s="8"/>
+      <c r="F1213" s="8"/>
+    </row>
+    <row r="1214" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1214" s="2">
         <v>46314</v>
       </c>
-      <c r="B1214" s="15">
+      <c r="B1214" s="10">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C1214" s="16" t="s">
+      <c r="C1214" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="D1214" s="19" t="s">
+      <c r="D1214" s="8" t="s">
         <v>500</v>
       </c>
-      <c r="E1214" s="19"/>
-      <c r="F1214" s="19"/>
-      <c r="G1214" s="18"/>
-    </row>
-    <row r="1215" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1215" s="14">
+      <c r="E1214" s="8"/>
+      <c r="F1214" s="8"/>
+    </row>
+    <row r="1215" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1215" s="2">
         <v>46314</v>
       </c>
-      <c r="B1215" s="15"/>
-      <c r="C1215" s="16" t="s">
+      <c r="B1215" s="10"/>
+      <c r="C1215" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="D1215" s="19" t="s">
+      <c r="D1215" s="8" t="s">
         <v>501</v>
       </c>
-      <c r="E1215" s="19"/>
-      <c r="F1215" s="19"/>
-      <c r="G1215" s="18"/>
-    </row>
-    <row r="1216" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1216" s="14">
+      <c r="E1215" s="8"/>
+      <c r="F1215" s="8"/>
+    </row>
+    <row r="1216" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1216" s="2">
         <v>46314</v>
       </c>
-      <c r="B1216" s="15">
+      <c r="B1216" s="10">
         <v>0.35069444444444442</v>
       </c>
-      <c r="C1216" s="16" t="s">
+      <c r="C1216" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="D1216" s="19" t="s">
+      <c r="D1216" s="8" t="s">
         <v>502</v>
       </c>
-      <c r="E1216" s="19"/>
-      <c r="F1216" s="19"/>
-      <c r="G1216" s="18"/>
-    </row>
-    <row r="1217" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1217" s="14">
+      <c r="E1216" s="8"/>
+      <c r="F1216" s="8"/>
+    </row>
+    <row r="1217" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1217" s="2">
         <v>46314</v>
       </c>
-      <c r="B1217" s="15">
+      <c r="B1217" s="10">
         <v>0.3576388888888889</v>
       </c>
-      <c r="C1217" s="16" t="s">
+      <c r="C1217" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="D1217" s="19" t="s">
+      <c r="D1217" s="8" t="s">
         <v>503</v>
       </c>
-      <c r="E1217" s="19"/>
-      <c r="F1217" s="19"/>
-      <c r="G1217" s="18"/>
-    </row>
-    <row r="1218" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1218" s="14">
+      <c r="E1217" s="8"/>
+      <c r="F1217" s="8"/>
+    </row>
+    <row r="1218" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1218" s="2">
         <v>46314</v>
       </c>
-      <c r="B1218" s="15">
+      <c r="B1218" s="10">
         <v>0.375</v>
       </c>
-      <c r="C1218" s="16" t="s">
+      <c r="C1218" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="D1218" s="19" t="s">
+      <c r="D1218" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="E1218" s="19"/>
-      <c r="F1218" s="19"/>
-      <c r="G1218" s="18"/>
-    </row>
-    <row r="1219" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1219" s="14">
+      <c r="E1218" s="8"/>
+      <c r="F1218" s="8"/>
+    </row>
+    <row r="1219" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1219" s="2">
         <v>46314</v>
       </c>
-      <c r="B1219" s="15"/>
-      <c r="C1219" s="16" t="s">
+      <c r="B1219" s="10"/>
+      <c r="C1219" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="D1219" s="19" t="s">
+      <c r="D1219" s="8" t="s">
         <v>480</v>
       </c>
-      <c r="E1219" s="19"/>
-      <c r="F1219" s="19"/>
-      <c r="G1219" s="18"/>
-    </row>
-    <row r="1220" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1220" s="14">
+      <c r="E1219" s="8"/>
+      <c r="F1219" s="8"/>
+    </row>
+    <row r="1220" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1220" s="2">
         <v>46314</v>
       </c>
-      <c r="B1220" s="15"/>
-      <c r="C1220" s="16" t="s">
+      <c r="B1220" s="10"/>
+      <c r="C1220" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="D1220" s="19" t="s">
+      <c r="D1220" s="8" t="s">
         <v>516</v>
       </c>
-      <c r="E1220" s="19"/>
-      <c r="F1220" s="19"/>
-      <c r="G1220" s="18"/>
-    </row>
-    <row r="1221" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1221" s="14">
+      <c r="E1220" s="8"/>
+      <c r="F1220" s="8"/>
+    </row>
+    <row r="1221" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1221" s="2">
         <v>46314</v>
       </c>
-      <c r="B1221" s="15"/>
-      <c r="C1221" s="16" t="s">
+      <c r="B1221" s="10"/>
+      <c r="C1221" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="D1221" s="19" t="s">
+      <c r="D1221" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="E1221" s="19"/>
-      <c r="F1221" s="19"/>
-      <c r="G1221" s="18"/>
-    </row>
-    <row r="1222" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1222" s="14">
+      <c r="E1221" s="8"/>
+      <c r="F1221" s="8"/>
+    </row>
+    <row r="1222" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1222" s="2">
         <v>46314</v>
       </c>
-      <c r="B1222" s="15">
+      <c r="B1222" s="10">
         <v>0.53472222222222221</v>
       </c>
-      <c r="C1222" s="16" t="s">
+      <c r="C1222" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="D1222" s="19" t="s">
+      <c r="D1222" s="8" t="s">
         <v>481</v>
       </c>
-      <c r="E1222" s="19"/>
-      <c r="F1222" s="19"/>
-      <c r="G1222" s="18"/>
-    </row>
-    <row r="1223" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1223" s="14">
+      <c r="E1222" s="8"/>
+      <c r="F1222" s="8"/>
+    </row>
+    <row r="1223" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1223" s="2">
         <v>46314</v>
       </c>
-      <c r="B1223" s="15">
+      <c r="B1223" s="10">
         <v>0.55347222222222225</v>
       </c>
-      <c r="C1223" s="16" t="s">
+      <c r="C1223" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="D1223" s="19" t="s">
+      <c r="D1223" s="8" t="s">
         <v>517</v>
       </c>
-      <c r="E1223" s="19"/>
-      <c r="F1223" s="19"/>
-      <c r="G1223" s="18"/>
-    </row>
-    <row r="1224" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1224" s="14">
+      <c r="E1223" s="8"/>
+      <c r="F1223" s="8"/>
+    </row>
+    <row r="1224" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1224" s="2">
         <v>46314</v>
       </c>
-      <c r="B1224" s="15">
+      <c r="B1224" s="10">
         <v>0.5625</v>
       </c>
-      <c r="C1224" s="16" t="s">
+      <c r="C1224" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="D1224" s="19" t="s">
+      <c r="D1224" s="8" t="s">
         <v>507</v>
       </c>
-      <c r="E1224" s="19"/>
-      <c r="F1224" s="19"/>
-      <c r="G1224" s="18"/>
-    </row>
-    <row r="1225" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1225" s="14">
+      <c r="E1224" s="8"/>
+      <c r="F1224" s="8"/>
+    </row>
+    <row r="1225" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1225" s="2">
         <v>46314</v>
       </c>
-      <c r="B1225" s="15">
+      <c r="B1225" s="10">
         <v>0.57430555555555551</v>
       </c>
-      <c r="C1225" s="16" t="s">
+      <c r="C1225" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="D1225" s="19" t="s">
+      <c r="D1225" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="E1225" s="19"/>
-      <c r="F1225" s="19"/>
-      <c r="G1225" s="18"/>
-    </row>
-    <row r="1226" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1226" s="14">
+      <c r="E1225" s="8"/>
+      <c r="F1225" s="8"/>
+    </row>
+    <row r="1226" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1226" s="2">
         <v>46314</v>
       </c>
-      <c r="B1226" s="15">
+      <c r="B1226" s="10">
         <v>0.66666666666666663</v>
       </c>
-      <c r="C1226" s="16" t="s">
+      <c r="C1226" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="D1226" s="19" t="s">
+      <c r="D1226" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="E1226" s="19"/>
-      <c r="F1226" s="19"/>
-      <c r="G1226" s="18"/>
-    </row>
-    <row r="1227" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1227" s="14">
+      <c r="E1226" s="8"/>
+      <c r="F1226" s="8"/>
+    </row>
+    <row r="1227" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1227" s="2">
         <v>46314</v>
       </c>
-      <c r="B1227" s="15"/>
-      <c r="C1227" s="16" t="s">
+      <c r="B1227" s="10"/>
+      <c r="C1227" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="D1227" s="19" t="s">
+      <c r="D1227" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E1227" s="19"/>
-      <c r="F1227" s="19"/>
-      <c r="G1227" s="18"/>
-    </row>
-    <row r="1228" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1228" s="14">
+      <c r="E1227" s="8"/>
+      <c r="F1227" s="8"/>
+    </row>
+    <row r="1228" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1228" s="2">
         <v>46314</v>
       </c>
-      <c r="B1228" s="15">
+      <c r="B1228" s="10">
         <v>0.25694444444444442</v>
       </c>
-      <c r="C1228" s="16" t="s">
+      <c r="C1228" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1228" s="17" t="s">
+      <c r="D1228" s="12" t="s">
         <v>460</v>
       </c>
-      <c r="E1228" s="16"/>
-      <c r="F1228" s="16"/>
-      <c r="G1228" s="18"/>
-    </row>
-    <row r="1229" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1229" s="14">
+    </row>
+    <row r="1229" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1229" s="2">
         <v>46314</v>
       </c>
-      <c r="B1229" s="15"/>
-      <c r="C1229" s="16" t="s">
+      <c r="B1229" s="10"/>
+      <c r="C1229" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1229" s="17" t="s">
+      <c r="D1229" s="12" t="s">
         <v>461</v>
       </c>
-      <c r="E1229" s="16"/>
-      <c r="F1229" s="16"/>
-      <c r="G1229" s="18"/>
-    </row>
-    <row r="1230" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1230" s="14">
+    </row>
+    <row r="1230" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1230" s="2">
         <v>46314</v>
       </c>
-      <c r="B1230" s="15">
+      <c r="B1230" s="10">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C1230" s="16" t="s">
+      <c r="C1230" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1230" s="17" t="s">
+      <c r="D1230" s="12" t="s">
         <v>518</v>
       </c>
-      <c r="E1230" s="16"/>
-      <c r="F1230" s="16"/>
-      <c r="G1230" s="18"/>
-    </row>
-    <row r="1231" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1231" s="14">
+    </row>
+    <row r="1231" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1231" s="2">
         <v>46314</v>
       </c>
-      <c r="B1231" s="15">
+      <c r="B1231" s="10">
         <v>0.34375</v>
       </c>
-      <c r="C1231" s="16" t="s">
+      <c r="C1231" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1231" s="17" t="s">
+      <c r="D1231" s="12" t="s">
         <v>492</v>
       </c>
-      <c r="E1231" s="16"/>
-      <c r="F1231" s="16"/>
-      <c r="G1231" s="18"/>
-    </row>
-    <row r="1232" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1232" s="14">
+    </row>
+    <row r="1232" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1232" s="2">
         <v>46314</v>
       </c>
-      <c r="B1232" s="15"/>
-      <c r="C1232" s="16" t="s">
+      <c r="B1232" s="10"/>
+      <c r="C1232" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1232" s="17" t="s">
+      <c r="D1232" s="12" t="s">
         <v>519</v>
       </c>
-      <c r="E1232" s="16"/>
-      <c r="F1232" s="16"/>
-      <c r="G1232" s="18"/>
-    </row>
-    <row r="1233" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1233" s="14">
+    </row>
+    <row r="1233" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1233" s="2">
         <v>46314</v>
       </c>
-      <c r="B1233" s="15"/>
-      <c r="C1233" s="16" t="s">
+      <c r="B1233" s="10"/>
+      <c r="C1233" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1233" s="17" t="s">
+      <c r="D1233" s="12" t="s">
         <v>511</v>
       </c>
-      <c r="E1233" s="16"/>
-      <c r="F1233" s="16"/>
-      <c r="G1233" s="18"/>
-    </row>
-    <row r="1234" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1234" s="14">
+    </row>
+    <row r="1234" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1234" s="2">
         <v>46314</v>
       </c>
-      <c r="B1234" s="15">
+      <c r="B1234" s="10">
         <v>0.36319444444444443</v>
       </c>
-      <c r="C1234" s="16" t="s">
+      <c r="C1234" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1234" s="17" t="s">
+      <c r="D1234" s="12" t="s">
         <v>520</v>
       </c>
-      <c r="E1234" s="16"/>
-      <c r="F1234" s="16"/>
-      <c r="G1234" s="18"/>
-    </row>
-    <row r="1235" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1235" s="14">
+    </row>
+    <row r="1235" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1235" s="2">
         <v>46314</v>
       </c>
-      <c r="B1235" s="15"/>
-      <c r="C1235" s="16" t="s">
+      <c r="B1235" s="10"/>
+      <c r="C1235" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1235" s="17" t="s">
+      <c r="D1235" s="12" t="s">
         <v>521</v>
       </c>
-      <c r="E1235" s="16"/>
-      <c r="F1235" s="16"/>
-      <c r="G1235" s="18"/>
-    </row>
-    <row r="1236" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1236" s="14">
+    </row>
+    <row r="1236" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1236" s="2">
         <v>46314</v>
       </c>
-      <c r="B1236" s="15">
+      <c r="B1236" s="10">
         <v>0.53680555555555554</v>
       </c>
-      <c r="C1236" s="16" t="s">
+      <c r="C1236" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1236" s="17" t="s">
+      <c r="D1236" s="12" t="s">
         <v>496</v>
       </c>
-      <c r="E1236" s="16"/>
-      <c r="F1236" s="16"/>
-      <c r="G1236" s="18"/>
-    </row>
-    <row r="1237" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1237" s="14">
+    </row>
+    <row r="1237" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1237" s="2">
         <v>46314</v>
       </c>
-      <c r="B1237" s="15">
+      <c r="B1237" s="10">
         <v>0.5708333333333333</v>
       </c>
-      <c r="C1237" s="16" t="s">
+      <c r="C1237" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1237" s="17" t="s">
+      <c r="D1237" s="12" t="s">
         <v>470</v>
       </c>
-      <c r="E1237" s="16"/>
-      <c r="F1237" s="16"/>
-      <c r="G1237" s="18"/>
-    </row>
-    <row r="1238" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1238" s="14">
+    </row>
+    <row r="1238" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1238" s="2">
         <v>46314</v>
       </c>
-      <c r="B1238" s="15">
+      <c r="B1238" s="10">
         <v>0.57430555555555551</v>
       </c>
-      <c r="C1238" s="16" t="s">
+      <c r="C1238" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1238" s="17" t="s">
+      <c r="D1238" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="E1238" s="16"/>
-      <c r="F1238" s="16"/>
-      <c r="G1238" s="18"/>
-    </row>
-    <row r="1239" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1239" s="14">
+    </row>
+    <row r="1239" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1239" s="2">
         <v>46314</v>
       </c>
-      <c r="B1239" s="15"/>
-      <c r="C1239" s="16" t="s">
+      <c r="B1239" s="10"/>
+      <c r="C1239" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D1239" s="17" t="s">
+      <c r="D1239" s="12" t="s">
         <v>473</v>
       </c>
-      <c r="E1239" s="16"/>
-      <c r="F1239" s="16"/>
-      <c r="G1239" s="18"/>
-    </row>
-    <row r="1240" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1240" s="14">
         <v>46314</v>
       </c>
@@ -19714,8 +19676,10 @@
       <c r="E1240" s="16"/>
       <c r="F1240" s="16"/>
       <c r="G1240" s="18"/>
-    </row>
-    <row r="1241" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1240" s="18"/>
+      <c r="I1240" s="18"/>
+    </row>
+    <row r="1241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1241" s="14">
         <v>46314</v>
       </c>
@@ -19729,27 +19693,681 @@
       <c r="E1241" s="16"/>
       <c r="F1241" s="16"/>
       <c r="G1241" s="18"/>
-    </row>
-    <row r="1242" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1242" s="16"/>
-      <c r="B1242" s="16"/>
-      <c r="C1242" s="16"/>
-      <c r="D1242" s="16"/>
-      <c r="E1242" s="16"/>
-      <c r="F1242" s="16"/>
+      <c r="H1241" s="18"/>
+      <c r="I1241" s="18"/>
+    </row>
+    <row r="1242" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1242" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1242" s="15">
+        <v>0.2638888888888889</v>
+      </c>
+      <c r="C1242" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1242" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="E1242" s="19"/>
+      <c r="F1242" s="19"/>
       <c r="G1242" s="18"/>
-    </row>
-    <row r="1243" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1243" s="16"/>
-      <c r="B1243" s="16"/>
-      <c r="C1243" s="16"/>
-      <c r="D1243" s="16"/>
-      <c r="E1243" s="16"/>
-      <c r="F1243" s="16"/>
+      <c r="H1242" s="18"/>
+      <c r="I1242" s="18"/>
+    </row>
+    <row r="1243" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1243" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1243" s="15">
+        <v>0.34722222222222221</v>
+      </c>
+      <c r="C1243" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1243" s="19" t="s">
+        <v>500</v>
+      </c>
+      <c r="E1243" s="19"/>
+      <c r="F1243" s="19"/>
       <c r="G1243" s="18"/>
+      <c r="H1243" s="18"/>
+      <c r="I1243" s="18"/>
+    </row>
+    <row r="1244" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1244" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1244" s="15"/>
+      <c r="C1244" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1244" s="19" t="s">
+        <v>501</v>
+      </c>
+      <c r="E1244" s="19"/>
+      <c r="F1244" s="19"/>
+      <c r="G1244" s="18"/>
+      <c r="H1244" s="18"/>
+      <c r="I1244" s="18"/>
+    </row>
+    <row r="1245" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1245" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1245" s="15">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="C1245" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1245" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="E1245" s="19"/>
+      <c r="F1245" s="19"/>
+      <c r="G1245" s="18"/>
+      <c r="H1245" s="18"/>
+      <c r="I1245" s="18"/>
+    </row>
+    <row r="1246" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1246" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1246" s="15">
+        <v>0.36805555555555558</v>
+      </c>
+      <c r="C1246" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1246" s="19" t="s">
+        <v>503</v>
+      </c>
+      <c r="E1246" s="19"/>
+      <c r="F1246" s="19"/>
+      <c r="G1246" s="18"/>
+      <c r="H1246" s="18"/>
+      <c r="I1246" s="18"/>
+    </row>
+    <row r="1247" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1247" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1247" s="15">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="C1247" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1247" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="E1247" s="19"/>
+      <c r="F1247" s="19"/>
+      <c r="G1247" s="18"/>
+      <c r="H1247" s="18"/>
+      <c r="I1247" s="18"/>
+    </row>
+    <row r="1248" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1248" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1248" s="15"/>
+      <c r="C1248" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1248" s="19" t="s">
+        <v>480</v>
+      </c>
+      <c r="E1248" s="19"/>
+      <c r="F1248" s="19"/>
+      <c r="G1248" s="18"/>
+      <c r="H1248" s="18"/>
+      <c r="I1248" s="18"/>
+    </row>
+    <row r="1249" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1249" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1249" s="15">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C1249" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1249" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1249" s="19"/>
+      <c r="F1249" s="19"/>
+      <c r="G1249" s="18"/>
+      <c r="H1249" s="18"/>
+      <c r="I1249" s="18"/>
+    </row>
+    <row r="1250" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1250" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1250" s="15"/>
+      <c r="C1250" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1250" s="19" t="s">
+        <v>481</v>
+      </c>
+      <c r="E1250" s="19"/>
+      <c r="F1250" s="19"/>
+      <c r="G1250" s="18"/>
+      <c r="H1250" s="18"/>
+      <c r="I1250" s="18"/>
+    </row>
+    <row r="1251" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1251" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1251" s="15">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1251" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1251" s="19" t="s">
+        <v>517</v>
+      </c>
+      <c r="E1251" s="19"/>
+      <c r="F1251" s="19"/>
+      <c r="G1251" s="18"/>
+      <c r="H1251" s="18"/>
+      <c r="I1251" s="18"/>
+    </row>
+    <row r="1252" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1252" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1252" s="15">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="C1252" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1252" s="19" t="s">
+        <v>507</v>
+      </c>
+      <c r="E1252" s="19"/>
+      <c r="F1252" s="19"/>
+      <c r="G1252" s="18"/>
+      <c r="H1252" s="18"/>
+      <c r="I1252" s="18"/>
+    </row>
+    <row r="1253" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1253" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1253" s="15">
+        <v>0.56944444444444442</v>
+      </c>
+      <c r="C1253" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1253" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="E1253" s="19"/>
+      <c r="F1253" s="19"/>
+      <c r="G1253" s="18"/>
+      <c r="H1253" s="18"/>
+      <c r="I1253" s="18"/>
+    </row>
+    <row r="1254" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1254" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1254" s="15">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C1254" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1254" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="E1254" s="19"/>
+      <c r="F1254" s="19"/>
+      <c r="G1254" s="18"/>
+      <c r="H1254" s="18"/>
+      <c r="I1254" s="18"/>
+    </row>
+    <row r="1255" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1255" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1255" s="15"/>
+      <c r="C1255" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D1255" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1255" s="19"/>
+      <c r="F1255" s="19"/>
+      <c r="G1255" s="18"/>
+      <c r="H1255" s="18"/>
+      <c r="I1255" s="18"/>
+    </row>
+    <row r="1256" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1256" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1256" s="15">
+        <v>0.2638888888888889</v>
+      </c>
+      <c r="C1256" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1256" s="17" t="s">
+        <v>460</v>
+      </c>
+      <c r="E1256" s="16"/>
+      <c r="F1256" s="16"/>
+      <c r="G1256" s="18"/>
+      <c r="H1256" s="18"/>
+      <c r="I1256" s="18"/>
+    </row>
+    <row r="1257" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1257" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1257" s="15"/>
+      <c r="C1257" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1257" s="17" t="s">
+        <v>461</v>
+      </c>
+      <c r="E1257" s="16"/>
+      <c r="F1257" s="16"/>
+      <c r="G1257" s="18"/>
+      <c r="H1257" s="18"/>
+      <c r="I1257" s="18"/>
+    </row>
+    <row r="1258" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1258" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1258" s="15">
+        <v>0.34722222222222221</v>
+      </c>
+      <c r="C1258" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1258" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="E1258" s="16"/>
+      <c r="F1258" s="16"/>
+      <c r="G1258" s="18"/>
+      <c r="H1258" s="18"/>
+      <c r="I1258" s="18"/>
+    </row>
+    <row r="1259" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1259" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1259" s="15"/>
+      <c r="C1259" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1259" s="17" t="s">
+        <v>523</v>
+      </c>
+      <c r="E1259" s="16"/>
+      <c r="F1259" s="16"/>
+      <c r="G1259" s="18"/>
+      <c r="H1259" s="18"/>
+      <c r="I1259" s="18"/>
+    </row>
+    <row r="1260" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1260" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1260" s="15">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C1260" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1260" s="17" t="s">
+        <v>464</v>
+      </c>
+      <c r="E1260" s="16"/>
+      <c r="F1260" s="16"/>
+      <c r="G1260" s="18"/>
+      <c r="H1260" s="18"/>
+      <c r="I1260" s="18"/>
+    </row>
+    <row r="1261" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1261" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1261" s="15"/>
+      <c r="C1261" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1261" s="17" t="s">
+        <v>519</v>
+      </c>
+      <c r="E1261" s="16"/>
+      <c r="F1261" s="16"/>
+      <c r="G1261" s="18"/>
+      <c r="H1261" s="18"/>
+      <c r="I1261" s="18"/>
+    </row>
+    <row r="1262" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1262" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1262" s="15"/>
+      <c r="C1262" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1262" s="17" t="s">
+        <v>524</v>
+      </c>
+      <c r="E1262" s="16"/>
+      <c r="F1262" s="16"/>
+      <c r="G1262" s="18"/>
+      <c r="H1262" s="18"/>
+      <c r="I1262" s="18"/>
+    </row>
+    <row r="1263" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1263" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1263" s="15">
+        <v>0.36388888888888887</v>
+      </c>
+      <c r="C1263" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1263" s="17" t="s">
+        <v>525</v>
+      </c>
+      <c r="E1263" s="16"/>
+      <c r="F1263" s="16"/>
+      <c r="G1263" s="18"/>
+      <c r="H1263" s="18"/>
+      <c r="I1263" s="18"/>
+    </row>
+    <row r="1264" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1264" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1264" s="15"/>
+      <c r="C1264" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1264" s="17" t="s">
+        <v>526</v>
+      </c>
+      <c r="E1264" s="16"/>
+      <c r="F1264" s="16"/>
+      <c r="G1264" s="18"/>
+      <c r="H1264" s="18"/>
+      <c r="I1264" s="18"/>
+    </row>
+    <row r="1265" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1265" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1265" s="15">
+        <v>0.40486111111111112</v>
+      </c>
+      <c r="C1265" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1265" s="17" t="s">
+        <v>527</v>
+      </c>
+      <c r="E1265" s="16"/>
+      <c r="F1265" s="16"/>
+      <c r="G1265" s="18"/>
+      <c r="H1265" s="18"/>
+      <c r="I1265" s="18"/>
+    </row>
+    <row r="1266" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1266" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1266" s="15">
+        <v>0.52013888888888893</v>
+      </c>
+      <c r="C1266" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1266" s="17" t="s">
+        <v>496</v>
+      </c>
+      <c r="E1266" s="16"/>
+      <c r="F1266" s="16"/>
+      <c r="G1266" s="18"/>
+      <c r="H1266" s="18"/>
+      <c r="I1266" s="18"/>
+    </row>
+    <row r="1267" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1267" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1267" s="15">
+        <v>0.56597222222222221</v>
+      </c>
+      <c r="C1267" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1267" s="17" t="s">
+        <v>470</v>
+      </c>
+      <c r="E1267" s="16"/>
+      <c r="F1267" s="16"/>
+      <c r="G1267" s="18"/>
+      <c r="H1267" s="18"/>
+      <c r="I1267" s="18"/>
+    </row>
+    <row r="1268" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1268" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1268" s="15">
+        <v>0.56944444444444442</v>
+      </c>
+      <c r="C1268" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1268" s="17" t="s">
+        <v>472</v>
+      </c>
+      <c r="E1268" s="16"/>
+      <c r="F1268" s="16"/>
+      <c r="G1268" s="18"/>
+      <c r="H1268" s="18"/>
+      <c r="I1268" s="18"/>
+    </row>
+    <row r="1269" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1269" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1269" s="15"/>
+      <c r="C1269" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1269" s="17" t="s">
+        <v>523</v>
+      </c>
+      <c r="E1269" s="16"/>
+      <c r="F1269" s="16"/>
+      <c r="G1269" s="18"/>
+      <c r="H1269" s="18"/>
+      <c r="I1269" s="18"/>
+    </row>
+    <row r="1270" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1270" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1270" s="15"/>
+      <c r="C1270" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1270" s="17" t="s">
+        <v>473</v>
+      </c>
+      <c r="E1270" s="16"/>
+      <c r="F1270" s="16"/>
+      <c r="G1270" s="18"/>
+      <c r="H1270" s="18"/>
+      <c r="I1270" s="18"/>
+    </row>
+    <row r="1271" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1271" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1271" s="15">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C1271" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1271" s="17" t="s">
+        <v>474</v>
+      </c>
+      <c r="E1271" s="16"/>
+      <c r="F1271" s="16"/>
+      <c r="G1271" s="18"/>
+      <c r="H1271" s="18"/>
+      <c r="I1271" s="18"/>
+    </row>
+    <row r="1272" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1272" s="14">
+        <v>46315</v>
+      </c>
+      <c r="B1272" s="15"/>
+      <c r="C1272" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1272" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1272" s="16"/>
+      <c r="F1272" s="16"/>
+      <c r="G1272" s="18"/>
+      <c r="H1272" s="18"/>
+      <c r="I1272" s="18"/>
+    </row>
+    <row r="1273" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1273" s="14">
+        <v>46316</v>
+      </c>
+      <c r="B1273" s="10">
+        <v>0.375</v>
+      </c>
+      <c r="C1273" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1273" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="E1273" s="16"/>
+      <c r="F1273" s="16"/>
+      <c r="G1273" s="18"/>
+      <c r="H1273" s="18"/>
+      <c r="I1273" s="18"/>
+    </row>
+    <row r="1274" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1274" s="14">
+        <v>46316</v>
+      </c>
+      <c r="B1274" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="C1274" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1274" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1274" s="16"/>
+      <c r="F1274" s="16"/>
+      <c r="G1274" s="18"/>
+      <c r="H1274" s="18"/>
+      <c r="I1274" s="18"/>
+    </row>
+    <row r="1275" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1275" s="14">
+        <v>46316</v>
+      </c>
+      <c r="B1275" s="10">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C1275" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1275" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1276" s="14">
+        <v>46316</v>
+      </c>
+      <c r="B1276" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="C1276" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1276" s="8" t="s">
+        <v>109</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="D1078:F1078"/>
+    <mergeCell ref="D1072:F1072"/>
+    <mergeCell ref="D1070:F1070"/>
+    <mergeCell ref="D1071:F1071"/>
+    <mergeCell ref="D1077:F1077"/>
+    <mergeCell ref="D1074:F1074"/>
+    <mergeCell ref="D1075:F1075"/>
+    <mergeCell ref="D1076:F1076"/>
+    <mergeCell ref="D1069:F1069"/>
+    <mergeCell ref="D1066:F1066"/>
+    <mergeCell ref="D1067:F1067"/>
+    <mergeCell ref="D1052:F1052"/>
+    <mergeCell ref="D1053:F1053"/>
+    <mergeCell ref="D1054:F1054"/>
+    <mergeCell ref="D1055:F1055"/>
+    <mergeCell ref="D1056:F1056"/>
+    <mergeCell ref="D1057:F1057"/>
+    <mergeCell ref="D1058:F1058"/>
+    <mergeCell ref="D1059:F1059"/>
+    <mergeCell ref="D1060:F1060"/>
+    <mergeCell ref="D1061:F1061"/>
+    <mergeCell ref="D1049:F1049"/>
+    <mergeCell ref="D1050:F1050"/>
+    <mergeCell ref="D1051:F1051"/>
+    <mergeCell ref="D1065:F1065"/>
+    <mergeCell ref="D1068:F1068"/>
+    <mergeCell ref="D1064:F1064"/>
+    <mergeCell ref="D1062:F1062"/>
+    <mergeCell ref="D1063:F1063"/>
+    <mergeCell ref="D1047:F1047"/>
+    <mergeCell ref="D1048:F1048"/>
+    <mergeCell ref="D987:F987"/>
+    <mergeCell ref="D988:F988"/>
+    <mergeCell ref="D981:F981"/>
+    <mergeCell ref="D982:F982"/>
+    <mergeCell ref="D983:F983"/>
+    <mergeCell ref="D984:F984"/>
+    <mergeCell ref="D985:F985"/>
+    <mergeCell ref="D986:F986"/>
     <mergeCell ref="D965:F965"/>
     <mergeCell ref="D966:F966"/>
     <mergeCell ref="D967:F967"/>
@@ -19766,45 +20384,6 @@
     <mergeCell ref="D977:F977"/>
     <mergeCell ref="D978:F978"/>
     <mergeCell ref="D979:F979"/>
-    <mergeCell ref="D1047:F1047"/>
-    <mergeCell ref="D1048:F1048"/>
-    <mergeCell ref="D987:F987"/>
-    <mergeCell ref="D988:F988"/>
-    <mergeCell ref="D981:F981"/>
-    <mergeCell ref="D982:F982"/>
-    <mergeCell ref="D983:F983"/>
-    <mergeCell ref="D984:F984"/>
-    <mergeCell ref="D985:F985"/>
-    <mergeCell ref="D986:F986"/>
-    <mergeCell ref="D1049:F1049"/>
-    <mergeCell ref="D1050:F1050"/>
-    <mergeCell ref="D1051:F1051"/>
-    <mergeCell ref="D1065:F1065"/>
-    <mergeCell ref="D1068:F1068"/>
-    <mergeCell ref="D1064:F1064"/>
-    <mergeCell ref="D1062:F1062"/>
-    <mergeCell ref="D1063:F1063"/>
-    <mergeCell ref="D1069:F1069"/>
-    <mergeCell ref="D1066:F1066"/>
-    <mergeCell ref="D1067:F1067"/>
-    <mergeCell ref="D1052:F1052"/>
-    <mergeCell ref="D1053:F1053"/>
-    <mergeCell ref="D1054:F1054"/>
-    <mergeCell ref="D1055:F1055"/>
-    <mergeCell ref="D1056:F1056"/>
-    <mergeCell ref="D1057:F1057"/>
-    <mergeCell ref="D1058:F1058"/>
-    <mergeCell ref="D1059:F1059"/>
-    <mergeCell ref="D1060:F1060"/>
-    <mergeCell ref="D1061:F1061"/>
-    <mergeCell ref="D1078:F1078"/>
-    <mergeCell ref="D1072:F1072"/>
-    <mergeCell ref="D1070:F1070"/>
-    <mergeCell ref="D1071:F1071"/>
-    <mergeCell ref="D1077:F1077"/>
-    <mergeCell ref="D1074:F1074"/>
-    <mergeCell ref="D1075:F1075"/>
-    <mergeCell ref="D1076:F1076"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
